--- a/data/EVISO.MI.xlsx
+++ b/data/EVISO.MI.xlsx
@@ -33661,7 +33661,7 @@
         <v>20485</v>
       </c>
       <c r="C1448" t="n">
-        <v>11.460000038147</v>
+        <v>11.5</v>
       </c>
       <c r="D1448" t="n">
         <v>11</v>
@@ -33673,6 +33673,29 @@
         <v>11.5</v>
       </c>
       <c r="G1448" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1449">
+      <c r="A1449" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B1449" t="n">
+        <v>12351</v>
+      </c>
+      <c r="C1449" t="n">
+        <v>11.5200004577637</v>
+      </c>
+      <c r="D1449" t="n">
+        <v>11</v>
+      </c>
+      <c r="E1449" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="F1449" t="n">
+        <v>11.2399997711182</v>
+      </c>
+      <c r="G1449" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/EVISO.MI.xlsx
+++ b/data/EVISO.MI.xlsx
@@ -33699,6 +33699,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1450">
+      <c r="A1450" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B1450" t="n">
+        <v>9640</v>
+      </c>
+      <c r="C1450" t="n">
+        <v>11.1000003814697</v>
+      </c>
+      <c r="D1450" t="n">
+        <v>10.4799995422363</v>
+      </c>
+      <c r="E1450" t="n">
+        <v>11.1000003814697</v>
+      </c>
+      <c r="F1450" t="n">
+        <v>10.8800001144409</v>
+      </c>
+      <c r="G1450" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/EVISO.MI.xlsx
+++ b/data/EVISO.MI.xlsx
@@ -33722,6 +33722,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1451">
+      <c r="A1451" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B1451" t="n">
+        <v>7617</v>
+      </c>
+      <c r="C1451" t="n">
+        <v>11.1199998855591</v>
+      </c>
+      <c r="D1451" t="n">
+        <v>10.6800003051758</v>
+      </c>
+      <c r="E1451" t="n">
+        <v>11.1199998855591</v>
+      </c>
+      <c r="F1451" t="n">
+        <v>10.8199996948242</v>
+      </c>
+      <c r="G1451" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/EVISO.MI.xlsx
+++ b/data/EVISO.MI.xlsx
@@ -33745,6 +33745,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1452">
+      <c r="A1452" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B1452" t="n">
+        <v>14950</v>
+      </c>
+      <c r="C1452" t="n">
+        <v>10.960000038147</v>
+      </c>
+      <c r="D1452" t="n">
+        <v>10.5799999237061</v>
+      </c>
+      <c r="E1452" t="n">
+        <v>10.8199996948242</v>
+      </c>
+      <c r="F1452" t="n">
+        <v>10.6999998092651</v>
+      </c>
+      <c r="G1452" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/EVISO.MI.xlsx
+++ b/data/EVISO.MI.xlsx
@@ -33586,22 +33586,22 @@
     </row>
     <row r="1445">
       <c r="A1445" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B1445" t="n">
-        <v>45906</v>
+        <v>34040</v>
       </c>
       <c r="C1445" t="n">
-        <v>11.1999998092651</v>
+        <v>10.960000038147</v>
       </c>
       <c r="D1445" t="n">
-        <v>10.7200002670288</v>
+        <v>10.6000003814697</v>
       </c>
       <c r="E1445" t="n">
-        <v>10.9799995422363</v>
+        <v>10.6000003814697</v>
       </c>
       <c r="F1445" t="n">
-        <v>11.1999998092651</v>
+        <v>10.960000038147</v>
       </c>
       <c r="G1445" t="s">
         <v>7</v>
@@ -33609,22 +33609,22 @@
     </row>
     <row r="1446">
       <c r="A1446" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B1446" t="n">
-        <v>60468</v>
+        <v>45906</v>
       </c>
       <c r="C1446" t="n">
-        <v>11.6000003814697</v>
+        <v>11.1999998092651</v>
       </c>
       <c r="D1446" t="n">
-        <v>10.2399997711182</v>
+        <v>10.7200002670288</v>
       </c>
       <c r="E1446" t="n">
-        <v>11.2399997711182</v>
+        <v>10.9799995422363</v>
       </c>
       <c r="F1446" t="n">
-        <v>10.4799995422363</v>
+        <v>11.1999998092651</v>
       </c>
       <c r="G1446" t="s">
         <v>7</v>
@@ -33632,22 +33632,22 @@
     </row>
     <row r="1447">
       <c r="A1447" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B1447" t="n">
-        <v>21695</v>
+        <v>60468</v>
       </c>
       <c r="C1447" t="n">
-        <v>10.960000038147</v>
+        <v>11.6000003814697</v>
       </c>
       <c r="D1447" t="n">
-        <v>10.5600004196167</v>
+        <v>10.2399997711182</v>
       </c>
       <c r="E1447" t="n">
-        <v>10.6000003814697</v>
+        <v>11.2399997711182</v>
       </c>
       <c r="F1447" t="n">
-        <v>10.960000038147</v>
+        <v>10.4799995422363</v>
       </c>
       <c r="G1447" t="s">
         <v>7</v>
@@ -33655,22 +33655,22 @@
     </row>
     <row r="1448">
       <c r="A1448" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B1448" t="n">
-        <v>20485</v>
+        <v>21695</v>
       </c>
       <c r="C1448" t="n">
-        <v>11.5</v>
+        <v>10.960000038147</v>
       </c>
       <c r="D1448" t="n">
-        <v>11</v>
+        <v>10.5600004196167</v>
       </c>
       <c r="E1448" t="n">
-        <v>11</v>
+        <v>10.6000003814697</v>
       </c>
       <c r="F1448" t="n">
-        <v>11.5</v>
+        <v>10.960000038147</v>
       </c>
       <c r="G1448" t="s">
         <v>7</v>
@@ -33678,22 +33678,22 @@
     </row>
     <row r="1449">
       <c r="A1449" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B1449" t="n">
-        <v>12351</v>
+        <v>20485</v>
       </c>
       <c r="C1449" t="n">
-        <v>11.5200004577637</v>
+        <v>11.5</v>
       </c>
       <c r="D1449" t="n">
         <v>11</v>
       </c>
       <c r="E1449" t="n">
+        <v>11</v>
+      </c>
+      <c r="F1449" t="n">
         <v>11.5</v>
-      </c>
-      <c r="F1449" t="n">
-        <v>11.2399997711182</v>
       </c>
       <c r="G1449" t="s">
         <v>7</v>
@@ -33701,22 +33701,22 @@
     </row>
     <row r="1450">
       <c r="A1450" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B1450" t="n">
-        <v>9640</v>
+        <v>12351</v>
       </c>
       <c r="C1450" t="n">
-        <v>11.1000003814697</v>
+        <v>11.5200004577637</v>
       </c>
       <c r="D1450" t="n">
-        <v>10.4799995422363</v>
+        <v>11</v>
       </c>
       <c r="E1450" t="n">
-        <v>11.1000003814697</v>
+        <v>11.5</v>
       </c>
       <c r="F1450" t="n">
-        <v>10.8800001144409</v>
+        <v>11.2399997711182</v>
       </c>
       <c r="G1450" t="s">
         <v>7</v>
@@ -33724,22 +33724,22 @@
     </row>
     <row r="1451">
       <c r="A1451" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B1451" t="n">
-        <v>7617</v>
+        <v>9640</v>
       </c>
       <c r="C1451" t="n">
-        <v>11.1199998855591</v>
+        <v>11.1000003814697</v>
       </c>
       <c r="D1451" t="n">
-        <v>10.6800003051758</v>
+        <v>10.4799995422363</v>
       </c>
       <c r="E1451" t="n">
-        <v>11.1199998855591</v>
+        <v>11.1000003814697</v>
       </c>
       <c r="F1451" t="n">
-        <v>10.8199996948242</v>
+        <v>10.8800001144409</v>
       </c>
       <c r="G1451" t="s">
         <v>7</v>
@@ -33747,24 +33747,47 @@
     </row>
     <row r="1452">
       <c r="A1452" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B1452" t="n">
-        <v>14950</v>
+        <v>7617</v>
       </c>
       <c r="C1452" t="n">
-        <v>10.960000038147</v>
+        <v>11.1199998855591</v>
       </c>
       <c r="D1452" t="n">
-        <v>10.5799999237061</v>
+        <v>10.6800003051758</v>
       </c>
       <c r="E1452" t="n">
+        <v>11.1199998855591</v>
+      </c>
+      <c r="F1452" t="n">
         <v>10.8199996948242</v>
       </c>
-      <c r="F1452" t="n">
-        <v>10.6999998092651</v>
-      </c>
       <c r="G1452" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1453">
+      <c r="A1453" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B1453" t="n">
+        <v>7065</v>
+      </c>
+      <c r="C1453" t="n">
+        <v>10.8199996948242</v>
+      </c>
+      <c r="D1453" t="n">
+        <v>10.5600004196167</v>
+      </c>
+      <c r="E1453" t="n">
+        <v>10.8199996948242</v>
+      </c>
+      <c r="F1453" t="n">
+        <v>10.6800003051758</v>
+      </c>
+      <c r="G1453" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/EVISO.MI.xlsx
+++ b/data/EVISO.MI.xlsx
@@ -473,7 +473,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G4" t="n">
-        <v>2.11304259300232</v>
+        <v>2.11304235458374</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G8" t="n">
-        <v>2.09347701072693</v>
+        <v>2.09347724914551</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G10" t="n">
-        <v>1.99565076828003</v>
+        <v>1.99565100669861</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>2</v>
       </c>
       <c r="G11" t="n">
-        <v>1.95652067661285</v>
+        <v>1.95652055740356</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>2</v>
       </c>
       <c r="G12" t="n">
-        <v>1.95652067661285</v>
+        <v>1.95652055740356</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>2</v>
       </c>
       <c r="G13" t="n">
-        <v>1.95652067661285</v>
+        <v>1.95652055740356</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G14" t="n">
-        <v>1.93695557117462</v>
+        <v>1.93695533275604</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G15" t="n">
-        <v>1.95162928104401</v>
+        <v>1.9516294002533</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>2</v>
       </c>
       <c r="G18" t="n">
-        <v>1.95652067661285</v>
+        <v>1.95652055740356</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G19" t="n">
-        <v>1.96630311012268</v>
+        <v>1.96630322933197</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>2</v>
       </c>
       <c r="G20" t="n">
-        <v>1.95652067661285</v>
+        <v>1.95652055740356</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G22" t="n">
-        <v>1.96630311012268</v>
+        <v>1.96630322933197</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>2</v>
       </c>
       <c r="G23" t="n">
-        <v>1.95652067661285</v>
+        <v>1.95652055740356</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G24" t="n">
-        <v>1.99565076828003</v>
+        <v>1.99565100669861</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G25" t="n">
-        <v>1.96630311012268</v>
+        <v>1.96630322933197</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G26" t="n">
-        <v>1.96630311012268</v>
+        <v>1.96630322933197</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>2</v>
       </c>
       <c r="G27" t="n">
-        <v>1.95652067661285</v>
+        <v>1.95652055740356</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G28" t="n">
-        <v>1.95162928104401</v>
+        <v>1.9516294002533</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>2</v>
       </c>
       <c r="G29" t="n">
-        <v>1.95652067661285</v>
+        <v>1.95652055740356</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G37" t="n">
-        <v>2.21086859703064</v>
+        <v>2.21086835861206</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G38" t="n">
-        <v>2.28912878036499</v>
+        <v>2.28912925720215</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G39" t="n">
-        <v>2.26956367492676</v>
+        <v>2.26956415176392</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G41" t="n">
-        <v>2.3184769153595</v>
+        <v>2.31847667694092</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G43" t="n">
-        <v>2.32825970649719</v>
+        <v>2.32825946807861</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G46" t="n">
-        <v>2.28912878036499</v>
+        <v>2.28912925720215</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G48" t="n">
-        <v>2.28912878036499</v>
+        <v>2.28912925720215</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G49" t="n">
-        <v>2.26956367492676</v>
+        <v>2.26956415176392</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G50" t="n">
-        <v>2.28912878036499</v>
+        <v>2.28912925720215</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G51" t="n">
-        <v>2.26956367492676</v>
+        <v>2.26956415176392</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G61" t="n">
-        <v>2.23043370246887</v>
+        <v>2.23043346405029</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G64" t="n">
-        <v>2.21086859703064</v>
+        <v>2.21086835861206</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G65" t="n">
-        <v>2.17173790931702</v>
+        <v>2.1717381477356</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G68" t="n">
-        <v>2.23043370246887</v>
+        <v>2.23043346405029</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G76" t="n">
-        <v>2.17173790931702</v>
+        <v>2.1717381477356</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G79" t="n">
-        <v>2.23043370246887</v>
+        <v>2.23043346405029</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G81" t="n">
-        <v>2.21086859703064</v>
+        <v>2.21086835861206</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G83" t="n">
-        <v>2.21086859703064</v>
+        <v>2.21086835861206</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G93" t="n">
-        <v>2.32825970649719</v>
+        <v>2.32825946807861</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G95" t="n">
-        <v>2.26956367492676</v>
+        <v>2.26956415176392</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G102" t="n">
-        <v>2.42608571052551</v>
+        <v>2.42608547210693</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G104" t="n">
-        <v>2.65108561515808</v>
+        <v>2.6510853767395</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G105" t="n">
-        <v>2.73912882804871</v>
+        <v>2.73912906646729</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G107" t="n">
-        <v>2.69999837875366</v>
+        <v>2.69999861717224</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G110" t="n">
-        <v>2.61195492744446</v>
+        <v>2.61195516586304</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G111" t="n">
-        <v>2.53369402885437</v>
+        <v>2.53369426727295</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G112" t="n">
-        <v>2.54347681999207</v>
+        <v>2.54347658157349</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G113" t="n">
-        <v>2.54347681999207</v>
+        <v>2.54347658157349</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G114" t="n">
-        <v>2.53369402885437</v>
+        <v>2.53369426727295</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G116" t="n">
-        <v>2.51412892341614</v>
+        <v>2.51412916183472</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G117" t="n">
-        <v>2.54347681999207</v>
+        <v>2.54347658157349</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G118" t="n">
-        <v>2.49456357955933</v>
+        <v>2.49456381797791</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G119" t="n">
-        <v>2.51412892341614</v>
+        <v>2.51412916183472</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G120" t="n">
-        <v>2.47499847412109</v>
+        <v>2.47499871253967</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G122" t="n">
-        <v>2.39673781394958</v>
+        <v>2.39673805236816</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G123" t="n">
-        <v>2.4065203666687</v>
+        <v>2.40652012825012</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G124" t="n">
-        <v>2.3184769153595</v>
+        <v>2.31847667694092</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G125" t="n">
-        <v>2.4163031578064</v>
+        <v>2.41630291938782</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G126" t="n">
-        <v>2.4065203666687</v>
+        <v>2.40652012825012</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G127" t="n">
-        <v>2.53369402885437</v>
+        <v>2.53369426727295</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G128" t="n">
-        <v>2.48478102684021</v>
+        <v>2.48478126525879</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G129" t="n">
-        <v>2.49456357955933</v>
+        <v>2.49456381797791</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G130" t="n">
-        <v>2.52391171455383</v>
+        <v>2.52391147613525</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G132" t="n">
-        <v>2.49456357955933</v>
+        <v>2.49456381797791</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G134" t="n">
-        <v>2.51412892341614</v>
+        <v>2.51412916183472</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G137" t="n">
-        <v>2.47499847412109</v>
+        <v>2.47499871253967</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G138" t="n">
-        <v>2.39673781394958</v>
+        <v>2.39673805236816</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G139" t="n">
-        <v>2.3184769153595</v>
+        <v>2.31847667694092</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G141" t="n">
-        <v>2.4163031578064</v>
+        <v>2.41630291938782</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G142" t="n">
-        <v>2.4065203666687</v>
+        <v>2.40652012825012</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G143" t="n">
-        <v>2.42608571052551</v>
+        <v>2.42608547210693</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G144" t="n">
-        <v>2.42608571052551</v>
+        <v>2.42608547210693</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G145" t="n">
-        <v>2.42608571052551</v>
+        <v>2.42608547210693</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G148" t="n">
-        <v>2.4065203666687</v>
+        <v>2.40652012825012</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G150" t="n">
-        <v>2.42608571052551</v>
+        <v>2.42608547210693</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G151" t="n">
-        <v>2.39673781394958</v>
+        <v>2.39673805236816</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G154" t="n">
-        <v>2.48478102684021</v>
+        <v>2.48478126525879</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G156" t="n">
-        <v>2.49456357955933</v>
+        <v>2.49456381797791</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G157" t="n">
-        <v>2.49456357955933</v>
+        <v>2.49456381797791</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G159" t="n">
-        <v>2.4163031578064</v>
+        <v>2.41630291938782</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G160" t="n">
-        <v>2.39673781394958</v>
+        <v>2.39673805236816</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G161" t="n">
-        <v>2.42608571052551</v>
+        <v>2.42608547210693</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G162" t="n">
-        <v>2.42608571052551</v>
+        <v>2.42608547210693</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G163" t="n">
-        <v>2.61195492744446</v>
+        <v>2.61195516586304</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G164" t="n">
-        <v>2.81738972663879</v>
+        <v>2.81738996505737</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G165" t="n">
-        <v>2.81738972663879</v>
+        <v>2.81738996505737</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G166" t="n">
-        <v>2.92499828338623</v>
+        <v>2.92499852180481</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G167" t="n">
-        <v>2.92499828338623</v>
+        <v>2.92499852180481</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G168" t="n">
-        <v>2.90543293952942</v>
+        <v>2.905433177948</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G169" t="n">
-        <v>2.92499828338623</v>
+        <v>2.92499852180481</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G170" t="n">
-        <v>2.92499828338623</v>
+        <v>2.92499852180481</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G172" t="n">
-        <v>2.7489116191864</v>
+        <v>2.74891138076782</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G174" t="n">
-        <v>2.73912882804871</v>
+        <v>2.73912906646729</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G180" t="n">
-        <v>2.67065072059631</v>
+        <v>2.67065048217773</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G186" t="n">
-        <v>2.70978093147278</v>
+        <v>2.70978116989136</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G189" t="n">
-        <v>2.7489116191864</v>
+        <v>2.74891138076782</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G190" t="n">
-        <v>2.51412892341614</v>
+        <v>2.51412916183472</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G191" t="n">
-        <v>2.68043303489685</v>
+        <v>2.68043327331543</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G193" t="n">
-        <v>2.69999837875366</v>
+        <v>2.69999861717224</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G194" t="n">
-        <v>2.64130306243896</v>
+        <v>2.64130282402039</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G195" t="n">
-        <v>2.63152027130127</v>
+        <v>2.63152003288269</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G198" t="n">
-        <v>2.61195492744446</v>
+        <v>2.61195516586304</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G201" t="n">
-        <v>2.54347681999207</v>
+        <v>2.54347658157349</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G203" t="n">
-        <v>2.61195492744446</v>
+        <v>2.61195516586304</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G204" t="n">
-        <v>2.64130306243896</v>
+        <v>2.64130282402039</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G205" t="n">
-        <v>2.70978093147278</v>
+        <v>2.70978116989136</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G206" t="n">
-        <v>2.73912882804871</v>
+        <v>2.73912906646729</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G207" t="n">
-        <v>2.69999837875366</v>
+        <v>2.69999861717224</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G209" t="n">
-        <v>2.67065072059631</v>
+        <v>2.67065048217773</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G212" t="n">
-        <v>2.67065072059631</v>
+        <v>2.67065048217773</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G215" t="n">
-        <v>2.68043303489685</v>
+        <v>2.68043327331543</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G216" t="n">
-        <v>2.65108561515808</v>
+        <v>2.6510853767395</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G217" t="n">
-        <v>2.64130306243896</v>
+        <v>2.64130282402039</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G220" t="n">
-        <v>2.63691425323486</v>
+        <v>2.63691449165344</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G221" t="n">
-        <v>2.64675354957581</v>
+        <v>2.64675331115723</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G222" t="n">
-        <v>2.62707495689392</v>
+        <v>2.6270751953125</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G227" t="n">
-        <v>2.51884317398071</v>
+        <v>2.51884341239929</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G228" t="n">
-        <v>2.49916481971741</v>
+        <v>2.49916505813599</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G229" t="n">
-        <v>2.52868247032166</v>
+        <v>2.52868270874023</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G232" t="n">
-        <v>2.43029046058655</v>
+        <v>2.43029022216797</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G234" t="n">
-        <v>2.51884317398071</v>
+        <v>2.51884341239929</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G238" t="n">
-        <v>2.55820035934448</v>
+        <v>2.5582001209259</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G240" t="n">
-        <v>2.62707495689392</v>
+        <v>2.6270751953125</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G244" t="n">
-        <v>2.49916481971741</v>
+        <v>2.49916505813599</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G246" t="n">
-        <v>2.48932552337646</v>
+        <v>2.48932576179504</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G249" t="n">
-        <v>2.43029046058655</v>
+        <v>2.43029022216797</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G252" t="n">
-        <v>2.48932552337646</v>
+        <v>2.48932576179504</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G256" t="n">
-        <v>2.42045116424561</v>
+        <v>2.42045092582703</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G257" t="n">
-        <v>2.42045116424561</v>
+        <v>2.42045092582703</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G259" t="n">
-        <v>2.48932552337646</v>
+        <v>2.48932576179504</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G260" t="n">
-        <v>2.48932552337646</v>
+        <v>2.48932576179504</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G262" t="n">
-        <v>2.42045116424561</v>
+        <v>2.42045092582703</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G264" t="n">
-        <v>2.43029046058655</v>
+        <v>2.43029022216797</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G268" t="n">
-        <v>2.43029046058655</v>
+        <v>2.43029022216797</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G269" t="n">
-        <v>2.42045116424561</v>
+        <v>2.42045092582703</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G272" t="n">
-        <v>2.27286243438721</v>
+        <v>2.27286267280579</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G274" t="n">
-        <v>2.41061186790466</v>
+        <v>2.41061210632324</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G276" t="n">
-        <v>2.42045116424561</v>
+        <v>2.42045092582703</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G280" t="n">
-        <v>2.41061186790466</v>
+        <v>2.41061210632324</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G281" t="n">
-        <v>2.41061186790466</v>
+        <v>2.41061210632324</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G282" t="n">
-        <v>2.41061186790466</v>
+        <v>2.41061210632324</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G283" t="n">
-        <v>2.35157680511475</v>
+        <v>2.35157656669617</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G284" t="n">
-        <v>2.42045116424561</v>
+        <v>2.42045092582703</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G285" t="n">
-        <v>2.52868247032166</v>
+        <v>2.52868270874023</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G295" t="n">
-        <v>2.30238008499146</v>
+        <v>2.30238032341003</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G299" t="n">
-        <v>2.27286243438721</v>
+        <v>2.27286267280579</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G300" t="n">
-        <v>2.20398807525635</v>
+        <v>2.20398783683777</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G304" t="n">
-        <v>2.27286243438721</v>
+        <v>2.27286267280579</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G306" t="n">
-        <v>2.30238008499146</v>
+        <v>2.30238032341003</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G312" t="n">
-        <v>2.35157680511475</v>
+        <v>2.35157656669617</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G313" t="n">
-        <v>2.41061186790466</v>
+        <v>2.41061210632324</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G321" t="n">
-        <v>2.27286243438721</v>
+        <v>2.27286267280579</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G322" t="n">
-        <v>2.28270173072815</v>
+        <v>2.28270196914673</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G326" t="n">
-        <v>2.35157680511475</v>
+        <v>2.35157656669617</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G329" t="n">
-        <v>2.28270173072815</v>
+        <v>2.28270196914673</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G330" t="n">
-        <v>2.30238008499146</v>
+        <v>2.30238032341003</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G332" t="n">
-        <v>2.30238008499146</v>
+        <v>2.30238032341003</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G334" t="n">
-        <v>2.20398807525635</v>
+        <v>2.20398783683777</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>2.25</v>
       </c>
       <c r="G337" t="n">
-        <v>2.21382737159729</v>
+        <v>2.21382713317871</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G343" t="n">
-        <v>2.41061186790466</v>
+        <v>2.41061210632324</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G344" t="n">
-        <v>2.41061186790466</v>
+        <v>2.41061210632324</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G345" t="n">
-        <v>2.28270173072815</v>
+        <v>2.28270196914673</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G349" t="n">
-        <v>2.35157680511475</v>
+        <v>2.35157656669617</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G351" t="n">
-        <v>2.28270173072815</v>
+        <v>2.28270196914673</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G353" t="n">
-        <v>2.28270173072815</v>
+        <v>2.28270196914673</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G354" t="n">
-        <v>2.28270173072815</v>
+        <v>2.28270196914673</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G355" t="n">
-        <v>2.27286243438721</v>
+        <v>2.27286267280579</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G356" t="n">
-        <v>2.28270173072815</v>
+        <v>2.28270196914673</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G358" t="n">
-        <v>2.28270173072815</v>
+        <v>2.28270196914673</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G359" t="n">
-        <v>2.27286243438721</v>
+        <v>2.27286267280579</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G360" t="n">
-        <v>2.28270173072815</v>
+        <v>2.28270196914673</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G361" t="n">
-        <v>2.30238008499146</v>
+        <v>2.30238032341003</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G362" t="n">
-        <v>2.30238008499146</v>
+        <v>2.30238032341003</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G363" t="n">
-        <v>2.30238008499146</v>
+        <v>2.30238032341003</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G365" t="n">
-        <v>2.41061186790466</v>
+        <v>2.41061210632324</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G369" t="n">
-        <v>2.53852200508118</v>
+        <v>2.5385217666626</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G372" t="n">
-        <v>2.48932552337646</v>
+        <v>2.48932576179504</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G379" t="n">
-        <v>2.35157680511475</v>
+        <v>2.35157656669617</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G385" t="n">
-        <v>2.43029046058655</v>
+        <v>2.43029022216797</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G387" t="n">
-        <v>2.43029046058655</v>
+        <v>2.43029022216797</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G393" t="n">
-        <v>2.35157680511475</v>
+        <v>2.35157656669617</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G407" t="n">
-        <v>2.42045116424561</v>
+        <v>2.42045092582703</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G411" t="n">
-        <v>2.48932552337646</v>
+        <v>2.48932576179504</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G412" t="n">
-        <v>2.48932552337646</v>
+        <v>2.48932576179504</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G413" t="n">
-        <v>2.42045116424561</v>
+        <v>2.42045092582703</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G421" t="n">
-        <v>2.49916481971741</v>
+        <v>2.49916505813599</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G424" t="n">
-        <v>2.49916481971741</v>
+        <v>2.49916505813599</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G427" t="n">
-        <v>2.55820035934448</v>
+        <v>2.5582001209259</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G428" t="n">
-        <v>2.52868247032166</v>
+        <v>2.52868270874023</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G432" t="n">
-        <v>2.51884317398071</v>
+        <v>2.51884341239929</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G434" t="n">
-        <v>2.55820035934448</v>
+        <v>2.5582001209259</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G435" t="n">
-        <v>2.52868247032166</v>
+        <v>2.52868270874023</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G437" t="n">
-        <v>2.52868247032166</v>
+        <v>2.52868270874023</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G438" t="n">
-        <v>2.51884317398071</v>
+        <v>2.51884341239929</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G439" t="n">
-        <v>2.52868247032166</v>
+        <v>2.52868270874023</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G440" t="n">
-        <v>2.43029046058655</v>
+        <v>2.43029022216797</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G443" t="n">
-        <v>2.41061186790466</v>
+        <v>2.41061210632324</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G445" t="n">
-        <v>2.49916481971741</v>
+        <v>2.49916505813599</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G447" t="n">
-        <v>2.28270173072815</v>
+        <v>2.28270196914673</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G448" t="n">
-        <v>2.28270173072815</v>
+        <v>2.28270196914673</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G452" t="n">
-        <v>2.43029046058655</v>
+        <v>2.43029022216797</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G457" t="n">
-        <v>2.49916481971741</v>
+        <v>2.49916505813599</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G458" t="n">
-        <v>2.51884317398071</v>
+        <v>2.51884341239929</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G459" t="n">
-        <v>2.51884317398071</v>
+        <v>2.51884341239929</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G460" t="n">
-        <v>2.43029046058655</v>
+        <v>2.43029022216797</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G464" t="n">
-        <v>2.42045116424561</v>
+        <v>2.42045092582703</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G465" t="n">
-        <v>2.41061186790466</v>
+        <v>2.41061210632324</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G468" t="n">
-        <v>2.42045116424561</v>
+        <v>2.42045092582703</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G469" t="n">
-        <v>2.42045116424561</v>
+        <v>2.42045092582703</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G471" t="n">
-        <v>2.43029046058655</v>
+        <v>2.43029022216797</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G475" t="n">
-        <v>2.42045116424561</v>
+        <v>2.42045092582703</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G479" t="n">
-        <v>2.43029046058655</v>
+        <v>2.43029022216797</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G481" t="n">
-        <v>2.42045116424561</v>
+        <v>2.42045092582703</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G483" t="n">
-        <v>2.42045116424561</v>
+        <v>2.42045092582703</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G487" t="n">
-        <v>2.41061186790466</v>
+        <v>2.41061210632324</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G488" t="n">
-        <v>2.41061186790466</v>
+        <v>2.41061210632324</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G490" t="n">
-        <v>2.41061186790466</v>
+        <v>2.41061210632324</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G493" t="n">
-        <v>2.41061186790466</v>
+        <v>2.41061210632324</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G494" t="n">
-        <v>2.41061186790466</v>
+        <v>2.41061210632324</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G495" t="n">
-        <v>2.41061186790466</v>
+        <v>2.41061210632324</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G500" t="n">
-        <v>2.48932552337646</v>
+        <v>2.48932576179504</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G501" t="n">
-        <v>2.41061186790466</v>
+        <v>2.41061210632324</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G504" t="n">
-        <v>2.42045116424561</v>
+        <v>2.42045092582703</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G505" t="n">
-        <v>2.42045116424561</v>
+        <v>2.42045092582703</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G507" t="n">
-        <v>2.42045116424561</v>
+        <v>2.42045092582703</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G509" t="n">
-        <v>2.43029046058655</v>
+        <v>2.43029022216797</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G510" t="n">
-        <v>2.43029046058655</v>
+        <v>2.43029022216797</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G512" t="n">
-        <v>2.49916481971741</v>
+        <v>2.49916505813599</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G515" t="n">
-        <v>2.48932552337646</v>
+        <v>2.48932576179504</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G523" t="n">
-        <v>2.55820035934448</v>
+        <v>2.5582001209259</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G528" t="n">
-        <v>2.55820035934448</v>
+        <v>2.5582001209259</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G529" t="n">
-        <v>2.52868247032166</v>
+        <v>2.52868270874023</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G530" t="n">
-        <v>2.55820035934448</v>
+        <v>2.5582001209259</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G533" t="n">
-        <v>2.63691425323486</v>
+        <v>2.63691449165344</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G535" t="n">
-        <v>2.53852200508118</v>
+        <v>2.5385217666626</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G536" t="n">
-        <v>2.55820035934448</v>
+        <v>2.5582001209259</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G538" t="n">
-        <v>2.55820035934448</v>
+        <v>2.5582001209259</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G539" t="n">
-        <v>2.55820035934448</v>
+        <v>2.5582001209259</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G540" t="n">
-        <v>2.53852200508118</v>
+        <v>2.5385217666626</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G541" t="n">
-        <v>2.55820035934448</v>
+        <v>2.5582001209259</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G542" t="n">
-        <v>2.55820035934448</v>
+        <v>2.5582001209259</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G544" t="n">
-        <v>2.64675354957581</v>
+        <v>2.64675331115723</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G545" t="n">
-        <v>2.64675354957581</v>
+        <v>2.64675331115723</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G547" t="n">
-        <v>2.35157680511475</v>
+        <v>2.35157656669617</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G550" t="n">
-        <v>2.30238008499146</v>
+        <v>2.30238032341003</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G553" t="n">
-        <v>2.28270173072815</v>
+        <v>2.28270196914673</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G557" t="n">
-        <v>2.27286243438721</v>
+        <v>2.27286267280579</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G558" t="n">
-        <v>2.27286243438721</v>
+        <v>2.27286267280579</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G559" t="n">
-        <v>2.27286243438721</v>
+        <v>2.27286267280579</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G560" t="n">
-        <v>2.28270173072815</v>
+        <v>2.28270196914673</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G562" t="n">
-        <v>2.24334502220154</v>
+        <v>2.24334478378296</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G563" t="n">
-        <v>2.20398807525635</v>
+        <v>2.20398783683777</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>2.25</v>
       </c>
       <c r="G565" t="n">
-        <v>2.21382737159729</v>
+        <v>2.21382713317871</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G566" t="n">
-        <v>2.27286243438721</v>
+        <v>2.27286267280579</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G570" t="n">
-        <v>2.24334502220154</v>
+        <v>2.24334478378296</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G573" t="n">
-        <v>2.28270173072815</v>
+        <v>2.28270196914673</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G574" t="n">
-        <v>2.20398807525635</v>
+        <v>2.20398783683777</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G578" t="n">
-        <v>2.28270173072815</v>
+        <v>2.28270196914673</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G580" t="n">
-        <v>2.27286243438721</v>
+        <v>2.27286267280579</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G581" t="n">
-        <v>2.28270173072815</v>
+        <v>2.28270196914673</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G583" t="n">
-        <v>2.30238008499146</v>
+        <v>2.30238032341003</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G596" t="n">
-        <v>2.28270173072815</v>
+        <v>2.28270196914673</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G599" t="n">
-        <v>2.30238008499146</v>
+        <v>2.30238032341003</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G601" t="n">
-        <v>2.24334502220154</v>
+        <v>2.24334478378296</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G602" t="n">
-        <v>2.27286243438721</v>
+        <v>2.27286267280579</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G603" t="n">
-        <v>2.27286243438721</v>
+        <v>2.27286267280579</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G605" t="n">
-        <v>2.30238008499146</v>
+        <v>2.30238032341003</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G606" t="n">
-        <v>2.30238008499146</v>
+        <v>2.30238032341003</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G607" t="n">
-        <v>2.30238008499146</v>
+        <v>2.30238032341003</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G608" t="n">
-        <v>2.30238008499146</v>
+        <v>2.30238032341003</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G609" t="n">
-        <v>2.30238008499146</v>
+        <v>2.30238032341003</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G611" t="n">
-        <v>2.30238008499146</v>
+        <v>2.30238032341003</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G613" t="n">
-        <v>2.27286243438721</v>
+        <v>2.27286267280579</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G622" t="n">
-        <v>2.24334502220154</v>
+        <v>2.24334478378296</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>2.25</v>
       </c>
       <c r="G623" t="n">
-        <v>2.21382737159729</v>
+        <v>2.21382713317871</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G625" t="n">
-        <v>2.24334502220154</v>
+        <v>2.24334478378296</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G629" t="n">
-        <v>2.24334502220154</v>
+        <v>2.24334478378296</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G630" t="n">
-        <v>2.28270173072815</v>
+        <v>2.28270196914673</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G631" t="n">
-        <v>2.28270173072815</v>
+        <v>2.28270196914673</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G633" t="n">
-        <v>2.28270173072815</v>
+        <v>2.28270196914673</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G634" t="n">
-        <v>2.28270173072815</v>
+        <v>2.28270196914673</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G639" t="n">
-        <v>2.27286243438721</v>
+        <v>2.27286267280579</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G640" t="n">
-        <v>2.28270173072815</v>
+        <v>2.28270196914673</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G642" t="n">
-        <v>2.24334502220154</v>
+        <v>2.24334478378296</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>2.25</v>
       </c>
       <c r="G645" t="n">
-        <v>2.21382737159729</v>
+        <v>2.21382713317871</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G647" t="n">
-        <v>2.20398807525635</v>
+        <v>2.20398783683777</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>2.25</v>
       </c>
       <c r="G649" t="n">
-        <v>2.21382737159729</v>
+        <v>2.21382713317871</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G653" t="n">
-        <v>2.13511323928833</v>
+        <v>2.13511347770691</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G654" t="n">
-        <v>2.14495253562927</v>
+        <v>2.14495277404785</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>2.25</v>
       </c>
       <c r="G659" t="n">
-        <v>2.21382737159729</v>
+        <v>2.21382713317871</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>2.25</v>
       </c>
       <c r="G661" t="n">
-        <v>2.21382737159729</v>
+        <v>2.21382713317871</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G666" t="n">
-        <v>2.24334502220154</v>
+        <v>2.24334478378296</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G670" t="n">
-        <v>2.20398807525635</v>
+        <v>2.20398783683777</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G671" t="n">
-        <v>2.24334502220154</v>
+        <v>2.24334478378296</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G672" t="n">
-        <v>2.24334502220154</v>
+        <v>2.24334478378296</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G673" t="n">
-        <v>2.24334502220154</v>
+        <v>2.24334478378296</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G676" t="n">
-        <v>2.20398807525635</v>
+        <v>2.20398783683777</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G681" t="n">
-        <v>2.27286243438721</v>
+        <v>2.27286267280579</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G685" t="n">
-        <v>2.35157680511475</v>
+        <v>2.35157656669617</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G688" t="n">
-        <v>2.35157680511475</v>
+        <v>2.35157656669617</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G703" t="n">
-        <v>2.30238008499146</v>
+        <v>2.30238032341003</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G704" t="n">
-        <v>2.30238008499146</v>
+        <v>2.30238032341003</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G705" t="n">
-        <v>2.30238008499146</v>
+        <v>2.30238032341003</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G706" t="n">
-        <v>2.28270173072815</v>
+        <v>2.28270196914673</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G707" t="n">
-        <v>2.24334502220154</v>
+        <v>2.24334478378296</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G711" t="n">
-        <v>2.43029046058655</v>
+        <v>2.43029022216797</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G712" t="n">
-        <v>2.43029046058655</v>
+        <v>2.43029022216797</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G716" t="n">
-        <v>2.35157680511475</v>
+        <v>2.35157656669617</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G717" t="n">
-        <v>2.43029046058655</v>
+        <v>2.43029022216797</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G722" t="n">
-        <v>2.35157680511475</v>
+        <v>2.35157656669617</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G724" t="n">
-        <v>2.35157680511475</v>
+        <v>2.35157656669617</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G726" t="n">
-        <v>2.41061186790466</v>
+        <v>2.41061210632324</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G727" t="n">
-        <v>2.43029046058655</v>
+        <v>2.43029022216797</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G728" t="n">
-        <v>2.43029046058655</v>
+        <v>2.43029022216797</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G732" t="n">
-        <v>2.41061186790466</v>
+        <v>2.41061210632324</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G738" t="n">
-        <v>2.35157680511475</v>
+        <v>2.35157656669617</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G742" t="n">
-        <v>2.49916481971741</v>
+        <v>2.49916505813599</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G744" t="n">
-        <v>2.48932552337646</v>
+        <v>2.48932576179504</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G746" t="n">
-        <v>2.48932552337646</v>
+        <v>2.48932576179504</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G747" t="n">
-        <v>2.51884317398071</v>
+        <v>2.51884341239929</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G748" t="n">
-        <v>2.52868247032166</v>
+        <v>2.52868270874023</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G753" t="n">
-        <v>2.63691425323486</v>
+        <v>2.63691449165344</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G755" t="n">
-        <v>2.77466344833374</v>
+        <v>2.77466320991516</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G757" t="n">
-        <v>2.71562790870667</v>
+        <v>2.71562814712524</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G759" t="n">
-        <v>2.77466344833374</v>
+        <v>2.77466320991516</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G760" t="n">
-        <v>2.77466344833374</v>
+        <v>2.77466320991516</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G761" t="n">
-        <v>2.77466344833374</v>
+        <v>2.77466320991516</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G766" t="n">
-        <v>2.77466344833374</v>
+        <v>2.77466320991516</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G768" t="n">
-        <v>2.77466344833374</v>
+        <v>2.77466320991516</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G773" t="n">
-        <v>3.00096583366394</v>
+        <v>3.00096559524536</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G776" t="n">
-        <v>3.00096583366394</v>
+        <v>3.00096559524536</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G779" t="n">
-        <v>3.00096583366394</v>
+        <v>3.00096559524536</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G781" t="n">
-        <v>3.00096583366394</v>
+        <v>3.00096559524536</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G788" t="n">
-        <v>2.9124128818512</v>
+        <v>2.91241264343262</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G790" t="n">
-        <v>2.84353804588318</v>
+        <v>2.84353828430176</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G791" t="n">
-        <v>2.92225217819214</v>
+        <v>2.92225193977356</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -20987,7 +20987,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G793" t="n">
-        <v>2.92225217819214</v>
+        <v>2.92225193977356</v>
       </c>
       <c r="H793" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G794" t="n">
-        <v>2.90257334709167</v>
+        <v>2.90257358551025</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G798" t="n">
-        <v>2.9124128818512</v>
+        <v>2.91241264343262</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G806" t="n">
-        <v>3.09935832023621</v>
+        <v>3.09935808181763</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G808" t="n">
-        <v>3.1387152671814</v>
+        <v>3.13871502876282</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G815" t="n">
-        <v>3.16823267936707</v>
+        <v>3.16823291778564</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G822" t="n">
-        <v>3.32566070556641</v>
+        <v>3.32566046714783</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G827" t="n">
-        <v>3.41421341896057</v>
+        <v>3.41421365737915</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G828" t="n">
-        <v>3.42405271530151</v>
+        <v>3.42405295372009</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G829" t="n">
-        <v>3.48308825492859</v>
+        <v>3.48308801651001</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G831" t="n">
-        <v>3.57164144515991</v>
+        <v>3.57164120674133</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G834" t="n">
-        <v>4.12263822555542</v>
+        <v>4.12263870239258</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>4.25</v>
       </c>
       <c r="G835" t="n">
-        <v>4.18167400360107</v>
+        <v>4.18167352676392</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G839" t="n">
-        <v>4.22103071212769</v>
+        <v>4.22103023529053</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G841" t="n">
-        <v>4.28990507125854</v>
+        <v>4.2899055480957</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G843" t="n">
-        <v>4.39813661575317</v>
+        <v>4.39813613891602</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G849" t="n">
-        <v>5.07704401016235</v>
+        <v>5.0770435333252</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G850" t="n">
-        <v>4.99832963943481</v>
+        <v>4.99833011627197</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G852" t="n">
-        <v>5.03768634796143</v>
+        <v>5.03768682479858</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G857" t="n">
-        <v>5.03768634796143</v>
+        <v>5.03768682479858</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G859" t="n">
-        <v>4.8605809211731</v>
+        <v>4.86058044433594</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G860" t="n">
-        <v>4.83106279373169</v>
+        <v>4.83106327056885</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G861" t="n">
-        <v>4.89009857177734</v>
+        <v>4.89009809494019</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G864" t="n">
-        <v>4.89009857177734</v>
+        <v>4.89009809494019</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G867" t="n">
-        <v>5.29350709915161</v>
+        <v>5.29350662231445</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G869" t="n">
-        <v>5.70675468444824</v>
+        <v>5.7067551612854</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G870" t="n">
-        <v>5.80514669418335</v>
+        <v>5.80514717102051</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G871" t="n">
-        <v>5.68707609176636</v>
+        <v>5.68707656860352</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G873" t="n">
-        <v>5.43125581741333</v>
+        <v>5.43125629425049</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G876" t="n">
-        <v>5.27382850646973</v>
+        <v>5.27382898330688</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G877" t="n">
-        <v>5.29350709915161</v>
+        <v>5.29350662231445</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G879" t="n">
-        <v>5.05736494064331</v>
+        <v>5.05736541748047</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G881" t="n">
-        <v>5.03768634796143</v>
+        <v>5.03768682479858</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G883" t="n">
-        <v>5.03768634796143</v>
+        <v>5.03768682479858</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G885" t="n">
-        <v>5.07704401016235</v>
+        <v>5.0770435333252</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G891" t="n">
-        <v>5.27382850646973</v>
+        <v>5.27382898330688</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G892" t="n">
-        <v>5.11640071868896</v>
+        <v>5.11640024185181</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G893" t="n">
-        <v>5.05736494064331</v>
+        <v>5.05736541748047</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G894" t="n">
-        <v>5.03768634796143</v>
+        <v>5.03768682479858</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G895" t="n">
-        <v>5.03768634796143</v>
+        <v>5.03768682479858</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23691,7 +23691,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G897" t="n">
-        <v>5.11640071868896</v>
+        <v>5.11640024185181</v>
       </c>
       <c r="H897" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G898" t="n">
-        <v>4.99832963943481</v>
+        <v>4.99833011627197</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G899" t="n">
-        <v>4.83106279373169</v>
+        <v>4.83106327056885</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G903" t="n">
-        <v>4.28990507125854</v>
+        <v>4.2899055480957</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G904" t="n">
-        <v>4.5654034614563</v>
+        <v>4.56540393829346</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G906" t="n">
-        <v>4.83106279373169</v>
+        <v>4.83106327056885</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G907" t="n">
-        <v>4.89009857177734</v>
+        <v>4.89009809494019</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G909" t="n">
-        <v>4.84090232849121</v>
+        <v>4.84090185165405</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G910" t="n">
-        <v>4.83106279373169</v>
+        <v>4.83106327056885</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G912" t="n">
-        <v>4.89009857177734</v>
+        <v>4.89009809494019</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G916" t="n">
-        <v>4.82122373580933</v>
+        <v>4.82122421264648</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G918" t="n">
-        <v>5.03768634796143</v>
+        <v>5.03768682479858</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G919" t="n">
-        <v>5.07704401016235</v>
+        <v>5.0770435333252</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G922" t="n">
-        <v>5.11640071868896</v>
+        <v>5.11640024185181</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G926" t="n">
-        <v>5.25414991378784</v>
+        <v>5.254150390625</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G928" t="n">
-        <v>5.27382850646973</v>
+        <v>5.27382898330688</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G929" t="n">
-        <v>5.29350709915161</v>
+        <v>5.29350662231445</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G930" t="n">
-        <v>5.29350709915161</v>
+        <v>5.29350662231445</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G937" t="n">
-        <v>5.11640071868896</v>
+        <v>5.11640024185181</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G939" t="n">
-        <v>5.11640071868896</v>
+        <v>5.11640024185181</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G941" t="n">
-        <v>5.07704401016235</v>
+        <v>5.0770435333252</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G944" t="n">
-        <v>5.13607931137085</v>
+        <v>5.13607883453369</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G949" t="n">
-        <v>5.25414991378784</v>
+        <v>5.254150390625</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25069,7 +25069,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G950" t="n">
-        <v>5.29350709915161</v>
+        <v>5.29350662231445</v>
       </c>
       <c r="H950" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G958" t="n">
-        <v>5.68707609176636</v>
+        <v>5.68707656860352</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25303,7 +25303,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G959" t="n">
-        <v>5.68707609176636</v>
+        <v>5.68707656860352</v>
       </c>
       <c r="H959" t="s">
         <v>8</v>
@@ -25381,7 +25381,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G962" t="n">
-        <v>5.80514669418335</v>
+        <v>5.80514717102051</v>
       </c>
       <c r="H962" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G965" t="n">
-        <v>5.80514669418335</v>
+        <v>5.80514717102051</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G969" t="n">
-        <v>6.1396803855896</v>
+        <v>6.13968086242676</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25589,7 +25589,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G970" t="n">
-        <v>6.19871664047241</v>
+        <v>6.19871616363525</v>
       </c>
       <c r="H970" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G971" t="n">
-        <v>6.33646535873413</v>
+        <v>6.33646583557129</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25641,7 +25641,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G972" t="n">
-        <v>6.27743053436279</v>
+        <v>6.27743005752563</v>
       </c>
       <c r="H972" t="s">
         <v>8</v>
@@ -25693,7 +25693,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G974" t="n">
-        <v>6.1396803855896</v>
+        <v>6.13968086242676</v>
       </c>
       <c r="H974" t="s">
         <v>8</v>
@@ -25771,7 +25771,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G977" t="n">
-        <v>6.00193166732788</v>
+        <v>6.00193119049072</v>
       </c>
       <c r="H977" t="s">
         <v>8</v>
@@ -38202,6 +38202,32 @@
         <v>10.5200004577637</v>
       </c>
       <c r="H1455" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1456">
+      <c r="A1456" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B1456" t="n">
+        <v>16922</v>
+      </c>
+      <c r="C1456" t="n">
+        <v>10.7600002288818</v>
+      </c>
+      <c r="D1456" t="n">
+        <v>10.5200004577637</v>
+      </c>
+      <c r="E1456" t="n">
+        <v>10.5200004577637</v>
+      </c>
+      <c r="F1456" t="n">
+        <v>10.5200004577637</v>
+      </c>
+      <c r="G1456" t="n">
+        <v>10.5200004577637</v>
+      </c>
+      <c r="H1456" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/EVISO.MI.xlsx
+++ b/data/EVISO.MI.xlsx
@@ -473,7 +473,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G4" t="n">
-        <v>2.11304235458374</v>
+        <v>2.11304259300232</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G8" t="n">
-        <v>2.09347724914551</v>
+        <v>2.09347701072693</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G10" t="n">
-        <v>1.99565100669861</v>
+        <v>1.99565076828003</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>2</v>
       </c>
       <c r="G11" t="n">
-        <v>1.95652055740356</v>
+        <v>1.95652067661285</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>2</v>
       </c>
       <c r="G12" t="n">
-        <v>1.95652055740356</v>
+        <v>1.95652067661285</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>2</v>
       </c>
       <c r="G13" t="n">
-        <v>1.95652055740356</v>
+        <v>1.95652067661285</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G14" t="n">
-        <v>1.93695533275604</v>
+        <v>1.93695557117462</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G15" t="n">
-        <v>1.9516294002533</v>
+        <v>1.95162928104401</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>2</v>
       </c>
       <c r="G18" t="n">
-        <v>1.95652055740356</v>
+        <v>1.95652067661285</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G19" t="n">
-        <v>1.96630322933197</v>
+        <v>1.96630311012268</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>2</v>
       </c>
       <c r="G20" t="n">
-        <v>1.95652055740356</v>
+        <v>1.95652067661285</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G22" t="n">
-        <v>1.96630322933197</v>
+        <v>1.96630311012268</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>2</v>
       </c>
       <c r="G23" t="n">
-        <v>1.95652055740356</v>
+        <v>1.95652067661285</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G24" t="n">
-        <v>1.99565100669861</v>
+        <v>1.99565076828003</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G25" t="n">
-        <v>1.96630322933197</v>
+        <v>1.96630311012268</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G26" t="n">
-        <v>1.96630322933197</v>
+        <v>1.96630311012268</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>2</v>
       </c>
       <c r="G27" t="n">
-        <v>1.95652055740356</v>
+        <v>1.95652067661285</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G28" t="n">
-        <v>1.9516294002533</v>
+        <v>1.95162928104401</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>2</v>
       </c>
       <c r="G29" t="n">
-        <v>1.95652055740356</v>
+        <v>1.95652067661285</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G37" t="n">
-        <v>2.21086835861206</v>
+        <v>2.21086859703064</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G38" t="n">
-        <v>2.28912925720215</v>
+        <v>2.28912878036499</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G39" t="n">
-        <v>2.26956415176392</v>
+        <v>2.26956367492676</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G41" t="n">
-        <v>2.31847667694092</v>
+        <v>2.3184769153595</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G43" t="n">
-        <v>2.32825946807861</v>
+        <v>2.32825970649719</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G46" t="n">
-        <v>2.28912925720215</v>
+        <v>2.28912878036499</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G48" t="n">
-        <v>2.28912925720215</v>
+        <v>2.28912878036499</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G49" t="n">
-        <v>2.26956415176392</v>
+        <v>2.26956367492676</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G50" t="n">
-        <v>2.28912925720215</v>
+        <v>2.28912878036499</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G51" t="n">
-        <v>2.26956415176392</v>
+        <v>2.26956367492676</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G61" t="n">
-        <v>2.23043346405029</v>
+        <v>2.23043370246887</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G64" t="n">
-        <v>2.21086835861206</v>
+        <v>2.21086859703064</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G65" t="n">
-        <v>2.1717381477356</v>
+        <v>2.17173790931702</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G68" t="n">
-        <v>2.23043346405029</v>
+        <v>2.23043370246887</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G76" t="n">
-        <v>2.1717381477356</v>
+        <v>2.17173790931702</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G79" t="n">
-        <v>2.23043346405029</v>
+        <v>2.23043370246887</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G81" t="n">
-        <v>2.21086835861206</v>
+        <v>2.21086859703064</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G83" t="n">
-        <v>2.21086835861206</v>
+        <v>2.21086859703064</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G93" t="n">
-        <v>2.32825946807861</v>
+        <v>2.32825970649719</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G95" t="n">
-        <v>2.26956415176392</v>
+        <v>2.26956367492676</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G102" t="n">
-        <v>2.42608547210693</v>
+        <v>2.42608571052551</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G104" t="n">
-        <v>2.6510853767395</v>
+        <v>2.65108561515808</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G105" t="n">
-        <v>2.73912906646729</v>
+        <v>2.73912882804871</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G107" t="n">
-        <v>2.69999861717224</v>
+        <v>2.69999837875366</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G110" t="n">
-        <v>2.61195516586304</v>
+        <v>2.61195492744446</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G111" t="n">
-        <v>2.53369426727295</v>
+        <v>2.53369402885437</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G112" t="n">
-        <v>2.54347658157349</v>
+        <v>2.54347681999207</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G113" t="n">
-        <v>2.54347658157349</v>
+        <v>2.54347681999207</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G114" t="n">
-        <v>2.53369426727295</v>
+        <v>2.53369402885437</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G116" t="n">
-        <v>2.51412916183472</v>
+        <v>2.51412892341614</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G117" t="n">
-        <v>2.54347658157349</v>
+        <v>2.54347681999207</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G118" t="n">
-        <v>2.49456381797791</v>
+        <v>2.49456357955933</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G119" t="n">
-        <v>2.51412916183472</v>
+        <v>2.51412892341614</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G120" t="n">
-        <v>2.47499871253967</v>
+        <v>2.47499847412109</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G122" t="n">
-        <v>2.39673805236816</v>
+        <v>2.39673781394958</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G123" t="n">
-        <v>2.40652012825012</v>
+        <v>2.4065203666687</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G124" t="n">
-        <v>2.31847667694092</v>
+        <v>2.3184769153595</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G125" t="n">
-        <v>2.41630291938782</v>
+        <v>2.4163031578064</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G126" t="n">
-        <v>2.40652012825012</v>
+        <v>2.4065203666687</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G127" t="n">
-        <v>2.53369426727295</v>
+        <v>2.53369402885437</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G128" t="n">
-        <v>2.48478126525879</v>
+        <v>2.48478102684021</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G129" t="n">
-        <v>2.49456381797791</v>
+        <v>2.49456357955933</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G130" t="n">
-        <v>2.52391147613525</v>
+        <v>2.52391171455383</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G132" t="n">
-        <v>2.49456381797791</v>
+        <v>2.49456357955933</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G134" t="n">
-        <v>2.51412916183472</v>
+        <v>2.51412892341614</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G137" t="n">
-        <v>2.47499871253967</v>
+        <v>2.47499847412109</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G138" t="n">
-        <v>2.39673805236816</v>
+        <v>2.39673781394958</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G139" t="n">
-        <v>2.31847667694092</v>
+        <v>2.3184769153595</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G141" t="n">
-        <v>2.41630291938782</v>
+        <v>2.4163031578064</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G142" t="n">
-        <v>2.40652012825012</v>
+        <v>2.4065203666687</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G143" t="n">
-        <v>2.42608547210693</v>
+        <v>2.42608571052551</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G144" t="n">
-        <v>2.42608547210693</v>
+        <v>2.42608571052551</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G145" t="n">
-        <v>2.42608547210693</v>
+        <v>2.42608571052551</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G148" t="n">
-        <v>2.40652012825012</v>
+        <v>2.4065203666687</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G150" t="n">
-        <v>2.42608547210693</v>
+        <v>2.42608571052551</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G151" t="n">
-        <v>2.39673805236816</v>
+        <v>2.39673781394958</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G154" t="n">
-        <v>2.48478126525879</v>
+        <v>2.48478102684021</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G156" t="n">
-        <v>2.49456381797791</v>
+        <v>2.49456357955933</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G157" t="n">
-        <v>2.49456381797791</v>
+        <v>2.49456357955933</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G159" t="n">
-        <v>2.41630291938782</v>
+        <v>2.4163031578064</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G160" t="n">
-        <v>2.39673805236816</v>
+        <v>2.39673781394958</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G161" t="n">
-        <v>2.42608547210693</v>
+        <v>2.42608571052551</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G162" t="n">
-        <v>2.42608547210693</v>
+        <v>2.42608571052551</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G163" t="n">
-        <v>2.61195516586304</v>
+        <v>2.61195492744446</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G164" t="n">
-        <v>2.81738996505737</v>
+        <v>2.81738972663879</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G165" t="n">
-        <v>2.81738996505737</v>
+        <v>2.81738972663879</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G166" t="n">
-        <v>2.92499852180481</v>
+        <v>2.92499828338623</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G167" t="n">
-        <v>2.92499852180481</v>
+        <v>2.92499828338623</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G168" t="n">
-        <v>2.905433177948</v>
+        <v>2.90543293952942</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G169" t="n">
-        <v>2.92499852180481</v>
+        <v>2.92499828338623</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G170" t="n">
-        <v>2.92499852180481</v>
+        <v>2.92499828338623</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G172" t="n">
-        <v>2.74891138076782</v>
+        <v>2.7489116191864</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G174" t="n">
-        <v>2.73912906646729</v>
+        <v>2.73912882804871</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G180" t="n">
-        <v>2.67065048217773</v>
+        <v>2.67065072059631</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G186" t="n">
-        <v>2.70978116989136</v>
+        <v>2.70978093147278</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G189" t="n">
-        <v>2.74891138076782</v>
+        <v>2.7489116191864</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G190" t="n">
-        <v>2.51412916183472</v>
+        <v>2.51412892341614</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G191" t="n">
-        <v>2.68043327331543</v>
+        <v>2.68043303489685</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G193" t="n">
-        <v>2.69999861717224</v>
+        <v>2.69999837875366</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G194" t="n">
-        <v>2.64130282402039</v>
+        <v>2.64130306243896</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G195" t="n">
-        <v>2.63152003288269</v>
+        <v>2.63152027130127</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G198" t="n">
-        <v>2.61195516586304</v>
+        <v>2.61195492744446</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G201" t="n">
-        <v>2.54347658157349</v>
+        <v>2.54347681999207</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G203" t="n">
-        <v>2.61195516586304</v>
+        <v>2.61195492744446</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G204" t="n">
-        <v>2.64130282402039</v>
+        <v>2.64130306243896</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G205" t="n">
-        <v>2.70978116989136</v>
+        <v>2.70978093147278</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G206" t="n">
-        <v>2.73912906646729</v>
+        <v>2.73912882804871</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G207" t="n">
-        <v>2.69999861717224</v>
+        <v>2.69999837875366</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G209" t="n">
-        <v>2.67065048217773</v>
+        <v>2.67065072059631</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G212" t="n">
-        <v>2.67065048217773</v>
+        <v>2.67065072059631</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G215" t="n">
-        <v>2.68043327331543</v>
+        <v>2.68043303489685</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G216" t="n">
-        <v>2.6510853767395</v>
+        <v>2.65108561515808</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G217" t="n">
-        <v>2.64130282402039</v>
+        <v>2.64130306243896</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G220" t="n">
-        <v>2.63691449165344</v>
+        <v>2.63691425323486</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G221" t="n">
-        <v>2.64675331115723</v>
+        <v>2.64675354957581</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G222" t="n">
-        <v>2.6270751953125</v>
+        <v>2.62707495689392</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G227" t="n">
-        <v>2.51884341239929</v>
+        <v>2.51884317398071</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G228" t="n">
-        <v>2.49916505813599</v>
+        <v>2.49916481971741</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G229" t="n">
-        <v>2.52868270874023</v>
+        <v>2.52868247032166</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G232" t="n">
-        <v>2.43029022216797</v>
+        <v>2.43029046058655</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G234" t="n">
-        <v>2.51884341239929</v>
+        <v>2.51884317398071</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G238" t="n">
-        <v>2.5582001209259</v>
+        <v>2.55820035934448</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G240" t="n">
-        <v>2.6270751953125</v>
+        <v>2.62707495689392</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G244" t="n">
-        <v>2.49916505813599</v>
+        <v>2.49916481971741</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G246" t="n">
-        <v>2.48932576179504</v>
+        <v>2.48932552337646</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G249" t="n">
-        <v>2.43029022216797</v>
+        <v>2.43029046058655</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G252" t="n">
-        <v>2.48932576179504</v>
+        <v>2.48932552337646</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G256" t="n">
-        <v>2.42045092582703</v>
+        <v>2.42045116424561</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G257" t="n">
-        <v>2.42045092582703</v>
+        <v>2.42045116424561</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G259" t="n">
-        <v>2.48932576179504</v>
+        <v>2.48932552337646</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G260" t="n">
-        <v>2.48932576179504</v>
+        <v>2.48932552337646</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G262" t="n">
-        <v>2.42045092582703</v>
+        <v>2.42045116424561</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G264" t="n">
-        <v>2.43029022216797</v>
+        <v>2.43029046058655</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G268" t="n">
-        <v>2.43029022216797</v>
+        <v>2.43029046058655</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G269" t="n">
-        <v>2.42045092582703</v>
+        <v>2.42045116424561</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G272" t="n">
-        <v>2.27286267280579</v>
+        <v>2.27286243438721</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G274" t="n">
-        <v>2.41061210632324</v>
+        <v>2.41061186790466</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G276" t="n">
-        <v>2.42045092582703</v>
+        <v>2.42045116424561</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G280" t="n">
-        <v>2.41061210632324</v>
+        <v>2.41061186790466</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G281" t="n">
-        <v>2.41061210632324</v>
+        <v>2.41061186790466</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G282" t="n">
-        <v>2.41061210632324</v>
+        <v>2.41061186790466</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G283" t="n">
-        <v>2.35157656669617</v>
+        <v>2.35157680511475</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G284" t="n">
-        <v>2.42045092582703</v>
+        <v>2.42045116424561</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G285" t="n">
-        <v>2.52868270874023</v>
+        <v>2.52868247032166</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G295" t="n">
-        <v>2.30238032341003</v>
+        <v>2.30238008499146</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G299" t="n">
-        <v>2.27286267280579</v>
+        <v>2.27286243438721</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G300" t="n">
-        <v>2.20398783683777</v>
+        <v>2.20398807525635</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G304" t="n">
-        <v>2.27286267280579</v>
+        <v>2.27286243438721</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G306" t="n">
-        <v>2.30238032341003</v>
+        <v>2.30238008499146</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G312" t="n">
-        <v>2.35157656669617</v>
+        <v>2.35157680511475</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G313" t="n">
-        <v>2.41061210632324</v>
+        <v>2.41061186790466</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G321" t="n">
-        <v>2.27286267280579</v>
+        <v>2.27286243438721</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G322" t="n">
-        <v>2.28270196914673</v>
+        <v>2.28270173072815</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G326" t="n">
-        <v>2.35157656669617</v>
+        <v>2.35157680511475</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G329" t="n">
-        <v>2.28270196914673</v>
+        <v>2.28270173072815</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G330" t="n">
-        <v>2.30238032341003</v>
+        <v>2.30238008499146</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G332" t="n">
-        <v>2.30238032341003</v>
+        <v>2.30238008499146</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G334" t="n">
-        <v>2.20398783683777</v>
+        <v>2.20398807525635</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>2.25</v>
       </c>
       <c r="G337" t="n">
-        <v>2.21382713317871</v>
+        <v>2.21382737159729</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G343" t="n">
-        <v>2.41061210632324</v>
+        <v>2.41061186790466</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G344" t="n">
-        <v>2.41061210632324</v>
+        <v>2.41061186790466</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G345" t="n">
-        <v>2.28270196914673</v>
+        <v>2.28270173072815</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G349" t="n">
-        <v>2.35157656669617</v>
+        <v>2.35157680511475</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G351" t="n">
-        <v>2.28270196914673</v>
+        <v>2.28270173072815</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G353" t="n">
-        <v>2.28270196914673</v>
+        <v>2.28270173072815</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G354" t="n">
-        <v>2.28270196914673</v>
+        <v>2.28270173072815</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G355" t="n">
-        <v>2.27286267280579</v>
+        <v>2.27286243438721</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G356" t="n">
-        <v>2.28270196914673</v>
+        <v>2.28270173072815</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G358" t="n">
-        <v>2.28270196914673</v>
+        <v>2.28270173072815</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G359" t="n">
-        <v>2.27286267280579</v>
+        <v>2.27286243438721</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G360" t="n">
-        <v>2.28270196914673</v>
+        <v>2.28270173072815</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G361" t="n">
-        <v>2.30238032341003</v>
+        <v>2.30238008499146</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G362" t="n">
-        <v>2.30238032341003</v>
+        <v>2.30238008499146</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G363" t="n">
-        <v>2.30238032341003</v>
+        <v>2.30238008499146</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G365" t="n">
-        <v>2.41061210632324</v>
+        <v>2.41061186790466</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G369" t="n">
-        <v>2.5385217666626</v>
+        <v>2.53852200508118</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G372" t="n">
-        <v>2.48932576179504</v>
+        <v>2.48932552337646</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G379" t="n">
-        <v>2.35157656669617</v>
+        <v>2.35157680511475</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G385" t="n">
-        <v>2.43029022216797</v>
+        <v>2.43029046058655</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G387" t="n">
-        <v>2.43029022216797</v>
+        <v>2.43029046058655</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G393" t="n">
-        <v>2.35157656669617</v>
+        <v>2.35157680511475</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G407" t="n">
-        <v>2.42045092582703</v>
+        <v>2.42045116424561</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G411" t="n">
-        <v>2.48932576179504</v>
+        <v>2.48932552337646</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G412" t="n">
-        <v>2.48932576179504</v>
+        <v>2.48932552337646</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G413" t="n">
-        <v>2.42045092582703</v>
+        <v>2.42045116424561</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G421" t="n">
-        <v>2.49916505813599</v>
+        <v>2.49916481971741</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G424" t="n">
-        <v>2.49916505813599</v>
+        <v>2.49916481971741</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G427" t="n">
-        <v>2.5582001209259</v>
+        <v>2.55820035934448</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G428" t="n">
-        <v>2.52868270874023</v>
+        <v>2.52868247032166</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G432" t="n">
-        <v>2.51884341239929</v>
+        <v>2.51884317398071</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G434" t="n">
-        <v>2.5582001209259</v>
+        <v>2.55820035934448</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G435" t="n">
-        <v>2.52868270874023</v>
+        <v>2.52868247032166</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G437" t="n">
-        <v>2.52868270874023</v>
+        <v>2.52868247032166</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G438" t="n">
-        <v>2.51884341239929</v>
+        <v>2.51884317398071</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G439" t="n">
-        <v>2.52868270874023</v>
+        <v>2.52868247032166</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G440" t="n">
-        <v>2.43029022216797</v>
+        <v>2.43029046058655</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G443" t="n">
-        <v>2.41061210632324</v>
+        <v>2.41061186790466</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G445" t="n">
-        <v>2.49916505813599</v>
+        <v>2.49916481971741</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G447" t="n">
-        <v>2.28270196914673</v>
+        <v>2.28270173072815</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G448" t="n">
-        <v>2.28270196914673</v>
+        <v>2.28270173072815</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G452" t="n">
-        <v>2.43029022216797</v>
+        <v>2.43029046058655</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G457" t="n">
-        <v>2.49916505813599</v>
+        <v>2.49916481971741</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G458" t="n">
-        <v>2.51884341239929</v>
+        <v>2.51884317398071</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G459" t="n">
-        <v>2.51884341239929</v>
+        <v>2.51884317398071</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G460" t="n">
-        <v>2.43029022216797</v>
+        <v>2.43029046058655</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G464" t="n">
-        <v>2.42045092582703</v>
+        <v>2.42045116424561</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G465" t="n">
-        <v>2.41061210632324</v>
+        <v>2.41061186790466</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G468" t="n">
-        <v>2.42045092582703</v>
+        <v>2.42045116424561</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G469" t="n">
-        <v>2.42045092582703</v>
+        <v>2.42045116424561</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G471" t="n">
-        <v>2.43029022216797</v>
+        <v>2.43029046058655</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G475" t="n">
-        <v>2.42045092582703</v>
+        <v>2.42045116424561</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G479" t="n">
-        <v>2.43029022216797</v>
+        <v>2.43029046058655</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G481" t="n">
-        <v>2.42045092582703</v>
+        <v>2.42045116424561</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G483" t="n">
-        <v>2.42045092582703</v>
+        <v>2.42045116424561</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G487" t="n">
-        <v>2.41061210632324</v>
+        <v>2.41061186790466</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G488" t="n">
-        <v>2.41061210632324</v>
+        <v>2.41061186790466</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G490" t="n">
-        <v>2.41061210632324</v>
+        <v>2.41061186790466</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G493" t="n">
-        <v>2.41061210632324</v>
+        <v>2.41061186790466</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G494" t="n">
-        <v>2.41061210632324</v>
+        <v>2.41061186790466</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G495" t="n">
-        <v>2.41061210632324</v>
+        <v>2.41061186790466</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G500" t="n">
-        <v>2.48932576179504</v>
+        <v>2.48932552337646</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G501" t="n">
-        <v>2.41061210632324</v>
+        <v>2.41061186790466</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G504" t="n">
-        <v>2.42045092582703</v>
+        <v>2.42045116424561</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G505" t="n">
-        <v>2.42045092582703</v>
+        <v>2.42045116424561</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G507" t="n">
-        <v>2.42045092582703</v>
+        <v>2.42045116424561</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G509" t="n">
-        <v>2.43029022216797</v>
+        <v>2.43029046058655</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G510" t="n">
-        <v>2.43029022216797</v>
+        <v>2.43029046058655</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G512" t="n">
-        <v>2.49916505813599</v>
+        <v>2.49916481971741</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G515" t="n">
-        <v>2.48932576179504</v>
+        <v>2.48932552337646</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G523" t="n">
-        <v>2.5582001209259</v>
+        <v>2.55820035934448</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G528" t="n">
-        <v>2.5582001209259</v>
+        <v>2.55820035934448</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G529" t="n">
-        <v>2.52868270874023</v>
+        <v>2.52868247032166</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G530" t="n">
-        <v>2.5582001209259</v>
+        <v>2.55820035934448</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G533" t="n">
-        <v>2.63691449165344</v>
+        <v>2.63691425323486</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G535" t="n">
-        <v>2.5385217666626</v>
+        <v>2.53852200508118</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G536" t="n">
-        <v>2.5582001209259</v>
+        <v>2.55820035934448</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G538" t="n">
-        <v>2.5582001209259</v>
+        <v>2.55820035934448</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G539" t="n">
-        <v>2.5582001209259</v>
+        <v>2.55820035934448</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G540" t="n">
-        <v>2.5385217666626</v>
+        <v>2.53852200508118</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G541" t="n">
-        <v>2.5582001209259</v>
+        <v>2.55820035934448</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G542" t="n">
-        <v>2.5582001209259</v>
+        <v>2.55820035934448</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G544" t="n">
-        <v>2.64675331115723</v>
+        <v>2.64675354957581</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G545" t="n">
-        <v>2.64675331115723</v>
+        <v>2.64675354957581</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G547" t="n">
-        <v>2.35157656669617</v>
+        <v>2.35157680511475</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G550" t="n">
-        <v>2.30238032341003</v>
+        <v>2.30238008499146</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G553" t="n">
-        <v>2.28270196914673</v>
+        <v>2.28270173072815</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G557" t="n">
-        <v>2.27286267280579</v>
+        <v>2.27286243438721</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G558" t="n">
-        <v>2.27286267280579</v>
+        <v>2.27286243438721</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G559" t="n">
-        <v>2.27286267280579</v>
+        <v>2.27286243438721</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G560" t="n">
-        <v>2.28270196914673</v>
+        <v>2.28270173072815</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G562" t="n">
-        <v>2.24334478378296</v>
+        <v>2.24334502220154</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G563" t="n">
-        <v>2.20398783683777</v>
+        <v>2.20398807525635</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>2.25</v>
       </c>
       <c r="G565" t="n">
-        <v>2.21382713317871</v>
+        <v>2.21382737159729</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G566" t="n">
-        <v>2.27286267280579</v>
+        <v>2.27286243438721</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G570" t="n">
-        <v>2.24334478378296</v>
+        <v>2.24334502220154</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G573" t="n">
-        <v>2.28270196914673</v>
+        <v>2.28270173072815</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G574" t="n">
-        <v>2.20398783683777</v>
+        <v>2.20398807525635</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G578" t="n">
-        <v>2.28270196914673</v>
+        <v>2.28270173072815</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G580" t="n">
-        <v>2.27286267280579</v>
+        <v>2.27286243438721</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G581" t="n">
-        <v>2.28270196914673</v>
+        <v>2.28270173072815</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G583" t="n">
-        <v>2.30238032341003</v>
+        <v>2.30238008499146</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G596" t="n">
-        <v>2.28270196914673</v>
+        <v>2.28270173072815</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G599" t="n">
-        <v>2.30238032341003</v>
+        <v>2.30238008499146</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G601" t="n">
-        <v>2.24334478378296</v>
+        <v>2.24334502220154</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G602" t="n">
-        <v>2.27286267280579</v>
+        <v>2.27286243438721</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G603" t="n">
-        <v>2.27286267280579</v>
+        <v>2.27286243438721</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G605" t="n">
-        <v>2.30238032341003</v>
+        <v>2.30238008499146</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G606" t="n">
-        <v>2.30238032341003</v>
+        <v>2.30238008499146</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G607" t="n">
-        <v>2.30238032341003</v>
+        <v>2.30238008499146</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G608" t="n">
-        <v>2.30238032341003</v>
+        <v>2.30238008499146</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G609" t="n">
-        <v>2.30238032341003</v>
+        <v>2.30238008499146</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G611" t="n">
-        <v>2.30238032341003</v>
+        <v>2.30238008499146</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G613" t="n">
-        <v>2.27286267280579</v>
+        <v>2.27286243438721</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G622" t="n">
-        <v>2.24334478378296</v>
+        <v>2.24334502220154</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>2.25</v>
       </c>
       <c r="G623" t="n">
-        <v>2.21382713317871</v>
+        <v>2.21382737159729</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G625" t="n">
-        <v>2.24334478378296</v>
+        <v>2.24334502220154</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G629" t="n">
-        <v>2.24334478378296</v>
+        <v>2.24334502220154</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G630" t="n">
-        <v>2.28270196914673</v>
+        <v>2.28270173072815</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G631" t="n">
-        <v>2.28270196914673</v>
+        <v>2.28270173072815</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G633" t="n">
-        <v>2.28270196914673</v>
+        <v>2.28270173072815</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G634" t="n">
-        <v>2.28270196914673</v>
+        <v>2.28270173072815</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G639" t="n">
-        <v>2.27286267280579</v>
+        <v>2.27286243438721</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G640" t="n">
-        <v>2.28270196914673</v>
+        <v>2.28270173072815</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G642" t="n">
-        <v>2.24334478378296</v>
+        <v>2.24334502220154</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>2.25</v>
       </c>
       <c r="G645" t="n">
-        <v>2.21382713317871</v>
+        <v>2.21382737159729</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G647" t="n">
-        <v>2.20398783683777</v>
+        <v>2.20398807525635</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>2.25</v>
       </c>
       <c r="G649" t="n">
-        <v>2.21382713317871</v>
+        <v>2.21382737159729</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G653" t="n">
-        <v>2.13511347770691</v>
+        <v>2.13511323928833</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G654" t="n">
-        <v>2.14495277404785</v>
+        <v>2.14495253562927</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>2.25</v>
       </c>
       <c r="G659" t="n">
-        <v>2.21382713317871</v>
+        <v>2.21382737159729</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>2.25</v>
       </c>
       <c r="G661" t="n">
-        <v>2.21382713317871</v>
+        <v>2.21382737159729</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G666" t="n">
-        <v>2.24334478378296</v>
+        <v>2.24334502220154</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G670" t="n">
-        <v>2.20398783683777</v>
+        <v>2.20398807525635</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G671" t="n">
-        <v>2.24334478378296</v>
+        <v>2.24334502220154</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G672" t="n">
-        <v>2.24334478378296</v>
+        <v>2.24334502220154</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G673" t="n">
-        <v>2.24334478378296</v>
+        <v>2.24334502220154</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G676" t="n">
-        <v>2.20398783683777</v>
+        <v>2.20398807525635</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G681" t="n">
-        <v>2.27286267280579</v>
+        <v>2.27286243438721</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G685" t="n">
-        <v>2.35157656669617</v>
+        <v>2.35157680511475</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G688" t="n">
-        <v>2.35157656669617</v>
+        <v>2.35157680511475</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G703" t="n">
-        <v>2.30238032341003</v>
+        <v>2.30238008499146</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G704" t="n">
-        <v>2.30238032341003</v>
+        <v>2.30238008499146</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G705" t="n">
-        <v>2.30238032341003</v>
+        <v>2.30238008499146</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G706" t="n">
-        <v>2.28270196914673</v>
+        <v>2.28270173072815</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G707" t="n">
-        <v>2.24334478378296</v>
+        <v>2.24334502220154</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G711" t="n">
-        <v>2.43029022216797</v>
+        <v>2.43029046058655</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G712" t="n">
-        <v>2.43029022216797</v>
+        <v>2.43029046058655</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G716" t="n">
-        <v>2.35157656669617</v>
+        <v>2.35157680511475</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G717" t="n">
-        <v>2.43029022216797</v>
+        <v>2.43029046058655</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G722" t="n">
-        <v>2.35157656669617</v>
+        <v>2.35157680511475</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G724" t="n">
-        <v>2.35157656669617</v>
+        <v>2.35157680511475</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G726" t="n">
-        <v>2.41061210632324</v>
+        <v>2.41061186790466</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G727" t="n">
-        <v>2.43029022216797</v>
+        <v>2.43029046058655</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G728" t="n">
-        <v>2.43029022216797</v>
+        <v>2.43029046058655</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G732" t="n">
-        <v>2.41061210632324</v>
+        <v>2.41061186790466</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G738" t="n">
-        <v>2.35157656669617</v>
+        <v>2.35157680511475</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G742" t="n">
-        <v>2.49916505813599</v>
+        <v>2.49916481971741</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G744" t="n">
-        <v>2.48932576179504</v>
+        <v>2.48932552337646</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G746" t="n">
-        <v>2.48932576179504</v>
+        <v>2.48932552337646</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G747" t="n">
-        <v>2.51884341239929</v>
+        <v>2.51884317398071</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G748" t="n">
-        <v>2.52868270874023</v>
+        <v>2.52868247032166</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G753" t="n">
-        <v>2.63691449165344</v>
+        <v>2.63691425323486</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G755" t="n">
-        <v>2.77466320991516</v>
+        <v>2.77466344833374</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G757" t="n">
-        <v>2.71562814712524</v>
+        <v>2.71562790870667</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G759" t="n">
-        <v>2.77466320991516</v>
+        <v>2.77466344833374</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G760" t="n">
-        <v>2.77466320991516</v>
+        <v>2.77466344833374</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G761" t="n">
-        <v>2.77466320991516</v>
+        <v>2.77466344833374</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G766" t="n">
-        <v>2.77466320991516</v>
+        <v>2.77466344833374</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G768" t="n">
-        <v>2.77466320991516</v>
+        <v>2.77466344833374</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G773" t="n">
-        <v>3.00096559524536</v>
+        <v>3.00096583366394</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G776" t="n">
-        <v>3.00096559524536</v>
+        <v>3.00096583366394</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G779" t="n">
-        <v>3.00096559524536</v>
+        <v>3.00096583366394</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G781" t="n">
-        <v>3.00096559524536</v>
+        <v>3.00096583366394</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G788" t="n">
-        <v>2.91241264343262</v>
+        <v>2.9124128818512</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G790" t="n">
-        <v>2.84353828430176</v>
+        <v>2.84353804588318</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G791" t="n">
-        <v>2.92225193977356</v>
+        <v>2.92225217819214</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -20987,7 +20987,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G793" t="n">
-        <v>2.92225193977356</v>
+        <v>2.92225217819214</v>
       </c>
       <c r="H793" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G794" t="n">
-        <v>2.90257358551025</v>
+        <v>2.90257334709167</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G798" t="n">
-        <v>2.91241264343262</v>
+        <v>2.9124128818512</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G806" t="n">
-        <v>3.09935808181763</v>
+        <v>3.09935832023621</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G808" t="n">
-        <v>3.13871502876282</v>
+        <v>3.1387152671814</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G815" t="n">
-        <v>3.16823291778564</v>
+        <v>3.16823267936707</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G822" t="n">
-        <v>3.32566046714783</v>
+        <v>3.32566070556641</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G827" t="n">
-        <v>3.41421365737915</v>
+        <v>3.41421341896057</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G828" t="n">
-        <v>3.42405295372009</v>
+        <v>3.42405271530151</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G829" t="n">
-        <v>3.48308801651001</v>
+        <v>3.48308825492859</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G831" t="n">
-        <v>3.57164120674133</v>
+        <v>3.57164144515991</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G834" t="n">
-        <v>4.12263870239258</v>
+        <v>4.12263822555542</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>4.25</v>
       </c>
       <c r="G835" t="n">
-        <v>4.18167352676392</v>
+        <v>4.18167400360107</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G839" t="n">
-        <v>4.22103023529053</v>
+        <v>4.22103071212769</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G841" t="n">
-        <v>4.2899055480957</v>
+        <v>4.28990507125854</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G843" t="n">
-        <v>4.39813613891602</v>
+        <v>4.39813661575317</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G849" t="n">
-        <v>5.0770435333252</v>
+        <v>5.07704401016235</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G850" t="n">
-        <v>4.99833011627197</v>
+        <v>4.99832963943481</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G852" t="n">
-        <v>5.03768682479858</v>
+        <v>5.03768634796143</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G857" t="n">
-        <v>5.03768682479858</v>
+        <v>5.03768634796143</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G859" t="n">
-        <v>4.86058044433594</v>
+        <v>4.8605809211731</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G860" t="n">
-        <v>4.83106327056885</v>
+        <v>4.83106279373169</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G861" t="n">
-        <v>4.89009809494019</v>
+        <v>4.89009857177734</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G864" t="n">
-        <v>4.89009809494019</v>
+        <v>4.89009857177734</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G867" t="n">
-        <v>5.29350662231445</v>
+        <v>5.29350709915161</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G869" t="n">
-        <v>5.7067551612854</v>
+        <v>5.70675468444824</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G870" t="n">
-        <v>5.80514717102051</v>
+        <v>5.80514669418335</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G871" t="n">
-        <v>5.68707656860352</v>
+        <v>5.68707609176636</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G873" t="n">
-        <v>5.43125629425049</v>
+        <v>5.43125581741333</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G876" t="n">
-        <v>5.27382898330688</v>
+        <v>5.27382850646973</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G877" t="n">
-        <v>5.29350662231445</v>
+        <v>5.29350709915161</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G879" t="n">
-        <v>5.05736541748047</v>
+        <v>5.05736494064331</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G881" t="n">
-        <v>5.03768682479858</v>
+        <v>5.03768634796143</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G883" t="n">
-        <v>5.03768682479858</v>
+        <v>5.03768634796143</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G885" t="n">
-        <v>5.0770435333252</v>
+        <v>5.07704401016235</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G891" t="n">
-        <v>5.27382898330688</v>
+        <v>5.27382850646973</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G892" t="n">
-        <v>5.11640024185181</v>
+        <v>5.11640071868896</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G893" t="n">
-        <v>5.05736541748047</v>
+        <v>5.05736494064331</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G894" t="n">
-        <v>5.03768682479858</v>
+        <v>5.03768634796143</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G895" t="n">
-        <v>5.03768682479858</v>
+        <v>5.03768634796143</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23691,7 +23691,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G897" t="n">
-        <v>5.11640024185181</v>
+        <v>5.11640071868896</v>
       </c>
       <c r="H897" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G898" t="n">
-        <v>4.99833011627197</v>
+        <v>4.99832963943481</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G899" t="n">
-        <v>4.83106327056885</v>
+        <v>4.83106279373169</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G903" t="n">
-        <v>4.2899055480957</v>
+        <v>4.28990507125854</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G904" t="n">
-        <v>4.56540393829346</v>
+        <v>4.5654034614563</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G906" t="n">
-        <v>4.83106327056885</v>
+        <v>4.83106279373169</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G907" t="n">
-        <v>4.89009809494019</v>
+        <v>4.89009857177734</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G909" t="n">
-        <v>4.84090185165405</v>
+        <v>4.84090232849121</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G910" t="n">
-        <v>4.83106327056885</v>
+        <v>4.83106279373169</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G912" t="n">
-        <v>4.89009809494019</v>
+        <v>4.89009857177734</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G916" t="n">
-        <v>4.82122421264648</v>
+        <v>4.82122373580933</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G918" t="n">
-        <v>5.03768682479858</v>
+        <v>5.03768634796143</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G919" t="n">
-        <v>5.0770435333252</v>
+        <v>5.07704401016235</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G922" t="n">
-        <v>5.11640024185181</v>
+        <v>5.11640071868896</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G926" t="n">
-        <v>5.254150390625</v>
+        <v>5.25414991378784</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G928" t="n">
-        <v>5.27382898330688</v>
+        <v>5.27382850646973</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G929" t="n">
-        <v>5.29350662231445</v>
+        <v>5.29350709915161</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G930" t="n">
-        <v>5.29350662231445</v>
+        <v>5.29350709915161</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G937" t="n">
-        <v>5.11640024185181</v>
+        <v>5.11640071868896</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G939" t="n">
-        <v>5.11640024185181</v>
+        <v>5.11640071868896</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G941" t="n">
-        <v>5.0770435333252</v>
+        <v>5.07704401016235</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G944" t="n">
-        <v>5.13607883453369</v>
+        <v>5.13607931137085</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G949" t="n">
-        <v>5.254150390625</v>
+        <v>5.25414991378784</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25069,7 +25069,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G950" t="n">
-        <v>5.29350662231445</v>
+        <v>5.29350709915161</v>
       </c>
       <c r="H950" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G958" t="n">
-        <v>5.68707656860352</v>
+        <v>5.68707609176636</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25303,7 +25303,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G959" t="n">
-        <v>5.68707656860352</v>
+        <v>5.68707609176636</v>
       </c>
       <c r="H959" t="s">
         <v>8</v>
@@ -25381,7 +25381,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G962" t="n">
-        <v>5.80514717102051</v>
+        <v>5.80514669418335</v>
       </c>
       <c r="H962" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G965" t="n">
-        <v>5.80514717102051</v>
+        <v>5.80514669418335</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G969" t="n">
-        <v>6.13968086242676</v>
+        <v>6.1396803855896</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25589,7 +25589,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G970" t="n">
-        <v>6.19871616363525</v>
+        <v>6.19871664047241</v>
       </c>
       <c r="H970" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G971" t="n">
-        <v>6.33646583557129</v>
+        <v>6.33646535873413</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25641,7 +25641,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G972" t="n">
-        <v>6.27743005752563</v>
+        <v>6.27743053436279</v>
       </c>
       <c r="H972" t="s">
         <v>8</v>
@@ -25693,7 +25693,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G974" t="n">
-        <v>6.13968086242676</v>
+        <v>6.1396803855896</v>
       </c>
       <c r="H974" t="s">
         <v>8</v>
@@ -25771,7 +25771,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G977" t="n">
-        <v>6.00193119049072</v>
+        <v>6.00193166732788</v>
       </c>
       <c r="H977" t="s">
         <v>8</v>
@@ -38228,6 +38228,32 @@
         <v>10.5200004577637</v>
       </c>
       <c r="H1456" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1457">
+      <c r="A1457" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B1457" t="n">
+        <v>17798</v>
+      </c>
+      <c r="C1457" t="n">
+        <v>10.6999998092651</v>
+      </c>
+      <c r="D1457" t="n">
+        <v>10.1400003433228</v>
+      </c>
+      <c r="E1457" t="n">
+        <v>10.5200004577637</v>
+      </c>
+      <c r="F1457" t="n">
+        <v>10.3800001144409</v>
+      </c>
+      <c r="G1457" t="n">
+        <v>10.3800001144409</v>
+      </c>
+      <c r="H1457" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/EVISO.MI.xlsx
+++ b/data/EVISO.MI.xlsx
@@ -473,7 +473,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G4" t="n">
-        <v>2.11304259300232</v>
+        <v>2.11304235458374</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G10" t="n">
-        <v>1.99565076828003</v>
+        <v>1.9956511259079</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G14" t="n">
-        <v>1.93695557117462</v>
+        <v>1.93695545196533</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G16" t="n">
-        <v>1.87825977802277</v>
+        <v>1.87825965881348</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G19" t="n">
-        <v>1.96630311012268</v>
+        <v>1.96630322933197</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G22" t="n">
-        <v>1.96630311012268</v>
+        <v>1.96630322933197</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G24" t="n">
-        <v>1.99565076828003</v>
+        <v>1.9956511259079</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G25" t="n">
-        <v>1.96630311012268</v>
+        <v>1.96630322933197</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G26" t="n">
-        <v>1.96630311012268</v>
+        <v>1.96630322933197</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G30" t="n">
-        <v>2.08369445800781</v>
+        <v>2.08369469642639</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G35" t="n">
-        <v>2.33804225921631</v>
+        <v>2.33804202079773</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G37" t="n">
-        <v>2.21086859703064</v>
+        <v>2.21086835861206</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G38" t="n">
-        <v>2.28912878036499</v>
+        <v>2.28912901878357</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G39" t="n">
-        <v>2.26956367492676</v>
+        <v>2.26956391334534</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G44" t="n">
-        <v>2.27934646606445</v>
+        <v>2.27934670448303</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G46" t="n">
-        <v>2.28912878036499</v>
+        <v>2.28912901878357</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G48" t="n">
-        <v>2.28912878036499</v>
+        <v>2.28912901878357</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G49" t="n">
-        <v>2.26956367492676</v>
+        <v>2.26956391334534</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G50" t="n">
-        <v>2.28912878036499</v>
+        <v>2.28912901878357</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G51" t="n">
-        <v>2.26956367492676</v>
+        <v>2.26956391334534</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G53" t="n">
-        <v>2.2499988079071</v>
+        <v>2.24999856948853</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G55" t="n">
-        <v>2.2499988079071</v>
+        <v>2.24999856948853</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G56" t="n">
-        <v>2.2499988079071</v>
+        <v>2.24999856948853</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G61" t="n">
-        <v>2.23043370246887</v>
+        <v>2.23043346405029</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G64" t="n">
-        <v>2.21086859703064</v>
+        <v>2.21086835861206</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G65" t="n">
-        <v>2.17173790931702</v>
+        <v>2.1717381477356</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G68" t="n">
-        <v>2.23043370246887</v>
+        <v>2.23043346405029</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G76" t="n">
-        <v>2.17173790931702</v>
+        <v>2.1717381477356</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G79" t="n">
-        <v>2.23043370246887</v>
+        <v>2.23043346405029</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G81" t="n">
-        <v>2.21086859703064</v>
+        <v>2.21086835861206</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G83" t="n">
-        <v>2.21086859703064</v>
+        <v>2.21086835861206</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G91" t="n">
-        <v>2.33804225921631</v>
+        <v>2.33804202079773</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G94" t="n">
-        <v>2.27934646606445</v>
+        <v>2.27934670448303</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G95" t="n">
-        <v>2.26956367492676</v>
+        <v>2.26956391334534</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G96" t="n">
-        <v>2.2499988079071</v>
+        <v>2.24999856948853</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G97" t="n">
-        <v>2.27934646606445</v>
+        <v>2.27934670448303</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G100" t="n">
-        <v>2.33804225921631</v>
+        <v>2.33804202079773</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G104" t="n">
-        <v>2.65108561515808</v>
+        <v>2.6510853767395</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G105" t="n">
-        <v>2.73912882804871</v>
+        <v>2.73912906646729</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G110" t="n">
-        <v>2.61195492744446</v>
+        <v>2.61195516586304</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G111" t="n">
-        <v>2.53369402885437</v>
+        <v>2.53369426727295</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G112" t="n">
-        <v>2.54347681999207</v>
+        <v>2.54347658157349</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G113" t="n">
-        <v>2.54347681999207</v>
+        <v>2.54347658157349</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G114" t="n">
-        <v>2.53369402885437</v>
+        <v>2.53369426727295</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G116" t="n">
-        <v>2.51412892341614</v>
+        <v>2.51412916183472</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G117" t="n">
-        <v>2.54347681999207</v>
+        <v>2.54347658157349</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G118" t="n">
-        <v>2.49456357955933</v>
+        <v>2.49456381797791</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G119" t="n">
-        <v>2.51412892341614</v>
+        <v>2.51412916183472</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G120" t="n">
-        <v>2.47499847412109</v>
+        <v>2.47499871253967</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>2.5</v>
       </c>
       <c r="G121" t="n">
-        <v>2.44565081596375</v>
+        <v>2.44565057754517</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G125" t="n">
-        <v>2.4163031578064</v>
+        <v>2.41630291938782</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G127" t="n">
-        <v>2.53369402885437</v>
+        <v>2.53369426727295</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G128" t="n">
-        <v>2.48478102684021</v>
+        <v>2.48478126525879</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G129" t="n">
-        <v>2.49456357955933</v>
+        <v>2.49456381797791</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G130" t="n">
-        <v>2.52391171455383</v>
+        <v>2.52391147613525</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G132" t="n">
-        <v>2.49456357955933</v>
+        <v>2.49456381797791</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G134" t="n">
-        <v>2.51412892341614</v>
+        <v>2.51412916183472</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>2.5</v>
       </c>
       <c r="G135" t="n">
-        <v>2.44565081596375</v>
+        <v>2.44565057754517</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>2.5</v>
       </c>
       <c r="G136" t="n">
-        <v>2.44565081596375</v>
+        <v>2.44565057754517</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G137" t="n">
-        <v>2.47499847412109</v>
+        <v>2.47499871253967</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G141" t="n">
-        <v>2.4163031578064</v>
+        <v>2.41630291938782</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>2.5</v>
       </c>
       <c r="G146" t="n">
-        <v>2.44565081596375</v>
+        <v>2.44565057754517</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>2.5</v>
       </c>
       <c r="G147" t="n">
-        <v>2.44565081596375</v>
+        <v>2.44565057754517</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>2.5</v>
       </c>
       <c r="G152" t="n">
-        <v>2.44565081596375</v>
+        <v>2.44565057754517</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>2.5</v>
       </c>
       <c r="G153" t="n">
-        <v>2.44565081596375</v>
+        <v>2.44565057754517</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G154" t="n">
-        <v>2.48478102684021</v>
+        <v>2.48478126525879</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G156" t="n">
-        <v>2.49456357955933</v>
+        <v>2.49456381797791</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G157" t="n">
-        <v>2.49456357955933</v>
+        <v>2.49456381797791</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G159" t="n">
-        <v>2.4163031578064</v>
+        <v>2.41630291938782</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G163" t="n">
-        <v>2.61195492744446</v>
+        <v>2.61195516586304</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G164" t="n">
-        <v>2.81738972663879</v>
+        <v>2.81738996505737</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G165" t="n">
-        <v>2.81738972663879</v>
+        <v>2.81738996505737</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G166" t="n">
-        <v>2.92499828338623</v>
+        <v>2.92499852180481</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G167" t="n">
-        <v>2.92499828338623</v>
+        <v>2.92499852180481</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G168" t="n">
-        <v>2.90543293952942</v>
+        <v>2.905433177948</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G169" t="n">
-        <v>2.92499828338623</v>
+        <v>2.92499852180481</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G170" t="n">
-        <v>2.92499828338623</v>
+        <v>2.92499852180481</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G171" t="n">
-        <v>2.83695507049561</v>
+        <v>2.83695530891418</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G172" t="n">
-        <v>2.7489116191864</v>
+        <v>2.74891138076782</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G174" t="n">
-        <v>2.73912882804871</v>
+        <v>2.73912906646729</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G181" t="n">
-        <v>2.6608681678772</v>
+        <v>2.66086792945862</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G184" t="n">
-        <v>2.6608681678772</v>
+        <v>2.66086792945862</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G186" t="n">
-        <v>2.70978093147278</v>
+        <v>2.70978116989136</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G189" t="n">
-        <v>2.7489116191864</v>
+        <v>2.74891138076782</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G190" t="n">
-        <v>2.51412892341614</v>
+        <v>2.51412916183472</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G191" t="n">
-        <v>2.68043303489685</v>
+        <v>2.68043327331543</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G192" t="n">
-        <v>2.6608681678772</v>
+        <v>2.66086792945862</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G194" t="n">
-        <v>2.64130306243896</v>
+        <v>2.64130282402039</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G198" t="n">
-        <v>2.61195492744446</v>
+        <v>2.61195516586304</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G201" t="n">
-        <v>2.54347681999207</v>
+        <v>2.54347658157349</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G203" t="n">
-        <v>2.61195492744446</v>
+        <v>2.61195516586304</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G204" t="n">
-        <v>2.64130306243896</v>
+        <v>2.64130282402039</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G205" t="n">
-        <v>2.70978093147278</v>
+        <v>2.70978116989136</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G206" t="n">
-        <v>2.73912882804871</v>
+        <v>2.73912906646729</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G208" t="n">
-        <v>2.6608681678772</v>
+        <v>2.66086792945862</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G210" t="n">
-        <v>2.6608681678772</v>
+        <v>2.66086792945862</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G211" t="n">
-        <v>2.6608681678772</v>
+        <v>2.66086792945862</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G213" t="n">
-        <v>2.6608681678772</v>
+        <v>2.66086792945862</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G214" t="n">
-        <v>2.6608681678772</v>
+        <v>2.66086792945862</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G215" t="n">
-        <v>2.68043303489685</v>
+        <v>2.68043327331543</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G216" t="n">
-        <v>2.65108561515808</v>
+        <v>2.6510853767395</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G217" t="n">
-        <v>2.64130306243896</v>
+        <v>2.64130282402039</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G220" t="n">
-        <v>2.63691425323486</v>
+        <v>2.63691449165344</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G221" t="n">
-        <v>2.64675354957581</v>
+        <v>2.64675331115723</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G222" t="n">
-        <v>2.62707495689392</v>
+        <v>2.6270751953125</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G227" t="n">
-        <v>2.51884317398071</v>
+        <v>2.51884341239929</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G228" t="n">
-        <v>2.49916481971741</v>
+        <v>2.49916505813599</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G229" t="n">
-        <v>2.52868247032166</v>
+        <v>2.52868270874023</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G232" t="n">
-        <v>2.43029046058655</v>
+        <v>2.43029022216797</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G234" t="n">
-        <v>2.51884317398071</v>
+        <v>2.51884341239929</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G238" t="n">
-        <v>2.55820035934448</v>
+        <v>2.5582001209259</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G240" t="n">
-        <v>2.62707495689392</v>
+        <v>2.6270751953125</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G244" t="n">
-        <v>2.49916481971741</v>
+        <v>2.49916505813599</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G246" t="n">
-        <v>2.48932552337646</v>
+        <v>2.48932576179504</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G249" t="n">
-        <v>2.43029046058655</v>
+        <v>2.43029022216797</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G252" t="n">
-        <v>2.48932552337646</v>
+        <v>2.48932576179504</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G256" t="n">
-        <v>2.42045116424561</v>
+        <v>2.42045092582703</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G257" t="n">
-        <v>2.42045116424561</v>
+        <v>2.42045092582703</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G259" t="n">
-        <v>2.48932552337646</v>
+        <v>2.48932576179504</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G260" t="n">
-        <v>2.48932552337646</v>
+        <v>2.48932576179504</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G262" t="n">
-        <v>2.42045116424561</v>
+        <v>2.42045092582703</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G264" t="n">
-        <v>2.43029046058655</v>
+        <v>2.43029022216797</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G268" t="n">
-        <v>2.43029046058655</v>
+        <v>2.43029022216797</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G269" t="n">
-        <v>2.42045116424561</v>
+        <v>2.42045092582703</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G272" t="n">
-        <v>2.27286243438721</v>
+        <v>2.27286267280579</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G274" t="n">
-        <v>2.41061186790466</v>
+        <v>2.41061210632324</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G276" t="n">
-        <v>2.42045116424561</v>
+        <v>2.42045092582703</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G280" t="n">
-        <v>2.41061186790466</v>
+        <v>2.41061210632324</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G281" t="n">
-        <v>2.41061186790466</v>
+        <v>2.41061210632324</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G282" t="n">
-        <v>2.41061186790466</v>
+        <v>2.41061210632324</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G283" t="n">
-        <v>2.35157680511475</v>
+        <v>2.35157656669617</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G284" t="n">
-        <v>2.42045116424561</v>
+        <v>2.42045092582703</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G285" t="n">
-        <v>2.52868247032166</v>
+        <v>2.52868270874023</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G295" t="n">
-        <v>2.30238008499146</v>
+        <v>2.30238032341003</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G299" t="n">
-        <v>2.27286243438721</v>
+        <v>2.27286267280579</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G300" t="n">
-        <v>2.20398807525635</v>
+        <v>2.20398783683777</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G304" t="n">
-        <v>2.27286243438721</v>
+        <v>2.27286267280579</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G306" t="n">
-        <v>2.30238008499146</v>
+        <v>2.30238032341003</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G312" t="n">
-        <v>2.35157680511475</v>
+        <v>2.35157656669617</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G313" t="n">
-        <v>2.41061186790466</v>
+        <v>2.41061210632324</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G321" t="n">
-        <v>2.27286243438721</v>
+        <v>2.27286267280579</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G322" t="n">
-        <v>2.28270173072815</v>
+        <v>2.28270196914673</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G326" t="n">
-        <v>2.35157680511475</v>
+        <v>2.35157656669617</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G329" t="n">
-        <v>2.28270173072815</v>
+        <v>2.28270196914673</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G330" t="n">
-        <v>2.30238008499146</v>
+        <v>2.30238032341003</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G332" t="n">
-        <v>2.30238008499146</v>
+        <v>2.30238032341003</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G334" t="n">
-        <v>2.20398807525635</v>
+        <v>2.20398783683777</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>2.25</v>
       </c>
       <c r="G337" t="n">
-        <v>2.21382737159729</v>
+        <v>2.21382713317871</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G343" t="n">
-        <v>2.41061186790466</v>
+        <v>2.41061210632324</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G344" t="n">
-        <v>2.41061186790466</v>
+        <v>2.41061210632324</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G345" t="n">
-        <v>2.28270173072815</v>
+        <v>2.28270196914673</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G349" t="n">
-        <v>2.35157680511475</v>
+        <v>2.35157656669617</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G351" t="n">
-        <v>2.28270173072815</v>
+        <v>2.28270196914673</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G353" t="n">
-        <v>2.28270173072815</v>
+        <v>2.28270196914673</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G354" t="n">
-        <v>2.28270173072815</v>
+        <v>2.28270196914673</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G355" t="n">
-        <v>2.27286243438721</v>
+        <v>2.27286267280579</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G356" t="n">
-        <v>2.28270173072815</v>
+        <v>2.28270196914673</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G358" t="n">
-        <v>2.28270173072815</v>
+        <v>2.28270196914673</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G359" t="n">
-        <v>2.27286243438721</v>
+        <v>2.27286267280579</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G360" t="n">
-        <v>2.28270173072815</v>
+        <v>2.28270196914673</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G361" t="n">
-        <v>2.30238008499146</v>
+        <v>2.30238032341003</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G362" t="n">
-        <v>2.30238008499146</v>
+        <v>2.30238032341003</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G363" t="n">
-        <v>2.30238008499146</v>
+        <v>2.30238032341003</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G365" t="n">
-        <v>2.41061186790466</v>
+        <v>2.41061210632324</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G369" t="n">
-        <v>2.53852200508118</v>
+        <v>2.5385217666626</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G372" t="n">
-        <v>2.48932552337646</v>
+        <v>2.48932576179504</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G379" t="n">
-        <v>2.35157680511475</v>
+        <v>2.35157656669617</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G385" t="n">
-        <v>2.43029046058655</v>
+        <v>2.43029022216797</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G387" t="n">
-        <v>2.43029046058655</v>
+        <v>2.43029022216797</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G393" t="n">
-        <v>2.35157680511475</v>
+        <v>2.35157656669617</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G407" t="n">
-        <v>2.42045116424561</v>
+        <v>2.42045092582703</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G411" t="n">
-        <v>2.48932552337646</v>
+        <v>2.48932576179504</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G412" t="n">
-        <v>2.48932552337646</v>
+        <v>2.48932576179504</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G413" t="n">
-        <v>2.42045116424561</v>
+        <v>2.42045092582703</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G421" t="n">
-        <v>2.49916481971741</v>
+        <v>2.49916505813599</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G424" t="n">
-        <v>2.49916481971741</v>
+        <v>2.49916505813599</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G427" t="n">
-        <v>2.55820035934448</v>
+        <v>2.5582001209259</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G428" t="n">
-        <v>2.52868247032166</v>
+        <v>2.52868270874023</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G432" t="n">
-        <v>2.51884317398071</v>
+        <v>2.51884341239929</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G434" t="n">
-        <v>2.55820035934448</v>
+        <v>2.5582001209259</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G435" t="n">
-        <v>2.52868247032166</v>
+        <v>2.52868270874023</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G437" t="n">
-        <v>2.52868247032166</v>
+        <v>2.52868270874023</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G438" t="n">
-        <v>2.51884317398071</v>
+        <v>2.51884341239929</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G439" t="n">
-        <v>2.52868247032166</v>
+        <v>2.52868270874023</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G440" t="n">
-        <v>2.43029046058655</v>
+        <v>2.43029022216797</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G443" t="n">
-        <v>2.41061186790466</v>
+        <v>2.41061210632324</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G445" t="n">
-        <v>2.49916481971741</v>
+        <v>2.49916505813599</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G447" t="n">
-        <v>2.28270173072815</v>
+        <v>2.28270196914673</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G448" t="n">
-        <v>2.28270173072815</v>
+        <v>2.28270196914673</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G452" t="n">
-        <v>2.43029046058655</v>
+        <v>2.43029022216797</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G457" t="n">
-        <v>2.49916481971741</v>
+        <v>2.49916505813599</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G458" t="n">
-        <v>2.51884317398071</v>
+        <v>2.51884341239929</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G459" t="n">
-        <v>2.51884317398071</v>
+        <v>2.51884341239929</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G460" t="n">
-        <v>2.43029046058655</v>
+        <v>2.43029022216797</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G464" t="n">
-        <v>2.42045116424561</v>
+        <v>2.42045092582703</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G465" t="n">
-        <v>2.41061186790466</v>
+        <v>2.41061210632324</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G468" t="n">
-        <v>2.42045116424561</v>
+        <v>2.42045092582703</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G469" t="n">
-        <v>2.42045116424561</v>
+        <v>2.42045092582703</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G471" t="n">
-        <v>2.43029046058655</v>
+        <v>2.43029022216797</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G475" t="n">
-        <v>2.42045116424561</v>
+        <v>2.42045092582703</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G479" t="n">
-        <v>2.43029046058655</v>
+        <v>2.43029022216797</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G481" t="n">
-        <v>2.42045116424561</v>
+        <v>2.42045092582703</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G483" t="n">
-        <v>2.42045116424561</v>
+        <v>2.42045092582703</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G487" t="n">
-        <v>2.41061186790466</v>
+        <v>2.41061210632324</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G488" t="n">
-        <v>2.41061186790466</v>
+        <v>2.41061210632324</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G490" t="n">
-        <v>2.41061186790466</v>
+        <v>2.41061210632324</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G493" t="n">
-        <v>2.41061186790466</v>
+        <v>2.41061210632324</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G494" t="n">
-        <v>2.41061186790466</v>
+        <v>2.41061210632324</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G495" t="n">
-        <v>2.41061186790466</v>
+        <v>2.41061210632324</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G500" t="n">
-        <v>2.48932552337646</v>
+        <v>2.48932576179504</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G501" t="n">
-        <v>2.41061186790466</v>
+        <v>2.41061210632324</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G504" t="n">
-        <v>2.42045116424561</v>
+        <v>2.42045092582703</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G505" t="n">
-        <v>2.42045116424561</v>
+        <v>2.42045092582703</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G507" t="n">
-        <v>2.42045116424561</v>
+        <v>2.42045092582703</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G509" t="n">
-        <v>2.43029046058655</v>
+        <v>2.43029022216797</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G510" t="n">
-        <v>2.43029046058655</v>
+        <v>2.43029022216797</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G512" t="n">
-        <v>2.49916481971741</v>
+        <v>2.49916505813599</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G515" t="n">
-        <v>2.48932552337646</v>
+        <v>2.48932576179504</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G523" t="n">
-        <v>2.55820035934448</v>
+        <v>2.5582001209259</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G528" t="n">
-        <v>2.55820035934448</v>
+        <v>2.5582001209259</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G529" t="n">
-        <v>2.52868247032166</v>
+        <v>2.52868270874023</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G530" t="n">
-        <v>2.55820035934448</v>
+        <v>2.5582001209259</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G533" t="n">
-        <v>2.63691425323486</v>
+        <v>2.63691449165344</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G535" t="n">
-        <v>2.53852200508118</v>
+        <v>2.5385217666626</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G536" t="n">
-        <v>2.55820035934448</v>
+        <v>2.5582001209259</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G538" t="n">
-        <v>2.55820035934448</v>
+        <v>2.5582001209259</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G539" t="n">
-        <v>2.55820035934448</v>
+        <v>2.5582001209259</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G540" t="n">
-        <v>2.53852200508118</v>
+        <v>2.5385217666626</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G541" t="n">
-        <v>2.55820035934448</v>
+        <v>2.5582001209259</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G542" t="n">
-        <v>2.55820035934448</v>
+        <v>2.5582001209259</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G544" t="n">
-        <v>2.64675354957581</v>
+        <v>2.64675331115723</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G545" t="n">
-        <v>2.64675354957581</v>
+        <v>2.64675331115723</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G547" t="n">
-        <v>2.35157680511475</v>
+        <v>2.35157656669617</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G550" t="n">
-        <v>2.30238008499146</v>
+        <v>2.30238032341003</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G553" t="n">
-        <v>2.28270173072815</v>
+        <v>2.28270196914673</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G557" t="n">
-        <v>2.27286243438721</v>
+        <v>2.27286267280579</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G558" t="n">
-        <v>2.27286243438721</v>
+        <v>2.27286267280579</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G559" t="n">
-        <v>2.27286243438721</v>
+        <v>2.27286267280579</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G560" t="n">
-        <v>2.28270173072815</v>
+        <v>2.28270196914673</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G562" t="n">
-        <v>2.24334502220154</v>
+        <v>2.24334478378296</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G563" t="n">
-        <v>2.20398807525635</v>
+        <v>2.20398783683777</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>2.25</v>
       </c>
       <c r="G565" t="n">
-        <v>2.21382737159729</v>
+        <v>2.21382713317871</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G566" t="n">
-        <v>2.27286243438721</v>
+        <v>2.27286267280579</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G570" t="n">
-        <v>2.24334502220154</v>
+        <v>2.24334478378296</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G573" t="n">
-        <v>2.28270173072815</v>
+        <v>2.28270196914673</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G574" t="n">
-        <v>2.20398807525635</v>
+        <v>2.20398783683777</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G578" t="n">
-        <v>2.28270173072815</v>
+        <v>2.28270196914673</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G580" t="n">
-        <v>2.27286243438721</v>
+        <v>2.27286267280579</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G581" t="n">
-        <v>2.28270173072815</v>
+        <v>2.28270196914673</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G583" t="n">
-        <v>2.30238008499146</v>
+        <v>2.30238032341003</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G596" t="n">
-        <v>2.28270173072815</v>
+        <v>2.28270196914673</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G599" t="n">
-        <v>2.30238008499146</v>
+        <v>2.30238032341003</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G601" t="n">
-        <v>2.24334502220154</v>
+        <v>2.24334478378296</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G602" t="n">
-        <v>2.27286243438721</v>
+        <v>2.27286267280579</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G603" t="n">
-        <v>2.27286243438721</v>
+        <v>2.27286267280579</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G605" t="n">
-        <v>2.30238008499146</v>
+        <v>2.30238032341003</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G606" t="n">
-        <v>2.30238008499146</v>
+        <v>2.30238032341003</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G607" t="n">
-        <v>2.30238008499146</v>
+        <v>2.30238032341003</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G608" t="n">
-        <v>2.30238008499146</v>
+        <v>2.30238032341003</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G609" t="n">
-        <v>2.30238008499146</v>
+        <v>2.30238032341003</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G611" t="n">
-        <v>2.30238008499146</v>
+        <v>2.30238032341003</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G613" t="n">
-        <v>2.27286243438721</v>
+        <v>2.27286267280579</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G622" t="n">
-        <v>2.24334502220154</v>
+        <v>2.24334478378296</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>2.25</v>
       </c>
       <c r="G623" t="n">
-        <v>2.21382737159729</v>
+        <v>2.21382713317871</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G625" t="n">
-        <v>2.24334502220154</v>
+        <v>2.24334478378296</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G629" t="n">
-        <v>2.24334502220154</v>
+        <v>2.24334478378296</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G630" t="n">
-        <v>2.28270173072815</v>
+        <v>2.28270196914673</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G631" t="n">
-        <v>2.28270173072815</v>
+        <v>2.28270196914673</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G633" t="n">
-        <v>2.28270173072815</v>
+        <v>2.28270196914673</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G634" t="n">
-        <v>2.28270173072815</v>
+        <v>2.28270196914673</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G639" t="n">
-        <v>2.27286243438721</v>
+        <v>2.27286267280579</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G640" t="n">
-        <v>2.28270173072815</v>
+        <v>2.28270196914673</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G642" t="n">
-        <v>2.24334502220154</v>
+        <v>2.24334478378296</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>2.25</v>
       </c>
       <c r="G645" t="n">
-        <v>2.21382737159729</v>
+        <v>2.21382713317871</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G647" t="n">
-        <v>2.20398807525635</v>
+        <v>2.20398783683777</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>2.25</v>
       </c>
       <c r="G649" t="n">
-        <v>2.21382737159729</v>
+        <v>2.21382713317871</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G653" t="n">
-        <v>2.13511323928833</v>
+        <v>2.13511347770691</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G654" t="n">
-        <v>2.14495253562927</v>
+        <v>2.14495277404785</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>2.25</v>
       </c>
       <c r="G659" t="n">
-        <v>2.21382737159729</v>
+        <v>2.21382713317871</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>2.25</v>
       </c>
       <c r="G661" t="n">
-        <v>2.21382737159729</v>
+        <v>2.21382713317871</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G666" t="n">
-        <v>2.24334502220154</v>
+        <v>2.24334478378296</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G670" t="n">
-        <v>2.20398807525635</v>
+        <v>2.20398783683777</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G671" t="n">
-        <v>2.24334502220154</v>
+        <v>2.24334478378296</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G672" t="n">
-        <v>2.24334502220154</v>
+        <v>2.24334478378296</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G673" t="n">
-        <v>2.24334502220154</v>
+        <v>2.24334478378296</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G676" t="n">
-        <v>2.20398807525635</v>
+        <v>2.20398783683777</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G681" t="n">
-        <v>2.27286243438721</v>
+        <v>2.27286267280579</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G685" t="n">
-        <v>2.35157680511475</v>
+        <v>2.35157656669617</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G688" t="n">
-        <v>2.35157680511475</v>
+        <v>2.35157656669617</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G703" t="n">
-        <v>2.30238008499146</v>
+        <v>2.30238032341003</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G704" t="n">
-        <v>2.30238008499146</v>
+        <v>2.30238032341003</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G705" t="n">
-        <v>2.30238008499146</v>
+        <v>2.30238032341003</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G706" t="n">
-        <v>2.28270173072815</v>
+        <v>2.28270196914673</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G707" t="n">
-        <v>2.24334502220154</v>
+        <v>2.24334478378296</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G711" t="n">
-        <v>2.43029046058655</v>
+        <v>2.43029022216797</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G712" t="n">
-        <v>2.43029046058655</v>
+        <v>2.43029022216797</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G716" t="n">
-        <v>2.35157680511475</v>
+        <v>2.35157656669617</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G717" t="n">
-        <v>2.43029046058655</v>
+        <v>2.43029022216797</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G722" t="n">
-        <v>2.35157680511475</v>
+        <v>2.35157656669617</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G724" t="n">
-        <v>2.35157680511475</v>
+        <v>2.35157656669617</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G726" t="n">
-        <v>2.41061186790466</v>
+        <v>2.41061210632324</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G727" t="n">
-        <v>2.43029046058655</v>
+        <v>2.43029022216797</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G728" t="n">
-        <v>2.43029046058655</v>
+        <v>2.43029022216797</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G732" t="n">
-        <v>2.41061186790466</v>
+        <v>2.41061210632324</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G738" t="n">
-        <v>2.35157680511475</v>
+        <v>2.35157656669617</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G742" t="n">
-        <v>2.49916481971741</v>
+        <v>2.49916505813599</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G744" t="n">
-        <v>2.48932552337646</v>
+        <v>2.48932576179504</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G746" t="n">
-        <v>2.48932552337646</v>
+        <v>2.48932576179504</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G747" t="n">
-        <v>2.51884317398071</v>
+        <v>2.51884341239929</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G748" t="n">
-        <v>2.52868247032166</v>
+        <v>2.52868270874023</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G753" t="n">
-        <v>2.63691425323486</v>
+        <v>2.63691449165344</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G755" t="n">
-        <v>2.77466344833374</v>
+        <v>2.77466320991516</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G757" t="n">
-        <v>2.71562790870667</v>
+        <v>2.71562814712524</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G759" t="n">
-        <v>2.77466344833374</v>
+        <v>2.77466320991516</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G760" t="n">
-        <v>2.77466344833374</v>
+        <v>2.77466320991516</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G761" t="n">
-        <v>2.77466344833374</v>
+        <v>2.77466320991516</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G766" t="n">
-        <v>2.77466344833374</v>
+        <v>2.77466320991516</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G768" t="n">
-        <v>2.77466344833374</v>
+        <v>2.77466320991516</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G773" t="n">
-        <v>3.00096583366394</v>
+        <v>3.00096559524536</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G776" t="n">
-        <v>3.00096583366394</v>
+        <v>3.00096559524536</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G779" t="n">
-        <v>3.00096583366394</v>
+        <v>3.00096559524536</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G781" t="n">
-        <v>3.00096583366394</v>
+        <v>3.00096559524536</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G788" t="n">
-        <v>2.9124128818512</v>
+        <v>2.91241264343262</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G790" t="n">
-        <v>2.84353804588318</v>
+        <v>2.84353828430176</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G791" t="n">
-        <v>2.92225217819214</v>
+        <v>2.92225193977356</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -20987,7 +20987,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G793" t="n">
-        <v>2.92225217819214</v>
+        <v>2.92225193977356</v>
       </c>
       <c r="H793" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G794" t="n">
-        <v>2.90257334709167</v>
+        <v>2.90257358551025</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G798" t="n">
-        <v>2.9124128818512</v>
+        <v>2.91241264343262</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G806" t="n">
-        <v>3.09935832023621</v>
+        <v>3.09935808181763</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G808" t="n">
-        <v>3.1387152671814</v>
+        <v>3.13871502876282</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G815" t="n">
-        <v>3.16823267936707</v>
+        <v>3.16823291778564</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G822" t="n">
-        <v>3.32566070556641</v>
+        <v>3.32566046714783</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G827" t="n">
-        <v>3.41421341896057</v>
+        <v>3.41421365737915</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G828" t="n">
-        <v>3.42405271530151</v>
+        <v>3.42405295372009</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G829" t="n">
-        <v>3.48308825492859</v>
+        <v>3.48308801651001</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G831" t="n">
-        <v>3.57164144515991</v>
+        <v>3.57164120674133</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G834" t="n">
-        <v>4.12263822555542</v>
+        <v>4.12263870239258</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>4.25</v>
       </c>
       <c r="G835" t="n">
-        <v>4.18167400360107</v>
+        <v>4.18167352676392</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G839" t="n">
-        <v>4.22103071212769</v>
+        <v>4.22103023529053</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G841" t="n">
-        <v>4.28990507125854</v>
+        <v>4.2899055480957</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G843" t="n">
-        <v>4.39813661575317</v>
+        <v>4.39813613891602</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G849" t="n">
-        <v>5.07704401016235</v>
+        <v>5.0770435333252</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G850" t="n">
-        <v>4.99832963943481</v>
+        <v>4.99833011627197</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G852" t="n">
-        <v>5.03768634796143</v>
+        <v>5.03768682479858</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G857" t="n">
-        <v>5.03768634796143</v>
+        <v>5.03768682479858</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G859" t="n">
-        <v>4.8605809211731</v>
+        <v>4.86058044433594</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G860" t="n">
-        <v>4.83106279373169</v>
+        <v>4.83106327056885</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G861" t="n">
-        <v>4.89009857177734</v>
+        <v>4.89009809494019</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G864" t="n">
-        <v>4.89009857177734</v>
+        <v>4.89009809494019</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G867" t="n">
-        <v>5.29350709915161</v>
+        <v>5.29350662231445</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G869" t="n">
-        <v>5.70675468444824</v>
+        <v>5.7067551612854</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G870" t="n">
-        <v>5.80514669418335</v>
+        <v>5.80514717102051</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G871" t="n">
-        <v>5.68707609176636</v>
+        <v>5.68707656860352</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G873" t="n">
-        <v>5.43125581741333</v>
+        <v>5.43125629425049</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G876" t="n">
-        <v>5.27382850646973</v>
+        <v>5.27382898330688</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G877" t="n">
-        <v>5.29350709915161</v>
+        <v>5.29350662231445</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G879" t="n">
-        <v>5.05736494064331</v>
+        <v>5.05736541748047</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G881" t="n">
-        <v>5.03768634796143</v>
+        <v>5.03768682479858</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G883" t="n">
-        <v>5.03768634796143</v>
+        <v>5.03768682479858</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G885" t="n">
-        <v>5.07704401016235</v>
+        <v>5.0770435333252</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G891" t="n">
-        <v>5.27382850646973</v>
+        <v>5.27382898330688</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G892" t="n">
-        <v>5.11640071868896</v>
+        <v>5.11640024185181</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G893" t="n">
-        <v>5.05736494064331</v>
+        <v>5.05736541748047</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G894" t="n">
-        <v>5.03768634796143</v>
+        <v>5.03768682479858</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G895" t="n">
-        <v>5.03768634796143</v>
+        <v>5.03768682479858</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23691,7 +23691,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G897" t="n">
-        <v>5.11640071868896</v>
+        <v>5.11640024185181</v>
       </c>
       <c r="H897" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G898" t="n">
-        <v>4.99832963943481</v>
+        <v>4.99833011627197</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G899" t="n">
-        <v>4.83106279373169</v>
+        <v>4.83106327056885</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G903" t="n">
-        <v>4.28990507125854</v>
+        <v>4.2899055480957</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G904" t="n">
-        <v>4.5654034614563</v>
+        <v>4.56540393829346</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G906" t="n">
-        <v>4.83106279373169</v>
+        <v>4.83106327056885</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G907" t="n">
-        <v>4.89009857177734</v>
+        <v>4.89009809494019</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G909" t="n">
-        <v>4.84090232849121</v>
+        <v>4.84090185165405</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G910" t="n">
-        <v>4.83106279373169</v>
+        <v>4.83106327056885</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G912" t="n">
-        <v>4.89009857177734</v>
+        <v>4.89009809494019</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G916" t="n">
-        <v>4.82122373580933</v>
+        <v>4.82122421264648</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G918" t="n">
-        <v>5.03768634796143</v>
+        <v>5.03768682479858</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G919" t="n">
-        <v>5.07704401016235</v>
+        <v>5.0770435333252</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G922" t="n">
-        <v>5.11640071868896</v>
+        <v>5.11640024185181</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G926" t="n">
-        <v>5.25414991378784</v>
+        <v>5.254150390625</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G928" t="n">
-        <v>5.27382850646973</v>
+        <v>5.27382898330688</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G929" t="n">
-        <v>5.29350709915161</v>
+        <v>5.29350662231445</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G930" t="n">
-        <v>5.29350709915161</v>
+        <v>5.29350662231445</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G937" t="n">
-        <v>5.11640071868896</v>
+        <v>5.11640024185181</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G939" t="n">
-        <v>5.11640071868896</v>
+        <v>5.11640024185181</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G941" t="n">
-        <v>5.07704401016235</v>
+        <v>5.0770435333252</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G944" t="n">
-        <v>5.13607931137085</v>
+        <v>5.13607883453369</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G949" t="n">
-        <v>5.25414991378784</v>
+        <v>5.254150390625</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25069,7 +25069,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G950" t="n">
-        <v>5.29350709915161</v>
+        <v>5.29350662231445</v>
       </c>
       <c r="H950" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G958" t="n">
-        <v>5.68707609176636</v>
+        <v>5.68707656860352</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25303,7 +25303,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G959" t="n">
-        <v>5.68707609176636</v>
+        <v>5.68707656860352</v>
       </c>
       <c r="H959" t="s">
         <v>8</v>
@@ -25381,7 +25381,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G962" t="n">
-        <v>5.80514669418335</v>
+        <v>5.80514717102051</v>
       </c>
       <c r="H962" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G965" t="n">
-        <v>5.80514669418335</v>
+        <v>5.80514717102051</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G969" t="n">
-        <v>6.1396803855896</v>
+        <v>6.13968086242676</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25589,7 +25589,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G970" t="n">
-        <v>6.19871664047241</v>
+        <v>6.19871616363525</v>
       </c>
       <c r="H970" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G971" t="n">
-        <v>6.33646535873413</v>
+        <v>6.33646583557129</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25641,7 +25641,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G972" t="n">
-        <v>6.27743053436279</v>
+        <v>6.27743005752563</v>
       </c>
       <c r="H972" t="s">
         <v>8</v>
@@ -25693,7 +25693,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G974" t="n">
-        <v>6.1396803855896</v>
+        <v>6.13968086242676</v>
       </c>
       <c r="H974" t="s">
         <v>8</v>
@@ -25771,7 +25771,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G977" t="n">
-        <v>6.00193166732788</v>
+        <v>6.00193119049072</v>
       </c>
       <c r="H977" t="s">
         <v>8</v>
@@ -38254,6 +38254,32 @@
         <v>10.3800001144409</v>
       </c>
       <c r="H1457" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1458">
+      <c r="A1458" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B1458" t="n">
+        <v>22142</v>
+      </c>
+      <c r="C1458" t="n">
+        <v>10.3000001907349</v>
+      </c>
+      <c r="D1458" t="n">
+        <v>9.80000019073486</v>
+      </c>
+      <c r="E1458" t="n">
+        <v>10.2799997329712</v>
+      </c>
+      <c r="F1458" t="n">
+        <v>9.94999980926514</v>
+      </c>
+      <c r="G1458" t="n">
+        <v>9.94999980926514</v>
+      </c>
+      <c r="H1458" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/EVISO.MI.xlsx
+++ b/data/EVISO.MI.xlsx
@@ -473,7 +473,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G4" t="n">
-        <v>2.11304235458374</v>
+        <v>2.11304259300232</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G10" t="n">
-        <v>1.9956511259079</v>
+        <v>1.99565076828003</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G14" t="n">
-        <v>1.93695545196533</v>
+        <v>1.93695557117462</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G16" t="n">
-        <v>1.87825965881348</v>
+        <v>1.87825977802277</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G19" t="n">
-        <v>1.96630322933197</v>
+        <v>1.96630311012268</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G22" t="n">
-        <v>1.96630322933197</v>
+        <v>1.96630311012268</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G24" t="n">
-        <v>1.9956511259079</v>
+        <v>1.99565076828003</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G25" t="n">
-        <v>1.96630322933197</v>
+        <v>1.96630311012268</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G26" t="n">
-        <v>1.96630322933197</v>
+        <v>1.96630311012268</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G30" t="n">
-        <v>2.08369469642639</v>
+        <v>2.08369445800781</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G35" t="n">
-        <v>2.33804202079773</v>
+        <v>2.33804225921631</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G37" t="n">
-        <v>2.21086835861206</v>
+        <v>2.21086859703064</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G38" t="n">
-        <v>2.28912901878357</v>
+        <v>2.28912878036499</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G39" t="n">
-        <v>2.26956391334534</v>
+        <v>2.26956367492676</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G44" t="n">
-        <v>2.27934670448303</v>
+        <v>2.27934646606445</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G46" t="n">
-        <v>2.28912901878357</v>
+        <v>2.28912878036499</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G48" t="n">
-        <v>2.28912901878357</v>
+        <v>2.28912878036499</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G49" t="n">
-        <v>2.26956391334534</v>
+        <v>2.26956367492676</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G50" t="n">
-        <v>2.28912901878357</v>
+        <v>2.28912878036499</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G51" t="n">
-        <v>2.26956391334534</v>
+        <v>2.26956367492676</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G53" t="n">
-        <v>2.24999856948853</v>
+        <v>2.2499988079071</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G55" t="n">
-        <v>2.24999856948853</v>
+        <v>2.2499988079071</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G56" t="n">
-        <v>2.24999856948853</v>
+        <v>2.2499988079071</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G61" t="n">
-        <v>2.23043346405029</v>
+        <v>2.23043370246887</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G64" t="n">
-        <v>2.21086835861206</v>
+        <v>2.21086859703064</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G65" t="n">
-        <v>2.1717381477356</v>
+        <v>2.17173790931702</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G68" t="n">
-        <v>2.23043346405029</v>
+        <v>2.23043370246887</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G76" t="n">
-        <v>2.1717381477356</v>
+        <v>2.17173790931702</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G79" t="n">
-        <v>2.23043346405029</v>
+        <v>2.23043370246887</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G81" t="n">
-        <v>2.21086835861206</v>
+        <v>2.21086859703064</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G83" t="n">
-        <v>2.21086835861206</v>
+        <v>2.21086859703064</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G91" t="n">
-        <v>2.33804202079773</v>
+        <v>2.33804225921631</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G94" t="n">
-        <v>2.27934670448303</v>
+        <v>2.27934646606445</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G95" t="n">
-        <v>2.26956391334534</v>
+        <v>2.26956367492676</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G96" t="n">
-        <v>2.24999856948853</v>
+        <v>2.2499988079071</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G97" t="n">
-        <v>2.27934670448303</v>
+        <v>2.27934646606445</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G100" t="n">
-        <v>2.33804202079773</v>
+        <v>2.33804225921631</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G104" t="n">
-        <v>2.6510853767395</v>
+        <v>2.65108561515808</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G105" t="n">
-        <v>2.73912906646729</v>
+        <v>2.73912882804871</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G110" t="n">
-        <v>2.61195516586304</v>
+        <v>2.61195492744446</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G111" t="n">
-        <v>2.53369426727295</v>
+        <v>2.53369402885437</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G112" t="n">
-        <v>2.54347658157349</v>
+        <v>2.54347681999207</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G113" t="n">
-        <v>2.54347658157349</v>
+        <v>2.54347681999207</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G114" t="n">
-        <v>2.53369426727295</v>
+        <v>2.53369402885437</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G116" t="n">
-        <v>2.51412916183472</v>
+        <v>2.51412892341614</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G117" t="n">
-        <v>2.54347658157349</v>
+        <v>2.54347681999207</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G118" t="n">
-        <v>2.49456381797791</v>
+        <v>2.49456357955933</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G119" t="n">
-        <v>2.51412916183472</v>
+        <v>2.51412892341614</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G120" t="n">
-        <v>2.47499871253967</v>
+        <v>2.47499847412109</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>2.5</v>
       </c>
       <c r="G121" t="n">
-        <v>2.44565057754517</v>
+        <v>2.44565081596375</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G125" t="n">
-        <v>2.41630291938782</v>
+        <v>2.4163031578064</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G127" t="n">
-        <v>2.53369426727295</v>
+        <v>2.53369402885437</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G128" t="n">
-        <v>2.48478126525879</v>
+        <v>2.48478102684021</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G129" t="n">
-        <v>2.49456381797791</v>
+        <v>2.49456357955933</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G130" t="n">
-        <v>2.52391147613525</v>
+        <v>2.52391171455383</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G132" t="n">
-        <v>2.49456381797791</v>
+        <v>2.49456357955933</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G134" t="n">
-        <v>2.51412916183472</v>
+        <v>2.51412892341614</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>2.5</v>
       </c>
       <c r="G135" t="n">
-        <v>2.44565057754517</v>
+        <v>2.44565081596375</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>2.5</v>
       </c>
       <c r="G136" t="n">
-        <v>2.44565057754517</v>
+        <v>2.44565081596375</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G137" t="n">
-        <v>2.47499871253967</v>
+        <v>2.47499847412109</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G141" t="n">
-        <v>2.41630291938782</v>
+        <v>2.4163031578064</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>2.5</v>
       </c>
       <c r="G146" t="n">
-        <v>2.44565057754517</v>
+        <v>2.44565081596375</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>2.5</v>
       </c>
       <c r="G147" t="n">
-        <v>2.44565057754517</v>
+        <v>2.44565081596375</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>2.5</v>
       </c>
       <c r="G152" t="n">
-        <v>2.44565057754517</v>
+        <v>2.44565081596375</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>2.5</v>
       </c>
       <c r="G153" t="n">
-        <v>2.44565057754517</v>
+        <v>2.44565081596375</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G154" t="n">
-        <v>2.48478126525879</v>
+        <v>2.48478102684021</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G156" t="n">
-        <v>2.49456381797791</v>
+        <v>2.49456357955933</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G157" t="n">
-        <v>2.49456381797791</v>
+        <v>2.49456357955933</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G159" t="n">
-        <v>2.41630291938782</v>
+        <v>2.4163031578064</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G163" t="n">
-        <v>2.61195516586304</v>
+        <v>2.61195492744446</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G164" t="n">
-        <v>2.81738996505737</v>
+        <v>2.81738972663879</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G165" t="n">
-        <v>2.81738996505737</v>
+        <v>2.81738972663879</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G166" t="n">
-        <v>2.92499852180481</v>
+        <v>2.92499828338623</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G167" t="n">
-        <v>2.92499852180481</v>
+        <v>2.92499828338623</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G168" t="n">
-        <v>2.905433177948</v>
+        <v>2.90543293952942</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G169" t="n">
-        <v>2.92499852180481</v>
+        <v>2.92499828338623</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G170" t="n">
-        <v>2.92499852180481</v>
+        <v>2.92499828338623</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G171" t="n">
-        <v>2.83695530891418</v>
+        <v>2.83695507049561</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G172" t="n">
-        <v>2.74891138076782</v>
+        <v>2.7489116191864</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G174" t="n">
-        <v>2.73912906646729</v>
+        <v>2.73912882804871</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G181" t="n">
-        <v>2.66086792945862</v>
+        <v>2.6608681678772</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G184" t="n">
-        <v>2.66086792945862</v>
+        <v>2.6608681678772</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G186" t="n">
-        <v>2.70978116989136</v>
+        <v>2.70978093147278</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G189" t="n">
-        <v>2.74891138076782</v>
+        <v>2.7489116191864</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G190" t="n">
-        <v>2.51412916183472</v>
+        <v>2.51412892341614</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G191" t="n">
-        <v>2.68043327331543</v>
+        <v>2.68043303489685</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G192" t="n">
-        <v>2.66086792945862</v>
+        <v>2.6608681678772</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G194" t="n">
-        <v>2.64130282402039</v>
+        <v>2.64130306243896</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G198" t="n">
-        <v>2.61195516586304</v>
+        <v>2.61195492744446</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G201" t="n">
-        <v>2.54347658157349</v>
+        <v>2.54347681999207</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G203" t="n">
-        <v>2.61195516586304</v>
+        <v>2.61195492744446</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G204" t="n">
-        <v>2.64130282402039</v>
+        <v>2.64130306243896</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G205" t="n">
-        <v>2.70978116989136</v>
+        <v>2.70978093147278</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G206" t="n">
-        <v>2.73912906646729</v>
+        <v>2.73912882804871</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G208" t="n">
-        <v>2.66086792945862</v>
+        <v>2.6608681678772</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G210" t="n">
-        <v>2.66086792945862</v>
+        <v>2.6608681678772</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G211" t="n">
-        <v>2.66086792945862</v>
+        <v>2.6608681678772</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G213" t="n">
-        <v>2.66086792945862</v>
+        <v>2.6608681678772</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G214" t="n">
-        <v>2.66086792945862</v>
+        <v>2.6608681678772</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G215" t="n">
-        <v>2.68043327331543</v>
+        <v>2.68043303489685</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G216" t="n">
-        <v>2.6510853767395</v>
+        <v>2.65108561515808</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G217" t="n">
-        <v>2.64130282402039</v>
+        <v>2.64130306243896</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G220" t="n">
-        <v>2.63691449165344</v>
+        <v>2.63691425323486</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G221" t="n">
-        <v>2.64675331115723</v>
+        <v>2.64675354957581</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G222" t="n">
-        <v>2.6270751953125</v>
+        <v>2.62707495689392</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G227" t="n">
-        <v>2.51884341239929</v>
+        <v>2.51884317398071</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G228" t="n">
-        <v>2.49916505813599</v>
+        <v>2.49916481971741</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G229" t="n">
-        <v>2.52868270874023</v>
+        <v>2.52868247032166</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G232" t="n">
-        <v>2.43029022216797</v>
+        <v>2.43029046058655</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G234" t="n">
-        <v>2.51884341239929</v>
+        <v>2.51884317398071</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G238" t="n">
-        <v>2.5582001209259</v>
+        <v>2.55820035934448</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G240" t="n">
-        <v>2.6270751953125</v>
+        <v>2.62707495689392</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G244" t="n">
-        <v>2.49916505813599</v>
+        <v>2.49916481971741</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G246" t="n">
-        <v>2.48932576179504</v>
+        <v>2.48932552337646</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G249" t="n">
-        <v>2.43029022216797</v>
+        <v>2.43029046058655</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G252" t="n">
-        <v>2.48932576179504</v>
+        <v>2.48932552337646</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G256" t="n">
-        <v>2.42045092582703</v>
+        <v>2.42045116424561</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G257" t="n">
-        <v>2.42045092582703</v>
+        <v>2.42045116424561</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G259" t="n">
-        <v>2.48932576179504</v>
+        <v>2.48932552337646</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G260" t="n">
-        <v>2.48932576179504</v>
+        <v>2.48932552337646</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G262" t="n">
-        <v>2.42045092582703</v>
+        <v>2.42045116424561</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G264" t="n">
-        <v>2.43029022216797</v>
+        <v>2.43029046058655</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G268" t="n">
-        <v>2.43029022216797</v>
+        <v>2.43029046058655</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G269" t="n">
-        <v>2.42045092582703</v>
+        <v>2.42045116424561</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G272" t="n">
-        <v>2.27286267280579</v>
+        <v>2.27286243438721</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G274" t="n">
-        <v>2.41061210632324</v>
+        <v>2.41061186790466</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G276" t="n">
-        <v>2.42045092582703</v>
+        <v>2.42045116424561</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G280" t="n">
-        <v>2.41061210632324</v>
+        <v>2.41061186790466</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G281" t="n">
-        <v>2.41061210632324</v>
+        <v>2.41061186790466</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G282" t="n">
-        <v>2.41061210632324</v>
+        <v>2.41061186790466</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G283" t="n">
-        <v>2.35157656669617</v>
+        <v>2.35157680511475</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G284" t="n">
-        <v>2.42045092582703</v>
+        <v>2.42045116424561</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G285" t="n">
-        <v>2.52868270874023</v>
+        <v>2.52868247032166</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G295" t="n">
-        <v>2.30238032341003</v>
+        <v>2.30238008499146</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G299" t="n">
-        <v>2.27286267280579</v>
+        <v>2.27286243438721</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G300" t="n">
-        <v>2.20398783683777</v>
+        <v>2.20398807525635</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G304" t="n">
-        <v>2.27286267280579</v>
+        <v>2.27286243438721</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G306" t="n">
-        <v>2.30238032341003</v>
+        <v>2.30238008499146</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G312" t="n">
-        <v>2.35157656669617</v>
+        <v>2.35157680511475</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G313" t="n">
-        <v>2.41061210632324</v>
+        <v>2.41061186790466</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G321" t="n">
-        <v>2.27286267280579</v>
+        <v>2.27286243438721</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G322" t="n">
-        <v>2.28270196914673</v>
+        <v>2.28270173072815</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G326" t="n">
-        <v>2.35157656669617</v>
+        <v>2.35157680511475</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G329" t="n">
-        <v>2.28270196914673</v>
+        <v>2.28270173072815</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G330" t="n">
-        <v>2.30238032341003</v>
+        <v>2.30238008499146</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G332" t="n">
-        <v>2.30238032341003</v>
+        <v>2.30238008499146</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G334" t="n">
-        <v>2.20398783683777</v>
+        <v>2.20398807525635</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>2.25</v>
       </c>
       <c r="G337" t="n">
-        <v>2.21382713317871</v>
+        <v>2.21382737159729</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G343" t="n">
-        <v>2.41061210632324</v>
+        <v>2.41061186790466</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G344" t="n">
-        <v>2.41061210632324</v>
+        <v>2.41061186790466</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G345" t="n">
-        <v>2.28270196914673</v>
+        <v>2.28270173072815</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G349" t="n">
-        <v>2.35157656669617</v>
+        <v>2.35157680511475</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G351" t="n">
-        <v>2.28270196914673</v>
+        <v>2.28270173072815</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G353" t="n">
-        <v>2.28270196914673</v>
+        <v>2.28270173072815</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G354" t="n">
-        <v>2.28270196914673</v>
+        <v>2.28270173072815</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G355" t="n">
-        <v>2.27286267280579</v>
+        <v>2.27286243438721</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G356" t="n">
-        <v>2.28270196914673</v>
+        <v>2.28270173072815</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G358" t="n">
-        <v>2.28270196914673</v>
+        <v>2.28270173072815</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G359" t="n">
-        <v>2.27286267280579</v>
+        <v>2.27286243438721</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G360" t="n">
-        <v>2.28270196914673</v>
+        <v>2.28270173072815</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G361" t="n">
-        <v>2.30238032341003</v>
+        <v>2.30238008499146</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G362" t="n">
-        <v>2.30238032341003</v>
+        <v>2.30238008499146</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G363" t="n">
-        <v>2.30238032341003</v>
+        <v>2.30238008499146</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G365" t="n">
-        <v>2.41061210632324</v>
+        <v>2.41061186790466</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G369" t="n">
-        <v>2.5385217666626</v>
+        <v>2.53852200508118</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G372" t="n">
-        <v>2.48932576179504</v>
+        <v>2.48932552337646</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G379" t="n">
-        <v>2.35157656669617</v>
+        <v>2.35157680511475</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G385" t="n">
-        <v>2.43029022216797</v>
+        <v>2.43029046058655</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G387" t="n">
-        <v>2.43029022216797</v>
+        <v>2.43029046058655</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G393" t="n">
-        <v>2.35157656669617</v>
+        <v>2.35157680511475</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G407" t="n">
-        <v>2.42045092582703</v>
+        <v>2.42045116424561</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G411" t="n">
-        <v>2.48932576179504</v>
+        <v>2.48932552337646</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G412" t="n">
-        <v>2.48932576179504</v>
+        <v>2.48932552337646</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G413" t="n">
-        <v>2.42045092582703</v>
+        <v>2.42045116424561</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G421" t="n">
-        <v>2.49916505813599</v>
+        <v>2.49916481971741</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G424" t="n">
-        <v>2.49916505813599</v>
+        <v>2.49916481971741</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G427" t="n">
-        <v>2.5582001209259</v>
+        <v>2.55820035934448</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G428" t="n">
-        <v>2.52868270874023</v>
+        <v>2.52868247032166</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G432" t="n">
-        <v>2.51884341239929</v>
+        <v>2.51884317398071</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G434" t="n">
-        <v>2.5582001209259</v>
+        <v>2.55820035934448</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G435" t="n">
-        <v>2.52868270874023</v>
+        <v>2.52868247032166</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G437" t="n">
-        <v>2.52868270874023</v>
+        <v>2.52868247032166</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G438" t="n">
-        <v>2.51884341239929</v>
+        <v>2.51884317398071</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G439" t="n">
-        <v>2.52868270874023</v>
+        <v>2.52868247032166</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G440" t="n">
-        <v>2.43029022216797</v>
+        <v>2.43029046058655</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G443" t="n">
-        <v>2.41061210632324</v>
+        <v>2.41061186790466</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G445" t="n">
-        <v>2.49916505813599</v>
+        <v>2.49916481971741</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G447" t="n">
-        <v>2.28270196914673</v>
+        <v>2.28270173072815</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G448" t="n">
-        <v>2.28270196914673</v>
+        <v>2.28270173072815</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G452" t="n">
-        <v>2.43029022216797</v>
+        <v>2.43029046058655</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G457" t="n">
-        <v>2.49916505813599</v>
+        <v>2.49916481971741</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G458" t="n">
-        <v>2.51884341239929</v>
+        <v>2.51884317398071</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G459" t="n">
-        <v>2.51884341239929</v>
+        <v>2.51884317398071</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G460" t="n">
-        <v>2.43029022216797</v>
+        <v>2.43029046058655</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G464" t="n">
-        <v>2.42045092582703</v>
+        <v>2.42045116424561</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G465" t="n">
-        <v>2.41061210632324</v>
+        <v>2.41061186790466</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G468" t="n">
-        <v>2.42045092582703</v>
+        <v>2.42045116424561</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G469" t="n">
-        <v>2.42045092582703</v>
+        <v>2.42045116424561</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G471" t="n">
-        <v>2.43029022216797</v>
+        <v>2.43029046058655</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G475" t="n">
-        <v>2.42045092582703</v>
+        <v>2.42045116424561</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G479" t="n">
-        <v>2.43029022216797</v>
+        <v>2.43029046058655</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G481" t="n">
-        <v>2.42045092582703</v>
+        <v>2.42045116424561</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G483" t="n">
-        <v>2.42045092582703</v>
+        <v>2.42045116424561</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G487" t="n">
-        <v>2.41061210632324</v>
+        <v>2.41061186790466</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G488" t="n">
-        <v>2.41061210632324</v>
+        <v>2.41061186790466</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G490" t="n">
-        <v>2.41061210632324</v>
+        <v>2.41061186790466</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G493" t="n">
-        <v>2.41061210632324</v>
+        <v>2.41061186790466</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G494" t="n">
-        <v>2.41061210632324</v>
+        <v>2.41061186790466</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G495" t="n">
-        <v>2.41061210632324</v>
+        <v>2.41061186790466</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G500" t="n">
-        <v>2.48932576179504</v>
+        <v>2.48932552337646</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G501" t="n">
-        <v>2.41061210632324</v>
+        <v>2.41061186790466</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G504" t="n">
-        <v>2.42045092582703</v>
+        <v>2.42045116424561</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G505" t="n">
-        <v>2.42045092582703</v>
+        <v>2.42045116424561</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G507" t="n">
-        <v>2.42045092582703</v>
+        <v>2.42045116424561</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G509" t="n">
-        <v>2.43029022216797</v>
+        <v>2.43029046058655</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G510" t="n">
-        <v>2.43029022216797</v>
+        <v>2.43029046058655</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G512" t="n">
-        <v>2.49916505813599</v>
+        <v>2.49916481971741</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G515" t="n">
-        <v>2.48932576179504</v>
+        <v>2.48932552337646</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G523" t="n">
-        <v>2.5582001209259</v>
+        <v>2.55820035934448</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G528" t="n">
-        <v>2.5582001209259</v>
+        <v>2.55820035934448</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G529" t="n">
-        <v>2.52868270874023</v>
+        <v>2.52868247032166</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G530" t="n">
-        <v>2.5582001209259</v>
+        <v>2.55820035934448</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G533" t="n">
-        <v>2.63691449165344</v>
+        <v>2.63691425323486</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G535" t="n">
-        <v>2.5385217666626</v>
+        <v>2.53852200508118</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G536" t="n">
-        <v>2.5582001209259</v>
+        <v>2.55820035934448</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G538" t="n">
-        <v>2.5582001209259</v>
+        <v>2.55820035934448</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G539" t="n">
-        <v>2.5582001209259</v>
+        <v>2.55820035934448</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G540" t="n">
-        <v>2.5385217666626</v>
+        <v>2.53852200508118</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G541" t="n">
-        <v>2.5582001209259</v>
+        <v>2.55820035934448</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G542" t="n">
-        <v>2.5582001209259</v>
+        <v>2.55820035934448</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G544" t="n">
-        <v>2.64675331115723</v>
+        <v>2.64675354957581</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G545" t="n">
-        <v>2.64675331115723</v>
+        <v>2.64675354957581</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G547" t="n">
-        <v>2.35157656669617</v>
+        <v>2.35157680511475</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G550" t="n">
-        <v>2.30238032341003</v>
+        <v>2.30238008499146</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G553" t="n">
-        <v>2.28270196914673</v>
+        <v>2.28270173072815</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G557" t="n">
-        <v>2.27286267280579</v>
+        <v>2.27286243438721</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G558" t="n">
-        <v>2.27286267280579</v>
+        <v>2.27286243438721</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G559" t="n">
-        <v>2.27286267280579</v>
+        <v>2.27286243438721</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G560" t="n">
-        <v>2.28270196914673</v>
+        <v>2.28270173072815</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G562" t="n">
-        <v>2.24334478378296</v>
+        <v>2.24334502220154</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G563" t="n">
-        <v>2.20398783683777</v>
+        <v>2.20398807525635</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>2.25</v>
       </c>
       <c r="G565" t="n">
-        <v>2.21382713317871</v>
+        <v>2.21382737159729</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G566" t="n">
-        <v>2.27286267280579</v>
+        <v>2.27286243438721</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G570" t="n">
-        <v>2.24334478378296</v>
+        <v>2.24334502220154</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G573" t="n">
-        <v>2.28270196914673</v>
+        <v>2.28270173072815</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G574" t="n">
-        <v>2.20398783683777</v>
+        <v>2.20398807525635</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G578" t="n">
-        <v>2.28270196914673</v>
+        <v>2.28270173072815</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G580" t="n">
-        <v>2.27286267280579</v>
+        <v>2.27286243438721</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G581" t="n">
-        <v>2.28270196914673</v>
+        <v>2.28270173072815</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G583" t="n">
-        <v>2.30238032341003</v>
+        <v>2.30238008499146</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G596" t="n">
-        <v>2.28270196914673</v>
+        <v>2.28270173072815</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G599" t="n">
-        <v>2.30238032341003</v>
+        <v>2.30238008499146</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G601" t="n">
-        <v>2.24334478378296</v>
+        <v>2.24334502220154</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G602" t="n">
-        <v>2.27286267280579</v>
+        <v>2.27286243438721</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G603" t="n">
-        <v>2.27286267280579</v>
+        <v>2.27286243438721</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G605" t="n">
-        <v>2.30238032341003</v>
+        <v>2.30238008499146</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G606" t="n">
-        <v>2.30238032341003</v>
+        <v>2.30238008499146</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G607" t="n">
-        <v>2.30238032341003</v>
+        <v>2.30238008499146</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G608" t="n">
-        <v>2.30238032341003</v>
+        <v>2.30238008499146</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G609" t="n">
-        <v>2.30238032341003</v>
+        <v>2.30238008499146</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G611" t="n">
-        <v>2.30238032341003</v>
+        <v>2.30238008499146</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G613" t="n">
-        <v>2.27286267280579</v>
+        <v>2.27286243438721</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G622" t="n">
-        <v>2.24334478378296</v>
+        <v>2.24334502220154</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>2.25</v>
       </c>
       <c r="G623" t="n">
-        <v>2.21382713317871</v>
+        <v>2.21382737159729</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G625" t="n">
-        <v>2.24334478378296</v>
+        <v>2.24334502220154</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G629" t="n">
-        <v>2.24334478378296</v>
+        <v>2.24334502220154</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G630" t="n">
-        <v>2.28270196914673</v>
+        <v>2.28270173072815</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G631" t="n">
-        <v>2.28270196914673</v>
+        <v>2.28270173072815</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G633" t="n">
-        <v>2.28270196914673</v>
+        <v>2.28270173072815</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G634" t="n">
-        <v>2.28270196914673</v>
+        <v>2.28270173072815</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G639" t="n">
-        <v>2.27286267280579</v>
+        <v>2.27286243438721</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G640" t="n">
-        <v>2.28270196914673</v>
+        <v>2.28270173072815</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G642" t="n">
-        <v>2.24334478378296</v>
+        <v>2.24334502220154</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>2.25</v>
       </c>
       <c r="G645" t="n">
-        <v>2.21382713317871</v>
+        <v>2.21382737159729</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G647" t="n">
-        <v>2.20398783683777</v>
+        <v>2.20398807525635</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>2.25</v>
       </c>
       <c r="G649" t="n">
-        <v>2.21382713317871</v>
+        <v>2.21382737159729</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G653" t="n">
-        <v>2.13511347770691</v>
+        <v>2.13511323928833</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G654" t="n">
-        <v>2.14495277404785</v>
+        <v>2.14495253562927</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>2.25</v>
       </c>
       <c r="G659" t="n">
-        <v>2.21382713317871</v>
+        <v>2.21382737159729</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>2.25</v>
       </c>
       <c r="G661" t="n">
-        <v>2.21382713317871</v>
+        <v>2.21382737159729</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G666" t="n">
-        <v>2.24334478378296</v>
+        <v>2.24334502220154</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G670" t="n">
-        <v>2.20398783683777</v>
+        <v>2.20398807525635</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G671" t="n">
-        <v>2.24334478378296</v>
+        <v>2.24334502220154</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G672" t="n">
-        <v>2.24334478378296</v>
+        <v>2.24334502220154</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G673" t="n">
-        <v>2.24334478378296</v>
+        <v>2.24334502220154</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G676" t="n">
-        <v>2.20398783683777</v>
+        <v>2.20398807525635</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G681" t="n">
-        <v>2.27286267280579</v>
+        <v>2.27286243438721</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G685" t="n">
-        <v>2.35157656669617</v>
+        <v>2.35157680511475</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G688" t="n">
-        <v>2.35157656669617</v>
+        <v>2.35157680511475</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G703" t="n">
-        <v>2.30238032341003</v>
+        <v>2.30238008499146</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G704" t="n">
-        <v>2.30238032341003</v>
+        <v>2.30238008499146</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G705" t="n">
-        <v>2.30238032341003</v>
+        <v>2.30238008499146</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G706" t="n">
-        <v>2.28270196914673</v>
+        <v>2.28270173072815</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G707" t="n">
-        <v>2.24334478378296</v>
+        <v>2.24334502220154</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G711" t="n">
-        <v>2.43029022216797</v>
+        <v>2.43029046058655</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G712" t="n">
-        <v>2.43029022216797</v>
+        <v>2.43029046058655</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G716" t="n">
-        <v>2.35157656669617</v>
+        <v>2.35157680511475</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G717" t="n">
-        <v>2.43029022216797</v>
+        <v>2.43029046058655</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G722" t="n">
-        <v>2.35157656669617</v>
+        <v>2.35157680511475</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G724" t="n">
-        <v>2.35157656669617</v>
+        <v>2.35157680511475</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G726" t="n">
-        <v>2.41061210632324</v>
+        <v>2.41061186790466</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G727" t="n">
-        <v>2.43029022216797</v>
+        <v>2.43029046058655</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G728" t="n">
-        <v>2.43029022216797</v>
+        <v>2.43029046058655</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G732" t="n">
-        <v>2.41061210632324</v>
+        <v>2.41061186790466</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G738" t="n">
-        <v>2.35157656669617</v>
+        <v>2.35157680511475</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G742" t="n">
-        <v>2.49916505813599</v>
+        <v>2.49916481971741</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G744" t="n">
-        <v>2.48932576179504</v>
+        <v>2.48932552337646</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G746" t="n">
-        <v>2.48932576179504</v>
+        <v>2.48932552337646</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G747" t="n">
-        <v>2.51884341239929</v>
+        <v>2.51884317398071</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G748" t="n">
-        <v>2.52868270874023</v>
+        <v>2.52868247032166</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G753" t="n">
-        <v>2.63691449165344</v>
+        <v>2.63691425323486</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G755" t="n">
-        <v>2.77466320991516</v>
+        <v>2.77466344833374</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G757" t="n">
-        <v>2.71562814712524</v>
+        <v>2.71562790870667</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G759" t="n">
-        <v>2.77466320991516</v>
+        <v>2.77466344833374</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G760" t="n">
-        <v>2.77466320991516</v>
+        <v>2.77466344833374</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G761" t="n">
-        <v>2.77466320991516</v>
+        <v>2.77466344833374</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G766" t="n">
-        <v>2.77466320991516</v>
+        <v>2.77466344833374</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G768" t="n">
-        <v>2.77466320991516</v>
+        <v>2.77466344833374</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G773" t="n">
-        <v>3.00096559524536</v>
+        <v>3.00096583366394</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G776" t="n">
-        <v>3.00096559524536</v>
+        <v>3.00096583366394</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G779" t="n">
-        <v>3.00096559524536</v>
+        <v>3.00096583366394</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G781" t="n">
-        <v>3.00096559524536</v>
+        <v>3.00096583366394</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G788" t="n">
-        <v>2.91241264343262</v>
+        <v>2.9124128818512</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G790" t="n">
-        <v>2.84353828430176</v>
+        <v>2.84353804588318</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G791" t="n">
-        <v>2.92225193977356</v>
+        <v>2.92225217819214</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -20987,7 +20987,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G793" t="n">
-        <v>2.92225193977356</v>
+        <v>2.92225217819214</v>
       </c>
       <c r="H793" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G794" t="n">
-        <v>2.90257358551025</v>
+        <v>2.90257334709167</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G798" t="n">
-        <v>2.91241264343262</v>
+        <v>2.9124128818512</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G806" t="n">
-        <v>3.09935808181763</v>
+        <v>3.09935832023621</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G808" t="n">
-        <v>3.13871502876282</v>
+        <v>3.1387152671814</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G815" t="n">
-        <v>3.16823291778564</v>
+        <v>3.16823267936707</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G822" t="n">
-        <v>3.32566046714783</v>
+        <v>3.32566070556641</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G827" t="n">
-        <v>3.41421365737915</v>
+        <v>3.41421341896057</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G828" t="n">
-        <v>3.42405295372009</v>
+        <v>3.42405271530151</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G829" t="n">
-        <v>3.48308801651001</v>
+        <v>3.48308825492859</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G831" t="n">
-        <v>3.57164120674133</v>
+        <v>3.57164144515991</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G834" t="n">
-        <v>4.12263870239258</v>
+        <v>4.12263822555542</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>4.25</v>
       </c>
       <c r="G835" t="n">
-        <v>4.18167352676392</v>
+        <v>4.18167400360107</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G839" t="n">
-        <v>4.22103023529053</v>
+        <v>4.22103071212769</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G841" t="n">
-        <v>4.2899055480957</v>
+        <v>4.28990507125854</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G843" t="n">
-        <v>4.39813613891602</v>
+        <v>4.39813661575317</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G849" t="n">
-        <v>5.0770435333252</v>
+        <v>5.07704401016235</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G850" t="n">
-        <v>4.99833011627197</v>
+        <v>4.99832963943481</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G852" t="n">
-        <v>5.03768682479858</v>
+        <v>5.03768634796143</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G857" t="n">
-        <v>5.03768682479858</v>
+        <v>5.03768634796143</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G859" t="n">
-        <v>4.86058044433594</v>
+        <v>4.8605809211731</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G860" t="n">
-        <v>4.83106327056885</v>
+        <v>4.83106279373169</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G861" t="n">
-        <v>4.89009809494019</v>
+        <v>4.89009857177734</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G864" t="n">
-        <v>4.89009809494019</v>
+        <v>4.89009857177734</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G867" t="n">
-        <v>5.29350662231445</v>
+        <v>5.29350709915161</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G869" t="n">
-        <v>5.7067551612854</v>
+        <v>5.70675468444824</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G870" t="n">
-        <v>5.80514717102051</v>
+        <v>5.80514669418335</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G871" t="n">
-        <v>5.68707656860352</v>
+        <v>5.68707609176636</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G873" t="n">
-        <v>5.43125629425049</v>
+        <v>5.43125581741333</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G876" t="n">
-        <v>5.27382898330688</v>
+        <v>5.27382850646973</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G877" t="n">
-        <v>5.29350662231445</v>
+        <v>5.29350709915161</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G879" t="n">
-        <v>5.05736541748047</v>
+        <v>5.05736494064331</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G881" t="n">
-        <v>5.03768682479858</v>
+        <v>5.03768634796143</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G883" t="n">
-        <v>5.03768682479858</v>
+        <v>5.03768634796143</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G885" t="n">
-        <v>5.0770435333252</v>
+        <v>5.07704401016235</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G891" t="n">
-        <v>5.27382898330688</v>
+        <v>5.27382850646973</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G892" t="n">
-        <v>5.11640024185181</v>
+        <v>5.11640071868896</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G893" t="n">
-        <v>5.05736541748047</v>
+        <v>5.05736494064331</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G894" t="n">
-        <v>5.03768682479858</v>
+        <v>5.03768634796143</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G895" t="n">
-        <v>5.03768682479858</v>
+        <v>5.03768634796143</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23691,7 +23691,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G897" t="n">
-        <v>5.11640024185181</v>
+        <v>5.11640071868896</v>
       </c>
       <c r="H897" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G898" t="n">
-        <v>4.99833011627197</v>
+        <v>4.99832963943481</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G899" t="n">
-        <v>4.83106327056885</v>
+        <v>4.83106279373169</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G903" t="n">
-        <v>4.2899055480957</v>
+        <v>4.28990507125854</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G904" t="n">
-        <v>4.56540393829346</v>
+        <v>4.5654034614563</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G906" t="n">
-        <v>4.83106327056885</v>
+        <v>4.83106279373169</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G907" t="n">
-        <v>4.89009809494019</v>
+        <v>4.89009857177734</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G909" t="n">
-        <v>4.84090185165405</v>
+        <v>4.84090232849121</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G910" t="n">
-        <v>4.83106327056885</v>
+        <v>4.83106279373169</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G912" t="n">
-        <v>4.89009809494019</v>
+        <v>4.89009857177734</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G916" t="n">
-        <v>4.82122421264648</v>
+        <v>4.82122373580933</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G918" t="n">
-        <v>5.03768682479858</v>
+        <v>5.03768634796143</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G919" t="n">
-        <v>5.0770435333252</v>
+        <v>5.07704401016235</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G922" t="n">
-        <v>5.11640024185181</v>
+        <v>5.11640071868896</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G926" t="n">
-        <v>5.254150390625</v>
+        <v>5.25414991378784</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G928" t="n">
-        <v>5.27382898330688</v>
+        <v>5.27382850646973</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G929" t="n">
-        <v>5.29350662231445</v>
+        <v>5.29350709915161</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G930" t="n">
-        <v>5.29350662231445</v>
+        <v>5.29350709915161</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G937" t="n">
-        <v>5.11640024185181</v>
+        <v>5.11640071868896</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G939" t="n">
-        <v>5.11640024185181</v>
+        <v>5.11640071868896</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G941" t="n">
-        <v>5.0770435333252</v>
+        <v>5.07704401016235</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G944" t="n">
-        <v>5.13607883453369</v>
+        <v>5.13607931137085</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G949" t="n">
-        <v>5.254150390625</v>
+        <v>5.25414991378784</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25069,7 +25069,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G950" t="n">
-        <v>5.29350662231445</v>
+        <v>5.29350709915161</v>
       </c>
       <c r="H950" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G958" t="n">
-        <v>5.68707656860352</v>
+        <v>5.68707609176636</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25303,7 +25303,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G959" t="n">
-        <v>5.68707656860352</v>
+        <v>5.68707609176636</v>
       </c>
       <c r="H959" t="s">
         <v>8</v>
@@ -25381,7 +25381,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G962" t="n">
-        <v>5.80514717102051</v>
+        <v>5.80514669418335</v>
       </c>
       <c r="H962" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G965" t="n">
-        <v>5.80514717102051</v>
+        <v>5.80514669418335</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G969" t="n">
-        <v>6.13968086242676</v>
+        <v>6.1396803855896</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25589,7 +25589,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G970" t="n">
-        <v>6.19871616363525</v>
+        <v>6.19871664047241</v>
       </c>
       <c r="H970" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G971" t="n">
-        <v>6.33646583557129</v>
+        <v>6.33646535873413</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25641,7 +25641,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G972" t="n">
-        <v>6.27743005752563</v>
+        <v>6.27743053436279</v>
       </c>
       <c r="H972" t="s">
         <v>8</v>
@@ -25693,7 +25693,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G974" t="n">
-        <v>6.13968086242676</v>
+        <v>6.1396803855896</v>
       </c>
       <c r="H974" t="s">
         <v>8</v>
@@ -25771,7 +25771,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G977" t="n">
-        <v>6.00193119049072</v>
+        <v>6.00193166732788</v>
       </c>
       <c r="H977" t="s">
         <v>8</v>
@@ -38280,6 +38280,32 @@
         <v>9.94999980926514</v>
       </c>
       <c r="H1458" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1459">
+      <c r="A1459" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B1459" t="n">
+        <v>10934</v>
+      </c>
+      <c r="C1459" t="n">
+        <v>10.1599998474121</v>
+      </c>
+      <c r="D1459" t="n">
+        <v>9.80000019073486</v>
+      </c>
+      <c r="E1459" t="n">
+        <v>9.94999980926514</v>
+      </c>
+      <c r="F1459" t="n">
+        <v>9.94999980926514</v>
+      </c>
+      <c r="G1459" t="n">
+        <v>9.94999980926514</v>
+      </c>
+      <c r="H1459" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/EVISO.MI.xlsx
+++ b/data/EVISO.MI.xlsx
@@ -38361,6 +38361,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1462">
+      <c r="A1462" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B1462" t="n">
+        <v>7191</v>
+      </c>
+      <c r="C1462" t="n">
+        <v>10.1800003051758</v>
+      </c>
+      <c r="D1462" t="n">
+        <v>9.67000007629395</v>
+      </c>
+      <c r="E1462" t="n">
+        <v>9.67000007629395</v>
+      </c>
+      <c r="F1462" t="n">
+        <v>10.1800003051758</v>
+      </c>
+      <c r="G1462" t="n">
+        <v>10.1800003051758</v>
+      </c>
+      <c r="H1462" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/EVISO.MI.xlsx
+++ b/data/EVISO.MI.xlsx
@@ -34060,8 +34060,31 @@
       <c r="E1465" t="n">
         <v>8.80000019073486</v>
       </c>
-      <c r="F1465"/>
+      <c r="F1465" t="n">
+        <v>8.5</v>
+      </c>
       <c r="G1465" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1466">
+      <c r="A1466" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B1466" t="n">
+        <v>39759</v>
+      </c>
+      <c r="C1466" t="n">
+        <v>8.76000022888184</v>
+      </c>
+      <c r="D1466" t="n">
+        <v>8.34000015258789</v>
+      </c>
+      <c r="E1466" t="n">
+        <v>8.69999980926514</v>
+      </c>
+      <c r="F1466"/>
+      <c r="G1466" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/EVISO.MI.xlsx
+++ b/data/EVISO.MI.xlsx
@@ -34083,8 +34083,31 @@
       <c r="E1466" t="n">
         <v>8.69999980926514</v>
       </c>
-      <c r="F1466"/>
+      <c r="F1466" t="n">
+        <v>8.5</v>
+      </c>
       <c r="G1466" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1467">
+      <c r="A1467" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B1467" t="n">
+        <v>107388</v>
+      </c>
+      <c r="C1467" t="n">
+        <v>8.52999973297119</v>
+      </c>
+      <c r="D1467" t="n">
+        <v>7.69000005722046</v>
+      </c>
+      <c r="E1467" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="F1467"/>
+      <c r="G1467" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/EVISO.MI.xlsx
+++ b/data/EVISO.MI.xlsx
@@ -34106,8 +34106,31 @@
       <c r="E1467" t="n">
         <v>8.5</v>
       </c>
-      <c r="F1467"/>
+      <c r="F1467" t="n">
+        <v>8.30000019073486</v>
+      </c>
       <c r="G1467" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1468">
+      <c r="A1468" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B1468" t="n">
+        <v>20553</v>
+      </c>
+      <c r="C1468" t="n">
+        <v>8.38000011444092</v>
+      </c>
+      <c r="D1468" t="n">
+        <v>7.92999982833862</v>
+      </c>
+      <c r="E1468" t="n">
+        <v>8.15999984741211</v>
+      </c>
+      <c r="F1468"/>
+      <c r="G1468" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/EVISO.MI.xlsx
+++ b/data/EVISO.MI.xlsx
@@ -34129,8 +34129,31 @@
       <c r="E1468" t="n">
         <v>8.15999984741211</v>
       </c>
-      <c r="F1468"/>
+      <c r="F1468" t="n">
+        <v>8.01000022888184</v>
+      </c>
       <c r="G1468" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1469">
+      <c r="A1469" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B1469" t="n">
+        <v>9797</v>
+      </c>
+      <c r="C1469" t="n">
+        <v>8.22999954223633</v>
+      </c>
+      <c r="D1469" t="n">
+        <v>8.03999996185303</v>
+      </c>
+      <c r="E1469" t="n">
+        <v>8.03999996185303</v>
+      </c>
+      <c r="F1469"/>
+      <c r="G1469" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/EVISO.MI.xlsx
+++ b/data/EVISO.MI.xlsx
@@ -34159,6 +34159,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1470">
+      <c r="A1470" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B1470" t="n">
+        <v>29833</v>
+      </c>
+      <c r="C1470" t="n">
+        <v>8.19999980926514</v>
+      </c>
+      <c r="D1470" t="n">
+        <v>7.94000005722046</v>
+      </c>
+      <c r="E1470" t="n">
+        <v>8.09000015258789</v>
+      </c>
+      <c r="F1470" t="n">
+        <v>8.05000019073486</v>
+      </c>
+      <c r="G1470" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/EVISO.MI.xlsx
+++ b/data/EVISO.MI.xlsx
@@ -38647,6 +38647,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1473">
+      <c r="A1473" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B1473" t="n">
+        <v>5842</v>
+      </c>
+      <c r="C1473" t="n">
+        <v>8.1899995803833</v>
+      </c>
+      <c r="D1473" t="n">
+        <v>7.90000009536743</v>
+      </c>
+      <c r="E1473" t="n">
+        <v>7.92000007629395</v>
+      </c>
+      <c r="F1473" t="n">
+        <v>8.07999992370605</v>
+      </c>
+      <c r="G1473" t="n">
+        <v>8.07999992370605</v>
+      </c>
+      <c r="H1473" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/EVISO.MI.xlsx
+++ b/data/EVISO.MI.xlsx
@@ -38673,6 +38673,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1474">
+      <c r="A1474" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B1474" t="n">
+        <v>8412</v>
+      </c>
+      <c r="C1474" t="n">
+        <v>8.18000030517578</v>
+      </c>
+      <c r="D1474" t="n">
+        <v>8</v>
+      </c>
+      <c r="E1474" t="n">
+        <v>8.18000030517578</v>
+      </c>
+      <c r="F1474" t="n">
+        <v>7.92999982833862</v>
+      </c>
+      <c r="G1474" t="n">
+        <v>7.92999982833862</v>
+      </c>
+      <c r="H1474" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/EVISO.MI.xlsx
+++ b/data/EVISO.MI.xlsx
@@ -43124,6 +43124,64 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1475">
+      <c r="A1475" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1475" s="1" t="n">
+        <v>46314.2916666667</v>
+      </c>
+      <c r="C1475" t="n">
+        <v>8.21000003814697</v>
+      </c>
+      <c r="D1475" t="n">
+        <v>8.21000003814697</v>
+      </c>
+      <c r="E1475" t="n">
+        <v>7.21999979019165</v>
+      </c>
+      <c r="F1475" t="n">
+        <v>7.30000019073486</v>
+      </c>
+      <c r="G1475" t="n">
+        <v>7.30000019073486</v>
+      </c>
+      <c r="H1475" t="n">
+        <v>63942</v>
+      </c>
+      <c r="I1475" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1476">
+      <c r="A1476" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1476" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C1476" t="n">
+        <v>7.32999992370605</v>
+      </c>
+      <c r="D1476" t="n">
+        <v>7.80999994277954</v>
+      </c>
+      <c r="E1476" t="n">
+        <v>7.09999990463257</v>
+      </c>
+      <c r="F1476" t="n">
+        <v>7.80999994277954</v>
+      </c>
+      <c r="G1476" t="n">
+        <v>7.80999994277954</v>
+      </c>
+      <c r="H1476" t="n">
+        <v>39797</v>
+      </c>
+      <c r="I1476" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/EVISO.MI.xlsx
+++ b/data/EVISO.MI.xlsx
@@ -485,7 +485,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G4" t="n">
-        <v>2.11304235458374</v>
+        <v>2.11304259300232</v>
       </c>
       <c r="H4" t="n">
         <v>187476</v>
@@ -659,7 +659,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G10" t="n">
-        <v>1.9956511259079</v>
+        <v>1.99565088748932</v>
       </c>
       <c r="H10" t="n">
         <v>58105</v>
@@ -978,7 +978,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G21" t="n">
-        <v>1.9858683347702</v>
+        <v>1.98586857318878</v>
       </c>
       <c r="H21" t="n">
         <v>29362</v>
@@ -1065,7 +1065,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G24" t="n">
-        <v>1.9956511259079</v>
+        <v>1.99565088748932</v>
       </c>
       <c r="H24" t="n">
         <v>10648</v>
@@ -1471,7 +1471,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G38" t="n">
-        <v>2.28912901878357</v>
+        <v>2.28912878036499</v>
       </c>
       <c r="H38" t="n">
         <v>46638</v>
@@ -1529,7 +1529,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G40" t="n">
-        <v>2.24021601676941</v>
+        <v>2.24021577835083</v>
       </c>
       <c r="H40" t="n">
         <v>33692</v>
@@ -1703,7 +1703,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G46" t="n">
-        <v>2.28912901878357</v>
+        <v>2.28912878036499</v>
       </c>
       <c r="H46" t="n">
         <v>34385</v>
@@ -1761,7 +1761,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G48" t="n">
-        <v>2.28912901878357</v>
+        <v>2.28912878036499</v>
       </c>
       <c r="H48" t="n">
         <v>32533</v>
@@ -1819,7 +1819,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G50" t="n">
-        <v>2.28912901878357</v>
+        <v>2.28912878036499</v>
       </c>
       <c r="H50" t="n">
         <v>198858</v>
@@ -1935,7 +1935,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G54" t="n">
-        <v>2.24021601676941</v>
+        <v>2.24021577835083</v>
       </c>
       <c r="H54" t="n">
         <v>46913</v>
@@ -2051,7 +2051,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G58" t="n">
-        <v>2.18152046203613</v>
+        <v>2.18152070045471</v>
       </c>
       <c r="H58" t="n">
         <v>219584</v>
@@ -2080,7 +2080,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G59" t="n">
-        <v>2.24021601676941</v>
+        <v>2.24021577835083</v>
       </c>
       <c r="H59" t="n">
         <v>145477</v>
@@ -2138,7 +2138,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G61" t="n">
-        <v>2.23043346405029</v>
+        <v>2.23043370246887</v>
       </c>
       <c r="H61" t="n">
         <v>30389</v>
@@ -2254,7 +2254,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G65" t="n">
-        <v>2.1717381477356</v>
+        <v>2.17173790931702</v>
       </c>
       <c r="H65" t="n">
         <v>41977</v>
@@ -2341,7 +2341,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G68" t="n">
-        <v>2.23043346405029</v>
+        <v>2.23043370246887</v>
       </c>
       <c r="H68" t="n">
         <v>59507</v>
@@ -2573,7 +2573,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G76" t="n">
-        <v>2.1717381477356</v>
+        <v>2.17173790931702</v>
       </c>
       <c r="H76" t="n">
         <v>12073</v>
@@ -2660,7 +2660,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G79" t="n">
-        <v>2.23043346405029</v>
+        <v>2.23043370246887</v>
       </c>
       <c r="H79" t="n">
         <v>133272</v>
@@ -2747,7 +2747,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G82" t="n">
-        <v>2.18152046203613</v>
+        <v>2.18152070045471</v>
       </c>
       <c r="H82" t="n">
         <v>13914</v>
@@ -2892,7 +2892,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G87" t="n">
-        <v>2.18152046203613</v>
+        <v>2.18152070045471</v>
       </c>
       <c r="H87" t="n">
         <v>15548</v>
@@ -2921,7 +2921,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G88" t="n">
-        <v>2.18152046203613</v>
+        <v>2.18152070045471</v>
       </c>
       <c r="H88" t="n">
         <v>16155</v>
@@ -2950,7 +2950,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G89" t="n">
-        <v>2.18152046203613</v>
+        <v>2.18152070045471</v>
       </c>
       <c r="H89" t="n">
         <v>21630</v>
@@ -3211,7 +3211,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G98" t="n">
-        <v>2.24021601676941</v>
+        <v>2.24021577835083</v>
       </c>
       <c r="H98" t="n">
         <v>3240</v>
@@ -3240,7 +3240,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G99" t="n">
-        <v>2.24021601676941</v>
+        <v>2.24021577835083</v>
       </c>
       <c r="H99" t="n">
         <v>3420</v>
@@ -3385,7 +3385,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G104" t="n">
-        <v>2.6510853767395</v>
+        <v>2.65108561515808</v>
       </c>
       <c r="H104" t="n">
         <v>222446</v>
@@ -3588,7 +3588,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G111" t="n">
-        <v>2.53369426727295</v>
+        <v>2.53369402885437</v>
       </c>
       <c r="H111" t="n">
         <v>56152</v>
@@ -3675,7 +3675,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G114" t="n">
-        <v>2.53369426727295</v>
+        <v>2.53369402885437</v>
       </c>
       <c r="H114" t="n">
         <v>51806</v>
@@ -3733,7 +3733,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G116" t="n">
-        <v>2.51412916183472</v>
+        <v>2.51412892341614</v>
       </c>
       <c r="H116" t="n">
         <v>8588</v>
@@ -3791,7 +3791,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G118" t="n">
-        <v>2.49456381797791</v>
+        <v>2.49456357955933</v>
       </c>
       <c r="H118" t="n">
         <v>42909</v>
@@ -3820,7 +3820,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G119" t="n">
-        <v>2.51412916183472</v>
+        <v>2.51412892341614</v>
       </c>
       <c r="H119" t="n">
         <v>5450</v>
@@ -3878,7 +3878,7 @@
         <v>2.5</v>
       </c>
       <c r="G121" t="n">
-        <v>2.44565057754517</v>
+        <v>2.44565081596375</v>
       </c>
       <c r="H121" t="n">
         <v>24840</v>
@@ -4052,7 +4052,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G127" t="n">
-        <v>2.53369426727295</v>
+        <v>2.53369402885437</v>
       </c>
       <c r="H127" t="n">
         <v>39898</v>
@@ -4110,7 +4110,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G129" t="n">
-        <v>2.49456381797791</v>
+        <v>2.49456357955933</v>
       </c>
       <c r="H129" t="n">
         <v>3606</v>
@@ -4139,7 +4139,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G130" t="n">
-        <v>2.52391147613525</v>
+        <v>2.52391171455383</v>
       </c>
       <c r="H130" t="n">
         <v>6239</v>
@@ -4197,7 +4197,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G132" t="n">
-        <v>2.49456381797791</v>
+        <v>2.49456357955933</v>
       </c>
       <c r="H132" t="n">
         <v>6780</v>
@@ -4255,7 +4255,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G134" t="n">
-        <v>2.51412916183472</v>
+        <v>2.51412892341614</v>
       </c>
       <c r="H134" t="n">
         <v>8450</v>
@@ -4284,7 +4284,7 @@
         <v>2.5</v>
       </c>
       <c r="G135" t="n">
-        <v>2.44565057754517</v>
+        <v>2.44565081596375</v>
       </c>
       <c r="H135" t="n">
         <v>40425</v>
@@ -4313,7 +4313,7 @@
         <v>2.5</v>
       </c>
       <c r="G136" t="n">
-        <v>2.44565057754517</v>
+        <v>2.44565081596375</v>
       </c>
       <c r="H136" t="n">
         <v>2530</v>
@@ -4603,7 +4603,7 @@
         <v>2.5</v>
       </c>
       <c r="G146" t="n">
-        <v>2.44565057754517</v>
+        <v>2.44565081596375</v>
       </c>
       <c r="H146" t="n">
         <v>5600</v>
@@ -4632,7 +4632,7 @@
         <v>2.5</v>
       </c>
       <c r="G147" t="n">
-        <v>2.44565057754517</v>
+        <v>2.44565081596375</v>
       </c>
       <c r="H147" t="n">
         <v>11043</v>
@@ -4777,7 +4777,7 @@
         <v>2.5</v>
       </c>
       <c r="G152" t="n">
-        <v>2.44565057754517</v>
+        <v>2.44565081596375</v>
       </c>
       <c r="H152" t="n">
         <v>10465</v>
@@ -4806,7 +4806,7 @@
         <v>2.5</v>
       </c>
       <c r="G153" t="n">
-        <v>2.44565057754517</v>
+        <v>2.44565081596375</v>
       </c>
       <c r="H153" t="n">
         <v>14241</v>
@@ -4893,7 +4893,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G156" t="n">
-        <v>2.49456381797791</v>
+        <v>2.49456357955933</v>
       </c>
       <c r="H156" t="n">
         <v>10595</v>
@@ -4922,7 +4922,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G157" t="n">
-        <v>2.49456381797791</v>
+        <v>2.49456357955933</v>
       </c>
       <c r="H157" t="n">
         <v>21750</v>
@@ -5183,7 +5183,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G166" t="n">
-        <v>2.92499852180481</v>
+        <v>2.92499828338623</v>
       </c>
       <c r="H166" t="n">
         <v>225121</v>
@@ -5212,7 +5212,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G167" t="n">
-        <v>2.92499852180481</v>
+        <v>2.92499828338623</v>
       </c>
       <c r="H167" t="n">
         <v>82576</v>
@@ -5270,7 +5270,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G169" t="n">
-        <v>2.92499852180481</v>
+        <v>2.92499828338623</v>
       </c>
       <c r="H169" t="n">
         <v>43188</v>
@@ -5299,7 +5299,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G170" t="n">
-        <v>2.92499852180481</v>
+        <v>2.92499828338623</v>
       </c>
       <c r="H170" t="n">
         <v>21615</v>
@@ -5328,7 +5328,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G171" t="n">
-        <v>2.83695530891418</v>
+        <v>2.83695507049561</v>
       </c>
       <c r="H171" t="n">
         <v>69207</v>
@@ -5763,7 +5763,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G186" t="n">
-        <v>2.70978116989136</v>
+        <v>2.70978093147278</v>
       </c>
       <c r="H186" t="n">
         <v>22094</v>
@@ -5879,7 +5879,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G190" t="n">
-        <v>2.51412916183472</v>
+        <v>2.51412892341614</v>
       </c>
       <c r="H190" t="n">
         <v>117768</v>
@@ -6169,7 +6169,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G200" t="n">
-        <v>2.57282471656799</v>
+        <v>2.57282495498657</v>
       </c>
       <c r="H200" t="n">
         <v>32375</v>
@@ -6227,7 +6227,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G202" t="n">
-        <v>2.57282471656799</v>
+        <v>2.57282495498657</v>
       </c>
       <c r="H202" t="n">
         <v>21340</v>
@@ -6314,7 +6314,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G205" t="n">
-        <v>2.70978116989136</v>
+        <v>2.70978093147278</v>
       </c>
       <c r="H205" t="n">
         <v>51440</v>
@@ -6633,7 +6633,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G216" t="n">
-        <v>2.6510853767395</v>
+        <v>2.65108561515808</v>
       </c>
       <c r="H216" t="n">
         <v>13564</v>
@@ -43179,6 +43179,35 @@
         <v>39797</v>
       </c>
       <c r="I1476" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1477">
+      <c r="A1477" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1477" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C1477" t="n">
+        <v>7.76000022888184</v>
+      </c>
+      <c r="D1477" t="n">
+        <v>7.94999980926514</v>
+      </c>
+      <c r="E1477" t="n">
+        <v>7.53999996185303</v>
+      </c>
+      <c r="F1477" t="n">
+        <v>7.76000022888184</v>
+      </c>
+      <c r="G1477" t="n">
+        <v>7.76000022888184</v>
+      </c>
+      <c r="H1477" t="n">
+        <v>11690</v>
+      </c>
+      <c r="I1477" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/EVISO.MI.xlsx
+++ b/data/EVISO.MI.xlsx
@@ -456,7 +456,7 @@
         <v>2.25</v>
       </c>
       <c r="G3" t="n">
-        <v>2.20108556747437</v>
+        <v>2.20108580589294</v>
       </c>
       <c r="H3" t="n">
         <v>232547</v>
@@ -485,7 +485,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G4" t="n">
-        <v>2.11304259300232</v>
+        <v>2.11304235458374</v>
       </c>
       <c r="H4" t="n">
         <v>187476</v>
@@ -601,7 +601,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G8" t="n">
-        <v>2.09347701072693</v>
+        <v>2.09347724914551</v>
       </c>
       <c r="H8" t="n">
         <v>78941</v>
@@ -659,7 +659,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G10" t="n">
-        <v>1.99565088748932</v>
+        <v>1.99565100669861</v>
       </c>
       <c r="H10" t="n">
         <v>58105</v>
@@ -688,7 +688,7 @@
         <v>2</v>
       </c>
       <c r="G11" t="n">
-        <v>1.95652067661285</v>
+        <v>1.95652055740356</v>
       </c>
       <c r="H11" t="n">
         <v>87109</v>
@@ -717,7 +717,7 @@
         <v>2</v>
       </c>
       <c r="G12" t="n">
-        <v>1.95652067661285</v>
+        <v>1.95652055740356</v>
       </c>
       <c r="H12" t="n">
         <v>33913</v>
@@ -746,7 +746,7 @@
         <v>2</v>
       </c>
       <c r="G13" t="n">
-        <v>1.95652067661285</v>
+        <v>1.95652055740356</v>
       </c>
       <c r="H13" t="n">
         <v>67232</v>
@@ -804,7 +804,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G15" t="n">
-        <v>1.95162928104401</v>
+        <v>1.9516294002533</v>
       </c>
       <c r="H15" t="n">
         <v>23112</v>
@@ -833,7 +833,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G16" t="n">
-        <v>1.87825965881348</v>
+        <v>1.87825977802277</v>
       </c>
       <c r="H16" t="n">
         <v>30535</v>
@@ -891,7 +891,7 @@
         <v>2</v>
       </c>
       <c r="G18" t="n">
-        <v>1.95652067661285</v>
+        <v>1.95652055740356</v>
       </c>
       <c r="H18" t="n">
         <v>259672</v>
@@ -949,7 +949,7 @@
         <v>2</v>
       </c>
       <c r="G20" t="n">
-        <v>1.95652067661285</v>
+        <v>1.95652055740356</v>
       </c>
       <c r="H20" t="n">
         <v>44963</v>
@@ -978,7 +978,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G21" t="n">
-        <v>1.98586857318878</v>
+        <v>1.98586845397949</v>
       </c>
       <c r="H21" t="n">
         <v>29362</v>
@@ -1036,7 +1036,7 @@
         <v>2</v>
       </c>
       <c r="G23" t="n">
-        <v>1.95652067661285</v>
+        <v>1.95652055740356</v>
       </c>
       <c r="H23" t="n">
         <v>29935</v>
@@ -1065,7 +1065,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G24" t="n">
-        <v>1.99565088748932</v>
+        <v>1.99565100669861</v>
       </c>
       <c r="H24" t="n">
         <v>10648</v>
@@ -1152,7 +1152,7 @@
         <v>2</v>
       </c>
       <c r="G27" t="n">
-        <v>1.95652067661285</v>
+        <v>1.95652055740356</v>
       </c>
       <c r="H27" t="n">
         <v>20889</v>
@@ -1181,7 +1181,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G28" t="n">
-        <v>1.95162928104401</v>
+        <v>1.9516294002533</v>
       </c>
       <c r="H28" t="n">
         <v>19385</v>
@@ -1210,7 +1210,7 @@
         <v>2</v>
       </c>
       <c r="G29" t="n">
-        <v>1.95652067661285</v>
+        <v>1.95652055740356</v>
       </c>
       <c r="H29" t="n">
         <v>28897</v>
@@ -1239,7 +1239,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G30" t="n">
-        <v>2.08369469642639</v>
+        <v>2.08369445800781</v>
       </c>
       <c r="H30" t="n">
         <v>401332</v>
@@ -1326,7 +1326,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G33" t="n">
-        <v>2.13260769844055</v>
+        <v>2.13260746002197</v>
       </c>
       <c r="H33" t="n">
         <v>250444</v>
@@ -1384,7 +1384,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G35" t="n">
-        <v>2.33804202079773</v>
+        <v>2.33804249763489</v>
       </c>
       <c r="H35" t="n">
         <v>424591</v>
@@ -1413,7 +1413,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G36" t="n">
-        <v>2.25978136062622</v>
+        <v>2.25978112220764</v>
       </c>
       <c r="H36" t="n">
         <v>179668</v>
@@ -1471,7 +1471,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G38" t="n">
-        <v>2.28912878036499</v>
+        <v>2.28912901878357</v>
       </c>
       <c r="H38" t="n">
         <v>46638</v>
@@ -1529,7 +1529,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G40" t="n">
-        <v>2.24021577835083</v>
+        <v>2.24021601676941</v>
       </c>
       <c r="H40" t="n">
         <v>33692</v>
@@ -1558,7 +1558,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G41" t="n">
-        <v>2.3184769153595</v>
+        <v>2.31847667694092</v>
       </c>
       <c r="H41" t="n">
         <v>41735</v>
@@ -1616,7 +1616,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G43" t="n">
-        <v>2.32825970649719</v>
+        <v>2.32825946807861</v>
       </c>
       <c r="H43" t="n">
         <v>29630</v>
@@ -1645,7 +1645,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G44" t="n">
-        <v>2.27934670448303</v>
+        <v>2.27934646606445</v>
       </c>
       <c r="H44" t="n">
         <v>35829</v>
@@ -1674,7 +1674,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G45" t="n">
-        <v>2.25978136062622</v>
+        <v>2.25978112220764</v>
       </c>
       <c r="H45" t="n">
         <v>25346</v>
@@ -1703,7 +1703,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G46" t="n">
-        <v>2.28912878036499</v>
+        <v>2.28912901878357</v>
       </c>
       <c r="H46" t="n">
         <v>34385</v>
@@ -1761,7 +1761,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G48" t="n">
-        <v>2.28912878036499</v>
+        <v>2.28912901878357</v>
       </c>
       <c r="H48" t="n">
         <v>32533</v>
@@ -1819,7 +1819,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G50" t="n">
-        <v>2.28912878036499</v>
+        <v>2.28912901878357</v>
       </c>
       <c r="H50" t="n">
         <v>198858</v>
@@ -1877,7 +1877,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G52" t="n">
-        <v>2.25978136062622</v>
+        <v>2.25978112220764</v>
       </c>
       <c r="H52" t="n">
         <v>40111</v>
@@ -1906,7 +1906,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G53" t="n">
-        <v>2.24999856948853</v>
+        <v>2.2499988079071</v>
       </c>
       <c r="H53" t="n">
         <v>15349</v>
@@ -1935,7 +1935,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G54" t="n">
-        <v>2.24021577835083</v>
+        <v>2.24021601676941</v>
       </c>
       <c r="H54" t="n">
         <v>46913</v>
@@ -1964,7 +1964,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G55" t="n">
-        <v>2.24999856948853</v>
+        <v>2.2499988079071</v>
       </c>
       <c r="H55" t="n">
         <v>23715</v>
@@ -1993,7 +1993,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G56" t="n">
-        <v>2.24999856948853</v>
+        <v>2.2499988079071</v>
       </c>
       <c r="H56" t="n">
         <v>20720</v>
@@ -2022,7 +2022,7 @@
         <v>2.25</v>
       </c>
       <c r="G57" t="n">
-        <v>2.20108556747437</v>
+        <v>2.20108580589294</v>
       </c>
       <c r="H57" t="n">
         <v>56053</v>
@@ -2051,7 +2051,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G58" t="n">
-        <v>2.18152070045471</v>
+        <v>2.18152046203613</v>
       </c>
       <c r="H58" t="n">
         <v>219584</v>
@@ -2080,7 +2080,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G59" t="n">
-        <v>2.24021577835083</v>
+        <v>2.24021601676941</v>
       </c>
       <c r="H59" t="n">
         <v>145477</v>
@@ -2167,7 +2167,7 @@
         <v>2.25</v>
       </c>
       <c r="G62" t="n">
-        <v>2.20108556747437</v>
+        <v>2.20108580589294</v>
       </c>
       <c r="H62" t="n">
         <v>17852</v>
@@ -2196,7 +2196,7 @@
         <v>2.25</v>
       </c>
       <c r="G63" t="n">
-        <v>2.20108556747437</v>
+        <v>2.20108580589294</v>
       </c>
       <c r="H63" t="n">
         <v>4750</v>
@@ -2254,7 +2254,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G65" t="n">
-        <v>2.17173790931702</v>
+        <v>2.1717381477356</v>
       </c>
       <c r="H65" t="n">
         <v>41977</v>
@@ -2283,7 +2283,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G66" t="n">
-        <v>2.19130301475525</v>
+        <v>2.19130325317383</v>
       </c>
       <c r="H66" t="n">
         <v>23995</v>
@@ -2312,7 +2312,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G67" t="n">
-        <v>2.19130301475525</v>
+        <v>2.19130325317383</v>
       </c>
       <c r="H67" t="n">
         <v>651</v>
@@ -2370,7 +2370,7 @@
         <v>2.25</v>
       </c>
       <c r="G69" t="n">
-        <v>2.20108556747437</v>
+        <v>2.20108580589294</v>
       </c>
       <c r="H69" t="n">
         <v>21435</v>
@@ -2399,7 +2399,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G70" t="n">
-        <v>2.19130301475525</v>
+        <v>2.19130325317383</v>
       </c>
       <c r="H70" t="n">
         <v>19650</v>
@@ -2457,7 +2457,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G72" t="n">
-        <v>2.19130301475525</v>
+        <v>2.19130325317383</v>
       </c>
       <c r="H72" t="n">
         <v>13730</v>
@@ -2486,7 +2486,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G73" t="n">
-        <v>2.19130301475525</v>
+        <v>2.19130325317383</v>
       </c>
       <c r="H73" t="n">
         <v>10901</v>
@@ -2573,7 +2573,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G76" t="n">
-        <v>2.17173790931702</v>
+        <v>2.1717381477356</v>
       </c>
       <c r="H76" t="n">
         <v>12073</v>
@@ -2631,7 +2631,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G78" t="n">
-        <v>2.13260769844055</v>
+        <v>2.13260746002197</v>
       </c>
       <c r="H78" t="n">
         <v>6844</v>
@@ -2747,7 +2747,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G82" t="n">
-        <v>2.18152070045471</v>
+        <v>2.18152046203613</v>
       </c>
       <c r="H82" t="n">
         <v>13914</v>
@@ -2805,7 +2805,7 @@
         <v>2.25</v>
       </c>
       <c r="G84" t="n">
-        <v>2.20108556747437</v>
+        <v>2.20108580589294</v>
       </c>
       <c r="H84" t="n">
         <v>5934</v>
@@ -2863,7 +2863,7 @@
         <v>2.25</v>
       </c>
       <c r="G86" t="n">
-        <v>2.20108556747437</v>
+        <v>2.20108580589294</v>
       </c>
       <c r="H86" t="n">
         <v>22122</v>
@@ -2892,7 +2892,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G87" t="n">
-        <v>2.18152070045471</v>
+        <v>2.18152046203613</v>
       </c>
       <c r="H87" t="n">
         <v>15548</v>
@@ -2921,7 +2921,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G88" t="n">
-        <v>2.18152070045471</v>
+        <v>2.18152046203613</v>
       </c>
       <c r="H88" t="n">
         <v>16155</v>
@@ -2950,7 +2950,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G89" t="n">
-        <v>2.18152070045471</v>
+        <v>2.18152046203613</v>
       </c>
       <c r="H89" t="n">
         <v>21630</v>
@@ -2979,7 +2979,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G90" t="n">
-        <v>2.19130301475525</v>
+        <v>2.19130325317383</v>
       </c>
       <c r="H90" t="n">
         <v>19878</v>
@@ -3008,7 +3008,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G91" t="n">
-        <v>2.33804202079773</v>
+        <v>2.33804249763489</v>
       </c>
       <c r="H91" t="n">
         <v>287103</v>
@@ -3066,7 +3066,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G93" t="n">
-        <v>2.32825970649719</v>
+        <v>2.32825946807861</v>
       </c>
       <c r="H93" t="n">
         <v>74115</v>
@@ -3095,7 +3095,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G94" t="n">
-        <v>2.27934670448303</v>
+        <v>2.27934646606445</v>
       </c>
       <c r="H94" t="n">
         <v>66519</v>
@@ -3153,7 +3153,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G96" t="n">
-        <v>2.24999856948853</v>
+        <v>2.2499988079071</v>
       </c>
       <c r="H96" t="n">
         <v>23541</v>
@@ -3182,7 +3182,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G97" t="n">
-        <v>2.27934670448303</v>
+        <v>2.27934646606445</v>
       </c>
       <c r="H97" t="n">
         <v>9745</v>
@@ -3211,7 +3211,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G98" t="n">
-        <v>2.24021577835083</v>
+        <v>2.24021601676941</v>
       </c>
       <c r="H98" t="n">
         <v>3240</v>
@@ -3240,7 +3240,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G99" t="n">
-        <v>2.24021577835083</v>
+        <v>2.24021601676941</v>
       </c>
       <c r="H99" t="n">
         <v>3420</v>
@@ -3269,7 +3269,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G100" t="n">
-        <v>2.33804202079773</v>
+        <v>2.33804249763489</v>
       </c>
       <c r="H100" t="n">
         <v>138592</v>
@@ -3327,7 +3327,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G102" t="n">
-        <v>2.42608571052551</v>
+        <v>2.42608547210693</v>
       </c>
       <c r="H102" t="n">
         <v>170798</v>
@@ -3385,7 +3385,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G104" t="n">
-        <v>2.65108561515808</v>
+        <v>2.6510853767395</v>
       </c>
       <c r="H104" t="n">
         <v>222446</v>
@@ -3559,7 +3559,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G110" t="n">
-        <v>2.61195516586304</v>
+        <v>2.61195492744446</v>
       </c>
       <c r="H110" t="n">
         <v>28158</v>
@@ -3588,7 +3588,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G111" t="n">
-        <v>2.53369402885437</v>
+        <v>2.53369426727295</v>
       </c>
       <c r="H111" t="n">
         <v>56152</v>
@@ -3617,7 +3617,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G112" t="n">
-        <v>2.54347658157349</v>
+        <v>2.54347681999207</v>
       </c>
       <c r="H112" t="n">
         <v>34901</v>
@@ -3646,7 +3646,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G113" t="n">
-        <v>2.54347658157349</v>
+        <v>2.54347681999207</v>
       </c>
       <c r="H113" t="n">
         <v>36680</v>
@@ -3675,7 +3675,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G114" t="n">
-        <v>2.53369402885437</v>
+        <v>2.53369426727295</v>
       </c>
       <c r="H114" t="n">
         <v>51806</v>
@@ -3704,7 +3704,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G115" t="n">
-        <v>2.50434637069702</v>
+        <v>2.50434613227844</v>
       </c>
       <c r="H115" t="n">
         <v>101303</v>
@@ -3762,7 +3762,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G117" t="n">
-        <v>2.54347658157349</v>
+        <v>2.54347681999207</v>
       </c>
       <c r="H117" t="n">
         <v>39029</v>
@@ -3791,7 +3791,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G118" t="n">
-        <v>2.49456357955933</v>
+        <v>2.49456381797791</v>
       </c>
       <c r="H118" t="n">
         <v>42909</v>
@@ -3849,7 +3849,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G120" t="n">
-        <v>2.47499871253967</v>
+        <v>2.47499847412109</v>
       </c>
       <c r="H120" t="n">
         <v>9520</v>
@@ -3965,7 +3965,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G124" t="n">
-        <v>2.3184769153595</v>
+        <v>2.31847667694092</v>
       </c>
       <c r="H124" t="n">
         <v>101860</v>
@@ -3994,7 +3994,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G125" t="n">
-        <v>2.41630291938782</v>
+        <v>2.4163031578064</v>
       </c>
       <c r="H125" t="n">
         <v>35694</v>
@@ -4052,7 +4052,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G127" t="n">
-        <v>2.53369402885437</v>
+        <v>2.53369426727295</v>
       </c>
       <c r="H127" t="n">
         <v>39898</v>
@@ -4081,7 +4081,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G128" t="n">
-        <v>2.48478126525879</v>
+        <v>2.48478102684021</v>
       </c>
       <c r="H128" t="n">
         <v>22629</v>
@@ -4110,7 +4110,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G129" t="n">
-        <v>2.49456357955933</v>
+        <v>2.49456381797791</v>
       </c>
       <c r="H129" t="n">
         <v>3606</v>
@@ -4168,7 +4168,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G131" t="n">
-        <v>2.50434637069702</v>
+        <v>2.50434613227844</v>
       </c>
       <c r="H131" t="n">
         <v>17915</v>
@@ -4197,7 +4197,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G132" t="n">
-        <v>2.49456357955933</v>
+        <v>2.49456381797791</v>
       </c>
       <c r="H132" t="n">
         <v>6780</v>
@@ -4342,7 +4342,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G137" t="n">
-        <v>2.47499871253967</v>
+        <v>2.47499847412109</v>
       </c>
       <c r="H137" t="n">
         <v>1750</v>
@@ -4400,7 +4400,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G139" t="n">
-        <v>2.3184769153595</v>
+        <v>2.31847667694092</v>
       </c>
       <c r="H139" t="n">
         <v>24490</v>
@@ -4458,7 +4458,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G141" t="n">
-        <v>2.41630291938782</v>
+        <v>2.4163031578064</v>
       </c>
       <c r="H141" t="n">
         <v>4028</v>
@@ -4516,7 +4516,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G143" t="n">
-        <v>2.42608571052551</v>
+        <v>2.42608547210693</v>
       </c>
       <c r="H143" t="n">
         <v>4605</v>
@@ -4545,7 +4545,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G144" t="n">
-        <v>2.42608571052551</v>
+        <v>2.42608547210693</v>
       </c>
       <c r="H144" t="n">
         <v>3188</v>
@@ -4574,7 +4574,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G145" t="n">
-        <v>2.42608571052551</v>
+        <v>2.42608547210693</v>
       </c>
       <c r="H145" t="n">
         <v>2500</v>
@@ -4719,7 +4719,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G150" t="n">
-        <v>2.42608571052551</v>
+        <v>2.42608547210693</v>
       </c>
       <c r="H150" t="n">
         <v>14700</v>
@@ -4835,7 +4835,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G154" t="n">
-        <v>2.48478126525879</v>
+        <v>2.48478102684021</v>
       </c>
       <c r="H154" t="n">
         <v>33850</v>
@@ -4864,7 +4864,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G155" t="n">
-        <v>2.50434637069702</v>
+        <v>2.50434613227844</v>
       </c>
       <c r="H155" t="n">
         <v>11685</v>
@@ -4893,7 +4893,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G156" t="n">
-        <v>2.49456357955933</v>
+        <v>2.49456381797791</v>
       </c>
       <c r="H156" t="n">
         <v>10595</v>
@@ -4922,7 +4922,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G157" t="n">
-        <v>2.49456357955933</v>
+        <v>2.49456381797791</v>
       </c>
       <c r="H157" t="n">
         <v>21750</v>
@@ -4980,7 +4980,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G159" t="n">
-        <v>2.41630291938782</v>
+        <v>2.4163031578064</v>
       </c>
       <c r="H159" t="n">
         <v>12350</v>
@@ -5038,7 +5038,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G161" t="n">
-        <v>2.42608571052551</v>
+        <v>2.42608547210693</v>
       </c>
       <c r="H161" t="n">
         <v>5543</v>
@@ -5067,7 +5067,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G162" t="n">
-        <v>2.42608571052551</v>
+        <v>2.42608547210693</v>
       </c>
       <c r="H162" t="n">
         <v>8850</v>
@@ -5096,7 +5096,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G163" t="n">
-        <v>2.61195516586304</v>
+        <v>2.61195492744446</v>
       </c>
       <c r="H163" t="n">
         <v>108022</v>
@@ -5183,7 +5183,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G166" t="n">
-        <v>2.92499828338623</v>
+        <v>2.92499852180481</v>
       </c>
       <c r="H166" t="n">
         <v>225121</v>
@@ -5212,7 +5212,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G167" t="n">
-        <v>2.92499828338623</v>
+        <v>2.92499852180481</v>
       </c>
       <c r="H167" t="n">
         <v>82576</v>
@@ -5241,7 +5241,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G168" t="n">
-        <v>2.905433177948</v>
+        <v>2.90543341636658</v>
       </c>
       <c r="H168" t="n">
         <v>40031</v>
@@ -5270,7 +5270,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G169" t="n">
-        <v>2.92499828338623</v>
+        <v>2.92499852180481</v>
       </c>
       <c r="H169" t="n">
         <v>43188</v>
@@ -5299,7 +5299,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G170" t="n">
-        <v>2.92499828338623</v>
+        <v>2.92499852180481</v>
       </c>
       <c r="H170" t="n">
         <v>21615</v>
@@ -5328,7 +5328,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G171" t="n">
-        <v>2.83695507049561</v>
+        <v>2.83695483207703</v>
       </c>
       <c r="H171" t="n">
         <v>69207</v>
@@ -5589,7 +5589,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G180" t="n">
-        <v>2.67065072059631</v>
+        <v>2.67065048217773</v>
       </c>
       <c r="H180" t="n">
         <v>5950</v>
@@ -5618,7 +5618,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G181" t="n">
-        <v>2.66086792945862</v>
+        <v>2.6608681678772</v>
       </c>
       <c r="H181" t="n">
         <v>6625</v>
@@ -5705,7 +5705,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G184" t="n">
-        <v>2.66086792945862</v>
+        <v>2.6608681678772</v>
       </c>
       <c r="H184" t="n">
         <v>12599</v>
@@ -5763,7 +5763,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G186" t="n">
-        <v>2.70978093147278</v>
+        <v>2.70978116989136</v>
       </c>
       <c r="H186" t="n">
         <v>22094</v>
@@ -5937,7 +5937,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G192" t="n">
-        <v>2.66086792945862</v>
+        <v>2.6608681678772</v>
       </c>
       <c r="H192" t="n">
         <v>32457</v>
@@ -6053,7 +6053,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G196" t="n">
-        <v>2.50434637069702</v>
+        <v>2.50434613227844</v>
       </c>
       <c r="H196" t="n">
         <v>18379</v>
@@ -6111,7 +6111,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G198" t="n">
-        <v>2.61195516586304</v>
+        <v>2.61195492744446</v>
       </c>
       <c r="H198" t="n">
         <v>20110</v>
@@ -6169,7 +6169,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G200" t="n">
-        <v>2.57282495498657</v>
+        <v>2.57282471656799</v>
       </c>
       <c r="H200" t="n">
         <v>32375</v>
@@ -6198,7 +6198,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G201" t="n">
-        <v>2.54347658157349</v>
+        <v>2.54347681999207</v>
       </c>
       <c r="H201" t="n">
         <v>32309</v>
@@ -6227,7 +6227,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G202" t="n">
-        <v>2.57282495498657</v>
+        <v>2.57282471656799</v>
       </c>
       <c r="H202" t="n">
         <v>21340</v>
@@ -6256,7 +6256,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G203" t="n">
-        <v>2.61195516586304</v>
+        <v>2.61195492744446</v>
       </c>
       <c r="H203" t="n">
         <v>23415</v>
@@ -6314,7 +6314,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G205" t="n">
-        <v>2.70978093147278</v>
+        <v>2.70978116989136</v>
       </c>
       <c r="H205" t="n">
         <v>51440</v>
@@ -6401,7 +6401,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G208" t="n">
-        <v>2.66086792945862</v>
+        <v>2.6608681678772</v>
       </c>
       <c r="H208" t="n">
         <v>13847</v>
@@ -6430,7 +6430,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G209" t="n">
-        <v>2.67065072059631</v>
+        <v>2.67065048217773</v>
       </c>
       <c r="H209" t="n">
         <v>30620</v>
@@ -6459,7 +6459,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G210" t="n">
-        <v>2.66086792945862</v>
+        <v>2.6608681678772</v>
       </c>
       <c r="H210" t="n">
         <v>23532</v>
@@ -6488,7 +6488,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G211" t="n">
-        <v>2.66086792945862</v>
+        <v>2.6608681678772</v>
       </c>
       <c r="H211" t="n">
         <v>16536</v>
@@ -6517,7 +6517,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G212" t="n">
-        <v>2.67065072059631</v>
+        <v>2.67065048217773</v>
       </c>
       <c r="H212" t="n">
         <v>9213</v>
@@ -6546,7 +6546,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G213" t="n">
-        <v>2.66086792945862</v>
+        <v>2.6608681678772</v>
       </c>
       <c r="H213" t="n">
         <v>11727</v>
@@ -6575,7 +6575,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G214" t="n">
-        <v>2.66086792945862</v>
+        <v>2.6608681678772</v>
       </c>
       <c r="H214" t="n">
         <v>22564</v>
@@ -6633,7 +6633,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G216" t="n">
-        <v>2.65108561515808</v>
+        <v>2.6510853767395</v>
       </c>
       <c r="H216" t="n">
         <v>13564</v>
@@ -6749,7 +6749,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G220" t="n">
-        <v>2.63691449165344</v>
+        <v>2.63691425323486</v>
       </c>
       <c r="H220" t="n">
         <v>54300</v>
@@ -6778,7 +6778,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G221" t="n">
-        <v>2.64675331115723</v>
+        <v>2.64675354957581</v>
       </c>
       <c r="H221" t="n">
         <v>42202</v>
@@ -6807,7 +6807,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G222" t="n">
-        <v>2.6270751953125</v>
+        <v>2.62707495689392</v>
       </c>
       <c r="H222" t="n">
         <v>18794</v>
@@ -6952,7 +6952,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G227" t="n">
-        <v>2.51884341239929</v>
+        <v>2.51884317398071</v>
       </c>
       <c r="H227" t="n">
         <v>30812</v>
@@ -6981,7 +6981,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G228" t="n">
-        <v>2.49916505813599</v>
+        <v>2.49916481971741</v>
       </c>
       <c r="H228" t="n">
         <v>48757</v>
@@ -7010,7 +7010,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G229" t="n">
-        <v>2.52868270874023</v>
+        <v>2.52868247032166</v>
       </c>
       <c r="H229" t="n">
         <v>15710</v>
@@ -7097,7 +7097,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G232" t="n">
-        <v>2.43029022216797</v>
+        <v>2.43029046058655</v>
       </c>
       <c r="H232" t="n">
         <v>31988</v>
@@ -7155,7 +7155,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G234" t="n">
-        <v>2.51884341239929</v>
+        <v>2.51884317398071</v>
       </c>
       <c r="H234" t="n">
         <v>39902</v>
@@ -7271,7 +7271,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G238" t="n">
-        <v>2.5582001209259</v>
+        <v>2.55820035934448</v>
       </c>
       <c r="H238" t="n">
         <v>26987</v>
@@ -7329,7 +7329,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G240" t="n">
-        <v>2.6270751953125</v>
+        <v>2.62707495689392</v>
       </c>
       <c r="H240" t="n">
         <v>3780</v>
@@ -7445,7 +7445,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G244" t="n">
-        <v>2.49916505813599</v>
+        <v>2.49916481971741</v>
       </c>
       <c r="H244" t="n">
         <v>24170</v>
@@ -7503,7 +7503,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G246" t="n">
-        <v>2.48932576179504</v>
+        <v>2.48932552337646</v>
       </c>
       <c r="H246" t="n">
         <v>1994</v>
@@ -7590,7 +7590,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G249" t="n">
-        <v>2.43029022216797</v>
+        <v>2.43029046058655</v>
       </c>
       <c r="H249" t="n">
         <v>5858</v>
@@ -7677,7 +7677,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G252" t="n">
-        <v>2.48932576179504</v>
+        <v>2.48932552337646</v>
       </c>
       <c r="H252" t="n">
         <v>810</v>
@@ -7793,7 +7793,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G256" t="n">
-        <v>2.42045092582703</v>
+        <v>2.42045116424561</v>
       </c>
       <c r="H256" t="n">
         <v>9824</v>
@@ -7822,7 +7822,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G257" t="n">
-        <v>2.42045092582703</v>
+        <v>2.42045116424561</v>
       </c>
       <c r="H257" t="n">
         <v>12307</v>
@@ -7880,7 +7880,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G259" t="n">
-        <v>2.48932576179504</v>
+        <v>2.48932552337646</v>
       </c>
       <c r="H259" t="n">
         <v>7500</v>
@@ -7909,7 +7909,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G260" t="n">
-        <v>2.48932576179504</v>
+        <v>2.48932552337646</v>
       </c>
       <c r="H260" t="n">
         <v>14171</v>
@@ -7967,7 +7967,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G262" t="n">
-        <v>2.42045092582703</v>
+        <v>2.42045116424561</v>
       </c>
       <c r="H262" t="n">
         <v>6545</v>
@@ -8025,7 +8025,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G264" t="n">
-        <v>2.43029022216797</v>
+        <v>2.43029046058655</v>
       </c>
       <c r="H264" t="n">
         <v>7020</v>
@@ -8141,7 +8141,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G268" t="n">
-        <v>2.43029022216797</v>
+        <v>2.43029046058655</v>
       </c>
       <c r="H268" t="n">
         <v>6909</v>
@@ -8170,7 +8170,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G269" t="n">
-        <v>2.42045092582703</v>
+        <v>2.42045116424561</v>
       </c>
       <c r="H269" t="n">
         <v>398</v>
@@ -8257,7 +8257,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G272" t="n">
-        <v>2.27286267280579</v>
+        <v>2.27286243438721</v>
       </c>
       <c r="H272" t="n">
         <v>19540</v>
@@ -8315,7 +8315,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G274" t="n">
-        <v>2.41061210632324</v>
+        <v>2.41061186790466</v>
       </c>
       <c r="H274" t="n">
         <v>2455</v>
@@ -8373,7 +8373,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G276" t="n">
-        <v>2.42045092582703</v>
+        <v>2.42045116424561</v>
       </c>
       <c r="H276" t="n">
         <v>4035</v>
@@ -8489,7 +8489,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G280" t="n">
-        <v>2.41061210632324</v>
+        <v>2.41061186790466</v>
       </c>
       <c r="H280" t="n">
         <v>2500</v>
@@ -8518,7 +8518,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G281" t="n">
-        <v>2.41061210632324</v>
+        <v>2.41061186790466</v>
       </c>
       <c r="H281" t="n">
         <v>3607</v>
@@ -8547,7 +8547,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G282" t="n">
-        <v>2.41061210632324</v>
+        <v>2.41061186790466</v>
       </c>
       <c r="H282" t="n">
         <v>3021</v>
@@ -8576,7 +8576,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G283" t="n">
-        <v>2.35157656669617</v>
+        <v>2.35157680511475</v>
       </c>
       <c r="H283" t="n">
         <v>3780</v>
@@ -8605,7 +8605,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G284" t="n">
-        <v>2.42045092582703</v>
+        <v>2.42045116424561</v>
       </c>
       <c r="H284" t="n">
         <v>7881</v>
@@ -8634,7 +8634,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G285" t="n">
-        <v>2.52868270874023</v>
+        <v>2.52868247032166</v>
       </c>
       <c r="H285" t="n">
         <v>42819</v>
@@ -8924,7 +8924,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G295" t="n">
-        <v>2.30238032341003</v>
+        <v>2.30238008499146</v>
       </c>
       <c r="H295" t="n">
         <v>44626</v>
@@ -9040,7 +9040,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G299" t="n">
-        <v>2.27286267280579</v>
+        <v>2.27286243438721</v>
       </c>
       <c r="H299" t="n">
         <v>50689</v>
@@ -9069,7 +9069,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G300" t="n">
-        <v>2.20398783683777</v>
+        <v>2.20398807525635</v>
       </c>
       <c r="H300" t="n">
         <v>34470</v>
@@ -9185,7 +9185,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G304" t="n">
-        <v>2.27286267280579</v>
+        <v>2.27286243438721</v>
       </c>
       <c r="H304" t="n">
         <v>15470</v>
@@ -9243,7 +9243,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G306" t="n">
-        <v>2.30238032341003</v>
+        <v>2.30238008499146</v>
       </c>
       <c r="H306" t="n">
         <v>1100</v>
@@ -9417,7 +9417,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G312" t="n">
-        <v>2.35157656669617</v>
+        <v>2.35157680511475</v>
       </c>
       <c r="H312" t="n">
         <v>25055</v>
@@ -9446,7 +9446,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G313" t="n">
-        <v>2.41061210632324</v>
+        <v>2.41061186790466</v>
       </c>
       <c r="H313" t="n">
         <v>37964</v>
@@ -9678,7 +9678,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G321" t="n">
-        <v>2.27286267280579</v>
+        <v>2.27286243438721</v>
       </c>
       <c r="H321" t="n">
         <v>3425</v>
@@ -9707,7 +9707,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G322" t="n">
-        <v>2.28270196914673</v>
+        <v>2.28270173072815</v>
       </c>
       <c r="H322" t="n">
         <v>16706</v>
@@ -9823,7 +9823,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G326" t="n">
-        <v>2.35157656669617</v>
+        <v>2.35157680511475</v>
       </c>
       <c r="H326" t="n">
         <v>2807</v>
@@ -9910,7 +9910,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G329" t="n">
-        <v>2.28270196914673</v>
+        <v>2.28270173072815</v>
       </c>
       <c r="H329" t="n">
         <v>4326</v>
@@ -9939,7 +9939,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G330" t="n">
-        <v>2.30238032341003</v>
+        <v>2.30238008499146</v>
       </c>
       <c r="H330" t="n">
         <v>2424</v>
@@ -9997,7 +9997,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G332" t="n">
-        <v>2.30238032341003</v>
+        <v>2.30238008499146</v>
       </c>
       <c r="H332" t="n">
         <v>1205</v>
@@ -10055,7 +10055,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G334" t="n">
-        <v>2.20398783683777</v>
+        <v>2.20398807525635</v>
       </c>
       <c r="H334" t="n">
         <v>12548</v>
@@ -10142,7 +10142,7 @@
         <v>2.25</v>
       </c>
       <c r="G337" t="n">
-        <v>2.21382713317871</v>
+        <v>2.21382737159729</v>
       </c>
       <c r="H337" t="n">
         <v>4451</v>
@@ -10316,7 +10316,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G343" t="n">
-        <v>2.41061210632324</v>
+        <v>2.41061186790466</v>
       </c>
       <c r="H343" t="n">
         <v>157345</v>
@@ -10345,7 +10345,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G344" t="n">
-        <v>2.41061210632324</v>
+        <v>2.41061186790466</v>
       </c>
       <c r="H344" t="n">
         <v>177569</v>
@@ -10374,7 +10374,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G345" t="n">
-        <v>2.28270196914673</v>
+        <v>2.28270173072815</v>
       </c>
       <c r="H345" t="n">
         <v>36620</v>
@@ -10490,7 +10490,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G349" t="n">
-        <v>2.35157656669617</v>
+        <v>2.35157680511475</v>
       </c>
       <c r="H349" t="n">
         <v>12100</v>
@@ -10548,7 +10548,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G351" t="n">
-        <v>2.28270196914673</v>
+        <v>2.28270173072815</v>
       </c>
       <c r="H351" t="n">
         <v>6350</v>
@@ -10606,7 +10606,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G353" t="n">
-        <v>2.28270196914673</v>
+        <v>2.28270173072815</v>
       </c>
       <c r="H353" t="n">
         <v>6000</v>
@@ -10635,7 +10635,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G354" t="n">
-        <v>2.28270196914673</v>
+        <v>2.28270173072815</v>
       </c>
       <c r="H354" t="n">
         <v>4900</v>
@@ -10664,7 +10664,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G355" t="n">
-        <v>2.27286267280579</v>
+        <v>2.27286243438721</v>
       </c>
       <c r="H355" t="n">
         <v>5466</v>
@@ -10693,7 +10693,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G356" t="n">
-        <v>2.28270196914673</v>
+        <v>2.28270173072815</v>
       </c>
       <c r="H356" t="n">
         <v>4255</v>
@@ -10751,7 +10751,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G358" t="n">
-        <v>2.28270196914673</v>
+        <v>2.28270173072815</v>
       </c>
       <c r="H358" t="n">
         <v>9650</v>
@@ -10780,7 +10780,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G359" t="n">
-        <v>2.27286267280579</v>
+        <v>2.27286243438721</v>
       </c>
       <c r="H359" t="n">
         <v>10142</v>
@@ -10809,7 +10809,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G360" t="n">
-        <v>2.28270196914673</v>
+        <v>2.28270173072815</v>
       </c>
       <c r="H360" t="n">
         <v>6650</v>
@@ -10838,7 +10838,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G361" t="n">
-        <v>2.30238032341003</v>
+        <v>2.30238008499146</v>
       </c>
       <c r="H361" t="n">
         <v>1405</v>
@@ -10867,7 +10867,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G362" t="n">
-        <v>2.30238032341003</v>
+        <v>2.30238008499146</v>
       </c>
       <c r="H362" t="n">
         <v>136082</v>
@@ -10896,7 +10896,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G363" t="n">
-        <v>2.30238032341003</v>
+        <v>2.30238008499146</v>
       </c>
       <c r="H363" t="n">
         <v>0</v>
@@ -10954,7 +10954,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G365" t="n">
-        <v>2.41061210632324</v>
+        <v>2.41061186790466</v>
       </c>
       <c r="H365" t="n">
         <v>46145</v>
@@ -11070,7 +11070,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G369" t="n">
-        <v>2.5385217666626</v>
+        <v>2.53852200508118</v>
       </c>
       <c r="H369" t="n">
         <v>58285</v>
@@ -11157,7 +11157,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G372" t="n">
-        <v>2.48932576179504</v>
+        <v>2.48932552337646</v>
       </c>
       <c r="H372" t="n">
         <v>30239</v>
@@ -11360,7 +11360,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G379" t="n">
-        <v>2.35157656669617</v>
+        <v>2.35157680511475</v>
       </c>
       <c r="H379" t="n">
         <v>1201</v>
@@ -11534,7 +11534,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G385" t="n">
-        <v>2.43029022216797</v>
+        <v>2.43029046058655</v>
       </c>
       <c r="H385" t="n">
         <v>25280</v>
@@ -11592,7 +11592,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G387" t="n">
-        <v>2.43029022216797</v>
+        <v>2.43029046058655</v>
       </c>
       <c r="H387" t="n">
         <v>13258</v>
@@ -11766,7 +11766,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G393" t="n">
-        <v>2.35157656669617</v>
+        <v>2.35157680511475</v>
       </c>
       <c r="H393" t="n">
         <v>1601</v>
@@ -12172,7 +12172,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G407" t="n">
-        <v>2.42045092582703</v>
+        <v>2.42045116424561</v>
       </c>
       <c r="H407" t="n">
         <v>11611</v>
@@ -12288,7 +12288,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G411" t="n">
-        <v>2.48932576179504</v>
+        <v>2.48932552337646</v>
       </c>
       <c r="H411" t="n">
         <v>11281</v>
@@ -12317,7 +12317,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G412" t="n">
-        <v>2.48932576179504</v>
+        <v>2.48932552337646</v>
       </c>
       <c r="H412" t="n">
         <v>951</v>
@@ -12346,7 +12346,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G413" t="n">
-        <v>2.42045092582703</v>
+        <v>2.42045116424561</v>
       </c>
       <c r="H413" t="n">
         <v>180</v>
@@ -12578,7 +12578,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G421" t="n">
-        <v>2.49916505813599</v>
+        <v>2.49916481971741</v>
       </c>
       <c r="H421" t="n">
         <v>16752</v>
@@ -12665,7 +12665,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G424" t="n">
-        <v>2.49916505813599</v>
+        <v>2.49916481971741</v>
       </c>
       <c r="H424" t="n">
         <v>35639</v>
@@ -12752,7 +12752,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G427" t="n">
-        <v>2.5582001209259</v>
+        <v>2.55820035934448</v>
       </c>
       <c r="H427" t="n">
         <v>559114</v>
@@ -12781,7 +12781,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G428" t="n">
-        <v>2.52868270874023</v>
+        <v>2.52868247032166</v>
       </c>
       <c r="H428" t="n">
         <v>29512</v>
@@ -12897,7 +12897,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G432" t="n">
-        <v>2.51884341239929</v>
+        <v>2.51884317398071</v>
       </c>
       <c r="H432" t="n">
         <v>60938</v>
@@ -12955,7 +12955,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G434" t="n">
-        <v>2.5582001209259</v>
+        <v>2.55820035934448</v>
       </c>
       <c r="H434" t="n">
         <v>47155</v>
@@ -12984,7 +12984,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G435" t="n">
-        <v>2.52868270874023</v>
+        <v>2.52868247032166</v>
       </c>
       <c r="H435" t="n">
         <v>20543</v>
@@ -13042,7 +13042,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G437" t="n">
-        <v>2.52868270874023</v>
+        <v>2.52868247032166</v>
       </c>
       <c r="H437" t="n">
         <v>12222</v>
@@ -13071,7 +13071,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G438" t="n">
-        <v>2.51884341239929</v>
+        <v>2.51884317398071</v>
       </c>
       <c r="H438" t="n">
         <v>18341</v>
@@ -13100,7 +13100,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G439" t="n">
-        <v>2.52868270874023</v>
+        <v>2.52868247032166</v>
       </c>
       <c r="H439" t="n">
         <v>19433</v>
@@ -13129,7 +13129,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G440" t="n">
-        <v>2.43029022216797</v>
+        <v>2.43029046058655</v>
       </c>
       <c r="H440" t="n">
         <v>23395</v>
@@ -13216,7 +13216,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G443" t="n">
-        <v>2.41061210632324</v>
+        <v>2.41061186790466</v>
       </c>
       <c r="H443" t="n">
         <v>15137</v>
@@ -13274,7 +13274,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G445" t="n">
-        <v>2.49916505813599</v>
+        <v>2.49916481971741</v>
       </c>
       <c r="H445" t="n">
         <v>52693</v>
@@ -13332,7 +13332,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G447" t="n">
-        <v>2.28270196914673</v>
+        <v>2.28270173072815</v>
       </c>
       <c r="H447" t="n">
         <v>23165</v>
@@ -13361,7 +13361,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G448" t="n">
-        <v>2.28270196914673</v>
+        <v>2.28270173072815</v>
       </c>
       <c r="H448" t="n">
         <v>40210</v>
@@ -13477,7 +13477,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G452" t="n">
-        <v>2.43029022216797</v>
+        <v>2.43029046058655</v>
       </c>
       <c r="H452" t="n">
         <v>37050</v>
@@ -13622,7 +13622,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G457" t="n">
-        <v>2.49916505813599</v>
+        <v>2.49916481971741</v>
       </c>
       <c r="H457" t="n">
         <v>35738</v>
@@ -13651,7 +13651,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G458" t="n">
-        <v>2.51884341239929</v>
+        <v>2.51884317398071</v>
       </c>
       <c r="H458" t="n">
         <v>18389</v>
@@ -13680,7 +13680,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G459" t="n">
-        <v>2.51884341239929</v>
+        <v>2.51884317398071</v>
       </c>
       <c r="H459" t="n">
         <v>0</v>
@@ -13709,7 +13709,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G460" t="n">
-        <v>2.43029022216797</v>
+        <v>2.43029046058655</v>
       </c>
       <c r="H460" t="n">
         <v>29119</v>
@@ -13825,7 +13825,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G464" t="n">
-        <v>2.42045092582703</v>
+        <v>2.42045116424561</v>
       </c>
       <c r="H464" t="n">
         <v>2155</v>
@@ -13854,7 +13854,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G465" t="n">
-        <v>2.41061210632324</v>
+        <v>2.41061186790466</v>
       </c>
       <c r="H465" t="n">
         <v>3505</v>
@@ -13941,7 +13941,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G468" t="n">
-        <v>2.42045092582703</v>
+        <v>2.42045116424561</v>
       </c>
       <c r="H468" t="n">
         <v>5886</v>
@@ -13970,7 +13970,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G469" t="n">
-        <v>2.42045092582703</v>
+        <v>2.42045116424561</v>
       </c>
       <c r="H469" t="n">
         <v>0</v>
@@ -14028,7 +14028,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G471" t="n">
-        <v>2.43029022216797</v>
+        <v>2.43029046058655</v>
       </c>
       <c r="H471" t="n">
         <v>8504</v>
@@ -14144,7 +14144,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G475" t="n">
-        <v>2.42045092582703</v>
+        <v>2.42045116424561</v>
       </c>
       <c r="H475" t="n">
         <v>5971</v>
@@ -14260,7 +14260,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G479" t="n">
-        <v>2.43029022216797</v>
+        <v>2.43029046058655</v>
       </c>
       <c r="H479" t="n">
         <v>7842</v>
@@ -14318,7 +14318,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G481" t="n">
-        <v>2.42045092582703</v>
+        <v>2.42045116424561</v>
       </c>
       <c r="H481" t="n">
         <v>3675</v>
@@ -14376,7 +14376,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G483" t="n">
-        <v>2.42045092582703</v>
+        <v>2.42045116424561</v>
       </c>
       <c r="H483" t="n">
         <v>6429</v>
@@ -14492,7 +14492,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G487" t="n">
-        <v>2.41061210632324</v>
+        <v>2.41061186790466</v>
       </c>
       <c r="H487" t="n">
         <v>1829</v>
@@ -14521,7 +14521,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G488" t="n">
-        <v>2.41061210632324</v>
+        <v>2.41061186790466</v>
       </c>
       <c r="H488" t="n">
         <v>0</v>
@@ -14579,7 +14579,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G490" t="n">
-        <v>2.41061210632324</v>
+        <v>2.41061186790466</v>
       </c>
       <c r="H490" t="n">
         <v>18612</v>
@@ -14666,7 +14666,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G493" t="n">
-        <v>2.41061210632324</v>
+        <v>2.41061186790466</v>
       </c>
       <c r="H493" t="n">
         <v>1</v>
@@ -14695,7 +14695,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G494" t="n">
-        <v>2.41061210632324</v>
+        <v>2.41061186790466</v>
       </c>
       <c r="H494" t="n">
         <v>0</v>
@@ -14724,7 +14724,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G495" t="n">
-        <v>2.41061210632324</v>
+        <v>2.41061186790466</v>
       </c>
       <c r="H495" t="n">
         <v>20619</v>
@@ -14869,7 +14869,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G500" t="n">
-        <v>2.48932576179504</v>
+        <v>2.48932552337646</v>
       </c>
       <c r="H500" t="n">
         <v>22406</v>
@@ -14898,7 +14898,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G501" t="n">
-        <v>2.41061210632324</v>
+        <v>2.41061186790466</v>
       </c>
       <c r="H501" t="n">
         <v>232</v>
@@ -14985,7 +14985,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G504" t="n">
-        <v>2.42045092582703</v>
+        <v>2.42045116424561</v>
       </c>
       <c r="H504" t="n">
         <v>3174</v>
@@ -15014,7 +15014,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G505" t="n">
-        <v>2.42045092582703</v>
+        <v>2.42045116424561</v>
       </c>
       <c r="H505" t="n">
         <v>0</v>
@@ -15072,7 +15072,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G507" t="n">
-        <v>2.42045092582703</v>
+        <v>2.42045116424561</v>
       </c>
       <c r="H507" t="n">
         <v>4</v>
@@ -15130,7 +15130,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G509" t="n">
-        <v>2.43029022216797</v>
+        <v>2.43029046058655</v>
       </c>
       <c r="H509" t="n">
         <v>6606</v>
@@ -15159,7 +15159,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G510" t="n">
-        <v>2.43029022216797</v>
+        <v>2.43029046058655</v>
       </c>
       <c r="H510" t="n">
         <v>4444</v>
@@ -15217,7 +15217,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G512" t="n">
-        <v>2.49916505813599</v>
+        <v>2.49916481971741</v>
       </c>
       <c r="H512" t="n">
         <v>18429</v>
@@ -15304,7 +15304,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G515" t="n">
-        <v>2.48932576179504</v>
+        <v>2.48932552337646</v>
       </c>
       <c r="H515" t="n">
         <v>421</v>
@@ -15536,7 +15536,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G523" t="n">
-        <v>2.5582001209259</v>
+        <v>2.55820035934448</v>
       </c>
       <c r="H523" t="n">
         <v>28775</v>
@@ -15681,7 +15681,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G528" t="n">
-        <v>2.5582001209259</v>
+        <v>2.55820035934448</v>
       </c>
       <c r="H528" t="n">
         <v>6832</v>
@@ -15710,7 +15710,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G529" t="n">
-        <v>2.52868270874023</v>
+        <v>2.52868247032166</v>
       </c>
       <c r="H529" t="n">
         <v>7700</v>
@@ -15739,7 +15739,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G530" t="n">
-        <v>2.5582001209259</v>
+        <v>2.55820035934448</v>
       </c>
       <c r="H530" t="n">
         <v>6304</v>
@@ -15826,7 +15826,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G533" t="n">
-        <v>2.63691449165344</v>
+        <v>2.63691425323486</v>
       </c>
       <c r="H533" t="n">
         <v>19150</v>
@@ -15884,7 +15884,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G535" t="n">
-        <v>2.5385217666626</v>
+        <v>2.53852200508118</v>
       </c>
       <c r="H535" t="n">
         <v>7600</v>
@@ -15913,7 +15913,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G536" t="n">
-        <v>2.5582001209259</v>
+        <v>2.55820035934448</v>
       </c>
       <c r="H536" t="n">
         <v>1850</v>
@@ -15971,7 +15971,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G538" t="n">
-        <v>2.5582001209259</v>
+        <v>2.55820035934448</v>
       </c>
       <c r="H538" t="n">
         <v>2300</v>
@@ -16000,7 +16000,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G539" t="n">
-        <v>2.5582001209259</v>
+        <v>2.55820035934448</v>
       </c>
       <c r="H539" t="n">
         <v>3806</v>
@@ -16029,7 +16029,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G540" t="n">
-        <v>2.5385217666626</v>
+        <v>2.53852200508118</v>
       </c>
       <c r="H540" t="n">
         <v>6800</v>
@@ -16058,7 +16058,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G541" t="n">
-        <v>2.5582001209259</v>
+        <v>2.55820035934448</v>
       </c>
       <c r="H541" t="n">
         <v>8509</v>
@@ -16087,7 +16087,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G542" t="n">
-        <v>2.5582001209259</v>
+        <v>2.55820035934448</v>
       </c>
       <c r="H542" t="n">
         <v>6554</v>
@@ -16145,7 +16145,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G544" t="n">
-        <v>2.64675331115723</v>
+        <v>2.64675354957581</v>
       </c>
       <c r="H544" t="n">
         <v>29045</v>
@@ -16174,7 +16174,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G545" t="n">
-        <v>2.64675331115723</v>
+        <v>2.64675354957581</v>
       </c>
       <c r="H545" t="n">
         <v>24168</v>
@@ -16232,7 +16232,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G547" t="n">
-        <v>2.35157656669617</v>
+        <v>2.35157680511475</v>
       </c>
       <c r="H547" t="n">
         <v>106601</v>
@@ -16319,7 +16319,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G550" t="n">
-        <v>2.30238032341003</v>
+        <v>2.30238008499146</v>
       </c>
       <c r="H550" t="n">
         <v>10856</v>
@@ -16406,7 +16406,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G553" t="n">
-        <v>2.28270196914673</v>
+        <v>2.28270173072815</v>
       </c>
       <c r="H553" t="n">
         <v>7360</v>
@@ -16522,7 +16522,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G557" t="n">
-        <v>2.27286267280579</v>
+        <v>2.27286243438721</v>
       </c>
       <c r="H557" t="n">
         <v>3150</v>
@@ -16551,7 +16551,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G558" t="n">
-        <v>2.27286267280579</v>
+        <v>2.27286243438721</v>
       </c>
       <c r="H558" t="n">
         <v>0</v>
@@ -16580,7 +16580,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G559" t="n">
-        <v>2.27286267280579</v>
+        <v>2.27286243438721</v>
       </c>
       <c r="H559" t="n">
         <v>4065</v>
@@ -16609,7 +16609,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G560" t="n">
-        <v>2.28270196914673</v>
+        <v>2.28270173072815</v>
       </c>
       <c r="H560" t="n">
         <v>890</v>
@@ -16667,7 +16667,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G562" t="n">
-        <v>2.24334478378296</v>
+        <v>2.24334502220154</v>
       </c>
       <c r="H562" t="n">
         <v>11905</v>
@@ -16696,7 +16696,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G563" t="n">
-        <v>2.20398783683777</v>
+        <v>2.20398807525635</v>
       </c>
       <c r="H563" t="n">
         <v>34790</v>
@@ -16754,7 +16754,7 @@
         <v>2.25</v>
       </c>
       <c r="G565" t="n">
-        <v>2.21382713317871</v>
+        <v>2.21382737159729</v>
       </c>
       <c r="H565" t="n">
         <v>1201</v>
@@ -16783,7 +16783,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G566" t="n">
-        <v>2.27286267280579</v>
+        <v>2.27286243438721</v>
       </c>
       <c r="H566" t="n">
         <v>500</v>
@@ -16899,7 +16899,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G570" t="n">
-        <v>2.24334478378296</v>
+        <v>2.24334502220154</v>
       </c>
       <c r="H570" t="n">
         <v>18090</v>
@@ -16986,7 +16986,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G573" t="n">
-        <v>2.28270196914673</v>
+        <v>2.28270173072815</v>
       </c>
       <c r="H573" t="n">
         <v>2415</v>
@@ -17015,7 +17015,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G574" t="n">
-        <v>2.20398783683777</v>
+        <v>2.20398807525635</v>
       </c>
       <c r="H574" t="n">
         <v>24592</v>
@@ -17131,7 +17131,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G578" t="n">
-        <v>2.28270196914673</v>
+        <v>2.28270173072815</v>
       </c>
       <c r="H578" t="n">
         <v>2017</v>
@@ -17189,7 +17189,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G580" t="n">
-        <v>2.27286267280579</v>
+        <v>2.27286243438721</v>
       </c>
       <c r="H580" t="n">
         <v>2648</v>
@@ -17218,7 +17218,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G581" t="n">
-        <v>2.28270196914673</v>
+        <v>2.28270173072815</v>
       </c>
       <c r="H581" t="n">
         <v>1455</v>
@@ -17276,7 +17276,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G583" t="n">
-        <v>2.30238032341003</v>
+        <v>2.30238008499146</v>
       </c>
       <c r="H583" t="n">
         <v>4608</v>
@@ -17653,7 +17653,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G596" t="n">
-        <v>2.28270196914673</v>
+        <v>2.28270173072815</v>
       </c>
       <c r="H596" t="n">
         <v>3802</v>
@@ -17740,7 +17740,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G599" t="n">
-        <v>2.30238032341003</v>
+        <v>2.30238008499146</v>
       </c>
       <c r="H599" t="n">
         <v>2949</v>
@@ -17798,7 +17798,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G601" t="n">
-        <v>2.24334478378296</v>
+        <v>2.24334502220154</v>
       </c>
       <c r="H601" t="n">
         <v>17283</v>
@@ -17827,7 +17827,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G602" t="n">
-        <v>2.27286267280579</v>
+        <v>2.27286243438721</v>
       </c>
       <c r="H602" t="n">
         <v>2094</v>
@@ -17856,7 +17856,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G603" t="n">
-        <v>2.27286267280579</v>
+        <v>2.27286243438721</v>
       </c>
       <c r="H603" t="n">
         <v>4262</v>
@@ -17914,7 +17914,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G605" t="n">
-        <v>2.30238032341003</v>
+        <v>2.30238008499146</v>
       </c>
       <c r="H605" t="n">
         <v>3421</v>
@@ -17943,7 +17943,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G606" t="n">
-        <v>2.30238032341003</v>
+        <v>2.30238008499146</v>
       </c>
       <c r="H606" t="n">
         <v>1394</v>
@@ -17972,7 +17972,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G607" t="n">
-        <v>2.30238032341003</v>
+        <v>2.30238008499146</v>
       </c>
       <c r="H607" t="n">
         <v>1488</v>
@@ -18001,7 +18001,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G608" t="n">
-        <v>2.30238032341003</v>
+        <v>2.30238008499146</v>
       </c>
       <c r="H608" t="n">
         <v>1944</v>
@@ -18030,7 +18030,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G609" t="n">
-        <v>2.30238032341003</v>
+        <v>2.30238008499146</v>
       </c>
       <c r="H609" t="n">
         <v>1543</v>
@@ -18088,7 +18088,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G611" t="n">
-        <v>2.30238032341003</v>
+        <v>2.30238008499146</v>
       </c>
       <c r="H611" t="n">
         <v>1209</v>
@@ -18146,7 +18146,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G613" t="n">
-        <v>2.27286267280579</v>
+        <v>2.27286243438721</v>
       </c>
       <c r="H613" t="n">
         <v>3339</v>
@@ -18407,7 +18407,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G622" t="n">
-        <v>2.24334478378296</v>
+        <v>2.24334502220154</v>
       </c>
       <c r="H622" t="n">
         <v>729</v>
@@ -18436,7 +18436,7 @@
         <v>2.25</v>
       </c>
       <c r="G623" t="n">
-        <v>2.21382713317871</v>
+        <v>2.21382737159729</v>
       </c>
       <c r="H623" t="n">
         <v>3507</v>
@@ -18494,7 +18494,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G625" t="n">
-        <v>2.24334478378296</v>
+        <v>2.24334502220154</v>
       </c>
       <c r="H625" t="n">
         <v>3357</v>
@@ -18610,7 +18610,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G629" t="n">
-        <v>2.24334478378296</v>
+        <v>2.24334502220154</v>
       </c>
       <c r="H629" t="n">
         <v>1003</v>
@@ -18639,7 +18639,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G630" t="n">
-        <v>2.28270196914673</v>
+        <v>2.28270173072815</v>
       </c>
       <c r="H630" t="n">
         <v>26686</v>
@@ -18668,7 +18668,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G631" t="n">
-        <v>2.28270196914673</v>
+        <v>2.28270173072815</v>
       </c>
       <c r="H631" t="n">
         <v>1654</v>
@@ -18726,7 +18726,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G633" t="n">
-        <v>2.28270196914673</v>
+        <v>2.28270173072815</v>
       </c>
       <c r="H633" t="n">
         <v>1752</v>
@@ -18755,7 +18755,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G634" t="n">
-        <v>2.28270196914673</v>
+        <v>2.28270173072815</v>
       </c>
       <c r="H634" t="n">
         <v>3413</v>
@@ -18900,7 +18900,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G639" t="n">
-        <v>2.27286267280579</v>
+        <v>2.27286243438721</v>
       </c>
       <c r="H639" t="n">
         <v>2152</v>
@@ -18929,7 +18929,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G640" t="n">
-        <v>2.28270196914673</v>
+        <v>2.28270173072815</v>
       </c>
       <c r="H640" t="n">
         <v>2342</v>
@@ -18987,7 +18987,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G642" t="n">
-        <v>2.24334478378296</v>
+        <v>2.24334502220154</v>
       </c>
       <c r="H642" t="n">
         <v>3219</v>
@@ -19074,7 +19074,7 @@
         <v>2.25</v>
       </c>
       <c r="G645" t="n">
-        <v>2.21382713317871</v>
+        <v>2.21382737159729</v>
       </c>
       <c r="H645" t="n">
         <v>5907</v>
@@ -19132,7 +19132,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G647" t="n">
-        <v>2.20398783683777</v>
+        <v>2.20398807525635</v>
       </c>
       <c r="H647" t="n">
         <v>2247</v>
@@ -19190,7 +19190,7 @@
         <v>2.25</v>
       </c>
       <c r="G649" t="n">
-        <v>2.21382713317871</v>
+        <v>2.21382737159729</v>
       </c>
       <c r="H649" t="n">
         <v>1413</v>
@@ -19306,7 +19306,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G653" t="n">
-        <v>2.13511347770691</v>
+        <v>2.13511323928833</v>
       </c>
       <c r="H653" t="n">
         <v>4940</v>
@@ -19335,7 +19335,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G654" t="n">
-        <v>2.14495277404785</v>
+        <v>2.14495253562927</v>
       </c>
       <c r="H654" t="n">
         <v>4916</v>
@@ -19480,7 +19480,7 @@
         <v>2.25</v>
       </c>
       <c r="G659" t="n">
-        <v>2.21382713317871</v>
+        <v>2.21382737159729</v>
       </c>
       <c r="H659" t="n">
         <v>8762</v>
@@ -19538,7 +19538,7 @@
         <v>2.25</v>
       </c>
       <c r="G661" t="n">
-        <v>2.21382713317871</v>
+        <v>2.21382737159729</v>
       </c>
       <c r="H661" t="n">
         <v>6280</v>
@@ -19683,7 +19683,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G666" t="n">
-        <v>2.24334478378296</v>
+        <v>2.24334502220154</v>
       </c>
       <c r="H666" t="n">
         <v>10498</v>
@@ -19799,7 +19799,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G670" t="n">
-        <v>2.20398783683777</v>
+        <v>2.20398807525635</v>
       </c>
       <c r="H670" t="n">
         <v>7844</v>
@@ -19828,7 +19828,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G671" t="n">
-        <v>2.24334478378296</v>
+        <v>2.24334502220154</v>
       </c>
       <c r="H671" t="n">
         <v>7122</v>
@@ -19857,7 +19857,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G672" t="n">
-        <v>2.24334478378296</v>
+        <v>2.24334502220154</v>
       </c>
       <c r="H672" t="n">
         <v>3472</v>
@@ -19886,7 +19886,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G673" t="n">
-        <v>2.24334478378296</v>
+        <v>2.24334502220154</v>
       </c>
       <c r="H673" t="n">
         <v>4302</v>
@@ -19973,7 +19973,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G676" t="n">
-        <v>2.20398783683777</v>
+        <v>2.20398807525635</v>
       </c>
       <c r="H676" t="n">
         <v>2219</v>
@@ -20118,7 +20118,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G681" t="n">
-        <v>2.27286267280579</v>
+        <v>2.27286243438721</v>
       </c>
       <c r="H681" t="n">
         <v>3394</v>
@@ -20234,7 +20234,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G685" t="n">
-        <v>2.35157656669617</v>
+        <v>2.35157680511475</v>
       </c>
       <c r="H685" t="n">
         <v>14060</v>
@@ -20321,7 +20321,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G688" t="n">
-        <v>2.35157656669617</v>
+        <v>2.35157680511475</v>
       </c>
       <c r="H688" t="n">
         <v>3921</v>
@@ -20756,7 +20756,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G703" t="n">
-        <v>2.30238032341003</v>
+        <v>2.30238008499146</v>
       </c>
       <c r="H703" t="n">
         <v>18619</v>
@@ -20785,7 +20785,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G704" t="n">
-        <v>2.30238032341003</v>
+        <v>2.30238008499146</v>
       </c>
       <c r="H704" t="n">
         <v>5776</v>
@@ -20814,7 +20814,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G705" t="n">
-        <v>2.30238032341003</v>
+        <v>2.30238008499146</v>
       </c>
       <c r="H705" t="n">
         <v>4067</v>
@@ -20843,7 +20843,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G706" t="n">
-        <v>2.28270196914673</v>
+        <v>2.28270173072815</v>
       </c>
       <c r="H706" t="n">
         <v>2590</v>
@@ -20872,7 +20872,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G707" t="n">
-        <v>2.24334478378296</v>
+        <v>2.24334502220154</v>
       </c>
       <c r="H707" t="n">
         <v>10831</v>
@@ -20988,7 +20988,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G711" t="n">
-        <v>2.43029022216797</v>
+        <v>2.43029046058655</v>
       </c>
       <c r="H711" t="n">
         <v>15029</v>
@@ -21017,7 +21017,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G712" t="n">
-        <v>2.43029022216797</v>
+        <v>2.43029046058655</v>
       </c>
       <c r="H712" t="n">
         <v>8791</v>
@@ -21133,7 +21133,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G716" t="n">
-        <v>2.35157656669617</v>
+        <v>2.35157680511475</v>
       </c>
       <c r="H716" t="n">
         <v>16386</v>
@@ -21162,7 +21162,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G717" t="n">
-        <v>2.43029022216797</v>
+        <v>2.43029046058655</v>
       </c>
       <c r="H717" t="n">
         <v>59441</v>
@@ -21307,7 +21307,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G722" t="n">
-        <v>2.35157656669617</v>
+        <v>2.35157680511475</v>
       </c>
       <c r="H722" t="n">
         <v>15797</v>
@@ -21365,7 +21365,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G724" t="n">
-        <v>2.35157656669617</v>
+        <v>2.35157680511475</v>
       </c>
       <c r="H724" t="n">
         <v>6782</v>
@@ -21423,7 +21423,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G726" t="n">
-        <v>2.41061210632324</v>
+        <v>2.41061186790466</v>
       </c>
       <c r="H726" t="n">
         <v>10601</v>
@@ -21452,7 +21452,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G727" t="n">
-        <v>2.43029022216797</v>
+        <v>2.43029046058655</v>
       </c>
       <c r="H727" t="n">
         <v>6641</v>
@@ -21481,7 +21481,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G728" t="n">
-        <v>2.43029022216797</v>
+        <v>2.43029046058655</v>
       </c>
       <c r="H728" t="n">
         <v>7749</v>
@@ -21597,7 +21597,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G732" t="n">
-        <v>2.41061210632324</v>
+        <v>2.41061186790466</v>
       </c>
       <c r="H732" t="n">
         <v>8506</v>
@@ -21771,7 +21771,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G738" t="n">
-        <v>2.35157656669617</v>
+        <v>2.35157680511475</v>
       </c>
       <c r="H738" t="n">
         <v>9988</v>
@@ -21887,7 +21887,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G742" t="n">
-        <v>2.49916505813599</v>
+        <v>2.49916481971741</v>
       </c>
       <c r="H742" t="n">
         <v>34943</v>
@@ -21945,7 +21945,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G744" t="n">
-        <v>2.48932576179504</v>
+        <v>2.48932552337646</v>
       </c>
       <c r="H744" t="n">
         <v>39865</v>
@@ -22003,7 +22003,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G746" t="n">
-        <v>2.48932576179504</v>
+        <v>2.48932552337646</v>
       </c>
       <c r="H746" t="n">
         <v>18877</v>
@@ -22032,7 +22032,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G747" t="n">
-        <v>2.51884341239929</v>
+        <v>2.51884317398071</v>
       </c>
       <c r="H747" t="n">
         <v>44586</v>
@@ -22061,7 +22061,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G748" t="n">
-        <v>2.52868270874023</v>
+        <v>2.52868247032166</v>
       </c>
       <c r="H748" t="n">
         <v>45070</v>
@@ -22206,7 +22206,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G753" t="n">
-        <v>2.63691449165344</v>
+        <v>2.63691425323486</v>
       </c>
       <c r="H753" t="n">
         <v>58392</v>
@@ -22264,7 +22264,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G755" t="n">
-        <v>2.77466320991516</v>
+        <v>2.77466344833374</v>
       </c>
       <c r="H755" t="n">
         <v>152514</v>
@@ -22322,7 +22322,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G757" t="n">
-        <v>2.71562814712524</v>
+        <v>2.71562790870667</v>
       </c>
       <c r="H757" t="n">
         <v>170397</v>
@@ -22380,7 +22380,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G759" t="n">
-        <v>2.77466320991516</v>
+        <v>2.77466344833374</v>
       </c>
       <c r="H759" t="n">
         <v>21143</v>
@@ -22409,7 +22409,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G760" t="n">
-        <v>2.77466320991516</v>
+        <v>2.77466344833374</v>
       </c>
       <c r="H760" t="n">
         <v>14482</v>
@@ -22438,7 +22438,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G761" t="n">
-        <v>2.77466320991516</v>
+        <v>2.77466344833374</v>
       </c>
       <c r="H761" t="n">
         <v>13481</v>
@@ -22583,7 +22583,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G766" t="n">
-        <v>2.77466320991516</v>
+        <v>2.77466344833374</v>
       </c>
       <c r="H766" t="n">
         <v>11073</v>
@@ -22641,7 +22641,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G768" t="n">
-        <v>2.77466320991516</v>
+        <v>2.77466344833374</v>
       </c>
       <c r="H768" t="n">
         <v>16757</v>
@@ -22786,7 +22786,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G773" t="n">
-        <v>3.00096559524536</v>
+        <v>3.00096583366394</v>
       </c>
       <c r="H773" t="n">
         <v>78428</v>
@@ -22873,7 +22873,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G776" t="n">
-        <v>3.00096559524536</v>
+        <v>3.00096583366394</v>
       </c>
       <c r="H776" t="n">
         <v>13843</v>
@@ -22960,7 +22960,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G779" t="n">
-        <v>3.00096559524536</v>
+        <v>3.00096583366394</v>
       </c>
       <c r="H779" t="n">
         <v>12842</v>
@@ -23018,7 +23018,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G781" t="n">
-        <v>3.00096559524536</v>
+        <v>3.00096583366394</v>
       </c>
       <c r="H781" t="n">
         <v>25556</v>
@@ -23221,7 +23221,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G788" t="n">
-        <v>2.91241264343262</v>
+        <v>2.9124128818512</v>
       </c>
       <c r="H788" t="n">
         <v>28876</v>
@@ -23279,7 +23279,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G790" t="n">
-        <v>2.84353828430176</v>
+        <v>2.84353804588318</v>
       </c>
       <c r="H790" t="n">
         <v>12028</v>
@@ -23308,7 +23308,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G791" t="n">
-        <v>2.92225193977356</v>
+        <v>2.92225217819214</v>
       </c>
       <c r="H791" t="n">
         <v>36996</v>
@@ -23366,7 +23366,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G793" t="n">
-        <v>2.92225193977356</v>
+        <v>2.92225217819214</v>
       </c>
       <c r="H793" t="n">
         <v>20612</v>
@@ -23395,7 +23395,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G794" t="n">
-        <v>2.90257358551025</v>
+        <v>2.90257334709167</v>
       </c>
       <c r="H794" t="n">
         <v>5153</v>
@@ -23511,7 +23511,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G798" t="n">
-        <v>2.91241264343262</v>
+        <v>2.9124128818512</v>
       </c>
       <c r="H798" t="n">
         <v>29046</v>
@@ -23743,7 +23743,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G806" t="n">
-        <v>3.09935808181763</v>
+        <v>3.09935832023621</v>
       </c>
       <c r="H806" t="n">
         <v>21409</v>
@@ -23801,7 +23801,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G808" t="n">
-        <v>3.13871502876282</v>
+        <v>3.1387152671814</v>
       </c>
       <c r="H808" t="n">
         <v>29053</v>
@@ -24004,7 +24004,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G815" t="n">
-        <v>3.16823291778564</v>
+        <v>3.16823267936707</v>
       </c>
       <c r="H815" t="n">
         <v>40945</v>
@@ -24207,7 +24207,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G822" t="n">
-        <v>3.32566046714783</v>
+        <v>3.32566070556641</v>
       </c>
       <c r="H822" t="n">
         <v>8250</v>
@@ -24352,7 +24352,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G827" t="n">
-        <v>3.41421365737915</v>
+        <v>3.41421341896057</v>
       </c>
       <c r="H827" t="n">
         <v>49728</v>
@@ -24381,7 +24381,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G828" t="n">
-        <v>3.42405295372009</v>
+        <v>3.42405271530151</v>
       </c>
       <c r="H828" t="n">
         <v>21052</v>
@@ -24410,7 +24410,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G829" t="n">
-        <v>3.48308801651001</v>
+        <v>3.48308825492859</v>
       </c>
       <c r="H829" t="n">
         <v>56595</v>
@@ -24468,7 +24468,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G831" t="n">
-        <v>3.57164120674133</v>
+        <v>3.57164144515991</v>
       </c>
       <c r="H831" t="n">
         <v>31184</v>
@@ -24555,7 +24555,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G834" t="n">
-        <v>4.12263870239258</v>
+        <v>4.12263822555542</v>
       </c>
       <c r="H834" t="n">
         <v>162852</v>
@@ -24584,7 +24584,7 @@
         <v>4.25</v>
       </c>
       <c r="G835" t="n">
-        <v>4.18167352676392</v>
+        <v>4.18167400360107</v>
       </c>
       <c r="H835" t="n">
         <v>105792</v>
@@ -24700,7 +24700,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G839" t="n">
-        <v>4.22103023529053</v>
+        <v>4.22103071212769</v>
       </c>
       <c r="H839" t="n">
         <v>31763</v>
@@ -24758,7 +24758,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G841" t="n">
-        <v>4.2899055480957</v>
+        <v>4.28990507125854</v>
       </c>
       <c r="H841" t="n">
         <v>33142</v>
@@ -24816,7 +24816,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G843" t="n">
-        <v>4.39813613891602</v>
+        <v>4.39813661575317</v>
       </c>
       <c r="H843" t="n">
         <v>122860</v>
@@ -24990,7 +24990,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G849" t="n">
-        <v>5.0770435333252</v>
+        <v>5.07704401016235</v>
       </c>
       <c r="H849" t="n">
         <v>125520</v>
@@ -25019,7 +25019,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G850" t="n">
-        <v>4.99833011627197</v>
+        <v>4.99832963943481</v>
       </c>
       <c r="H850" t="n">
         <v>94101</v>
@@ -25077,7 +25077,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G852" t="n">
-        <v>5.03768682479858</v>
+        <v>5.03768634796143</v>
       </c>
       <c r="H852" t="n">
         <v>39665</v>
@@ -25222,7 +25222,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G857" t="n">
-        <v>5.03768682479858</v>
+        <v>5.03768634796143</v>
       </c>
       <c r="H857" t="n">
         <v>29318</v>
@@ -25280,7 +25280,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G859" t="n">
-        <v>4.86058044433594</v>
+        <v>4.8605809211731</v>
       </c>
       <c r="H859" t="n">
         <v>18569</v>
@@ -25309,7 +25309,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G860" t="n">
-        <v>4.83106327056885</v>
+        <v>4.83106279373169</v>
       </c>
       <c r="H860" t="n">
         <v>56243</v>
@@ -25338,7 +25338,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G861" t="n">
-        <v>4.89009809494019</v>
+        <v>4.89009857177734</v>
       </c>
       <c r="H861" t="n">
         <v>26996</v>
@@ -25425,7 +25425,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G864" t="n">
-        <v>4.89009809494019</v>
+        <v>4.89009857177734</v>
       </c>
       <c r="H864" t="n">
         <v>17018</v>
@@ -25512,7 +25512,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G867" t="n">
-        <v>5.29350662231445</v>
+        <v>5.29350709915161</v>
       </c>
       <c r="H867" t="n">
         <v>54581</v>
@@ -25570,7 +25570,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G869" t="n">
-        <v>5.7067551612854</v>
+        <v>5.70675468444824</v>
       </c>
       <c r="H869" t="n">
         <v>193218</v>
@@ -25599,7 +25599,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G870" t="n">
-        <v>5.80514717102051</v>
+        <v>5.80514669418335</v>
       </c>
       <c r="H870" t="n">
         <v>93551</v>
@@ -25628,7 +25628,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G871" t="n">
-        <v>5.68707656860352</v>
+        <v>5.68707609176636</v>
       </c>
       <c r="H871" t="n">
         <v>93418</v>
@@ -25686,7 +25686,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G873" t="n">
-        <v>5.43125629425049</v>
+        <v>5.43125581741333</v>
       </c>
       <c r="H873" t="n">
         <v>19758</v>
@@ -25773,7 +25773,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G876" t="n">
-        <v>5.27382898330688</v>
+        <v>5.27382850646973</v>
       </c>
       <c r="H876" t="n">
         <v>74967</v>
@@ -25802,7 +25802,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G877" t="n">
-        <v>5.29350662231445</v>
+        <v>5.29350709915161</v>
       </c>
       <c r="H877" t="n">
         <v>29227</v>
@@ -25860,7 +25860,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G879" t="n">
-        <v>5.05736541748047</v>
+        <v>5.05736494064331</v>
       </c>
       <c r="H879" t="n">
         <v>31367</v>
@@ -25918,7 +25918,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G881" t="n">
-        <v>5.03768682479858</v>
+        <v>5.03768634796143</v>
       </c>
       <c r="H881" t="n">
         <v>10417</v>
@@ -25976,7 +25976,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G883" t="n">
-        <v>5.03768682479858</v>
+        <v>5.03768634796143</v>
       </c>
       <c r="H883" t="n">
         <v>19220</v>
@@ -26034,7 +26034,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G885" t="n">
-        <v>5.0770435333252</v>
+        <v>5.07704401016235</v>
       </c>
       <c r="H885" t="n">
         <v>8947</v>
@@ -26208,7 +26208,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G891" t="n">
-        <v>5.27382898330688</v>
+        <v>5.27382850646973</v>
       </c>
       <c r="H891" t="n">
         <v>7249</v>
@@ -26237,7 +26237,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G892" t="n">
-        <v>5.11640024185181</v>
+        <v>5.11640071868896</v>
       </c>
       <c r="H892" t="n">
         <v>12636</v>
@@ -26266,7 +26266,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G893" t="n">
-        <v>5.05736541748047</v>
+        <v>5.05736494064331</v>
       </c>
       <c r="H893" t="n">
         <v>9316</v>
@@ -26295,7 +26295,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G894" t="n">
-        <v>5.03768682479858</v>
+        <v>5.03768634796143</v>
       </c>
       <c r="H894" t="n">
         <v>6814</v>
@@ -26324,7 +26324,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G895" t="n">
-        <v>5.03768682479858</v>
+        <v>5.03768634796143</v>
       </c>
       <c r="H895" t="n">
         <v>7477</v>
@@ -26382,7 +26382,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G897" t="n">
-        <v>5.11640024185181</v>
+        <v>5.11640071868896</v>
       </c>
       <c r="H897" t="n">
         <v>6128</v>
@@ -26411,7 +26411,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G898" t="n">
-        <v>4.99833011627197</v>
+        <v>4.99832963943481</v>
       </c>
       <c r="H898" t="n">
         <v>29460</v>
@@ -26440,7 +26440,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G899" t="n">
-        <v>4.83106327056885</v>
+        <v>4.83106279373169</v>
       </c>
       <c r="H899" t="n">
         <v>72320</v>
@@ -26556,7 +26556,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G903" t="n">
-        <v>4.2899055480957</v>
+        <v>4.28990507125854</v>
       </c>
       <c r="H903" t="n">
         <v>28901</v>
@@ -26585,7 +26585,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G904" t="n">
-        <v>4.56540393829346</v>
+        <v>4.5654034614563</v>
       </c>
       <c r="H904" t="n">
         <v>47385</v>
@@ -26643,7 +26643,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G906" t="n">
-        <v>4.83106327056885</v>
+        <v>4.83106279373169</v>
       </c>
       <c r="H906" t="n">
         <v>107459</v>
@@ -26672,7 +26672,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G907" t="n">
-        <v>4.89009809494019</v>
+        <v>4.89009857177734</v>
       </c>
       <c r="H907" t="n">
         <v>18622</v>
@@ -26730,7 +26730,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G909" t="n">
-        <v>4.84090185165405</v>
+        <v>4.84090232849121</v>
       </c>
       <c r="H909" t="n">
         <v>11135</v>
@@ -26759,7 +26759,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G910" t="n">
-        <v>4.83106327056885</v>
+        <v>4.83106279373169</v>
       </c>
       <c r="H910" t="n">
         <v>9284</v>
@@ -26817,7 +26817,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G912" t="n">
-        <v>4.89009809494019</v>
+        <v>4.89009857177734</v>
       </c>
       <c r="H912" t="n">
         <v>3683</v>
@@ -26933,7 +26933,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G916" t="n">
-        <v>4.82122421264648</v>
+        <v>4.82122373580933</v>
       </c>
       <c r="H916" t="n">
         <v>15220</v>
@@ -26991,7 +26991,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G918" t="n">
-        <v>5.03768682479858</v>
+        <v>5.03768634796143</v>
       </c>
       <c r="H918" t="n">
         <v>45309</v>
@@ -27020,7 +27020,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G919" t="n">
-        <v>5.0770435333252</v>
+        <v>5.07704401016235</v>
       </c>
       <c r="H919" t="n">
         <v>22506</v>
@@ -27107,7 +27107,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G922" t="n">
-        <v>5.11640024185181</v>
+        <v>5.11640071868896</v>
       </c>
       <c r="H922" t="n">
         <v>20658</v>
@@ -27223,7 +27223,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G926" t="n">
-        <v>5.254150390625</v>
+        <v>5.25414991378784</v>
       </c>
       <c r="H926" t="n">
         <v>16523</v>
@@ -27281,7 +27281,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G928" t="n">
-        <v>5.27382898330688</v>
+        <v>5.27382850646973</v>
       </c>
       <c r="H928" t="n">
         <v>14860</v>
@@ -27310,7 +27310,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G929" t="n">
-        <v>5.29350662231445</v>
+        <v>5.29350709915161</v>
       </c>
       <c r="H929" t="n">
         <v>8491</v>
@@ -27339,7 +27339,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G930" t="n">
-        <v>5.29350662231445</v>
+        <v>5.29350709915161</v>
       </c>
       <c r="H930" t="n">
         <v>4930</v>
@@ -27542,7 +27542,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G937" t="n">
-        <v>5.11640024185181</v>
+        <v>5.11640071868896</v>
       </c>
       <c r="H937" t="n">
         <v>12717</v>
@@ -27600,7 +27600,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G939" t="n">
-        <v>5.11640024185181</v>
+        <v>5.11640071868896</v>
       </c>
       <c r="H939" t="n">
         <v>9615</v>
@@ -27658,7 +27658,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G941" t="n">
-        <v>5.0770435333252</v>
+        <v>5.07704401016235</v>
       </c>
       <c r="H941" t="n">
         <v>9588</v>
@@ -27745,7 +27745,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G944" t="n">
-        <v>5.13607883453369</v>
+        <v>5.13607931137085</v>
       </c>
       <c r="H944" t="n">
         <v>6542</v>
@@ -27890,7 +27890,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G949" t="n">
-        <v>5.254150390625</v>
+        <v>5.25414991378784</v>
       </c>
       <c r="H949" t="n">
         <v>10195</v>
@@ -27919,7 +27919,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G950" t="n">
-        <v>5.29350662231445</v>
+        <v>5.29350709915161</v>
       </c>
       <c r="H950" t="n">
         <v>11103</v>
@@ -28151,7 +28151,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G958" t="n">
-        <v>5.68707656860352</v>
+        <v>5.68707609176636</v>
       </c>
       <c r="H958" t="n">
         <v>24892</v>
@@ -28180,7 +28180,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G959" t="n">
-        <v>5.68707656860352</v>
+        <v>5.68707609176636</v>
       </c>
       <c r="H959" t="n">
         <v>8965</v>
@@ -28267,7 +28267,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G962" t="n">
-        <v>5.80514717102051</v>
+        <v>5.80514669418335</v>
       </c>
       <c r="H962" t="n">
         <v>18409</v>
@@ -28354,7 +28354,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G965" t="n">
-        <v>5.80514717102051</v>
+        <v>5.80514669418335</v>
       </c>
       <c r="H965" t="n">
         <v>16785</v>
@@ -28470,7 +28470,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G969" t="n">
-        <v>6.13968086242676</v>
+        <v>6.1396803855896</v>
       </c>
       <c r="H969" t="n">
         <v>75849</v>
@@ -28499,7 +28499,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G970" t="n">
-        <v>6.19871616363525</v>
+        <v>6.19871664047241</v>
       </c>
       <c r="H970" t="n">
         <v>62814</v>
@@ -28528,7 +28528,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G971" t="n">
-        <v>6.33646583557129</v>
+        <v>6.33646535873413</v>
       </c>
       <c r="H971" t="n">
         <v>50014</v>
@@ -28557,7 +28557,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G972" t="n">
-        <v>6.27743005752563</v>
+        <v>6.27743053436279</v>
       </c>
       <c r="H972" t="n">
         <v>43290</v>
@@ -28615,7 +28615,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G974" t="n">
-        <v>6.13968086242676</v>
+        <v>6.1396803855896</v>
       </c>
       <c r="H974" t="n">
         <v>10830</v>
@@ -28702,7 +28702,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G977" t="n">
-        <v>6.00193119049072</v>
+        <v>6.00193166732788</v>
       </c>
       <c r="H977" t="n">
         <v>35007</v>
@@ -43208,6 +43208,35 @@
         <v>11690</v>
       </c>
       <c r="I1477" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1478">
+      <c r="A1478" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1478" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C1478" t="n">
+        <v>7.71999979019165</v>
+      </c>
+      <c r="D1478" t="n">
+        <v>7.96000003814697</v>
+      </c>
+      <c r="E1478" t="n">
+        <v>7.46999979019165</v>
+      </c>
+      <c r="F1478" t="n">
+        <v>7.71000003814697</v>
+      </c>
+      <c r="G1478" t="n">
+        <v>7.71000003814697</v>
+      </c>
+      <c r="H1478" t="n">
+        <v>13064</v>
+      </c>
+      <c r="I1478" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/EVISO.MI.xlsx
+++ b/data/EVISO.MI.xlsx
@@ -456,7 +456,7 @@
         <v>2.25</v>
       </c>
       <c r="G3" t="n">
-        <v>2.20108580589294</v>
+        <v>2.20108556747437</v>
       </c>
       <c r="H3" t="n">
         <v>232547</v>
@@ -775,7 +775,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G14" t="n">
-        <v>1.93695545196533</v>
+        <v>1.93695533275604</v>
       </c>
       <c r="H14" t="n">
         <v>32193</v>
@@ -978,7 +978,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G21" t="n">
-        <v>1.98586845397949</v>
+        <v>1.9858683347702</v>
       </c>
       <c r="H21" t="n">
         <v>29362</v>
@@ -1326,7 +1326,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G33" t="n">
-        <v>2.13260746002197</v>
+        <v>2.13260769844055</v>
       </c>
       <c r="H33" t="n">
         <v>250444</v>
@@ -1384,7 +1384,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G35" t="n">
-        <v>2.33804249763489</v>
+        <v>2.33804225921631</v>
       </c>
       <c r="H35" t="n">
         <v>424591</v>
@@ -1413,7 +1413,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G36" t="n">
-        <v>2.25978112220764</v>
+        <v>2.25978136062622</v>
       </c>
       <c r="H36" t="n">
         <v>179668</v>
@@ -1471,7 +1471,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G38" t="n">
-        <v>2.28912901878357</v>
+        <v>2.28912925720215</v>
       </c>
       <c r="H38" t="n">
         <v>46638</v>
@@ -1500,7 +1500,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G39" t="n">
-        <v>2.26956391334534</v>
+        <v>2.26956415176392</v>
       </c>
       <c r="H39" t="n">
         <v>53117</v>
@@ -1674,7 +1674,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G45" t="n">
-        <v>2.25978112220764</v>
+        <v>2.25978136062622</v>
       </c>
       <c r="H45" t="n">
         <v>25346</v>
@@ -1703,7 +1703,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G46" t="n">
-        <v>2.28912901878357</v>
+        <v>2.28912925720215</v>
       </c>
       <c r="H46" t="n">
         <v>34385</v>
@@ -1761,7 +1761,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G48" t="n">
-        <v>2.28912901878357</v>
+        <v>2.28912925720215</v>
       </c>
       <c r="H48" t="n">
         <v>32533</v>
@@ -1790,7 +1790,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G49" t="n">
-        <v>2.26956391334534</v>
+        <v>2.26956415176392</v>
       </c>
       <c r="H49" t="n">
         <v>44339</v>
@@ -1819,7 +1819,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G50" t="n">
-        <v>2.28912901878357</v>
+        <v>2.28912925720215</v>
       </c>
       <c r="H50" t="n">
         <v>198858</v>
@@ -1848,7 +1848,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G51" t="n">
-        <v>2.26956391334534</v>
+        <v>2.26956415176392</v>
       </c>
       <c r="H51" t="n">
         <v>28573</v>
@@ -1877,7 +1877,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G52" t="n">
-        <v>2.25978112220764</v>
+        <v>2.25978136062622</v>
       </c>
       <c r="H52" t="n">
         <v>40111</v>
@@ -2022,7 +2022,7 @@
         <v>2.25</v>
       </c>
       <c r="G57" t="n">
-        <v>2.20108580589294</v>
+        <v>2.20108556747437</v>
       </c>
       <c r="H57" t="n">
         <v>56053</v>
@@ -2138,7 +2138,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G61" t="n">
-        <v>2.23043370246887</v>
+        <v>2.23043346405029</v>
       </c>
       <c r="H61" t="n">
         <v>30389</v>
@@ -2167,7 +2167,7 @@
         <v>2.25</v>
       </c>
       <c r="G62" t="n">
-        <v>2.20108580589294</v>
+        <v>2.20108556747437</v>
       </c>
       <c r="H62" t="n">
         <v>17852</v>
@@ -2196,7 +2196,7 @@
         <v>2.25</v>
       </c>
       <c r="G63" t="n">
-        <v>2.20108580589294</v>
+        <v>2.20108556747437</v>
       </c>
       <c r="H63" t="n">
         <v>4750</v>
@@ -2283,7 +2283,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G66" t="n">
-        <v>2.19130325317383</v>
+        <v>2.19130301475525</v>
       </c>
       <c r="H66" t="n">
         <v>23995</v>
@@ -2312,7 +2312,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G67" t="n">
-        <v>2.19130325317383</v>
+        <v>2.19130301475525</v>
       </c>
       <c r="H67" t="n">
         <v>651</v>
@@ -2341,7 +2341,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G68" t="n">
-        <v>2.23043370246887</v>
+        <v>2.23043346405029</v>
       </c>
       <c r="H68" t="n">
         <v>59507</v>
@@ -2370,7 +2370,7 @@
         <v>2.25</v>
       </c>
       <c r="G69" t="n">
-        <v>2.20108580589294</v>
+        <v>2.20108556747437</v>
       </c>
       <c r="H69" t="n">
         <v>21435</v>
@@ -2399,7 +2399,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G70" t="n">
-        <v>2.19130325317383</v>
+        <v>2.19130301475525</v>
       </c>
       <c r="H70" t="n">
         <v>19650</v>
@@ -2457,7 +2457,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G72" t="n">
-        <v>2.19130325317383</v>
+        <v>2.19130301475525</v>
       </c>
       <c r="H72" t="n">
         <v>13730</v>
@@ -2486,7 +2486,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G73" t="n">
-        <v>2.19130325317383</v>
+        <v>2.19130301475525</v>
       </c>
       <c r="H73" t="n">
         <v>10901</v>
@@ -2631,7 +2631,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G78" t="n">
-        <v>2.13260746002197</v>
+        <v>2.13260769844055</v>
       </c>
       <c r="H78" t="n">
         <v>6844</v>
@@ -2660,7 +2660,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G79" t="n">
-        <v>2.23043370246887</v>
+        <v>2.23043346405029</v>
       </c>
       <c r="H79" t="n">
         <v>133272</v>
@@ -2805,7 +2805,7 @@
         <v>2.25</v>
       </c>
       <c r="G84" t="n">
-        <v>2.20108580589294</v>
+        <v>2.20108556747437</v>
       </c>
       <c r="H84" t="n">
         <v>5934</v>
@@ -2863,7 +2863,7 @@
         <v>2.25</v>
       </c>
       <c r="G86" t="n">
-        <v>2.20108580589294</v>
+        <v>2.20108556747437</v>
       </c>
       <c r="H86" t="n">
         <v>22122</v>
@@ -2979,7 +2979,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G90" t="n">
-        <v>2.19130325317383</v>
+        <v>2.19130301475525</v>
       </c>
       <c r="H90" t="n">
         <v>19878</v>
@@ -3008,7 +3008,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G91" t="n">
-        <v>2.33804249763489</v>
+        <v>2.33804225921631</v>
       </c>
       <c r="H91" t="n">
         <v>287103</v>
@@ -3124,7 +3124,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G95" t="n">
-        <v>2.26956391334534</v>
+        <v>2.26956415176392</v>
       </c>
       <c r="H95" t="n">
         <v>10213</v>
@@ -3269,7 +3269,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G100" t="n">
-        <v>2.33804249763489</v>
+        <v>2.33804225921631</v>
       </c>
       <c r="H100" t="n">
         <v>138592</v>
@@ -3472,7 +3472,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G107" t="n">
-        <v>2.69999837875366</v>
+        <v>2.69999861717224</v>
       </c>
       <c r="H107" t="n">
         <v>144356</v>
@@ -3559,7 +3559,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G110" t="n">
-        <v>2.61195492744446</v>
+        <v>2.61195516586304</v>
       </c>
       <c r="H110" t="n">
         <v>28158</v>
@@ -3617,7 +3617,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G112" t="n">
-        <v>2.54347681999207</v>
+        <v>2.54347658157349</v>
       </c>
       <c r="H112" t="n">
         <v>34901</v>
@@ -3646,7 +3646,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G113" t="n">
-        <v>2.54347681999207</v>
+        <v>2.54347658157349</v>
       </c>
       <c r="H113" t="n">
         <v>36680</v>
@@ -3704,7 +3704,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G115" t="n">
-        <v>2.50434613227844</v>
+        <v>2.50434637069702</v>
       </c>
       <c r="H115" t="n">
         <v>101303</v>
@@ -3733,7 +3733,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G116" t="n">
-        <v>2.51412892341614</v>
+        <v>2.51412916183472</v>
       </c>
       <c r="H116" t="n">
         <v>8588</v>
@@ -3762,7 +3762,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G117" t="n">
-        <v>2.54347681999207</v>
+        <v>2.54347658157349</v>
       </c>
       <c r="H117" t="n">
         <v>39029</v>
@@ -3820,7 +3820,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G119" t="n">
-        <v>2.51412892341614</v>
+        <v>2.51412916183472</v>
       </c>
       <c r="H119" t="n">
         <v>5450</v>
@@ -3849,7 +3849,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G120" t="n">
-        <v>2.47499847412109</v>
+        <v>2.47499871253967</v>
       </c>
       <c r="H120" t="n">
         <v>9520</v>
@@ -3907,7 +3907,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G122" t="n">
-        <v>2.39673781394958</v>
+        <v>2.39673805236816</v>
       </c>
       <c r="H122" t="n">
         <v>21012</v>
@@ -3936,7 +3936,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G123" t="n">
-        <v>2.4065203666687</v>
+        <v>2.40652012825012</v>
       </c>
       <c r="H123" t="n">
         <v>14814</v>
@@ -3994,7 +3994,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G125" t="n">
-        <v>2.4163031578064</v>
+        <v>2.41630291938782</v>
       </c>
       <c r="H125" t="n">
         <v>35694</v>
@@ -4023,7 +4023,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G126" t="n">
-        <v>2.4065203666687</v>
+        <v>2.40652012825012</v>
       </c>
       <c r="H126" t="n">
         <v>17192</v>
@@ -4081,7 +4081,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G128" t="n">
-        <v>2.48478102684021</v>
+        <v>2.48478126525879</v>
       </c>
       <c r="H128" t="n">
         <v>22629</v>
@@ -4139,7 +4139,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G130" t="n">
-        <v>2.52391171455383</v>
+        <v>2.52391147613525</v>
       </c>
       <c r="H130" t="n">
         <v>6239</v>
@@ -4168,7 +4168,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G131" t="n">
-        <v>2.50434613227844</v>
+        <v>2.50434637069702</v>
       </c>
       <c r="H131" t="n">
         <v>17915</v>
@@ -4255,7 +4255,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G134" t="n">
-        <v>2.51412892341614</v>
+        <v>2.51412916183472</v>
       </c>
       <c r="H134" t="n">
         <v>8450</v>
@@ -4342,7 +4342,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G137" t="n">
-        <v>2.47499847412109</v>
+        <v>2.47499871253967</v>
       </c>
       <c r="H137" t="n">
         <v>1750</v>
@@ -4371,7 +4371,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G138" t="n">
-        <v>2.39673781394958</v>
+        <v>2.39673805236816</v>
       </c>
       <c r="H138" t="n">
         <v>15772</v>
@@ -4458,7 +4458,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G141" t="n">
-        <v>2.4163031578064</v>
+        <v>2.41630291938782</v>
       </c>
       <c r="H141" t="n">
         <v>4028</v>
@@ -4487,7 +4487,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G142" t="n">
-        <v>2.4065203666687</v>
+        <v>2.40652012825012</v>
       </c>
       <c r="H142" t="n">
         <v>11210</v>
@@ -4661,7 +4661,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G148" t="n">
-        <v>2.4065203666687</v>
+        <v>2.40652012825012</v>
       </c>
       <c r="H148" t="n">
         <v>42899</v>
@@ -4748,7 +4748,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G151" t="n">
-        <v>2.39673781394958</v>
+        <v>2.39673805236816</v>
       </c>
       <c r="H151" t="n">
         <v>3252</v>
@@ -4835,7 +4835,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G154" t="n">
-        <v>2.48478102684021</v>
+        <v>2.48478126525879</v>
       </c>
       <c r="H154" t="n">
         <v>33850</v>
@@ -4864,7 +4864,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G155" t="n">
-        <v>2.50434613227844</v>
+        <v>2.50434637069702</v>
       </c>
       <c r="H155" t="n">
         <v>11685</v>
@@ -4980,7 +4980,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G159" t="n">
-        <v>2.4163031578064</v>
+        <v>2.41630291938782</v>
       </c>
       <c r="H159" t="n">
         <v>12350</v>
@@ -5009,7 +5009,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G160" t="n">
-        <v>2.39673781394958</v>
+        <v>2.39673805236816</v>
       </c>
       <c r="H160" t="n">
         <v>10392</v>
@@ -5096,7 +5096,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G163" t="n">
-        <v>2.61195492744446</v>
+        <v>2.61195516586304</v>
       </c>
       <c r="H163" t="n">
         <v>108022</v>
@@ -5241,7 +5241,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G168" t="n">
-        <v>2.90543341636658</v>
+        <v>2.905433177948</v>
       </c>
       <c r="H168" t="n">
         <v>40031</v>
@@ -5328,7 +5328,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G171" t="n">
-        <v>2.83695483207703</v>
+        <v>2.83695507049561</v>
       </c>
       <c r="H171" t="n">
         <v>69207</v>
@@ -5879,7 +5879,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G190" t="n">
-        <v>2.51412892341614</v>
+        <v>2.51412916183472</v>
       </c>
       <c r="H190" t="n">
         <v>117768</v>
@@ -5966,7 +5966,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G193" t="n">
-        <v>2.69999837875366</v>
+        <v>2.69999861717224</v>
       </c>
       <c r="H193" t="n">
         <v>8525</v>
@@ -6024,7 +6024,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G195" t="n">
-        <v>2.63152027130127</v>
+        <v>2.63152003288269</v>
       </c>
       <c r="H195" t="n">
         <v>5445</v>
@@ -6053,7 +6053,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G196" t="n">
-        <v>2.50434613227844</v>
+        <v>2.50434637069702</v>
       </c>
       <c r="H196" t="n">
         <v>18379</v>
@@ -6111,7 +6111,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G198" t="n">
-        <v>2.61195492744446</v>
+        <v>2.61195516586304</v>
       </c>
       <c r="H198" t="n">
         <v>20110</v>
@@ -6198,7 +6198,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G201" t="n">
-        <v>2.54347681999207</v>
+        <v>2.54347658157349</v>
       </c>
       <c r="H201" t="n">
         <v>32309</v>
@@ -6256,7 +6256,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G203" t="n">
-        <v>2.61195492744446</v>
+        <v>2.61195516586304</v>
       </c>
       <c r="H203" t="n">
         <v>23415</v>
@@ -6372,7 +6372,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G207" t="n">
-        <v>2.69999837875366</v>
+        <v>2.69999861717224</v>
       </c>
       <c r="H207" t="n">
         <v>49435</v>
@@ -6749,7 +6749,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G220" t="n">
-        <v>2.63691425323486</v>
+        <v>2.63691449165344</v>
       </c>
       <c r="H220" t="n">
         <v>54300</v>
@@ -6778,7 +6778,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G221" t="n">
-        <v>2.64675354957581</v>
+        <v>2.64675331115723</v>
       </c>
       <c r="H221" t="n">
         <v>42202</v>
@@ -6807,7 +6807,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G222" t="n">
-        <v>2.62707495689392</v>
+        <v>2.6270751953125</v>
       </c>
       <c r="H222" t="n">
         <v>18794</v>
@@ -6952,7 +6952,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G227" t="n">
-        <v>2.51884317398071</v>
+        <v>2.51884341239929</v>
       </c>
       <c r="H227" t="n">
         <v>30812</v>
@@ -6981,7 +6981,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G228" t="n">
-        <v>2.49916481971741</v>
+        <v>2.49916505813599</v>
       </c>
       <c r="H228" t="n">
         <v>48757</v>
@@ -7010,7 +7010,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G229" t="n">
-        <v>2.52868247032166</v>
+        <v>2.52868270874023</v>
       </c>
       <c r="H229" t="n">
         <v>15710</v>
@@ -7097,7 +7097,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G232" t="n">
-        <v>2.43029046058655</v>
+        <v>2.43029022216797</v>
       </c>
       <c r="H232" t="n">
         <v>31988</v>
@@ -7155,7 +7155,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G234" t="n">
-        <v>2.51884317398071</v>
+        <v>2.51884341239929</v>
       </c>
       <c r="H234" t="n">
         <v>39902</v>
@@ -7271,7 +7271,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G238" t="n">
-        <v>2.55820035934448</v>
+        <v>2.5582001209259</v>
       </c>
       <c r="H238" t="n">
         <v>26987</v>
@@ -7329,7 +7329,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G240" t="n">
-        <v>2.62707495689392</v>
+        <v>2.6270751953125</v>
       </c>
       <c r="H240" t="n">
         <v>3780</v>
@@ -7445,7 +7445,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G244" t="n">
-        <v>2.49916481971741</v>
+        <v>2.49916505813599</v>
       </c>
       <c r="H244" t="n">
         <v>24170</v>
@@ -7503,7 +7503,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G246" t="n">
-        <v>2.48932552337646</v>
+        <v>2.48932576179504</v>
       </c>
       <c r="H246" t="n">
         <v>1994</v>
@@ -7590,7 +7590,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G249" t="n">
-        <v>2.43029046058655</v>
+        <v>2.43029022216797</v>
       </c>
       <c r="H249" t="n">
         <v>5858</v>
@@ -7677,7 +7677,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G252" t="n">
-        <v>2.48932552337646</v>
+        <v>2.48932576179504</v>
       </c>
       <c r="H252" t="n">
         <v>810</v>
@@ -7793,7 +7793,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G256" t="n">
-        <v>2.42045116424561</v>
+        <v>2.42045092582703</v>
       </c>
       <c r="H256" t="n">
         <v>9824</v>
@@ -7822,7 +7822,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G257" t="n">
-        <v>2.42045116424561</v>
+        <v>2.42045092582703</v>
       </c>
       <c r="H257" t="n">
         <v>12307</v>
@@ -7880,7 +7880,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G259" t="n">
-        <v>2.48932552337646</v>
+        <v>2.48932576179504</v>
       </c>
       <c r="H259" t="n">
         <v>7500</v>
@@ -7909,7 +7909,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G260" t="n">
-        <v>2.48932552337646</v>
+        <v>2.48932576179504</v>
       </c>
       <c r="H260" t="n">
         <v>14171</v>
@@ -7967,7 +7967,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G262" t="n">
-        <v>2.42045116424561</v>
+        <v>2.42045092582703</v>
       </c>
       <c r="H262" t="n">
         <v>6545</v>
@@ -8025,7 +8025,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G264" t="n">
-        <v>2.43029046058655</v>
+        <v>2.43029022216797</v>
       </c>
       <c r="H264" t="n">
         <v>7020</v>
@@ -8141,7 +8141,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G268" t="n">
-        <v>2.43029046058655</v>
+        <v>2.43029022216797</v>
       </c>
       <c r="H268" t="n">
         <v>6909</v>
@@ -8170,7 +8170,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G269" t="n">
-        <v>2.42045116424561</v>
+        <v>2.42045092582703</v>
       </c>
       <c r="H269" t="n">
         <v>398</v>
@@ -8257,7 +8257,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G272" t="n">
-        <v>2.27286243438721</v>
+        <v>2.27286267280579</v>
       </c>
       <c r="H272" t="n">
         <v>19540</v>
@@ -8315,7 +8315,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G274" t="n">
-        <v>2.41061186790466</v>
+        <v>2.41061210632324</v>
       </c>
       <c r="H274" t="n">
         <v>2455</v>
@@ -8373,7 +8373,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G276" t="n">
-        <v>2.42045116424561</v>
+        <v>2.42045092582703</v>
       </c>
       <c r="H276" t="n">
         <v>4035</v>
@@ -8489,7 +8489,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G280" t="n">
-        <v>2.41061186790466</v>
+        <v>2.41061210632324</v>
       </c>
       <c r="H280" t="n">
         <v>2500</v>
@@ -8518,7 +8518,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G281" t="n">
-        <v>2.41061186790466</v>
+        <v>2.41061210632324</v>
       </c>
       <c r="H281" t="n">
         <v>3607</v>
@@ -8547,7 +8547,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G282" t="n">
-        <v>2.41061186790466</v>
+        <v>2.41061210632324</v>
       </c>
       <c r="H282" t="n">
         <v>3021</v>
@@ -8576,7 +8576,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G283" t="n">
-        <v>2.35157680511475</v>
+        <v>2.35157656669617</v>
       </c>
       <c r="H283" t="n">
         <v>3780</v>
@@ -8605,7 +8605,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G284" t="n">
-        <v>2.42045116424561</v>
+        <v>2.42045092582703</v>
       </c>
       <c r="H284" t="n">
         <v>7881</v>
@@ -8634,7 +8634,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G285" t="n">
-        <v>2.52868247032166</v>
+        <v>2.52868270874023</v>
       </c>
       <c r="H285" t="n">
         <v>42819</v>
@@ -8924,7 +8924,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G295" t="n">
-        <v>2.30238008499146</v>
+        <v>2.30238032341003</v>
       </c>
       <c r="H295" t="n">
         <v>44626</v>
@@ -9040,7 +9040,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G299" t="n">
-        <v>2.27286243438721</v>
+        <v>2.27286267280579</v>
       </c>
       <c r="H299" t="n">
         <v>50689</v>
@@ -9069,7 +9069,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G300" t="n">
-        <v>2.20398807525635</v>
+        <v>2.20398783683777</v>
       </c>
       <c r="H300" t="n">
         <v>34470</v>
@@ -9185,7 +9185,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G304" t="n">
-        <v>2.27286243438721</v>
+        <v>2.27286267280579</v>
       </c>
       <c r="H304" t="n">
         <v>15470</v>
@@ -9243,7 +9243,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G306" t="n">
-        <v>2.30238008499146</v>
+        <v>2.30238032341003</v>
       </c>
       <c r="H306" t="n">
         <v>1100</v>
@@ -9417,7 +9417,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G312" t="n">
-        <v>2.35157680511475</v>
+        <v>2.35157656669617</v>
       </c>
       <c r="H312" t="n">
         <v>25055</v>
@@ -9446,7 +9446,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G313" t="n">
-        <v>2.41061186790466</v>
+        <v>2.41061210632324</v>
       </c>
       <c r="H313" t="n">
         <v>37964</v>
@@ -9678,7 +9678,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G321" t="n">
-        <v>2.27286243438721</v>
+        <v>2.27286267280579</v>
       </c>
       <c r="H321" t="n">
         <v>3425</v>
@@ -9707,7 +9707,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G322" t="n">
-        <v>2.28270173072815</v>
+        <v>2.28270196914673</v>
       </c>
       <c r="H322" t="n">
         <v>16706</v>
@@ -9823,7 +9823,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G326" t="n">
-        <v>2.35157680511475</v>
+        <v>2.35157656669617</v>
       </c>
       <c r="H326" t="n">
         <v>2807</v>
@@ -9910,7 +9910,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G329" t="n">
-        <v>2.28270173072815</v>
+        <v>2.28270196914673</v>
       </c>
       <c r="H329" t="n">
         <v>4326</v>
@@ -9939,7 +9939,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G330" t="n">
-        <v>2.30238008499146</v>
+        <v>2.30238032341003</v>
       </c>
       <c r="H330" t="n">
         <v>2424</v>
@@ -9997,7 +9997,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G332" t="n">
-        <v>2.30238008499146</v>
+        <v>2.30238032341003</v>
       </c>
       <c r="H332" t="n">
         <v>1205</v>
@@ -10055,7 +10055,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G334" t="n">
-        <v>2.20398807525635</v>
+        <v>2.20398783683777</v>
       </c>
       <c r="H334" t="n">
         <v>12548</v>
@@ -10142,7 +10142,7 @@
         <v>2.25</v>
       </c>
       <c r="G337" t="n">
-        <v>2.21382737159729</v>
+        <v>2.21382713317871</v>
       </c>
       <c r="H337" t="n">
         <v>4451</v>
@@ -10316,7 +10316,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G343" t="n">
-        <v>2.41061186790466</v>
+        <v>2.41061210632324</v>
       </c>
       <c r="H343" t="n">
         <v>157345</v>
@@ -10345,7 +10345,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G344" t="n">
-        <v>2.41061186790466</v>
+        <v>2.41061210632324</v>
       </c>
       <c r="H344" t="n">
         <v>177569</v>
@@ -10374,7 +10374,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G345" t="n">
-        <v>2.28270173072815</v>
+        <v>2.28270196914673</v>
       </c>
       <c r="H345" t="n">
         <v>36620</v>
@@ -10490,7 +10490,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G349" t="n">
-        <v>2.35157680511475</v>
+        <v>2.35157656669617</v>
       </c>
       <c r="H349" t="n">
         <v>12100</v>
@@ -10548,7 +10548,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G351" t="n">
-        <v>2.28270173072815</v>
+        <v>2.28270196914673</v>
       </c>
       <c r="H351" t="n">
         <v>6350</v>
@@ -10606,7 +10606,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G353" t="n">
-        <v>2.28270173072815</v>
+        <v>2.28270196914673</v>
       </c>
       <c r="H353" t="n">
         <v>6000</v>
@@ -10635,7 +10635,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G354" t="n">
-        <v>2.28270173072815</v>
+        <v>2.28270196914673</v>
       </c>
       <c r="H354" t="n">
         <v>4900</v>
@@ -10664,7 +10664,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G355" t="n">
-        <v>2.27286243438721</v>
+        <v>2.27286267280579</v>
       </c>
       <c r="H355" t="n">
         <v>5466</v>
@@ -10693,7 +10693,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G356" t="n">
-        <v>2.28270173072815</v>
+        <v>2.28270196914673</v>
       </c>
       <c r="H356" t="n">
         <v>4255</v>
@@ -10751,7 +10751,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G358" t="n">
-        <v>2.28270173072815</v>
+        <v>2.28270196914673</v>
       </c>
       <c r="H358" t="n">
         <v>9650</v>
@@ -10780,7 +10780,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G359" t="n">
-        <v>2.27286243438721</v>
+        <v>2.27286267280579</v>
       </c>
       <c r="H359" t="n">
         <v>10142</v>
@@ -10809,7 +10809,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G360" t="n">
-        <v>2.28270173072815</v>
+        <v>2.28270196914673</v>
       </c>
       <c r="H360" t="n">
         <v>6650</v>
@@ -10838,7 +10838,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G361" t="n">
-        <v>2.30238008499146</v>
+        <v>2.30238032341003</v>
       </c>
       <c r="H361" t="n">
         <v>1405</v>
@@ -10867,7 +10867,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G362" t="n">
-        <v>2.30238008499146</v>
+        <v>2.30238032341003</v>
       </c>
       <c r="H362" t="n">
         <v>136082</v>
@@ -10896,7 +10896,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G363" t="n">
-        <v>2.30238008499146</v>
+        <v>2.30238032341003</v>
       </c>
       <c r="H363" t="n">
         <v>0</v>
@@ -10954,7 +10954,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G365" t="n">
-        <v>2.41061186790466</v>
+        <v>2.41061210632324</v>
       </c>
       <c r="H365" t="n">
         <v>46145</v>
@@ -11070,7 +11070,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G369" t="n">
-        <v>2.53852200508118</v>
+        <v>2.5385217666626</v>
       </c>
       <c r="H369" t="n">
         <v>58285</v>
@@ -11157,7 +11157,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G372" t="n">
-        <v>2.48932552337646</v>
+        <v>2.48932576179504</v>
       </c>
       <c r="H372" t="n">
         <v>30239</v>
@@ -11360,7 +11360,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G379" t="n">
-        <v>2.35157680511475</v>
+        <v>2.35157656669617</v>
       </c>
       <c r="H379" t="n">
         <v>1201</v>
@@ -11534,7 +11534,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G385" t="n">
-        <v>2.43029046058655</v>
+        <v>2.43029022216797</v>
       </c>
       <c r="H385" t="n">
         <v>25280</v>
@@ -11592,7 +11592,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G387" t="n">
-        <v>2.43029046058655</v>
+        <v>2.43029022216797</v>
       </c>
       <c r="H387" t="n">
         <v>13258</v>
@@ -11766,7 +11766,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G393" t="n">
-        <v>2.35157680511475</v>
+        <v>2.35157656669617</v>
       </c>
       <c r="H393" t="n">
         <v>1601</v>
@@ -12172,7 +12172,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G407" t="n">
-        <v>2.42045116424561</v>
+        <v>2.42045092582703</v>
       </c>
       <c r="H407" t="n">
         <v>11611</v>
@@ -12288,7 +12288,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G411" t="n">
-        <v>2.48932552337646</v>
+        <v>2.48932576179504</v>
       </c>
       <c r="H411" t="n">
         <v>11281</v>
@@ -12317,7 +12317,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G412" t="n">
-        <v>2.48932552337646</v>
+        <v>2.48932576179504</v>
       </c>
       <c r="H412" t="n">
         <v>951</v>
@@ -12346,7 +12346,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G413" t="n">
-        <v>2.42045116424561</v>
+        <v>2.42045092582703</v>
       </c>
       <c r="H413" t="n">
         <v>180</v>
@@ -12578,7 +12578,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G421" t="n">
-        <v>2.49916481971741</v>
+        <v>2.49916505813599</v>
       </c>
       <c r="H421" t="n">
         <v>16752</v>
@@ -12665,7 +12665,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G424" t="n">
-        <v>2.49916481971741</v>
+        <v>2.49916505813599</v>
       </c>
       <c r="H424" t="n">
         <v>35639</v>
@@ -12752,7 +12752,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G427" t="n">
-        <v>2.55820035934448</v>
+        <v>2.5582001209259</v>
       </c>
       <c r="H427" t="n">
         <v>559114</v>
@@ -12781,7 +12781,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G428" t="n">
-        <v>2.52868247032166</v>
+        <v>2.52868270874023</v>
       </c>
       <c r="H428" t="n">
         <v>29512</v>
@@ -12897,7 +12897,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G432" t="n">
-        <v>2.51884317398071</v>
+        <v>2.51884341239929</v>
       </c>
       <c r="H432" t="n">
         <v>60938</v>
@@ -12955,7 +12955,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G434" t="n">
-        <v>2.55820035934448</v>
+        <v>2.5582001209259</v>
       </c>
       <c r="H434" t="n">
         <v>47155</v>
@@ -12984,7 +12984,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G435" t="n">
-        <v>2.52868247032166</v>
+        <v>2.52868270874023</v>
       </c>
       <c r="H435" t="n">
         <v>20543</v>
@@ -13042,7 +13042,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G437" t="n">
-        <v>2.52868247032166</v>
+        <v>2.52868270874023</v>
       </c>
       <c r="H437" t="n">
         <v>12222</v>
@@ -13071,7 +13071,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G438" t="n">
-        <v>2.51884317398071</v>
+        <v>2.51884341239929</v>
       </c>
       <c r="H438" t="n">
         <v>18341</v>
@@ -13100,7 +13100,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G439" t="n">
-        <v>2.52868247032166</v>
+        <v>2.52868270874023</v>
       </c>
       <c r="H439" t="n">
         <v>19433</v>
@@ -13129,7 +13129,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G440" t="n">
-        <v>2.43029046058655</v>
+        <v>2.43029022216797</v>
       </c>
       <c r="H440" t="n">
         <v>23395</v>
@@ -13216,7 +13216,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G443" t="n">
-        <v>2.41061186790466</v>
+        <v>2.41061210632324</v>
       </c>
       <c r="H443" t="n">
         <v>15137</v>
@@ -13274,7 +13274,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G445" t="n">
-        <v>2.49916481971741</v>
+        <v>2.49916505813599</v>
       </c>
       <c r="H445" t="n">
         <v>52693</v>
@@ -13332,7 +13332,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G447" t="n">
-        <v>2.28270173072815</v>
+        <v>2.28270196914673</v>
       </c>
       <c r="H447" t="n">
         <v>23165</v>
@@ -13361,7 +13361,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G448" t="n">
-        <v>2.28270173072815</v>
+        <v>2.28270196914673</v>
       </c>
       <c r="H448" t="n">
         <v>40210</v>
@@ -13477,7 +13477,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G452" t="n">
-        <v>2.43029046058655</v>
+        <v>2.43029022216797</v>
       </c>
       <c r="H452" t="n">
         <v>37050</v>
@@ -13622,7 +13622,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G457" t="n">
-        <v>2.49916481971741</v>
+        <v>2.49916505813599</v>
       </c>
       <c r="H457" t="n">
         <v>35738</v>
@@ -13651,7 +13651,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G458" t="n">
-        <v>2.51884317398071</v>
+        <v>2.51884341239929</v>
       </c>
       <c r="H458" t="n">
         <v>18389</v>
@@ -13680,7 +13680,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G459" t="n">
-        <v>2.51884317398071</v>
+        <v>2.51884341239929</v>
       </c>
       <c r="H459" t="n">
         <v>0</v>
@@ -13709,7 +13709,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G460" t="n">
-        <v>2.43029046058655</v>
+        <v>2.43029022216797</v>
       </c>
       <c r="H460" t="n">
         <v>29119</v>
@@ -13825,7 +13825,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G464" t="n">
-        <v>2.42045116424561</v>
+        <v>2.42045092582703</v>
       </c>
       <c r="H464" t="n">
         <v>2155</v>
@@ -13854,7 +13854,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G465" t="n">
-        <v>2.41061186790466</v>
+        <v>2.41061210632324</v>
       </c>
       <c r="H465" t="n">
         <v>3505</v>
@@ -13941,7 +13941,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G468" t="n">
-        <v>2.42045116424561</v>
+        <v>2.42045092582703</v>
       </c>
       <c r="H468" t="n">
         <v>5886</v>
@@ -13970,7 +13970,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G469" t="n">
-        <v>2.42045116424561</v>
+        <v>2.42045092582703</v>
       </c>
       <c r="H469" t="n">
         <v>0</v>
@@ -14028,7 +14028,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G471" t="n">
-        <v>2.43029046058655</v>
+        <v>2.43029022216797</v>
       </c>
       <c r="H471" t="n">
         <v>8504</v>
@@ -14144,7 +14144,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G475" t="n">
-        <v>2.42045116424561</v>
+        <v>2.42045092582703</v>
       </c>
       <c r="H475" t="n">
         <v>5971</v>
@@ -14260,7 +14260,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G479" t="n">
-        <v>2.43029046058655</v>
+        <v>2.43029022216797</v>
       </c>
       <c r="H479" t="n">
         <v>7842</v>
@@ -14318,7 +14318,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G481" t="n">
-        <v>2.42045116424561</v>
+        <v>2.42045092582703</v>
       </c>
       <c r="H481" t="n">
         <v>3675</v>
@@ -14376,7 +14376,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G483" t="n">
-        <v>2.42045116424561</v>
+        <v>2.42045092582703</v>
       </c>
       <c r="H483" t="n">
         <v>6429</v>
@@ -14492,7 +14492,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G487" t="n">
-        <v>2.41061186790466</v>
+        <v>2.41061210632324</v>
       </c>
       <c r="H487" t="n">
         <v>1829</v>
@@ -14521,7 +14521,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G488" t="n">
-        <v>2.41061186790466</v>
+        <v>2.41061210632324</v>
       </c>
       <c r="H488" t="n">
         <v>0</v>
@@ -14579,7 +14579,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G490" t="n">
-        <v>2.41061186790466</v>
+        <v>2.41061210632324</v>
       </c>
       <c r="H490" t="n">
         <v>18612</v>
@@ -14666,7 +14666,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G493" t="n">
-        <v>2.41061186790466</v>
+        <v>2.41061210632324</v>
       </c>
       <c r="H493" t="n">
         <v>1</v>
@@ -14695,7 +14695,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G494" t="n">
-        <v>2.41061186790466</v>
+        <v>2.41061210632324</v>
       </c>
       <c r="H494" t="n">
         <v>0</v>
@@ -14724,7 +14724,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G495" t="n">
-        <v>2.41061186790466</v>
+        <v>2.41061210632324</v>
       </c>
       <c r="H495" t="n">
         <v>20619</v>
@@ -14869,7 +14869,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G500" t="n">
-        <v>2.48932552337646</v>
+        <v>2.48932576179504</v>
       </c>
       <c r="H500" t="n">
         <v>22406</v>
@@ -14898,7 +14898,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G501" t="n">
-        <v>2.41061186790466</v>
+        <v>2.41061210632324</v>
       </c>
       <c r="H501" t="n">
         <v>232</v>
@@ -14985,7 +14985,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G504" t="n">
-        <v>2.42045116424561</v>
+        <v>2.42045092582703</v>
       </c>
       <c r="H504" t="n">
         <v>3174</v>
@@ -15014,7 +15014,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G505" t="n">
-        <v>2.42045116424561</v>
+        <v>2.42045092582703</v>
       </c>
       <c r="H505" t="n">
         <v>0</v>
@@ -15072,7 +15072,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G507" t="n">
-        <v>2.42045116424561</v>
+        <v>2.42045092582703</v>
       </c>
       <c r="H507" t="n">
         <v>4</v>
@@ -15130,7 +15130,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G509" t="n">
-        <v>2.43029046058655</v>
+        <v>2.43029022216797</v>
       </c>
       <c r="H509" t="n">
         <v>6606</v>
@@ -15159,7 +15159,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G510" t="n">
-        <v>2.43029046058655</v>
+        <v>2.43029022216797</v>
       </c>
       <c r="H510" t="n">
         <v>4444</v>
@@ -15217,7 +15217,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G512" t="n">
-        <v>2.49916481971741</v>
+        <v>2.49916505813599</v>
       </c>
       <c r="H512" t="n">
         <v>18429</v>
@@ -15304,7 +15304,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G515" t="n">
-        <v>2.48932552337646</v>
+        <v>2.48932576179504</v>
       </c>
       <c r="H515" t="n">
         <v>421</v>
@@ -15536,7 +15536,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G523" t="n">
-        <v>2.55820035934448</v>
+        <v>2.5582001209259</v>
       </c>
       <c r="H523" t="n">
         <v>28775</v>
@@ -15681,7 +15681,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G528" t="n">
-        <v>2.55820035934448</v>
+        <v>2.5582001209259</v>
       </c>
       <c r="H528" t="n">
         <v>6832</v>
@@ -15710,7 +15710,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G529" t="n">
-        <v>2.52868247032166</v>
+        <v>2.52868270874023</v>
       </c>
       <c r="H529" t="n">
         <v>7700</v>
@@ -15739,7 +15739,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G530" t="n">
-        <v>2.55820035934448</v>
+        <v>2.5582001209259</v>
       </c>
       <c r="H530" t="n">
         <v>6304</v>
@@ -15826,7 +15826,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G533" t="n">
-        <v>2.63691425323486</v>
+        <v>2.63691449165344</v>
       </c>
       <c r="H533" t="n">
         <v>19150</v>
@@ -15884,7 +15884,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G535" t="n">
-        <v>2.53852200508118</v>
+        <v>2.5385217666626</v>
       </c>
       <c r="H535" t="n">
         <v>7600</v>
@@ -15913,7 +15913,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G536" t="n">
-        <v>2.55820035934448</v>
+        <v>2.5582001209259</v>
       </c>
       <c r="H536" t="n">
         <v>1850</v>
@@ -15971,7 +15971,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G538" t="n">
-        <v>2.55820035934448</v>
+        <v>2.5582001209259</v>
       </c>
       <c r="H538" t="n">
         <v>2300</v>
@@ -16000,7 +16000,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G539" t="n">
-        <v>2.55820035934448</v>
+        <v>2.5582001209259</v>
       </c>
       <c r="H539" t="n">
         <v>3806</v>
@@ -16029,7 +16029,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G540" t="n">
-        <v>2.53852200508118</v>
+        <v>2.5385217666626</v>
       </c>
       <c r="H540" t="n">
         <v>6800</v>
@@ -16058,7 +16058,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G541" t="n">
-        <v>2.55820035934448</v>
+        <v>2.5582001209259</v>
       </c>
       <c r="H541" t="n">
         <v>8509</v>
@@ -16087,7 +16087,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G542" t="n">
-        <v>2.55820035934448</v>
+        <v>2.5582001209259</v>
       </c>
       <c r="H542" t="n">
         <v>6554</v>
@@ -16145,7 +16145,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G544" t="n">
-        <v>2.64675354957581</v>
+        <v>2.64675331115723</v>
       </c>
       <c r="H544" t="n">
         <v>29045</v>
@@ -16174,7 +16174,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G545" t="n">
-        <v>2.64675354957581</v>
+        <v>2.64675331115723</v>
       </c>
       <c r="H545" t="n">
         <v>24168</v>
@@ -16232,7 +16232,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G547" t="n">
-        <v>2.35157680511475</v>
+        <v>2.35157656669617</v>
       </c>
       <c r="H547" t="n">
         <v>106601</v>
@@ -16319,7 +16319,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G550" t="n">
-        <v>2.30238008499146</v>
+        <v>2.30238032341003</v>
       </c>
       <c r="H550" t="n">
         <v>10856</v>
@@ -16406,7 +16406,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G553" t="n">
-        <v>2.28270173072815</v>
+        <v>2.28270196914673</v>
       </c>
       <c r="H553" t="n">
         <v>7360</v>
@@ -16522,7 +16522,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G557" t="n">
-        <v>2.27286243438721</v>
+        <v>2.27286267280579</v>
       </c>
       <c r="H557" t="n">
         <v>3150</v>
@@ -16551,7 +16551,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G558" t="n">
-        <v>2.27286243438721</v>
+        <v>2.27286267280579</v>
       </c>
       <c r="H558" t="n">
         <v>0</v>
@@ -16580,7 +16580,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G559" t="n">
-        <v>2.27286243438721</v>
+        <v>2.27286267280579</v>
       </c>
       <c r="H559" t="n">
         <v>4065</v>
@@ -16609,7 +16609,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G560" t="n">
-        <v>2.28270173072815</v>
+        <v>2.28270196914673</v>
       </c>
       <c r="H560" t="n">
         <v>890</v>
@@ -16667,7 +16667,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G562" t="n">
-        <v>2.24334502220154</v>
+        <v>2.24334478378296</v>
       </c>
       <c r="H562" t="n">
         <v>11905</v>
@@ -16696,7 +16696,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G563" t="n">
-        <v>2.20398807525635</v>
+        <v>2.20398783683777</v>
       </c>
       <c r="H563" t="n">
         <v>34790</v>
@@ -16754,7 +16754,7 @@
         <v>2.25</v>
       </c>
       <c r="G565" t="n">
-        <v>2.21382737159729</v>
+        <v>2.21382713317871</v>
       </c>
       <c r="H565" t="n">
         <v>1201</v>
@@ -16783,7 +16783,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G566" t="n">
-        <v>2.27286243438721</v>
+        <v>2.27286267280579</v>
       </c>
       <c r="H566" t="n">
         <v>500</v>
@@ -16899,7 +16899,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G570" t="n">
-        <v>2.24334502220154</v>
+        <v>2.24334478378296</v>
       </c>
       <c r="H570" t="n">
         <v>18090</v>
@@ -16986,7 +16986,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G573" t="n">
-        <v>2.28270173072815</v>
+        <v>2.28270196914673</v>
       </c>
       <c r="H573" t="n">
         <v>2415</v>
@@ -17015,7 +17015,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G574" t="n">
-        <v>2.20398807525635</v>
+        <v>2.20398783683777</v>
       </c>
       <c r="H574" t="n">
         <v>24592</v>
@@ -17131,7 +17131,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G578" t="n">
-        <v>2.28270173072815</v>
+        <v>2.28270196914673</v>
       </c>
       <c r="H578" t="n">
         <v>2017</v>
@@ -17189,7 +17189,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G580" t="n">
-        <v>2.27286243438721</v>
+        <v>2.27286267280579</v>
       </c>
       <c r="H580" t="n">
         <v>2648</v>
@@ -17218,7 +17218,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G581" t="n">
-        <v>2.28270173072815</v>
+        <v>2.28270196914673</v>
       </c>
       <c r="H581" t="n">
         <v>1455</v>
@@ -17276,7 +17276,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G583" t="n">
-        <v>2.30238008499146</v>
+        <v>2.30238032341003</v>
       </c>
       <c r="H583" t="n">
         <v>4608</v>
@@ -17653,7 +17653,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G596" t="n">
-        <v>2.28270173072815</v>
+        <v>2.28270196914673</v>
       </c>
       <c r="H596" t="n">
         <v>3802</v>
@@ -17740,7 +17740,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G599" t="n">
-        <v>2.30238008499146</v>
+        <v>2.30238032341003</v>
       </c>
       <c r="H599" t="n">
         <v>2949</v>
@@ -17798,7 +17798,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G601" t="n">
-        <v>2.24334502220154</v>
+        <v>2.24334478378296</v>
       </c>
       <c r="H601" t="n">
         <v>17283</v>
@@ -17827,7 +17827,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G602" t="n">
-        <v>2.27286243438721</v>
+        <v>2.27286267280579</v>
       </c>
       <c r="H602" t="n">
         <v>2094</v>
@@ -17856,7 +17856,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G603" t="n">
-        <v>2.27286243438721</v>
+        <v>2.27286267280579</v>
       </c>
       <c r="H603" t="n">
         <v>4262</v>
@@ -17914,7 +17914,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G605" t="n">
-        <v>2.30238008499146</v>
+        <v>2.30238032341003</v>
       </c>
       <c r="H605" t="n">
         <v>3421</v>
@@ -17943,7 +17943,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G606" t="n">
-        <v>2.30238008499146</v>
+        <v>2.30238032341003</v>
       </c>
       <c r="H606" t="n">
         <v>1394</v>
@@ -17972,7 +17972,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G607" t="n">
-        <v>2.30238008499146</v>
+        <v>2.30238032341003</v>
       </c>
       <c r="H607" t="n">
         <v>1488</v>
@@ -18001,7 +18001,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G608" t="n">
-        <v>2.30238008499146</v>
+        <v>2.30238032341003</v>
       </c>
       <c r="H608" t="n">
         <v>1944</v>
@@ -18030,7 +18030,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G609" t="n">
-        <v>2.30238008499146</v>
+        <v>2.30238032341003</v>
       </c>
       <c r="H609" t="n">
         <v>1543</v>
@@ -18088,7 +18088,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G611" t="n">
-        <v>2.30238008499146</v>
+        <v>2.30238032341003</v>
       </c>
       <c r="H611" t="n">
         <v>1209</v>
@@ -18146,7 +18146,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G613" t="n">
-        <v>2.27286243438721</v>
+        <v>2.27286267280579</v>
       </c>
       <c r="H613" t="n">
         <v>3339</v>
@@ -18407,7 +18407,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G622" t="n">
-        <v>2.24334502220154</v>
+        <v>2.24334478378296</v>
       </c>
       <c r="H622" t="n">
         <v>729</v>
@@ -18436,7 +18436,7 @@
         <v>2.25</v>
       </c>
       <c r="G623" t="n">
-        <v>2.21382737159729</v>
+        <v>2.21382713317871</v>
       </c>
       <c r="H623" t="n">
         <v>3507</v>
@@ -18494,7 +18494,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G625" t="n">
-        <v>2.24334502220154</v>
+        <v>2.24334478378296</v>
       </c>
       <c r="H625" t="n">
         <v>3357</v>
@@ -18610,7 +18610,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G629" t="n">
-        <v>2.24334502220154</v>
+        <v>2.24334478378296</v>
       </c>
       <c r="H629" t="n">
         <v>1003</v>
@@ -18639,7 +18639,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G630" t="n">
-        <v>2.28270173072815</v>
+        <v>2.28270196914673</v>
       </c>
       <c r="H630" t="n">
         <v>26686</v>
@@ -18668,7 +18668,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G631" t="n">
-        <v>2.28270173072815</v>
+        <v>2.28270196914673</v>
       </c>
       <c r="H631" t="n">
         <v>1654</v>
@@ -18726,7 +18726,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G633" t="n">
-        <v>2.28270173072815</v>
+        <v>2.28270196914673</v>
       </c>
       <c r="H633" t="n">
         <v>1752</v>
@@ -18755,7 +18755,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G634" t="n">
-        <v>2.28270173072815</v>
+        <v>2.28270196914673</v>
       </c>
       <c r="H634" t="n">
         <v>3413</v>
@@ -18900,7 +18900,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G639" t="n">
-        <v>2.27286243438721</v>
+        <v>2.27286267280579</v>
       </c>
       <c r="H639" t="n">
         <v>2152</v>
@@ -18929,7 +18929,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G640" t="n">
-        <v>2.28270173072815</v>
+        <v>2.28270196914673</v>
       </c>
       <c r="H640" t="n">
         <v>2342</v>
@@ -18987,7 +18987,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G642" t="n">
-        <v>2.24334502220154</v>
+        <v>2.24334478378296</v>
       </c>
       <c r="H642" t="n">
         <v>3219</v>
@@ -19074,7 +19074,7 @@
         <v>2.25</v>
       </c>
       <c r="G645" t="n">
-        <v>2.21382737159729</v>
+        <v>2.21382713317871</v>
       </c>
       <c r="H645" t="n">
         <v>5907</v>
@@ -19132,7 +19132,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G647" t="n">
-        <v>2.20398807525635</v>
+        <v>2.20398783683777</v>
       </c>
       <c r="H647" t="n">
         <v>2247</v>
@@ -19190,7 +19190,7 @@
         <v>2.25</v>
       </c>
       <c r="G649" t="n">
-        <v>2.21382737159729</v>
+        <v>2.21382713317871</v>
       </c>
       <c r="H649" t="n">
         <v>1413</v>
@@ -19306,7 +19306,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G653" t="n">
-        <v>2.13511323928833</v>
+        <v>2.13511347770691</v>
       </c>
       <c r="H653" t="n">
         <v>4940</v>
@@ -19335,7 +19335,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G654" t="n">
-        <v>2.14495253562927</v>
+        <v>2.14495277404785</v>
       </c>
       <c r="H654" t="n">
         <v>4916</v>
@@ -19480,7 +19480,7 @@
         <v>2.25</v>
       </c>
       <c r="G659" t="n">
-        <v>2.21382737159729</v>
+        <v>2.21382713317871</v>
       </c>
       <c r="H659" t="n">
         <v>8762</v>
@@ -19538,7 +19538,7 @@
         <v>2.25</v>
       </c>
       <c r="G661" t="n">
-        <v>2.21382737159729</v>
+        <v>2.21382713317871</v>
       </c>
       <c r="H661" t="n">
         <v>6280</v>
@@ -19683,7 +19683,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G666" t="n">
-        <v>2.24334502220154</v>
+        <v>2.24334478378296</v>
       </c>
       <c r="H666" t="n">
         <v>10498</v>
@@ -19799,7 +19799,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G670" t="n">
-        <v>2.20398807525635</v>
+        <v>2.20398783683777</v>
       </c>
       <c r="H670" t="n">
         <v>7844</v>
@@ -19828,7 +19828,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G671" t="n">
-        <v>2.24334502220154</v>
+        <v>2.24334478378296</v>
       </c>
       <c r="H671" t="n">
         <v>7122</v>
@@ -19857,7 +19857,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G672" t="n">
-        <v>2.24334502220154</v>
+        <v>2.24334478378296</v>
       </c>
       <c r="H672" t="n">
         <v>3472</v>
@@ -19886,7 +19886,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G673" t="n">
-        <v>2.24334502220154</v>
+        <v>2.24334478378296</v>
       </c>
       <c r="H673" t="n">
         <v>4302</v>
@@ -19973,7 +19973,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G676" t="n">
-        <v>2.20398807525635</v>
+        <v>2.20398783683777</v>
       </c>
       <c r="H676" t="n">
         <v>2219</v>
@@ -20118,7 +20118,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G681" t="n">
-        <v>2.27286243438721</v>
+        <v>2.27286267280579</v>
       </c>
       <c r="H681" t="n">
         <v>3394</v>
@@ -20234,7 +20234,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G685" t="n">
-        <v>2.35157680511475</v>
+        <v>2.35157656669617</v>
       </c>
       <c r="H685" t="n">
         <v>14060</v>
@@ -20321,7 +20321,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G688" t="n">
-        <v>2.35157680511475</v>
+        <v>2.35157656669617</v>
       </c>
       <c r="H688" t="n">
         <v>3921</v>
@@ -20756,7 +20756,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G703" t="n">
-        <v>2.30238008499146</v>
+        <v>2.30238032341003</v>
       </c>
       <c r="H703" t="n">
         <v>18619</v>
@@ -20785,7 +20785,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G704" t="n">
-        <v>2.30238008499146</v>
+        <v>2.30238032341003</v>
       </c>
       <c r="H704" t="n">
         <v>5776</v>
@@ -20814,7 +20814,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G705" t="n">
-        <v>2.30238008499146</v>
+        <v>2.30238032341003</v>
       </c>
       <c r="H705" t="n">
         <v>4067</v>
@@ -20843,7 +20843,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G706" t="n">
-        <v>2.28270173072815</v>
+        <v>2.28270196914673</v>
       </c>
       <c r="H706" t="n">
         <v>2590</v>
@@ -20872,7 +20872,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G707" t="n">
-        <v>2.24334502220154</v>
+        <v>2.24334478378296</v>
       </c>
       <c r="H707" t="n">
         <v>10831</v>
@@ -20988,7 +20988,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G711" t="n">
-        <v>2.43029046058655</v>
+        <v>2.43029022216797</v>
       </c>
       <c r="H711" t="n">
         <v>15029</v>
@@ -21017,7 +21017,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G712" t="n">
-        <v>2.43029046058655</v>
+        <v>2.43029022216797</v>
       </c>
       <c r="H712" t="n">
         <v>8791</v>
@@ -21133,7 +21133,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G716" t="n">
-        <v>2.35157680511475</v>
+        <v>2.35157656669617</v>
       </c>
       <c r="H716" t="n">
         <v>16386</v>
@@ -21162,7 +21162,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G717" t="n">
-        <v>2.43029046058655</v>
+        <v>2.43029022216797</v>
       </c>
       <c r="H717" t="n">
         <v>59441</v>
@@ -21307,7 +21307,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G722" t="n">
-        <v>2.35157680511475</v>
+        <v>2.35157656669617</v>
       </c>
       <c r="H722" t="n">
         <v>15797</v>
@@ -21365,7 +21365,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G724" t="n">
-        <v>2.35157680511475</v>
+        <v>2.35157656669617</v>
       </c>
       <c r="H724" t="n">
         <v>6782</v>
@@ -21423,7 +21423,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G726" t="n">
-        <v>2.41061186790466</v>
+        <v>2.41061210632324</v>
       </c>
       <c r="H726" t="n">
         <v>10601</v>
@@ -21452,7 +21452,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G727" t="n">
-        <v>2.43029046058655</v>
+        <v>2.43029022216797</v>
       </c>
       <c r="H727" t="n">
         <v>6641</v>
@@ -21481,7 +21481,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G728" t="n">
-        <v>2.43029046058655</v>
+        <v>2.43029022216797</v>
       </c>
       <c r="H728" t="n">
         <v>7749</v>
@@ -21597,7 +21597,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G732" t="n">
-        <v>2.41061186790466</v>
+        <v>2.41061210632324</v>
       </c>
       <c r="H732" t="n">
         <v>8506</v>
@@ -21771,7 +21771,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G738" t="n">
-        <v>2.35157680511475</v>
+        <v>2.35157656669617</v>
       </c>
       <c r="H738" t="n">
         <v>9988</v>
@@ -21887,7 +21887,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G742" t="n">
-        <v>2.49916481971741</v>
+        <v>2.49916505813599</v>
       </c>
       <c r="H742" t="n">
         <v>34943</v>
@@ -21945,7 +21945,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G744" t="n">
-        <v>2.48932552337646</v>
+        <v>2.48932576179504</v>
       </c>
       <c r="H744" t="n">
         <v>39865</v>
@@ -22003,7 +22003,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G746" t="n">
-        <v>2.48932552337646</v>
+        <v>2.48932576179504</v>
       </c>
       <c r="H746" t="n">
         <v>18877</v>
@@ -22032,7 +22032,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G747" t="n">
-        <v>2.51884317398071</v>
+        <v>2.51884341239929</v>
       </c>
       <c r="H747" t="n">
         <v>44586</v>
@@ -22061,7 +22061,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G748" t="n">
-        <v>2.52868247032166</v>
+        <v>2.52868270874023</v>
       </c>
       <c r="H748" t="n">
         <v>45070</v>
@@ -22206,7 +22206,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G753" t="n">
-        <v>2.63691425323486</v>
+        <v>2.63691449165344</v>
       </c>
       <c r="H753" t="n">
         <v>58392</v>
@@ -22264,7 +22264,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G755" t="n">
-        <v>2.77466344833374</v>
+        <v>2.77466320991516</v>
       </c>
       <c r="H755" t="n">
         <v>152514</v>
@@ -22322,7 +22322,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G757" t="n">
-        <v>2.71562790870667</v>
+        <v>2.71562814712524</v>
       </c>
       <c r="H757" t="n">
         <v>170397</v>
@@ -22380,7 +22380,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G759" t="n">
-        <v>2.77466344833374</v>
+        <v>2.77466320991516</v>
       </c>
       <c r="H759" t="n">
         <v>21143</v>
@@ -22409,7 +22409,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G760" t="n">
-        <v>2.77466344833374</v>
+        <v>2.77466320991516</v>
       </c>
       <c r="H760" t="n">
         <v>14482</v>
@@ -22438,7 +22438,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G761" t="n">
-        <v>2.77466344833374</v>
+        <v>2.77466320991516</v>
       </c>
       <c r="H761" t="n">
         <v>13481</v>
@@ -22583,7 +22583,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G766" t="n">
-        <v>2.77466344833374</v>
+        <v>2.77466320991516</v>
       </c>
       <c r="H766" t="n">
         <v>11073</v>
@@ -22641,7 +22641,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G768" t="n">
-        <v>2.77466344833374</v>
+        <v>2.77466320991516</v>
       </c>
       <c r="H768" t="n">
         <v>16757</v>
@@ -22786,7 +22786,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G773" t="n">
-        <v>3.00096583366394</v>
+        <v>3.00096559524536</v>
       </c>
       <c r="H773" t="n">
         <v>78428</v>
@@ -22873,7 +22873,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G776" t="n">
-        <v>3.00096583366394</v>
+        <v>3.00096559524536</v>
       </c>
       <c r="H776" t="n">
         <v>13843</v>
@@ -22960,7 +22960,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G779" t="n">
-        <v>3.00096583366394</v>
+        <v>3.00096559524536</v>
       </c>
       <c r="H779" t="n">
         <v>12842</v>
@@ -23018,7 +23018,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G781" t="n">
-        <v>3.00096583366394</v>
+        <v>3.00096559524536</v>
       </c>
       <c r="H781" t="n">
         <v>25556</v>
@@ -23221,7 +23221,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G788" t="n">
-        <v>2.9124128818512</v>
+        <v>2.91241264343262</v>
       </c>
       <c r="H788" t="n">
         <v>28876</v>
@@ -23279,7 +23279,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G790" t="n">
-        <v>2.84353804588318</v>
+        <v>2.84353828430176</v>
       </c>
       <c r="H790" t="n">
         <v>12028</v>
@@ -23308,7 +23308,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G791" t="n">
-        <v>2.92225217819214</v>
+        <v>2.92225193977356</v>
       </c>
       <c r="H791" t="n">
         <v>36996</v>
@@ -23366,7 +23366,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G793" t="n">
-        <v>2.92225217819214</v>
+        <v>2.92225193977356</v>
       </c>
       <c r="H793" t="n">
         <v>20612</v>
@@ -23395,7 +23395,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G794" t="n">
-        <v>2.90257334709167</v>
+        <v>2.90257358551025</v>
       </c>
       <c r="H794" t="n">
         <v>5153</v>
@@ -23511,7 +23511,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G798" t="n">
-        <v>2.9124128818512</v>
+        <v>2.91241264343262</v>
       </c>
       <c r="H798" t="n">
         <v>29046</v>
@@ -23743,7 +23743,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G806" t="n">
-        <v>3.09935832023621</v>
+        <v>3.09935808181763</v>
       </c>
       <c r="H806" t="n">
         <v>21409</v>
@@ -23801,7 +23801,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G808" t="n">
-        <v>3.1387152671814</v>
+        <v>3.13871502876282</v>
       </c>
       <c r="H808" t="n">
         <v>29053</v>
@@ -24004,7 +24004,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G815" t="n">
-        <v>3.16823267936707</v>
+        <v>3.16823291778564</v>
       </c>
       <c r="H815" t="n">
         <v>40945</v>
@@ -24207,7 +24207,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G822" t="n">
-        <v>3.32566070556641</v>
+        <v>3.32566046714783</v>
       </c>
       <c r="H822" t="n">
         <v>8250</v>
@@ -24352,7 +24352,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G827" t="n">
-        <v>3.41421341896057</v>
+        <v>3.41421365737915</v>
       </c>
       <c r="H827" t="n">
         <v>49728</v>
@@ -24381,7 +24381,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G828" t="n">
-        <v>3.42405271530151</v>
+        <v>3.42405295372009</v>
       </c>
       <c r="H828" t="n">
         <v>21052</v>
@@ -24410,7 +24410,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G829" t="n">
-        <v>3.48308825492859</v>
+        <v>3.48308801651001</v>
       </c>
       <c r="H829" t="n">
         <v>56595</v>
@@ -24468,7 +24468,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G831" t="n">
-        <v>3.57164144515991</v>
+        <v>3.57164120674133</v>
       </c>
       <c r="H831" t="n">
         <v>31184</v>
@@ -24555,7 +24555,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G834" t="n">
-        <v>4.12263822555542</v>
+        <v>4.12263870239258</v>
       </c>
       <c r="H834" t="n">
         <v>162852</v>
@@ -24584,7 +24584,7 @@
         <v>4.25</v>
       </c>
       <c r="G835" t="n">
-        <v>4.18167400360107</v>
+        <v>4.18167352676392</v>
       </c>
       <c r="H835" t="n">
         <v>105792</v>
@@ -24700,7 +24700,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G839" t="n">
-        <v>4.22103071212769</v>
+        <v>4.22103023529053</v>
       </c>
       <c r="H839" t="n">
         <v>31763</v>
@@ -24758,7 +24758,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G841" t="n">
-        <v>4.28990507125854</v>
+        <v>4.2899055480957</v>
       </c>
       <c r="H841" t="n">
         <v>33142</v>
@@ -24816,7 +24816,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G843" t="n">
-        <v>4.39813661575317</v>
+        <v>4.39813613891602</v>
       </c>
       <c r="H843" t="n">
         <v>122860</v>
@@ -24990,7 +24990,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G849" t="n">
-        <v>5.07704401016235</v>
+        <v>5.0770435333252</v>
       </c>
       <c r="H849" t="n">
         <v>125520</v>
@@ -25019,7 +25019,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G850" t="n">
-        <v>4.99832963943481</v>
+        <v>4.99833011627197</v>
       </c>
       <c r="H850" t="n">
         <v>94101</v>
@@ -25077,7 +25077,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G852" t="n">
-        <v>5.03768634796143</v>
+        <v>5.03768682479858</v>
       </c>
       <c r="H852" t="n">
         <v>39665</v>
@@ -25222,7 +25222,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G857" t="n">
-        <v>5.03768634796143</v>
+        <v>5.03768682479858</v>
       </c>
       <c r="H857" t="n">
         <v>29318</v>
@@ -25280,7 +25280,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G859" t="n">
-        <v>4.8605809211731</v>
+        <v>4.86058044433594</v>
       </c>
       <c r="H859" t="n">
         <v>18569</v>
@@ -25309,7 +25309,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G860" t="n">
-        <v>4.83106279373169</v>
+        <v>4.83106327056885</v>
       </c>
       <c r="H860" t="n">
         <v>56243</v>
@@ -25338,7 +25338,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G861" t="n">
-        <v>4.89009857177734</v>
+        <v>4.89009809494019</v>
       </c>
       <c r="H861" t="n">
         <v>26996</v>
@@ -25425,7 +25425,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G864" t="n">
-        <v>4.89009857177734</v>
+        <v>4.89009809494019</v>
       </c>
       <c r="H864" t="n">
         <v>17018</v>
@@ -25512,7 +25512,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G867" t="n">
-        <v>5.29350709915161</v>
+        <v>5.29350662231445</v>
       </c>
       <c r="H867" t="n">
         <v>54581</v>
@@ -25570,7 +25570,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G869" t="n">
-        <v>5.70675468444824</v>
+        <v>5.7067551612854</v>
       </c>
       <c r="H869" t="n">
         <v>193218</v>
@@ -25599,7 +25599,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G870" t="n">
-        <v>5.80514669418335</v>
+        <v>5.80514717102051</v>
       </c>
       <c r="H870" t="n">
         <v>93551</v>
@@ -25628,7 +25628,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G871" t="n">
-        <v>5.68707609176636</v>
+        <v>5.68707656860352</v>
       </c>
       <c r="H871" t="n">
         <v>93418</v>
@@ -25686,7 +25686,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G873" t="n">
-        <v>5.43125581741333</v>
+        <v>5.43125629425049</v>
       </c>
       <c r="H873" t="n">
         <v>19758</v>
@@ -25773,7 +25773,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G876" t="n">
-        <v>5.27382850646973</v>
+        <v>5.27382898330688</v>
       </c>
       <c r="H876" t="n">
         <v>74967</v>
@@ -25802,7 +25802,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G877" t="n">
-        <v>5.29350709915161</v>
+        <v>5.29350662231445</v>
       </c>
       <c r="H877" t="n">
         <v>29227</v>
@@ -25860,7 +25860,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G879" t="n">
-        <v>5.05736494064331</v>
+        <v>5.05736541748047</v>
       </c>
       <c r="H879" t="n">
         <v>31367</v>
@@ -25918,7 +25918,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G881" t="n">
-        <v>5.03768634796143</v>
+        <v>5.03768682479858</v>
       </c>
       <c r="H881" t="n">
         <v>10417</v>
@@ -25976,7 +25976,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G883" t="n">
-        <v>5.03768634796143</v>
+        <v>5.03768682479858</v>
       </c>
       <c r="H883" t="n">
         <v>19220</v>
@@ -26034,7 +26034,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G885" t="n">
-        <v>5.07704401016235</v>
+        <v>5.0770435333252</v>
       </c>
       <c r="H885" t="n">
         <v>8947</v>
@@ -26208,7 +26208,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G891" t="n">
-        <v>5.27382850646973</v>
+        <v>5.27382898330688</v>
       </c>
       <c r="H891" t="n">
         <v>7249</v>
@@ -26237,7 +26237,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G892" t="n">
-        <v>5.11640071868896</v>
+        <v>5.11640024185181</v>
       </c>
       <c r="H892" t="n">
         <v>12636</v>
@@ -26266,7 +26266,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G893" t="n">
-        <v>5.05736494064331</v>
+        <v>5.05736541748047</v>
       </c>
       <c r="H893" t="n">
         <v>9316</v>
@@ -26295,7 +26295,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G894" t="n">
-        <v>5.03768634796143</v>
+        <v>5.03768682479858</v>
       </c>
       <c r="H894" t="n">
         <v>6814</v>
@@ -26324,7 +26324,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G895" t="n">
-        <v>5.03768634796143</v>
+        <v>5.03768682479858</v>
       </c>
       <c r="H895" t="n">
         <v>7477</v>
@@ -26382,7 +26382,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G897" t="n">
-        <v>5.11640071868896</v>
+        <v>5.11640024185181</v>
       </c>
       <c r="H897" t="n">
         <v>6128</v>
@@ -26411,7 +26411,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G898" t="n">
-        <v>4.99832963943481</v>
+        <v>4.99833011627197</v>
       </c>
       <c r="H898" t="n">
         <v>29460</v>
@@ -26440,7 +26440,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G899" t="n">
-        <v>4.83106279373169</v>
+        <v>4.83106327056885</v>
       </c>
       <c r="H899" t="n">
         <v>72320</v>
@@ -26556,7 +26556,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G903" t="n">
-        <v>4.28990507125854</v>
+        <v>4.2899055480957</v>
       </c>
       <c r="H903" t="n">
         <v>28901</v>
@@ -26585,7 +26585,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G904" t="n">
-        <v>4.5654034614563</v>
+        <v>4.56540393829346</v>
       </c>
       <c r="H904" t="n">
         <v>47385</v>
@@ -26643,7 +26643,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G906" t="n">
-        <v>4.83106279373169</v>
+        <v>4.83106327056885</v>
       </c>
       <c r="H906" t="n">
         <v>107459</v>
@@ -26672,7 +26672,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G907" t="n">
-        <v>4.89009857177734</v>
+        <v>4.89009809494019</v>
       </c>
       <c r="H907" t="n">
         <v>18622</v>
@@ -26730,7 +26730,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G909" t="n">
-        <v>4.84090232849121</v>
+        <v>4.84090185165405</v>
       </c>
       <c r="H909" t="n">
         <v>11135</v>
@@ -26759,7 +26759,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G910" t="n">
-        <v>4.83106279373169</v>
+        <v>4.83106327056885</v>
       </c>
       <c r="H910" t="n">
         <v>9284</v>
@@ -26817,7 +26817,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G912" t="n">
-        <v>4.89009857177734</v>
+        <v>4.89009809494019</v>
       </c>
       <c r="H912" t="n">
         <v>3683</v>
@@ -26933,7 +26933,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G916" t="n">
-        <v>4.82122373580933</v>
+        <v>4.82122421264648</v>
       </c>
       <c r="H916" t="n">
         <v>15220</v>
@@ -26991,7 +26991,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G918" t="n">
-        <v>5.03768634796143</v>
+        <v>5.03768682479858</v>
       </c>
       <c r="H918" t="n">
         <v>45309</v>
@@ -27020,7 +27020,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G919" t="n">
-        <v>5.07704401016235</v>
+        <v>5.0770435333252</v>
       </c>
       <c r="H919" t="n">
         <v>22506</v>
@@ -27107,7 +27107,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G922" t="n">
-        <v>5.11640071868896</v>
+        <v>5.11640024185181</v>
       </c>
       <c r="H922" t="n">
         <v>20658</v>
@@ -27223,7 +27223,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G926" t="n">
-        <v>5.25414991378784</v>
+        <v>5.254150390625</v>
       </c>
       <c r="H926" t="n">
         <v>16523</v>
@@ -27281,7 +27281,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G928" t="n">
-        <v>5.27382850646973</v>
+        <v>5.27382898330688</v>
       </c>
       <c r="H928" t="n">
         <v>14860</v>
@@ -27310,7 +27310,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G929" t="n">
-        <v>5.29350709915161</v>
+        <v>5.29350662231445</v>
       </c>
       <c r="H929" t="n">
         <v>8491</v>
@@ -27339,7 +27339,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G930" t="n">
-        <v>5.29350709915161</v>
+        <v>5.29350662231445</v>
       </c>
       <c r="H930" t="n">
         <v>4930</v>
@@ -27542,7 +27542,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G937" t="n">
-        <v>5.11640071868896</v>
+        <v>5.11640024185181</v>
       </c>
       <c r="H937" t="n">
         <v>12717</v>
@@ -27600,7 +27600,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G939" t="n">
-        <v>5.11640071868896</v>
+        <v>5.11640024185181</v>
       </c>
       <c r="H939" t="n">
         <v>9615</v>
@@ -27658,7 +27658,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G941" t="n">
-        <v>5.07704401016235</v>
+        <v>5.0770435333252</v>
       </c>
       <c r="H941" t="n">
         <v>9588</v>
@@ -27745,7 +27745,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G944" t="n">
-        <v>5.13607931137085</v>
+        <v>5.13607883453369</v>
       </c>
       <c r="H944" t="n">
         <v>6542</v>
@@ -27890,7 +27890,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G949" t="n">
-        <v>5.25414991378784</v>
+        <v>5.254150390625</v>
       </c>
       <c r="H949" t="n">
         <v>10195</v>
@@ -27919,7 +27919,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G950" t="n">
-        <v>5.29350709915161</v>
+        <v>5.29350662231445</v>
       </c>
       <c r="H950" t="n">
         <v>11103</v>
@@ -28151,7 +28151,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G958" t="n">
-        <v>5.68707609176636</v>
+        <v>5.68707656860352</v>
       </c>
       <c r="H958" t="n">
         <v>24892</v>
@@ -28180,7 +28180,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G959" t="n">
-        <v>5.68707609176636</v>
+        <v>5.68707656860352</v>
       </c>
       <c r="H959" t="n">
         <v>8965</v>
@@ -28267,7 +28267,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G962" t="n">
-        <v>5.80514669418335</v>
+        <v>5.80514717102051</v>
       </c>
       <c r="H962" t="n">
         <v>18409</v>
@@ -28354,7 +28354,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G965" t="n">
-        <v>5.80514669418335</v>
+        <v>5.80514717102051</v>
       </c>
       <c r="H965" t="n">
         <v>16785</v>
@@ -28470,7 +28470,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G969" t="n">
-        <v>6.1396803855896</v>
+        <v>6.13968086242676</v>
       </c>
       <c r="H969" t="n">
         <v>75849</v>
@@ -28499,7 +28499,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G970" t="n">
-        <v>6.19871664047241</v>
+        <v>6.19871616363525</v>
       </c>
       <c r="H970" t="n">
         <v>62814</v>
@@ -28528,7 +28528,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G971" t="n">
-        <v>6.33646535873413</v>
+        <v>6.33646583557129</v>
       </c>
       <c r="H971" t="n">
         <v>50014</v>
@@ -28557,7 +28557,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G972" t="n">
-        <v>6.27743053436279</v>
+        <v>6.27743005752563</v>
       </c>
       <c r="H972" t="n">
         <v>43290</v>
@@ -28615,7 +28615,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G974" t="n">
-        <v>6.1396803855896</v>
+        <v>6.13968086242676</v>
       </c>
       <c r="H974" t="n">
         <v>10830</v>
@@ -28702,7 +28702,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G977" t="n">
-        <v>6.00193166732788</v>
+        <v>6.00193119049072</v>
       </c>
       <c r="H977" t="n">
         <v>35007</v>
@@ -43237,6 +43237,35 @@
         <v>13064</v>
       </c>
       <c r="I1478" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1479">
+      <c r="A1479" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1479" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C1479" t="n">
+        <v>7.82000017166138</v>
+      </c>
+      <c r="D1479" t="n">
+        <v>7.82000017166138</v>
+      </c>
+      <c r="E1479" t="n">
+        <v>7.65999984741211</v>
+      </c>
+      <c r="F1479" t="n">
+        <v>7.67000007629395</v>
+      </c>
+      <c r="G1479" t="n">
+        <v>7.67000007629395</v>
+      </c>
+      <c r="H1479" t="n">
+        <v>187</v>
+      </c>
+      <c r="I1479" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/EVISO.MI.xlsx
+++ b/data/EVISO.MI.xlsx
@@ -456,7 +456,7 @@
         <v>2.25</v>
       </c>
       <c r="G3" t="n">
-        <v>2.20108556747437</v>
+        <v>2.20108580589294</v>
       </c>
       <c r="H3" t="n">
         <v>232547</v>
@@ -688,7 +688,7 @@
         <v>2</v>
       </c>
       <c r="G11" t="n">
-        <v>1.95652055740356</v>
+        <v>1.95652067661285</v>
       </c>
       <c r="H11" t="n">
         <v>87109</v>
@@ -717,7 +717,7 @@
         <v>2</v>
       </c>
       <c r="G12" t="n">
-        <v>1.95652055740356</v>
+        <v>1.95652067661285</v>
       </c>
       <c r="H12" t="n">
         <v>33913</v>
@@ -746,7 +746,7 @@
         <v>2</v>
       </c>
       <c r="G13" t="n">
-        <v>1.95652055740356</v>
+        <v>1.95652067661285</v>
       </c>
       <c r="H13" t="n">
         <v>67232</v>
@@ -775,7 +775,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G14" t="n">
-        <v>1.93695533275604</v>
+        <v>1.93695557117462</v>
       </c>
       <c r="H14" t="n">
         <v>32193</v>
@@ -891,7 +891,7 @@
         <v>2</v>
       </c>
       <c r="G18" t="n">
-        <v>1.95652055740356</v>
+        <v>1.95652067661285</v>
       </c>
       <c r="H18" t="n">
         <v>259672</v>
@@ -920,7 +920,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G19" t="n">
-        <v>1.96630322933197</v>
+        <v>1.96630311012268</v>
       </c>
       <c r="H19" t="n">
         <v>71780</v>
@@ -949,7 +949,7 @@
         <v>2</v>
       </c>
       <c r="G20" t="n">
-        <v>1.95652055740356</v>
+        <v>1.95652067661285</v>
       </c>
       <c r="H20" t="n">
         <v>44963</v>
@@ -978,7 +978,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G21" t="n">
-        <v>1.9858683347702</v>
+        <v>1.98586857318878</v>
       </c>
       <c r="H21" t="n">
         <v>29362</v>
@@ -1007,7 +1007,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G22" t="n">
-        <v>1.96630322933197</v>
+        <v>1.96630311012268</v>
       </c>
       <c r="H22" t="n">
         <v>29896</v>
@@ -1036,7 +1036,7 @@
         <v>2</v>
       </c>
       <c r="G23" t="n">
-        <v>1.95652055740356</v>
+        <v>1.95652067661285</v>
       </c>
       <c r="H23" t="n">
         <v>29935</v>
@@ -1094,7 +1094,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G25" t="n">
-        <v>1.96630322933197</v>
+        <v>1.96630311012268</v>
       </c>
       <c r="H25" t="n">
         <v>38840</v>
@@ -1123,7 +1123,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G26" t="n">
-        <v>1.96630322933197</v>
+        <v>1.96630311012268</v>
       </c>
       <c r="H26" t="n">
         <v>65217</v>
@@ -1152,7 +1152,7 @@
         <v>2</v>
       </c>
       <c r="G27" t="n">
-        <v>1.95652055740356</v>
+        <v>1.95652067661285</v>
       </c>
       <c r="H27" t="n">
         <v>20889</v>
@@ -1210,7 +1210,7 @@
         <v>2</v>
       </c>
       <c r="G29" t="n">
-        <v>1.95652055740356</v>
+        <v>1.95652067661285</v>
       </c>
       <c r="H29" t="n">
         <v>28897</v>
@@ -1326,7 +1326,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G33" t="n">
-        <v>2.13260769844055</v>
+        <v>2.13260746002197</v>
       </c>
       <c r="H33" t="n">
         <v>250444</v>
@@ -1384,7 +1384,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G35" t="n">
-        <v>2.33804225921631</v>
+        <v>2.33804249763489</v>
       </c>
       <c r="H35" t="n">
         <v>424591</v>
@@ -1471,7 +1471,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G38" t="n">
-        <v>2.28912925720215</v>
+        <v>2.28912878036499</v>
       </c>
       <c r="H38" t="n">
         <v>46638</v>
@@ -1500,7 +1500,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G39" t="n">
-        <v>2.26956415176392</v>
+        <v>2.26956367492676</v>
       </c>
       <c r="H39" t="n">
         <v>53117</v>
@@ -1703,7 +1703,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G46" t="n">
-        <v>2.28912925720215</v>
+        <v>2.28912878036499</v>
       </c>
       <c r="H46" t="n">
         <v>34385</v>
@@ -1761,7 +1761,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G48" t="n">
-        <v>2.28912925720215</v>
+        <v>2.28912878036499</v>
       </c>
       <c r="H48" t="n">
         <v>32533</v>
@@ -1790,7 +1790,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G49" t="n">
-        <v>2.26956415176392</v>
+        <v>2.26956367492676</v>
       </c>
       <c r="H49" t="n">
         <v>44339</v>
@@ -1819,7 +1819,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G50" t="n">
-        <v>2.28912925720215</v>
+        <v>2.28912878036499</v>
       </c>
       <c r="H50" t="n">
         <v>198858</v>
@@ -1848,7 +1848,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G51" t="n">
-        <v>2.26956415176392</v>
+        <v>2.26956367492676</v>
       </c>
       <c r="H51" t="n">
         <v>28573</v>
@@ -2022,7 +2022,7 @@
         <v>2.25</v>
       </c>
       <c r="G57" t="n">
-        <v>2.20108556747437</v>
+        <v>2.20108580589294</v>
       </c>
       <c r="H57" t="n">
         <v>56053</v>
@@ -2138,7 +2138,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G61" t="n">
-        <v>2.23043346405029</v>
+        <v>2.23043370246887</v>
       </c>
       <c r="H61" t="n">
         <v>30389</v>
@@ -2167,7 +2167,7 @@
         <v>2.25</v>
       </c>
       <c r="G62" t="n">
-        <v>2.20108556747437</v>
+        <v>2.20108580589294</v>
       </c>
       <c r="H62" t="n">
         <v>17852</v>
@@ -2196,7 +2196,7 @@
         <v>2.25</v>
       </c>
       <c r="G63" t="n">
-        <v>2.20108556747437</v>
+        <v>2.20108580589294</v>
       </c>
       <c r="H63" t="n">
         <v>4750</v>
@@ -2283,7 +2283,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G66" t="n">
-        <v>2.19130301475525</v>
+        <v>2.19130325317383</v>
       </c>
       <c r="H66" t="n">
         <v>23995</v>
@@ -2312,7 +2312,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G67" t="n">
-        <v>2.19130301475525</v>
+        <v>2.19130325317383</v>
       </c>
       <c r="H67" t="n">
         <v>651</v>
@@ -2341,7 +2341,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G68" t="n">
-        <v>2.23043346405029</v>
+        <v>2.23043370246887</v>
       </c>
       <c r="H68" t="n">
         <v>59507</v>
@@ -2370,7 +2370,7 @@
         <v>2.25</v>
       </c>
       <c r="G69" t="n">
-        <v>2.20108556747437</v>
+        <v>2.20108580589294</v>
       </c>
       <c r="H69" t="n">
         <v>21435</v>
@@ -2399,7 +2399,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G70" t="n">
-        <v>2.19130301475525</v>
+        <v>2.19130325317383</v>
       </c>
       <c r="H70" t="n">
         <v>19650</v>
@@ -2457,7 +2457,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G72" t="n">
-        <v>2.19130301475525</v>
+        <v>2.19130325317383</v>
       </c>
       <c r="H72" t="n">
         <v>13730</v>
@@ -2486,7 +2486,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G73" t="n">
-        <v>2.19130301475525</v>
+        <v>2.19130325317383</v>
       </c>
       <c r="H73" t="n">
         <v>10901</v>
@@ -2631,7 +2631,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G78" t="n">
-        <v>2.13260769844055</v>
+        <v>2.13260746002197</v>
       </c>
       <c r="H78" t="n">
         <v>6844</v>
@@ -2660,7 +2660,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G79" t="n">
-        <v>2.23043346405029</v>
+        <v>2.23043370246887</v>
       </c>
       <c r="H79" t="n">
         <v>133272</v>
@@ -2805,7 +2805,7 @@
         <v>2.25</v>
       </c>
       <c r="G84" t="n">
-        <v>2.20108556747437</v>
+        <v>2.20108580589294</v>
       </c>
       <c r="H84" t="n">
         <v>5934</v>
@@ -2863,7 +2863,7 @@
         <v>2.25</v>
       </c>
       <c r="G86" t="n">
-        <v>2.20108556747437</v>
+        <v>2.20108580589294</v>
       </c>
       <c r="H86" t="n">
         <v>22122</v>
@@ -2979,7 +2979,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G90" t="n">
-        <v>2.19130301475525</v>
+        <v>2.19130325317383</v>
       </c>
       <c r="H90" t="n">
         <v>19878</v>
@@ -3008,7 +3008,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G91" t="n">
-        <v>2.33804225921631</v>
+        <v>2.33804249763489</v>
       </c>
       <c r="H91" t="n">
         <v>287103</v>
@@ -3124,7 +3124,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G95" t="n">
-        <v>2.26956415176392</v>
+        <v>2.26956367492676</v>
       </c>
       <c r="H95" t="n">
         <v>10213</v>
@@ -3269,7 +3269,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G100" t="n">
-        <v>2.33804225921631</v>
+        <v>2.33804249763489</v>
       </c>
       <c r="H100" t="n">
         <v>138592</v>
@@ -3414,7 +3414,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G105" t="n">
-        <v>2.73912906646729</v>
+        <v>2.73912882804871</v>
       </c>
       <c r="H105" t="n">
         <v>254085</v>
@@ -3472,7 +3472,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G107" t="n">
-        <v>2.69999861717224</v>
+        <v>2.69999814033508</v>
       </c>
       <c r="H107" t="n">
         <v>144356</v>
@@ -3617,7 +3617,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G112" t="n">
-        <v>2.54347658157349</v>
+        <v>2.54347681999207</v>
       </c>
       <c r="H112" t="n">
         <v>34901</v>
@@ -3646,7 +3646,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G113" t="n">
-        <v>2.54347658157349</v>
+        <v>2.54347681999207</v>
       </c>
       <c r="H113" t="n">
         <v>36680</v>
@@ -3733,7 +3733,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G116" t="n">
-        <v>2.51412916183472</v>
+        <v>2.51412868499756</v>
       </c>
       <c r="H116" t="n">
         <v>8588</v>
@@ -3762,7 +3762,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G117" t="n">
-        <v>2.54347658157349</v>
+        <v>2.54347681999207</v>
       </c>
       <c r="H117" t="n">
         <v>39029</v>
@@ -3791,7 +3791,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G118" t="n">
-        <v>2.49456381797791</v>
+        <v>2.49456357955933</v>
       </c>
       <c r="H118" t="n">
         <v>42909</v>
@@ -3820,7 +3820,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G119" t="n">
-        <v>2.51412916183472</v>
+        <v>2.51412868499756</v>
       </c>
       <c r="H119" t="n">
         <v>5450</v>
@@ -3849,7 +3849,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G120" t="n">
-        <v>2.47499871253967</v>
+        <v>2.47499847412109</v>
       </c>
       <c r="H120" t="n">
         <v>9520</v>
@@ -3936,7 +3936,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G123" t="n">
-        <v>2.40652012825012</v>
+        <v>2.4065203666687</v>
       </c>
       <c r="H123" t="n">
         <v>14814</v>
@@ -3994,7 +3994,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G125" t="n">
-        <v>2.41630291938782</v>
+        <v>2.4163031578064</v>
       </c>
       <c r="H125" t="n">
         <v>35694</v>
@@ -4023,7 +4023,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G126" t="n">
-        <v>2.40652012825012</v>
+        <v>2.4065203666687</v>
       </c>
       <c r="H126" t="n">
         <v>17192</v>
@@ -4081,7 +4081,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G128" t="n">
-        <v>2.48478126525879</v>
+        <v>2.48478102684021</v>
       </c>
       <c r="H128" t="n">
         <v>22629</v>
@@ -4110,7 +4110,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G129" t="n">
-        <v>2.49456381797791</v>
+        <v>2.49456357955933</v>
       </c>
       <c r="H129" t="n">
         <v>3606</v>
@@ -4139,7 +4139,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G130" t="n">
-        <v>2.52391147613525</v>
+        <v>2.52391171455383</v>
       </c>
       <c r="H130" t="n">
         <v>6239</v>
@@ -4197,7 +4197,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G132" t="n">
-        <v>2.49456381797791</v>
+        <v>2.49456357955933</v>
       </c>
       <c r="H132" t="n">
         <v>6780</v>
@@ -4255,7 +4255,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G134" t="n">
-        <v>2.51412916183472</v>
+        <v>2.51412868499756</v>
       </c>
       <c r="H134" t="n">
         <v>8450</v>
@@ -4342,7 +4342,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G137" t="n">
-        <v>2.47499871253967</v>
+        <v>2.47499847412109</v>
       </c>
       <c r="H137" t="n">
         <v>1750</v>
@@ -4458,7 +4458,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G141" t="n">
-        <v>2.41630291938782</v>
+        <v>2.4163031578064</v>
       </c>
       <c r="H141" t="n">
         <v>4028</v>
@@ -4487,7 +4487,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G142" t="n">
-        <v>2.40652012825012</v>
+        <v>2.4065203666687</v>
       </c>
       <c r="H142" t="n">
         <v>11210</v>
@@ -4661,7 +4661,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G148" t="n">
-        <v>2.40652012825012</v>
+        <v>2.4065203666687</v>
       </c>
       <c r="H148" t="n">
         <v>42899</v>
@@ -4835,7 +4835,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G154" t="n">
-        <v>2.48478126525879</v>
+        <v>2.48478102684021</v>
       </c>
       <c r="H154" t="n">
         <v>33850</v>
@@ -4893,7 +4893,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G156" t="n">
-        <v>2.49456381797791</v>
+        <v>2.49456357955933</v>
       </c>
       <c r="H156" t="n">
         <v>10595</v>
@@ -4922,7 +4922,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G157" t="n">
-        <v>2.49456381797791</v>
+        <v>2.49456357955933</v>
       </c>
       <c r="H157" t="n">
         <v>21750</v>
@@ -4980,7 +4980,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G159" t="n">
-        <v>2.41630291938782</v>
+        <v>2.4163031578064</v>
       </c>
       <c r="H159" t="n">
         <v>12350</v>
@@ -5125,7 +5125,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G164" t="n">
-        <v>2.81738996505737</v>
+        <v>2.81738972663879</v>
       </c>
       <c r="H164" t="n">
         <v>432229</v>
@@ -5154,7 +5154,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G165" t="n">
-        <v>2.81738996505737</v>
+        <v>2.81738972663879</v>
       </c>
       <c r="H165" t="n">
         <v>148290</v>
@@ -5183,7 +5183,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G166" t="n">
-        <v>2.92499852180481</v>
+        <v>2.92499828338623</v>
       </c>
       <c r="H166" t="n">
         <v>225121</v>
@@ -5212,7 +5212,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G167" t="n">
-        <v>2.92499852180481</v>
+        <v>2.92499828338623</v>
       </c>
       <c r="H167" t="n">
         <v>82576</v>
@@ -5270,7 +5270,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G169" t="n">
-        <v>2.92499852180481</v>
+        <v>2.92499828338623</v>
       </c>
       <c r="H169" t="n">
         <v>43188</v>
@@ -5299,7 +5299,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G170" t="n">
-        <v>2.92499852180481</v>
+        <v>2.92499828338623</v>
       </c>
       <c r="H170" t="n">
         <v>21615</v>
@@ -5328,7 +5328,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G171" t="n">
-        <v>2.83695507049561</v>
+        <v>2.83695483207703</v>
       </c>
       <c r="H171" t="n">
         <v>69207</v>
@@ -5357,7 +5357,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G172" t="n">
-        <v>2.74891138076782</v>
+        <v>2.7489116191864</v>
       </c>
       <c r="H172" t="n">
         <v>92414</v>
@@ -5415,7 +5415,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G174" t="n">
-        <v>2.73912906646729</v>
+        <v>2.73912882804871</v>
       </c>
       <c r="H174" t="n">
         <v>33049</v>
@@ -5589,7 +5589,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G180" t="n">
-        <v>2.67065048217773</v>
+        <v>2.67065072059631</v>
       </c>
       <c r="H180" t="n">
         <v>5950</v>
@@ -5850,7 +5850,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G189" t="n">
-        <v>2.74891138076782</v>
+        <v>2.7489116191864</v>
       </c>
       <c r="H189" t="n">
         <v>35710</v>
@@ -5879,7 +5879,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G190" t="n">
-        <v>2.51412916183472</v>
+        <v>2.51412868499756</v>
       </c>
       <c r="H190" t="n">
         <v>117768</v>
@@ -5908,7 +5908,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G191" t="n">
-        <v>2.68043327331543</v>
+        <v>2.68043303489685</v>
       </c>
       <c r="H191" t="n">
         <v>61763</v>
@@ -5966,7 +5966,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G193" t="n">
-        <v>2.69999861717224</v>
+        <v>2.69999814033508</v>
       </c>
       <c r="H193" t="n">
         <v>8525</v>
@@ -5995,7 +5995,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G194" t="n">
-        <v>2.64130282402039</v>
+        <v>2.64130306243896</v>
       </c>
       <c r="H194" t="n">
         <v>13810</v>
@@ -6024,7 +6024,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G195" t="n">
-        <v>2.63152003288269</v>
+        <v>2.63152027130127</v>
       </c>
       <c r="H195" t="n">
         <v>5445</v>
@@ -6198,7 +6198,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G201" t="n">
-        <v>2.54347658157349</v>
+        <v>2.54347681999207</v>
       </c>
       <c r="H201" t="n">
         <v>32309</v>
@@ -6285,7 +6285,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G204" t="n">
-        <v>2.64130282402039</v>
+        <v>2.64130306243896</v>
       </c>
       <c r="H204" t="n">
         <v>60539</v>
@@ -6343,7 +6343,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G206" t="n">
-        <v>2.73912906646729</v>
+        <v>2.73912882804871</v>
       </c>
       <c r="H206" t="n">
         <v>36708</v>
@@ -6372,7 +6372,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G207" t="n">
-        <v>2.69999861717224</v>
+        <v>2.69999814033508</v>
       </c>
       <c r="H207" t="n">
         <v>49435</v>
@@ -6430,7 +6430,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G209" t="n">
-        <v>2.67065048217773</v>
+        <v>2.67065072059631</v>
       </c>
       <c r="H209" t="n">
         <v>30620</v>
@@ -6517,7 +6517,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G212" t="n">
-        <v>2.67065048217773</v>
+        <v>2.67065072059631</v>
       </c>
       <c r="H212" t="n">
         <v>9213</v>
@@ -6604,7 +6604,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G215" t="n">
-        <v>2.68043327331543</v>
+        <v>2.68043303489685</v>
       </c>
       <c r="H215" t="n">
         <v>17119</v>
@@ -6662,7 +6662,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G217" t="n">
-        <v>2.64130282402039</v>
+        <v>2.64130306243896</v>
       </c>
       <c r="H217" t="n">
         <v>19788</v>
@@ -6749,7 +6749,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G220" t="n">
-        <v>2.63691449165344</v>
+        <v>2.63691425323486</v>
       </c>
       <c r="H220" t="n">
         <v>54300</v>
@@ -6778,7 +6778,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G221" t="n">
-        <v>2.64675331115723</v>
+        <v>2.64675354957581</v>
       </c>
       <c r="H221" t="n">
         <v>42202</v>
@@ -6807,7 +6807,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G222" t="n">
-        <v>2.6270751953125</v>
+        <v>2.62707495689392</v>
       </c>
       <c r="H222" t="n">
         <v>18794</v>
@@ -6952,7 +6952,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G227" t="n">
-        <v>2.51884341239929</v>
+        <v>2.51884317398071</v>
       </c>
       <c r="H227" t="n">
         <v>30812</v>
@@ -6981,7 +6981,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G228" t="n">
-        <v>2.49916505813599</v>
+        <v>2.49916481971741</v>
       </c>
       <c r="H228" t="n">
         <v>48757</v>
@@ -7010,7 +7010,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G229" t="n">
-        <v>2.52868270874023</v>
+        <v>2.52868247032166</v>
       </c>
       <c r="H229" t="n">
         <v>15710</v>
@@ -7097,7 +7097,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G232" t="n">
-        <v>2.43029022216797</v>
+        <v>2.43029046058655</v>
       </c>
       <c r="H232" t="n">
         <v>31988</v>
@@ -7155,7 +7155,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G234" t="n">
-        <v>2.51884341239929</v>
+        <v>2.51884317398071</v>
       </c>
       <c r="H234" t="n">
         <v>39902</v>
@@ -7271,7 +7271,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G238" t="n">
-        <v>2.5582001209259</v>
+        <v>2.55820035934448</v>
       </c>
       <c r="H238" t="n">
         <v>26987</v>
@@ -7329,7 +7329,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G240" t="n">
-        <v>2.6270751953125</v>
+        <v>2.62707495689392</v>
       </c>
       <c r="H240" t="n">
         <v>3780</v>
@@ -7445,7 +7445,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G244" t="n">
-        <v>2.49916505813599</v>
+        <v>2.49916481971741</v>
       </c>
       <c r="H244" t="n">
         <v>24170</v>
@@ -7503,7 +7503,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G246" t="n">
-        <v>2.48932576179504</v>
+        <v>2.48932552337646</v>
       </c>
       <c r="H246" t="n">
         <v>1994</v>
@@ -7590,7 +7590,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G249" t="n">
-        <v>2.43029022216797</v>
+        <v>2.43029046058655</v>
       </c>
       <c r="H249" t="n">
         <v>5858</v>
@@ -7677,7 +7677,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G252" t="n">
-        <v>2.48932576179504</v>
+        <v>2.48932552337646</v>
       </c>
       <c r="H252" t="n">
         <v>810</v>
@@ -7793,7 +7793,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G256" t="n">
-        <v>2.42045092582703</v>
+        <v>2.42045116424561</v>
       </c>
       <c r="H256" t="n">
         <v>9824</v>
@@ -7822,7 +7822,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G257" t="n">
-        <v>2.42045092582703</v>
+        <v>2.42045116424561</v>
       </c>
       <c r="H257" t="n">
         <v>12307</v>
@@ -7880,7 +7880,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G259" t="n">
-        <v>2.48932576179504</v>
+        <v>2.48932552337646</v>
       </c>
       <c r="H259" t="n">
         <v>7500</v>
@@ -7909,7 +7909,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G260" t="n">
-        <v>2.48932576179504</v>
+        <v>2.48932552337646</v>
       </c>
       <c r="H260" t="n">
         <v>14171</v>
@@ -7967,7 +7967,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G262" t="n">
-        <v>2.42045092582703</v>
+        <v>2.42045116424561</v>
       </c>
       <c r="H262" t="n">
         <v>6545</v>
@@ -8025,7 +8025,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G264" t="n">
-        <v>2.43029022216797</v>
+        <v>2.43029046058655</v>
       </c>
       <c r="H264" t="n">
         <v>7020</v>
@@ -8141,7 +8141,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G268" t="n">
-        <v>2.43029022216797</v>
+        <v>2.43029046058655</v>
       </c>
       <c r="H268" t="n">
         <v>6909</v>
@@ -8170,7 +8170,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G269" t="n">
-        <v>2.42045092582703</v>
+        <v>2.42045116424561</v>
       </c>
       <c r="H269" t="n">
         <v>398</v>
@@ -8257,7 +8257,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G272" t="n">
-        <v>2.27286267280579</v>
+        <v>2.27286243438721</v>
       </c>
       <c r="H272" t="n">
         <v>19540</v>
@@ -8315,7 +8315,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G274" t="n">
-        <v>2.41061210632324</v>
+        <v>2.41061186790466</v>
       </c>
       <c r="H274" t="n">
         <v>2455</v>
@@ -8373,7 +8373,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G276" t="n">
-        <v>2.42045092582703</v>
+        <v>2.42045116424561</v>
       </c>
       <c r="H276" t="n">
         <v>4035</v>
@@ -8489,7 +8489,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G280" t="n">
-        <v>2.41061210632324</v>
+        <v>2.41061186790466</v>
       </c>
       <c r="H280" t="n">
         <v>2500</v>
@@ -8518,7 +8518,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G281" t="n">
-        <v>2.41061210632324</v>
+        <v>2.41061186790466</v>
       </c>
       <c r="H281" t="n">
         <v>3607</v>
@@ -8547,7 +8547,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G282" t="n">
-        <v>2.41061210632324</v>
+        <v>2.41061186790466</v>
       </c>
       <c r="H282" t="n">
         <v>3021</v>
@@ -8576,7 +8576,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G283" t="n">
-        <v>2.35157656669617</v>
+        <v>2.35157680511475</v>
       </c>
       <c r="H283" t="n">
         <v>3780</v>
@@ -8605,7 +8605,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G284" t="n">
-        <v>2.42045092582703</v>
+        <v>2.42045116424561</v>
       </c>
       <c r="H284" t="n">
         <v>7881</v>
@@ -8634,7 +8634,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G285" t="n">
-        <v>2.52868270874023</v>
+        <v>2.52868247032166</v>
       </c>
       <c r="H285" t="n">
         <v>42819</v>
@@ -8924,7 +8924,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G295" t="n">
-        <v>2.30238032341003</v>
+        <v>2.30238008499146</v>
       </c>
       <c r="H295" t="n">
         <v>44626</v>
@@ -9040,7 +9040,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G299" t="n">
-        <v>2.27286267280579</v>
+        <v>2.27286243438721</v>
       </c>
       <c r="H299" t="n">
         <v>50689</v>
@@ -9069,7 +9069,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G300" t="n">
-        <v>2.20398783683777</v>
+        <v>2.20398807525635</v>
       </c>
       <c r="H300" t="n">
         <v>34470</v>
@@ -9185,7 +9185,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G304" t="n">
-        <v>2.27286267280579</v>
+        <v>2.27286243438721</v>
       </c>
       <c r="H304" t="n">
         <v>15470</v>
@@ -9243,7 +9243,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G306" t="n">
-        <v>2.30238032341003</v>
+        <v>2.30238008499146</v>
       </c>
       <c r="H306" t="n">
         <v>1100</v>
@@ -9417,7 +9417,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G312" t="n">
-        <v>2.35157656669617</v>
+        <v>2.35157680511475</v>
       </c>
       <c r="H312" t="n">
         <v>25055</v>
@@ -9446,7 +9446,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G313" t="n">
-        <v>2.41061210632324</v>
+        <v>2.41061186790466</v>
       </c>
       <c r="H313" t="n">
         <v>37964</v>
@@ -9678,7 +9678,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G321" t="n">
-        <v>2.27286267280579</v>
+        <v>2.27286243438721</v>
       </c>
       <c r="H321" t="n">
         <v>3425</v>
@@ -9707,7 +9707,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G322" t="n">
-        <v>2.28270196914673</v>
+        <v>2.28270173072815</v>
       </c>
       <c r="H322" t="n">
         <v>16706</v>
@@ -9823,7 +9823,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G326" t="n">
-        <v>2.35157656669617</v>
+        <v>2.35157680511475</v>
       </c>
       <c r="H326" t="n">
         <v>2807</v>
@@ -9910,7 +9910,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G329" t="n">
-        <v>2.28270196914673</v>
+        <v>2.28270173072815</v>
       </c>
       <c r="H329" t="n">
         <v>4326</v>
@@ -9939,7 +9939,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G330" t="n">
-        <v>2.30238032341003</v>
+        <v>2.30238008499146</v>
       </c>
       <c r="H330" t="n">
         <v>2424</v>
@@ -9997,7 +9997,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G332" t="n">
-        <v>2.30238032341003</v>
+        <v>2.30238008499146</v>
       </c>
       <c r="H332" t="n">
         <v>1205</v>
@@ -10055,7 +10055,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G334" t="n">
-        <v>2.20398783683777</v>
+        <v>2.20398807525635</v>
       </c>
       <c r="H334" t="n">
         <v>12548</v>
@@ -10142,7 +10142,7 @@
         <v>2.25</v>
       </c>
       <c r="G337" t="n">
-        <v>2.21382713317871</v>
+        <v>2.21382737159729</v>
       </c>
       <c r="H337" t="n">
         <v>4451</v>
@@ -10316,7 +10316,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G343" t="n">
-        <v>2.41061210632324</v>
+        <v>2.41061186790466</v>
       </c>
       <c r="H343" t="n">
         <v>157345</v>
@@ -10345,7 +10345,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G344" t="n">
-        <v>2.41061210632324</v>
+        <v>2.41061186790466</v>
       </c>
       <c r="H344" t="n">
         <v>177569</v>
@@ -10374,7 +10374,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G345" t="n">
-        <v>2.28270196914673</v>
+        <v>2.28270173072815</v>
       </c>
       <c r="H345" t="n">
         <v>36620</v>
@@ -10490,7 +10490,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G349" t="n">
-        <v>2.35157656669617</v>
+        <v>2.35157680511475</v>
       </c>
       <c r="H349" t="n">
         <v>12100</v>
@@ -10548,7 +10548,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G351" t="n">
-        <v>2.28270196914673</v>
+        <v>2.28270173072815</v>
       </c>
       <c r="H351" t="n">
         <v>6350</v>
@@ -10606,7 +10606,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G353" t="n">
-        <v>2.28270196914673</v>
+        <v>2.28270173072815</v>
       </c>
       <c r="H353" t="n">
         <v>6000</v>
@@ -10635,7 +10635,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G354" t="n">
-        <v>2.28270196914673</v>
+        <v>2.28270173072815</v>
       </c>
       <c r="H354" t="n">
         <v>4900</v>
@@ -10664,7 +10664,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G355" t="n">
-        <v>2.27286267280579</v>
+        <v>2.27286243438721</v>
       </c>
       <c r="H355" t="n">
         <v>5466</v>
@@ -10693,7 +10693,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G356" t="n">
-        <v>2.28270196914673</v>
+        <v>2.28270173072815</v>
       </c>
       <c r="H356" t="n">
         <v>4255</v>
@@ -10751,7 +10751,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G358" t="n">
-        <v>2.28270196914673</v>
+        <v>2.28270173072815</v>
       </c>
       <c r="H358" t="n">
         <v>9650</v>
@@ -10780,7 +10780,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G359" t="n">
-        <v>2.27286267280579</v>
+        <v>2.27286243438721</v>
       </c>
       <c r="H359" t="n">
         <v>10142</v>
@@ -10809,7 +10809,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G360" t="n">
-        <v>2.28270196914673</v>
+        <v>2.28270173072815</v>
       </c>
       <c r="H360" t="n">
         <v>6650</v>
@@ -10838,7 +10838,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G361" t="n">
-        <v>2.30238032341003</v>
+        <v>2.30238008499146</v>
       </c>
       <c r="H361" t="n">
         <v>1405</v>
@@ -10867,7 +10867,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G362" t="n">
-        <v>2.30238032341003</v>
+        <v>2.30238008499146</v>
       </c>
       <c r="H362" t="n">
         <v>136082</v>
@@ -10896,7 +10896,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G363" t="n">
-        <v>2.30238032341003</v>
+        <v>2.30238008499146</v>
       </c>
       <c r="H363" t="n">
         <v>0</v>
@@ -10954,7 +10954,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G365" t="n">
-        <v>2.41061210632324</v>
+        <v>2.41061186790466</v>
       </c>
       <c r="H365" t="n">
         <v>46145</v>
@@ -11070,7 +11070,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G369" t="n">
-        <v>2.5385217666626</v>
+        <v>2.53852200508118</v>
       </c>
       <c r="H369" t="n">
         <v>58285</v>
@@ -11157,7 +11157,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G372" t="n">
-        <v>2.48932576179504</v>
+        <v>2.48932552337646</v>
       </c>
       <c r="H372" t="n">
         <v>30239</v>
@@ -11360,7 +11360,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G379" t="n">
-        <v>2.35157656669617</v>
+        <v>2.35157680511475</v>
       </c>
       <c r="H379" t="n">
         <v>1201</v>
@@ -11534,7 +11534,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G385" t="n">
-        <v>2.43029022216797</v>
+        <v>2.43029046058655</v>
       </c>
       <c r="H385" t="n">
         <v>25280</v>
@@ -11592,7 +11592,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G387" t="n">
-        <v>2.43029022216797</v>
+        <v>2.43029046058655</v>
       </c>
       <c r="H387" t="n">
         <v>13258</v>
@@ -11766,7 +11766,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G393" t="n">
-        <v>2.35157656669617</v>
+        <v>2.35157680511475</v>
       </c>
       <c r="H393" t="n">
         <v>1601</v>
@@ -12172,7 +12172,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G407" t="n">
-        <v>2.42045092582703</v>
+        <v>2.42045116424561</v>
       </c>
       <c r="H407" t="n">
         <v>11611</v>
@@ -12288,7 +12288,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G411" t="n">
-        <v>2.48932576179504</v>
+        <v>2.48932552337646</v>
       </c>
       <c r="H411" t="n">
         <v>11281</v>
@@ -12317,7 +12317,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G412" t="n">
-        <v>2.48932576179504</v>
+        <v>2.48932552337646</v>
       </c>
       <c r="H412" t="n">
         <v>951</v>
@@ -12346,7 +12346,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G413" t="n">
-        <v>2.42045092582703</v>
+        <v>2.42045116424561</v>
       </c>
       <c r="H413" t="n">
         <v>180</v>
@@ -12578,7 +12578,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G421" t="n">
-        <v>2.49916505813599</v>
+        <v>2.49916481971741</v>
       </c>
       <c r="H421" t="n">
         <v>16752</v>
@@ -12665,7 +12665,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G424" t="n">
-        <v>2.49916505813599</v>
+        <v>2.49916481971741</v>
       </c>
       <c r="H424" t="n">
         <v>35639</v>
@@ -12752,7 +12752,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G427" t="n">
-        <v>2.5582001209259</v>
+        <v>2.55820035934448</v>
       </c>
       <c r="H427" t="n">
         <v>559114</v>
@@ -12781,7 +12781,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G428" t="n">
-        <v>2.52868270874023</v>
+        <v>2.52868247032166</v>
       </c>
       <c r="H428" t="n">
         <v>29512</v>
@@ -12897,7 +12897,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G432" t="n">
-        <v>2.51884341239929</v>
+        <v>2.51884317398071</v>
       </c>
       <c r="H432" t="n">
         <v>60938</v>
@@ -12955,7 +12955,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G434" t="n">
-        <v>2.5582001209259</v>
+        <v>2.55820035934448</v>
       </c>
       <c r="H434" t="n">
         <v>47155</v>
@@ -12984,7 +12984,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G435" t="n">
-        <v>2.52868270874023</v>
+        <v>2.52868247032166</v>
       </c>
       <c r="H435" t="n">
         <v>20543</v>
@@ -13042,7 +13042,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G437" t="n">
-        <v>2.52868270874023</v>
+        <v>2.52868247032166</v>
       </c>
       <c r="H437" t="n">
         <v>12222</v>
@@ -13071,7 +13071,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G438" t="n">
-        <v>2.51884341239929</v>
+        <v>2.51884317398071</v>
       </c>
       <c r="H438" t="n">
         <v>18341</v>
@@ -13100,7 +13100,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G439" t="n">
-        <v>2.52868270874023</v>
+        <v>2.52868247032166</v>
       </c>
       <c r="H439" t="n">
         <v>19433</v>
@@ -13129,7 +13129,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G440" t="n">
-        <v>2.43029022216797</v>
+        <v>2.43029046058655</v>
       </c>
       <c r="H440" t="n">
         <v>23395</v>
@@ -13216,7 +13216,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G443" t="n">
-        <v>2.41061210632324</v>
+        <v>2.41061186790466</v>
       </c>
       <c r="H443" t="n">
         <v>15137</v>
@@ -13274,7 +13274,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G445" t="n">
-        <v>2.49916505813599</v>
+        <v>2.49916481971741</v>
       </c>
       <c r="H445" t="n">
         <v>52693</v>
@@ -13332,7 +13332,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G447" t="n">
-        <v>2.28270196914673</v>
+        <v>2.28270173072815</v>
       </c>
       <c r="H447" t="n">
         <v>23165</v>
@@ -13361,7 +13361,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G448" t="n">
-        <v>2.28270196914673</v>
+        <v>2.28270173072815</v>
       </c>
       <c r="H448" t="n">
         <v>40210</v>
@@ -13477,7 +13477,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G452" t="n">
-        <v>2.43029022216797</v>
+        <v>2.43029046058655</v>
       </c>
       <c r="H452" t="n">
         <v>37050</v>
@@ -13622,7 +13622,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G457" t="n">
-        <v>2.49916505813599</v>
+        <v>2.49916481971741</v>
       </c>
       <c r="H457" t="n">
         <v>35738</v>
@@ -13651,7 +13651,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G458" t="n">
-        <v>2.51884341239929</v>
+        <v>2.51884317398071</v>
       </c>
       <c r="H458" t="n">
         <v>18389</v>
@@ -13680,7 +13680,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G459" t="n">
-        <v>2.51884341239929</v>
+        <v>2.51884317398071</v>
       </c>
       <c r="H459" t="n">
         <v>0</v>
@@ -13709,7 +13709,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G460" t="n">
-        <v>2.43029022216797</v>
+        <v>2.43029046058655</v>
       </c>
       <c r="H460" t="n">
         <v>29119</v>
@@ -13825,7 +13825,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G464" t="n">
-        <v>2.42045092582703</v>
+        <v>2.42045116424561</v>
       </c>
       <c r="H464" t="n">
         <v>2155</v>
@@ -13854,7 +13854,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G465" t="n">
-        <v>2.41061210632324</v>
+        <v>2.41061186790466</v>
       </c>
       <c r="H465" t="n">
         <v>3505</v>
@@ -13941,7 +13941,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G468" t="n">
-        <v>2.42045092582703</v>
+        <v>2.42045116424561</v>
       </c>
       <c r="H468" t="n">
         <v>5886</v>
@@ -13970,7 +13970,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G469" t="n">
-        <v>2.42045092582703</v>
+        <v>2.42045116424561</v>
       </c>
       <c r="H469" t="n">
         <v>0</v>
@@ -14028,7 +14028,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G471" t="n">
-        <v>2.43029022216797</v>
+        <v>2.43029046058655</v>
       </c>
       <c r="H471" t="n">
         <v>8504</v>
@@ -14144,7 +14144,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G475" t="n">
-        <v>2.42045092582703</v>
+        <v>2.42045116424561</v>
       </c>
       <c r="H475" t="n">
         <v>5971</v>
@@ -14260,7 +14260,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G479" t="n">
-        <v>2.43029022216797</v>
+        <v>2.43029046058655</v>
       </c>
       <c r="H479" t="n">
         <v>7842</v>
@@ -14318,7 +14318,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G481" t="n">
-        <v>2.42045092582703</v>
+        <v>2.42045116424561</v>
       </c>
       <c r="H481" t="n">
         <v>3675</v>
@@ -14376,7 +14376,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G483" t="n">
-        <v>2.42045092582703</v>
+        <v>2.42045116424561</v>
       </c>
       <c r="H483" t="n">
         <v>6429</v>
@@ -14492,7 +14492,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G487" t="n">
-        <v>2.41061210632324</v>
+        <v>2.41061186790466</v>
       </c>
       <c r="H487" t="n">
         <v>1829</v>
@@ -14521,7 +14521,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G488" t="n">
-        <v>2.41061210632324</v>
+        <v>2.41061186790466</v>
       </c>
       <c r="H488" t="n">
         <v>0</v>
@@ -14579,7 +14579,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G490" t="n">
-        <v>2.41061210632324</v>
+        <v>2.41061186790466</v>
       </c>
       <c r="H490" t="n">
         <v>18612</v>
@@ -14666,7 +14666,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G493" t="n">
-        <v>2.41061210632324</v>
+        <v>2.41061186790466</v>
       </c>
       <c r="H493" t="n">
         <v>1</v>
@@ -14695,7 +14695,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G494" t="n">
-        <v>2.41061210632324</v>
+        <v>2.41061186790466</v>
       </c>
       <c r="H494" t="n">
         <v>0</v>
@@ -14724,7 +14724,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G495" t="n">
-        <v>2.41061210632324</v>
+        <v>2.41061186790466</v>
       </c>
       <c r="H495" t="n">
         <v>20619</v>
@@ -14869,7 +14869,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G500" t="n">
-        <v>2.48932576179504</v>
+        <v>2.48932552337646</v>
       </c>
       <c r="H500" t="n">
         <v>22406</v>
@@ -14898,7 +14898,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G501" t="n">
-        <v>2.41061210632324</v>
+        <v>2.41061186790466</v>
       </c>
       <c r="H501" t="n">
         <v>232</v>
@@ -14985,7 +14985,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G504" t="n">
-        <v>2.42045092582703</v>
+        <v>2.42045116424561</v>
       </c>
       <c r="H504" t="n">
         <v>3174</v>
@@ -15014,7 +15014,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G505" t="n">
-        <v>2.42045092582703</v>
+        <v>2.42045116424561</v>
       </c>
       <c r="H505" t="n">
         <v>0</v>
@@ -15072,7 +15072,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G507" t="n">
-        <v>2.42045092582703</v>
+        <v>2.42045116424561</v>
       </c>
       <c r="H507" t="n">
         <v>4</v>
@@ -15130,7 +15130,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G509" t="n">
-        <v>2.43029022216797</v>
+        <v>2.43029046058655</v>
       </c>
       <c r="H509" t="n">
         <v>6606</v>
@@ -15159,7 +15159,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G510" t="n">
-        <v>2.43029022216797</v>
+        <v>2.43029046058655</v>
       </c>
       <c r="H510" t="n">
         <v>4444</v>
@@ -15217,7 +15217,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G512" t="n">
-        <v>2.49916505813599</v>
+        <v>2.49916481971741</v>
       </c>
       <c r="H512" t="n">
         <v>18429</v>
@@ -15304,7 +15304,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G515" t="n">
-        <v>2.48932576179504</v>
+        <v>2.48932552337646</v>
       </c>
       <c r="H515" t="n">
         <v>421</v>
@@ -15536,7 +15536,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G523" t="n">
-        <v>2.5582001209259</v>
+        <v>2.55820035934448</v>
       </c>
       <c r="H523" t="n">
         <v>28775</v>
@@ -15681,7 +15681,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G528" t="n">
-        <v>2.5582001209259</v>
+        <v>2.55820035934448</v>
       </c>
       <c r="H528" t="n">
         <v>6832</v>
@@ -15710,7 +15710,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G529" t="n">
-        <v>2.52868270874023</v>
+        <v>2.52868247032166</v>
       </c>
       <c r="H529" t="n">
         <v>7700</v>
@@ -15739,7 +15739,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G530" t="n">
-        <v>2.5582001209259</v>
+        <v>2.55820035934448</v>
       </c>
       <c r="H530" t="n">
         <v>6304</v>
@@ -15826,7 +15826,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G533" t="n">
-        <v>2.63691449165344</v>
+        <v>2.63691425323486</v>
       </c>
       <c r="H533" t="n">
         <v>19150</v>
@@ -15884,7 +15884,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G535" t="n">
-        <v>2.5385217666626</v>
+        <v>2.53852200508118</v>
       </c>
       <c r="H535" t="n">
         <v>7600</v>
@@ -15913,7 +15913,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G536" t="n">
-        <v>2.5582001209259</v>
+        <v>2.55820035934448</v>
       </c>
       <c r="H536" t="n">
         <v>1850</v>
@@ -15971,7 +15971,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G538" t="n">
-        <v>2.5582001209259</v>
+        <v>2.55820035934448</v>
       </c>
       <c r="H538" t="n">
         <v>2300</v>
@@ -16000,7 +16000,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G539" t="n">
-        <v>2.5582001209259</v>
+        <v>2.55820035934448</v>
       </c>
       <c r="H539" t="n">
         <v>3806</v>
@@ -16029,7 +16029,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G540" t="n">
-        <v>2.5385217666626</v>
+        <v>2.53852200508118</v>
       </c>
       <c r="H540" t="n">
         <v>6800</v>
@@ -16058,7 +16058,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G541" t="n">
-        <v>2.5582001209259</v>
+        <v>2.55820035934448</v>
       </c>
       <c r="H541" t="n">
         <v>8509</v>
@@ -16087,7 +16087,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G542" t="n">
-        <v>2.5582001209259</v>
+        <v>2.55820035934448</v>
       </c>
       <c r="H542" t="n">
         <v>6554</v>
@@ -16145,7 +16145,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G544" t="n">
-        <v>2.64675331115723</v>
+        <v>2.64675354957581</v>
       </c>
       <c r="H544" t="n">
         <v>29045</v>
@@ -16174,7 +16174,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G545" t="n">
-        <v>2.64675331115723</v>
+        <v>2.64675354957581</v>
       </c>
       <c r="H545" t="n">
         <v>24168</v>
@@ -16232,7 +16232,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G547" t="n">
-        <v>2.35157656669617</v>
+        <v>2.35157680511475</v>
       </c>
       <c r="H547" t="n">
         <v>106601</v>
@@ -16319,7 +16319,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G550" t="n">
-        <v>2.30238032341003</v>
+        <v>2.30238008499146</v>
       </c>
       <c r="H550" t="n">
         <v>10856</v>
@@ -16406,7 +16406,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G553" t="n">
-        <v>2.28270196914673</v>
+        <v>2.28270173072815</v>
       </c>
       <c r="H553" t="n">
         <v>7360</v>
@@ -16522,7 +16522,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G557" t="n">
-        <v>2.27286267280579</v>
+        <v>2.27286243438721</v>
       </c>
       <c r="H557" t="n">
         <v>3150</v>
@@ -16551,7 +16551,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G558" t="n">
-        <v>2.27286267280579</v>
+        <v>2.27286243438721</v>
       </c>
       <c r="H558" t="n">
         <v>0</v>
@@ -16580,7 +16580,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G559" t="n">
-        <v>2.27286267280579</v>
+        <v>2.27286243438721</v>
       </c>
       <c r="H559" t="n">
         <v>4065</v>
@@ -16609,7 +16609,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G560" t="n">
-        <v>2.28270196914673</v>
+        <v>2.28270173072815</v>
       </c>
       <c r="H560" t="n">
         <v>890</v>
@@ -16667,7 +16667,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G562" t="n">
-        <v>2.24334478378296</v>
+        <v>2.24334502220154</v>
       </c>
       <c r="H562" t="n">
         <v>11905</v>
@@ -16696,7 +16696,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G563" t="n">
-        <v>2.20398783683777</v>
+        <v>2.20398807525635</v>
       </c>
       <c r="H563" t="n">
         <v>34790</v>
@@ -16754,7 +16754,7 @@
         <v>2.25</v>
       </c>
       <c r="G565" t="n">
-        <v>2.21382713317871</v>
+        <v>2.21382737159729</v>
       </c>
       <c r="H565" t="n">
         <v>1201</v>
@@ -16783,7 +16783,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G566" t="n">
-        <v>2.27286267280579</v>
+        <v>2.27286243438721</v>
       </c>
       <c r="H566" t="n">
         <v>500</v>
@@ -16899,7 +16899,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G570" t="n">
-        <v>2.24334478378296</v>
+        <v>2.24334502220154</v>
       </c>
       <c r="H570" t="n">
         <v>18090</v>
@@ -16986,7 +16986,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G573" t="n">
-        <v>2.28270196914673</v>
+        <v>2.28270173072815</v>
       </c>
       <c r="H573" t="n">
         <v>2415</v>
@@ -17015,7 +17015,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G574" t="n">
-        <v>2.20398783683777</v>
+        <v>2.20398807525635</v>
       </c>
       <c r="H574" t="n">
         <v>24592</v>
@@ -17131,7 +17131,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G578" t="n">
-        <v>2.28270196914673</v>
+        <v>2.28270173072815</v>
       </c>
       <c r="H578" t="n">
         <v>2017</v>
@@ -17189,7 +17189,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G580" t="n">
-        <v>2.27286267280579</v>
+        <v>2.27286243438721</v>
       </c>
       <c r="H580" t="n">
         <v>2648</v>
@@ -17218,7 +17218,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G581" t="n">
-        <v>2.28270196914673</v>
+        <v>2.28270173072815</v>
       </c>
       <c r="H581" t="n">
         <v>1455</v>
@@ -17276,7 +17276,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G583" t="n">
-        <v>2.30238032341003</v>
+        <v>2.30238008499146</v>
       </c>
       <c r="H583" t="n">
         <v>4608</v>
@@ -17653,7 +17653,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G596" t="n">
-        <v>2.28270196914673</v>
+        <v>2.28270173072815</v>
       </c>
       <c r="H596" t="n">
         <v>3802</v>
@@ -17740,7 +17740,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G599" t="n">
-        <v>2.30238032341003</v>
+        <v>2.30238008499146</v>
       </c>
       <c r="H599" t="n">
         <v>2949</v>
@@ -17798,7 +17798,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G601" t="n">
-        <v>2.24334478378296</v>
+        <v>2.24334502220154</v>
       </c>
       <c r="H601" t="n">
         <v>17283</v>
@@ -17827,7 +17827,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G602" t="n">
-        <v>2.27286267280579</v>
+        <v>2.27286243438721</v>
       </c>
       <c r="H602" t="n">
         <v>2094</v>
@@ -17856,7 +17856,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G603" t="n">
-        <v>2.27286267280579</v>
+        <v>2.27286243438721</v>
       </c>
       <c r="H603" t="n">
         <v>4262</v>
@@ -17914,7 +17914,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G605" t="n">
-        <v>2.30238032341003</v>
+        <v>2.30238008499146</v>
       </c>
       <c r="H605" t="n">
         <v>3421</v>
@@ -17943,7 +17943,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G606" t="n">
-        <v>2.30238032341003</v>
+        <v>2.30238008499146</v>
       </c>
       <c r="H606" t="n">
         <v>1394</v>
@@ -17972,7 +17972,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G607" t="n">
-        <v>2.30238032341003</v>
+        <v>2.30238008499146</v>
       </c>
       <c r="H607" t="n">
         <v>1488</v>
@@ -18001,7 +18001,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G608" t="n">
-        <v>2.30238032341003</v>
+        <v>2.30238008499146</v>
       </c>
       <c r="H608" t="n">
         <v>1944</v>
@@ -18030,7 +18030,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G609" t="n">
-        <v>2.30238032341003</v>
+        <v>2.30238008499146</v>
       </c>
       <c r="H609" t="n">
         <v>1543</v>
@@ -18088,7 +18088,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G611" t="n">
-        <v>2.30238032341003</v>
+        <v>2.30238008499146</v>
       </c>
       <c r="H611" t="n">
         <v>1209</v>
@@ -18146,7 +18146,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G613" t="n">
-        <v>2.27286267280579</v>
+        <v>2.27286243438721</v>
       </c>
       <c r="H613" t="n">
         <v>3339</v>
@@ -18407,7 +18407,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G622" t="n">
-        <v>2.24334478378296</v>
+        <v>2.24334502220154</v>
       </c>
       <c r="H622" t="n">
         <v>729</v>
@@ -18436,7 +18436,7 @@
         <v>2.25</v>
       </c>
       <c r="G623" t="n">
-        <v>2.21382713317871</v>
+        <v>2.21382737159729</v>
       </c>
       <c r="H623" t="n">
         <v>3507</v>
@@ -18494,7 +18494,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G625" t="n">
-        <v>2.24334478378296</v>
+        <v>2.24334502220154</v>
       </c>
       <c r="H625" t="n">
         <v>3357</v>
@@ -18610,7 +18610,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G629" t="n">
-        <v>2.24334478378296</v>
+        <v>2.24334502220154</v>
       </c>
       <c r="H629" t="n">
         <v>1003</v>
@@ -18639,7 +18639,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G630" t="n">
-        <v>2.28270196914673</v>
+        <v>2.28270173072815</v>
       </c>
       <c r="H630" t="n">
         <v>26686</v>
@@ -18668,7 +18668,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G631" t="n">
-        <v>2.28270196914673</v>
+        <v>2.28270173072815</v>
       </c>
       <c r="H631" t="n">
         <v>1654</v>
@@ -18726,7 +18726,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G633" t="n">
-        <v>2.28270196914673</v>
+        <v>2.28270173072815</v>
       </c>
       <c r="H633" t="n">
         <v>1752</v>
@@ -18755,7 +18755,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G634" t="n">
-        <v>2.28270196914673</v>
+        <v>2.28270173072815</v>
       </c>
       <c r="H634" t="n">
         <v>3413</v>
@@ -18900,7 +18900,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G639" t="n">
-        <v>2.27286267280579</v>
+        <v>2.27286243438721</v>
       </c>
       <c r="H639" t="n">
         <v>2152</v>
@@ -18929,7 +18929,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G640" t="n">
-        <v>2.28270196914673</v>
+        <v>2.28270173072815</v>
       </c>
       <c r="H640" t="n">
         <v>2342</v>
@@ -18987,7 +18987,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G642" t="n">
-        <v>2.24334478378296</v>
+        <v>2.24334502220154</v>
       </c>
       <c r="H642" t="n">
         <v>3219</v>
@@ -19074,7 +19074,7 @@
         <v>2.25</v>
       </c>
       <c r="G645" t="n">
-        <v>2.21382713317871</v>
+        <v>2.21382737159729</v>
       </c>
       <c r="H645" t="n">
         <v>5907</v>
@@ -19132,7 +19132,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G647" t="n">
-        <v>2.20398783683777</v>
+        <v>2.20398807525635</v>
       </c>
       <c r="H647" t="n">
         <v>2247</v>
@@ -19190,7 +19190,7 @@
         <v>2.25</v>
       </c>
       <c r="G649" t="n">
-        <v>2.21382713317871</v>
+        <v>2.21382737159729</v>
       </c>
       <c r="H649" t="n">
         <v>1413</v>
@@ -19306,7 +19306,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G653" t="n">
-        <v>2.13511347770691</v>
+        <v>2.13511323928833</v>
       </c>
       <c r="H653" t="n">
         <v>4940</v>
@@ -19335,7 +19335,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G654" t="n">
-        <v>2.14495277404785</v>
+        <v>2.14495253562927</v>
       </c>
       <c r="H654" t="n">
         <v>4916</v>
@@ -19480,7 +19480,7 @@
         <v>2.25</v>
       </c>
       <c r="G659" t="n">
-        <v>2.21382713317871</v>
+        <v>2.21382737159729</v>
       </c>
       <c r="H659" t="n">
         <v>8762</v>
@@ -19538,7 +19538,7 @@
         <v>2.25</v>
       </c>
       <c r="G661" t="n">
-        <v>2.21382713317871</v>
+        <v>2.21382737159729</v>
       </c>
       <c r="H661" t="n">
         <v>6280</v>
@@ -19683,7 +19683,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G666" t="n">
-        <v>2.24334478378296</v>
+        <v>2.24334502220154</v>
       </c>
       <c r="H666" t="n">
         <v>10498</v>
@@ -19799,7 +19799,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G670" t="n">
-        <v>2.20398783683777</v>
+        <v>2.20398807525635</v>
       </c>
       <c r="H670" t="n">
         <v>7844</v>
@@ -19828,7 +19828,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G671" t="n">
-        <v>2.24334478378296</v>
+        <v>2.24334502220154</v>
       </c>
       <c r="H671" t="n">
         <v>7122</v>
@@ -19857,7 +19857,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G672" t="n">
-        <v>2.24334478378296</v>
+        <v>2.24334502220154</v>
       </c>
       <c r="H672" t="n">
         <v>3472</v>
@@ -19886,7 +19886,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G673" t="n">
-        <v>2.24334478378296</v>
+        <v>2.24334502220154</v>
       </c>
       <c r="H673" t="n">
         <v>4302</v>
@@ -19973,7 +19973,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G676" t="n">
-        <v>2.20398783683777</v>
+        <v>2.20398807525635</v>
       </c>
       <c r="H676" t="n">
         <v>2219</v>
@@ -20118,7 +20118,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G681" t="n">
-        <v>2.27286267280579</v>
+        <v>2.27286243438721</v>
       </c>
       <c r="H681" t="n">
         <v>3394</v>
@@ -20234,7 +20234,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G685" t="n">
-        <v>2.35157656669617</v>
+        <v>2.35157680511475</v>
       </c>
       <c r="H685" t="n">
         <v>14060</v>
@@ -20321,7 +20321,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G688" t="n">
-        <v>2.35157656669617</v>
+        <v>2.35157680511475</v>
       </c>
       <c r="H688" t="n">
         <v>3921</v>
@@ -20756,7 +20756,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G703" t="n">
-        <v>2.30238032341003</v>
+        <v>2.30238008499146</v>
       </c>
       <c r="H703" t="n">
         <v>18619</v>
@@ -20785,7 +20785,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G704" t="n">
-        <v>2.30238032341003</v>
+        <v>2.30238008499146</v>
       </c>
       <c r="H704" t="n">
         <v>5776</v>
@@ -20814,7 +20814,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G705" t="n">
-        <v>2.30238032341003</v>
+        <v>2.30238008499146</v>
       </c>
       <c r="H705" t="n">
         <v>4067</v>
@@ -20843,7 +20843,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G706" t="n">
-        <v>2.28270196914673</v>
+        <v>2.28270173072815</v>
       </c>
       <c r="H706" t="n">
         <v>2590</v>
@@ -20872,7 +20872,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G707" t="n">
-        <v>2.24334478378296</v>
+        <v>2.24334502220154</v>
       </c>
       <c r="H707" t="n">
         <v>10831</v>
@@ -20988,7 +20988,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G711" t="n">
-        <v>2.43029022216797</v>
+        <v>2.43029046058655</v>
       </c>
       <c r="H711" t="n">
         <v>15029</v>
@@ -21017,7 +21017,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G712" t="n">
-        <v>2.43029022216797</v>
+        <v>2.43029046058655</v>
       </c>
       <c r="H712" t="n">
         <v>8791</v>
@@ -21133,7 +21133,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G716" t="n">
-        <v>2.35157656669617</v>
+        <v>2.35157680511475</v>
       </c>
       <c r="H716" t="n">
         <v>16386</v>
@@ -21162,7 +21162,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G717" t="n">
-        <v>2.43029022216797</v>
+        <v>2.43029046058655</v>
       </c>
       <c r="H717" t="n">
         <v>59441</v>
@@ -21307,7 +21307,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G722" t="n">
-        <v>2.35157656669617</v>
+        <v>2.35157680511475</v>
       </c>
       <c r="H722" t="n">
         <v>15797</v>
@@ -21365,7 +21365,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G724" t="n">
-        <v>2.35157656669617</v>
+        <v>2.35157680511475</v>
       </c>
       <c r="H724" t="n">
         <v>6782</v>
@@ -21423,7 +21423,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G726" t="n">
-        <v>2.41061210632324</v>
+        <v>2.41061186790466</v>
       </c>
       <c r="H726" t="n">
         <v>10601</v>
@@ -21452,7 +21452,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G727" t="n">
-        <v>2.43029022216797</v>
+        <v>2.43029046058655</v>
       </c>
       <c r="H727" t="n">
         <v>6641</v>
@@ -21481,7 +21481,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G728" t="n">
-        <v>2.43029022216797</v>
+        <v>2.43029046058655</v>
       </c>
       <c r="H728" t="n">
         <v>7749</v>
@@ -21597,7 +21597,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G732" t="n">
-        <v>2.41061210632324</v>
+        <v>2.41061186790466</v>
       </c>
       <c r="H732" t="n">
         <v>8506</v>
@@ -21771,7 +21771,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G738" t="n">
-        <v>2.35157656669617</v>
+        <v>2.35157680511475</v>
       </c>
       <c r="H738" t="n">
         <v>9988</v>
@@ -21887,7 +21887,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G742" t="n">
-        <v>2.49916505813599</v>
+        <v>2.49916481971741</v>
       </c>
       <c r="H742" t="n">
         <v>34943</v>
@@ -21945,7 +21945,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G744" t="n">
-        <v>2.48932576179504</v>
+        <v>2.48932552337646</v>
       </c>
       <c r="H744" t="n">
         <v>39865</v>
@@ -22003,7 +22003,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G746" t="n">
-        <v>2.48932576179504</v>
+        <v>2.48932552337646</v>
       </c>
       <c r="H746" t="n">
         <v>18877</v>
@@ -22032,7 +22032,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G747" t="n">
-        <v>2.51884341239929</v>
+        <v>2.51884317398071</v>
       </c>
       <c r="H747" t="n">
         <v>44586</v>
@@ -22061,7 +22061,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G748" t="n">
-        <v>2.52868270874023</v>
+        <v>2.52868247032166</v>
       </c>
       <c r="H748" t="n">
         <v>45070</v>
@@ -22206,7 +22206,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G753" t="n">
-        <v>2.63691449165344</v>
+        <v>2.63691425323486</v>
       </c>
       <c r="H753" t="n">
         <v>58392</v>
@@ -22264,7 +22264,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G755" t="n">
-        <v>2.77466320991516</v>
+        <v>2.77466344833374</v>
       </c>
       <c r="H755" t="n">
         <v>152514</v>
@@ -22322,7 +22322,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G757" t="n">
-        <v>2.71562814712524</v>
+        <v>2.71562790870667</v>
       </c>
       <c r="H757" t="n">
         <v>170397</v>
@@ -22380,7 +22380,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G759" t="n">
-        <v>2.77466320991516</v>
+        <v>2.77466344833374</v>
       </c>
       <c r="H759" t="n">
         <v>21143</v>
@@ -22409,7 +22409,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G760" t="n">
-        <v>2.77466320991516</v>
+        <v>2.77466344833374</v>
       </c>
       <c r="H760" t="n">
         <v>14482</v>
@@ -22438,7 +22438,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G761" t="n">
-        <v>2.77466320991516</v>
+        <v>2.77466344833374</v>
       </c>
       <c r="H761" t="n">
         <v>13481</v>
@@ -22583,7 +22583,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G766" t="n">
-        <v>2.77466320991516</v>
+        <v>2.77466344833374</v>
       </c>
       <c r="H766" t="n">
         <v>11073</v>
@@ -22641,7 +22641,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G768" t="n">
-        <v>2.77466320991516</v>
+        <v>2.77466344833374</v>
       </c>
       <c r="H768" t="n">
         <v>16757</v>
@@ -22786,7 +22786,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G773" t="n">
-        <v>3.00096559524536</v>
+        <v>3.00096583366394</v>
       </c>
       <c r="H773" t="n">
         <v>78428</v>
@@ -22873,7 +22873,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G776" t="n">
-        <v>3.00096559524536</v>
+        <v>3.00096583366394</v>
       </c>
       <c r="H776" t="n">
         <v>13843</v>
@@ -22960,7 +22960,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G779" t="n">
-        <v>3.00096559524536</v>
+        <v>3.00096583366394</v>
       </c>
       <c r="H779" t="n">
         <v>12842</v>
@@ -23018,7 +23018,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G781" t="n">
-        <v>3.00096559524536</v>
+        <v>3.00096583366394</v>
       </c>
       <c r="H781" t="n">
         <v>25556</v>
@@ -23221,7 +23221,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G788" t="n">
-        <v>2.91241264343262</v>
+        <v>2.9124128818512</v>
       </c>
       <c r="H788" t="n">
         <v>28876</v>
@@ -23279,7 +23279,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G790" t="n">
-        <v>2.84353828430176</v>
+        <v>2.84353804588318</v>
       </c>
       <c r="H790" t="n">
         <v>12028</v>
@@ -23308,7 +23308,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G791" t="n">
-        <v>2.92225193977356</v>
+        <v>2.92225217819214</v>
       </c>
       <c r="H791" t="n">
         <v>36996</v>
@@ -23366,7 +23366,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G793" t="n">
-        <v>2.92225193977356</v>
+        <v>2.92225217819214</v>
       </c>
       <c r="H793" t="n">
         <v>20612</v>
@@ -23395,7 +23395,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G794" t="n">
-        <v>2.90257358551025</v>
+        <v>2.90257334709167</v>
       </c>
       <c r="H794" t="n">
         <v>5153</v>
@@ -23511,7 +23511,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G798" t="n">
-        <v>2.91241264343262</v>
+        <v>2.9124128818512</v>
       </c>
       <c r="H798" t="n">
         <v>29046</v>
@@ -23743,7 +23743,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G806" t="n">
-        <v>3.09935808181763</v>
+        <v>3.09935832023621</v>
       </c>
       <c r="H806" t="n">
         <v>21409</v>
@@ -23801,7 +23801,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G808" t="n">
-        <v>3.13871502876282</v>
+        <v>3.1387152671814</v>
       </c>
       <c r="H808" t="n">
         <v>29053</v>
@@ -24004,7 +24004,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G815" t="n">
-        <v>3.16823291778564</v>
+        <v>3.16823267936707</v>
       </c>
       <c r="H815" t="n">
         <v>40945</v>
@@ -24207,7 +24207,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G822" t="n">
-        <v>3.32566046714783</v>
+        <v>3.32566070556641</v>
       </c>
       <c r="H822" t="n">
         <v>8250</v>
@@ -24352,7 +24352,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G827" t="n">
-        <v>3.41421365737915</v>
+        <v>3.41421341896057</v>
       </c>
       <c r="H827" t="n">
         <v>49728</v>
@@ -24381,7 +24381,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G828" t="n">
-        <v>3.42405295372009</v>
+        <v>3.42405271530151</v>
       </c>
       <c r="H828" t="n">
         <v>21052</v>
@@ -24410,7 +24410,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G829" t="n">
-        <v>3.48308801651001</v>
+        <v>3.48308825492859</v>
       </c>
       <c r="H829" t="n">
         <v>56595</v>
@@ -24468,7 +24468,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G831" t="n">
-        <v>3.57164120674133</v>
+        <v>3.57164144515991</v>
       </c>
       <c r="H831" t="n">
         <v>31184</v>
@@ -24555,7 +24555,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G834" t="n">
-        <v>4.12263870239258</v>
+        <v>4.12263822555542</v>
       </c>
       <c r="H834" t="n">
         <v>162852</v>
@@ -24584,7 +24584,7 @@
         <v>4.25</v>
       </c>
       <c r="G835" t="n">
-        <v>4.18167352676392</v>
+        <v>4.18167400360107</v>
       </c>
       <c r="H835" t="n">
         <v>105792</v>
@@ -24700,7 +24700,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G839" t="n">
-        <v>4.22103023529053</v>
+        <v>4.22103071212769</v>
       </c>
       <c r="H839" t="n">
         <v>31763</v>
@@ -24758,7 +24758,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G841" t="n">
-        <v>4.2899055480957</v>
+        <v>4.28990507125854</v>
       </c>
       <c r="H841" t="n">
         <v>33142</v>
@@ -24816,7 +24816,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G843" t="n">
-        <v>4.39813613891602</v>
+        <v>4.39813661575317</v>
       </c>
       <c r="H843" t="n">
         <v>122860</v>
@@ -24990,7 +24990,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G849" t="n">
-        <v>5.0770435333252</v>
+        <v>5.07704401016235</v>
       </c>
       <c r="H849" t="n">
         <v>125520</v>
@@ -25019,7 +25019,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G850" t="n">
-        <v>4.99833011627197</v>
+        <v>4.99832963943481</v>
       </c>
       <c r="H850" t="n">
         <v>94101</v>
@@ -25077,7 +25077,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G852" t="n">
-        <v>5.03768682479858</v>
+        <v>5.03768634796143</v>
       </c>
       <c r="H852" t="n">
         <v>39665</v>
@@ -25222,7 +25222,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G857" t="n">
-        <v>5.03768682479858</v>
+        <v>5.03768634796143</v>
       </c>
       <c r="H857" t="n">
         <v>29318</v>
@@ -25280,7 +25280,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G859" t="n">
-        <v>4.86058044433594</v>
+        <v>4.8605809211731</v>
       </c>
       <c r="H859" t="n">
         <v>18569</v>
@@ -25309,7 +25309,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G860" t="n">
-        <v>4.83106327056885</v>
+        <v>4.83106279373169</v>
       </c>
       <c r="H860" t="n">
         <v>56243</v>
@@ -25338,7 +25338,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G861" t="n">
-        <v>4.89009809494019</v>
+        <v>4.89009857177734</v>
       </c>
       <c r="H861" t="n">
         <v>26996</v>
@@ -25425,7 +25425,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G864" t="n">
-        <v>4.89009809494019</v>
+        <v>4.89009857177734</v>
       </c>
       <c r="H864" t="n">
         <v>17018</v>
@@ -25512,7 +25512,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G867" t="n">
-        <v>5.29350662231445</v>
+        <v>5.29350709915161</v>
       </c>
       <c r="H867" t="n">
         <v>54581</v>
@@ -25570,7 +25570,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G869" t="n">
-        <v>5.7067551612854</v>
+        <v>5.70675468444824</v>
       </c>
       <c r="H869" t="n">
         <v>193218</v>
@@ -25599,7 +25599,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G870" t="n">
-        <v>5.80514717102051</v>
+        <v>5.80514669418335</v>
       </c>
       <c r="H870" t="n">
         <v>93551</v>
@@ -25628,7 +25628,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G871" t="n">
-        <v>5.68707656860352</v>
+        <v>5.68707609176636</v>
       </c>
       <c r="H871" t="n">
         <v>93418</v>
@@ -25686,7 +25686,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G873" t="n">
-        <v>5.43125629425049</v>
+        <v>5.43125581741333</v>
       </c>
       <c r="H873" t="n">
         <v>19758</v>
@@ -25773,7 +25773,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G876" t="n">
-        <v>5.27382898330688</v>
+        <v>5.27382850646973</v>
       </c>
       <c r="H876" t="n">
         <v>74967</v>
@@ -25802,7 +25802,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G877" t="n">
-        <v>5.29350662231445</v>
+        <v>5.29350709915161</v>
       </c>
       <c r="H877" t="n">
         <v>29227</v>
@@ -25860,7 +25860,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G879" t="n">
-        <v>5.05736541748047</v>
+        <v>5.05736494064331</v>
       </c>
       <c r="H879" t="n">
         <v>31367</v>
@@ -25918,7 +25918,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G881" t="n">
-        <v>5.03768682479858</v>
+        <v>5.03768634796143</v>
       </c>
       <c r="H881" t="n">
         <v>10417</v>
@@ -25976,7 +25976,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G883" t="n">
-        <v>5.03768682479858</v>
+        <v>5.03768634796143</v>
       </c>
       <c r="H883" t="n">
         <v>19220</v>
@@ -26034,7 +26034,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G885" t="n">
-        <v>5.0770435333252</v>
+        <v>5.07704401016235</v>
       </c>
       <c r="H885" t="n">
         <v>8947</v>
@@ -26208,7 +26208,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G891" t="n">
-        <v>5.27382898330688</v>
+        <v>5.27382850646973</v>
       </c>
       <c r="H891" t="n">
         <v>7249</v>
@@ -26237,7 +26237,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G892" t="n">
-        <v>5.11640024185181</v>
+        <v>5.11640071868896</v>
       </c>
       <c r="H892" t="n">
         <v>12636</v>
@@ -26266,7 +26266,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G893" t="n">
-        <v>5.05736541748047</v>
+        <v>5.05736494064331</v>
       </c>
       <c r="H893" t="n">
         <v>9316</v>
@@ -26295,7 +26295,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G894" t="n">
-        <v>5.03768682479858</v>
+        <v>5.03768634796143</v>
       </c>
       <c r="H894" t="n">
         <v>6814</v>
@@ -26324,7 +26324,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G895" t="n">
-        <v>5.03768682479858</v>
+        <v>5.03768634796143</v>
       </c>
       <c r="H895" t="n">
         <v>7477</v>
@@ -26382,7 +26382,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G897" t="n">
-        <v>5.11640024185181</v>
+        <v>5.11640071868896</v>
       </c>
       <c r="H897" t="n">
         <v>6128</v>
@@ -26411,7 +26411,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G898" t="n">
-        <v>4.99833011627197</v>
+        <v>4.99832963943481</v>
       </c>
       <c r="H898" t="n">
         <v>29460</v>
@@ -26440,7 +26440,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G899" t="n">
-        <v>4.83106327056885</v>
+        <v>4.83106279373169</v>
       </c>
       <c r="H899" t="n">
         <v>72320</v>
@@ -26556,7 +26556,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G903" t="n">
-        <v>4.2899055480957</v>
+        <v>4.28990507125854</v>
       </c>
       <c r="H903" t="n">
         <v>28901</v>
@@ -26585,7 +26585,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G904" t="n">
-        <v>4.56540393829346</v>
+        <v>4.5654034614563</v>
       </c>
       <c r="H904" t="n">
         <v>47385</v>
@@ -26643,7 +26643,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G906" t="n">
-        <v>4.83106327056885</v>
+        <v>4.83106279373169</v>
       </c>
       <c r="H906" t="n">
         <v>107459</v>
@@ -26672,7 +26672,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G907" t="n">
-        <v>4.89009809494019</v>
+        <v>4.89009857177734</v>
       </c>
       <c r="H907" t="n">
         <v>18622</v>
@@ -26730,7 +26730,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G909" t="n">
-        <v>4.84090185165405</v>
+        <v>4.84090232849121</v>
       </c>
       <c r="H909" t="n">
         <v>11135</v>
@@ -26759,7 +26759,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G910" t="n">
-        <v>4.83106327056885</v>
+        <v>4.83106279373169</v>
       </c>
       <c r="H910" t="n">
         <v>9284</v>
@@ -26817,7 +26817,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G912" t="n">
-        <v>4.89009809494019</v>
+        <v>4.89009857177734</v>
       </c>
       <c r="H912" t="n">
         <v>3683</v>
@@ -26933,7 +26933,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G916" t="n">
-        <v>4.82122421264648</v>
+        <v>4.82122373580933</v>
       </c>
       <c r="H916" t="n">
         <v>15220</v>
@@ -26991,7 +26991,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G918" t="n">
-        <v>5.03768682479858</v>
+        <v>5.03768634796143</v>
       </c>
       <c r="H918" t="n">
         <v>45309</v>
@@ -27020,7 +27020,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G919" t="n">
-        <v>5.0770435333252</v>
+        <v>5.07704401016235</v>
       </c>
       <c r="H919" t="n">
         <v>22506</v>
@@ -27107,7 +27107,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G922" t="n">
-        <v>5.11640024185181</v>
+        <v>5.11640071868896</v>
       </c>
       <c r="H922" t="n">
         <v>20658</v>
@@ -27223,7 +27223,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G926" t="n">
-        <v>5.254150390625</v>
+        <v>5.25414991378784</v>
       </c>
       <c r="H926" t="n">
         <v>16523</v>
@@ -27281,7 +27281,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G928" t="n">
-        <v>5.27382898330688</v>
+        <v>5.27382850646973</v>
       </c>
       <c r="H928" t="n">
         <v>14860</v>
@@ -27310,7 +27310,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G929" t="n">
-        <v>5.29350662231445</v>
+        <v>5.29350709915161</v>
       </c>
       <c r="H929" t="n">
         <v>8491</v>
@@ -27339,7 +27339,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G930" t="n">
-        <v>5.29350662231445</v>
+        <v>5.29350709915161</v>
       </c>
       <c r="H930" t="n">
         <v>4930</v>
@@ -27542,7 +27542,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G937" t="n">
-        <v>5.11640024185181</v>
+        <v>5.11640071868896</v>
       </c>
       <c r="H937" t="n">
         <v>12717</v>
@@ -27600,7 +27600,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G939" t="n">
-        <v>5.11640024185181</v>
+        <v>5.11640071868896</v>
       </c>
       <c r="H939" t="n">
         <v>9615</v>
@@ -27658,7 +27658,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G941" t="n">
-        <v>5.0770435333252</v>
+        <v>5.07704401016235</v>
       </c>
       <c r="H941" t="n">
         <v>9588</v>
@@ -27745,7 +27745,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G944" t="n">
-        <v>5.13607883453369</v>
+        <v>5.13607931137085</v>
       </c>
       <c r="H944" t="n">
         <v>6542</v>
@@ -27890,7 +27890,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G949" t="n">
-        <v>5.254150390625</v>
+        <v>5.25414991378784</v>
       </c>
       <c r="H949" t="n">
         <v>10195</v>
@@ -27919,7 +27919,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G950" t="n">
-        <v>5.29350662231445</v>
+        <v>5.29350709915161</v>
       </c>
       <c r="H950" t="n">
         <v>11103</v>
@@ -28151,7 +28151,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G958" t="n">
-        <v>5.68707656860352</v>
+        <v>5.68707609176636</v>
       </c>
       <c r="H958" t="n">
         <v>24892</v>
@@ -28180,7 +28180,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G959" t="n">
-        <v>5.68707656860352</v>
+        <v>5.68707609176636</v>
       </c>
       <c r="H959" t="n">
         <v>8965</v>
@@ -28267,7 +28267,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G962" t="n">
-        <v>5.80514717102051</v>
+        <v>5.80514669418335</v>
       </c>
       <c r="H962" t="n">
         <v>18409</v>
@@ -28354,7 +28354,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G965" t="n">
-        <v>5.80514717102051</v>
+        <v>5.80514669418335</v>
       </c>
       <c r="H965" t="n">
         <v>16785</v>
@@ -28470,7 +28470,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G969" t="n">
-        <v>6.13968086242676</v>
+        <v>6.1396803855896</v>
       </c>
       <c r="H969" t="n">
         <v>75849</v>
@@ -28499,7 +28499,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G970" t="n">
-        <v>6.19871616363525</v>
+        <v>6.19871664047241</v>
       </c>
       <c r="H970" t="n">
         <v>62814</v>
@@ -28528,7 +28528,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G971" t="n">
-        <v>6.33646583557129</v>
+        <v>6.33646535873413</v>
       </c>
       <c r="H971" t="n">
         <v>50014</v>
@@ -28557,7 +28557,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G972" t="n">
-        <v>6.27743005752563</v>
+        <v>6.27743053436279</v>
       </c>
       <c r="H972" t="n">
         <v>43290</v>
@@ -28615,7 +28615,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G974" t="n">
-        <v>6.13968086242676</v>
+        <v>6.1396803855896</v>
       </c>
       <c r="H974" t="n">
         <v>10830</v>
@@ -28702,7 +28702,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G977" t="n">
-        <v>6.00193119049072</v>
+        <v>6.00193166732788</v>
       </c>
       <c r="H977" t="n">
         <v>35007</v>
@@ -43266,6 +43266,35 @@
         <v>187</v>
       </c>
       <c r="I1479" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1480">
+      <c r="A1480" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1480" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C1480" t="n">
+        <v>7.67000007629395</v>
+      </c>
+      <c r="D1480" t="n">
+        <v>7.98000001907349</v>
+      </c>
+      <c r="E1480" t="n">
+        <v>7.67000007629395</v>
+      </c>
+      <c r="F1480" t="n">
+        <v>7.94000005722046</v>
+      </c>
+      <c r="G1480" t="n">
+        <v>7.94000005722046</v>
+      </c>
+      <c r="H1480" t="n">
+        <v>2075</v>
+      </c>
+      <c r="I1480" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/EVISO.MI.xlsx
+++ b/data/EVISO.MI.xlsx
@@ -456,7 +456,7 @@
         <v>2.25</v>
       </c>
       <c r="G3" t="n">
-        <v>2.20108580589294</v>
+        <v>2.20108556747437</v>
       </c>
       <c r="H3" t="n">
         <v>232547</v>
@@ -485,7 +485,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G4" t="n">
-        <v>2.11304235458374</v>
+        <v>2.11304259300232</v>
       </c>
       <c r="H4" t="n">
         <v>187476</v>
@@ -601,7 +601,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G8" t="n">
-        <v>2.09347724914551</v>
+        <v>2.09347701072693</v>
       </c>
       <c r="H8" t="n">
         <v>78941</v>
@@ -659,7 +659,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G10" t="n">
-        <v>1.99565100669861</v>
+        <v>1.99565076828003</v>
       </c>
       <c r="H10" t="n">
         <v>58105</v>
@@ -804,7 +804,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G15" t="n">
-        <v>1.9516294002533</v>
+        <v>1.95162928104401</v>
       </c>
       <c r="H15" t="n">
         <v>23112</v>
@@ -978,7 +978,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G21" t="n">
-        <v>1.98586857318878</v>
+        <v>1.9858683347702</v>
       </c>
       <c r="H21" t="n">
         <v>29362</v>
@@ -1065,7 +1065,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G24" t="n">
-        <v>1.99565100669861</v>
+        <v>1.99565076828003</v>
       </c>
       <c r="H24" t="n">
         <v>10648</v>
@@ -1181,7 +1181,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G28" t="n">
-        <v>1.9516294002533</v>
+        <v>1.95162928104401</v>
       </c>
       <c r="H28" t="n">
         <v>19385</v>
@@ -1326,7 +1326,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G33" t="n">
-        <v>2.13260746002197</v>
+        <v>2.13260769844055</v>
       </c>
       <c r="H33" t="n">
         <v>250444</v>
@@ -1384,7 +1384,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G35" t="n">
-        <v>2.33804249763489</v>
+        <v>2.33804225921631</v>
       </c>
       <c r="H35" t="n">
         <v>424591</v>
@@ -1442,7 +1442,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G37" t="n">
-        <v>2.21086835861206</v>
+        <v>2.21086859703064</v>
       </c>
       <c r="H37" t="n">
         <v>41476</v>
@@ -1558,7 +1558,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G41" t="n">
-        <v>2.31847667694092</v>
+        <v>2.3184769153595</v>
       </c>
       <c r="H41" t="n">
         <v>41735</v>
@@ -1616,7 +1616,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G43" t="n">
-        <v>2.32825946807861</v>
+        <v>2.32825970649719</v>
       </c>
       <c r="H43" t="n">
         <v>29630</v>
@@ -2022,7 +2022,7 @@
         <v>2.25</v>
       </c>
       <c r="G57" t="n">
-        <v>2.20108580589294</v>
+        <v>2.20108556747437</v>
       </c>
       <c r="H57" t="n">
         <v>56053</v>
@@ -2167,7 +2167,7 @@
         <v>2.25</v>
       </c>
       <c r="G62" t="n">
-        <v>2.20108580589294</v>
+        <v>2.20108556747437</v>
       </c>
       <c r="H62" t="n">
         <v>17852</v>
@@ -2196,7 +2196,7 @@
         <v>2.25</v>
       </c>
       <c r="G63" t="n">
-        <v>2.20108580589294</v>
+        <v>2.20108556747437</v>
       </c>
       <c r="H63" t="n">
         <v>4750</v>
@@ -2225,7 +2225,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G64" t="n">
-        <v>2.21086835861206</v>
+        <v>2.21086859703064</v>
       </c>
       <c r="H64" t="n">
         <v>43289</v>
@@ -2254,7 +2254,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G65" t="n">
-        <v>2.1717381477356</v>
+        <v>2.17173790931702</v>
       </c>
       <c r="H65" t="n">
         <v>41977</v>
@@ -2283,7 +2283,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G66" t="n">
-        <v>2.19130325317383</v>
+        <v>2.19130301475525</v>
       </c>
       <c r="H66" t="n">
         <v>23995</v>
@@ -2312,7 +2312,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G67" t="n">
-        <v>2.19130325317383</v>
+        <v>2.19130301475525</v>
       </c>
       <c r="H67" t="n">
         <v>651</v>
@@ -2370,7 +2370,7 @@
         <v>2.25</v>
       </c>
       <c r="G69" t="n">
-        <v>2.20108580589294</v>
+        <v>2.20108556747437</v>
       </c>
       <c r="H69" t="n">
         <v>21435</v>
@@ -2399,7 +2399,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G70" t="n">
-        <v>2.19130325317383</v>
+        <v>2.19130301475525</v>
       </c>
       <c r="H70" t="n">
         <v>19650</v>
@@ -2457,7 +2457,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G72" t="n">
-        <v>2.19130325317383</v>
+        <v>2.19130301475525</v>
       </c>
       <c r="H72" t="n">
         <v>13730</v>
@@ -2486,7 +2486,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G73" t="n">
-        <v>2.19130325317383</v>
+        <v>2.19130301475525</v>
       </c>
       <c r="H73" t="n">
         <v>10901</v>
@@ -2573,7 +2573,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G76" t="n">
-        <v>2.1717381477356</v>
+        <v>2.17173790931702</v>
       </c>
       <c r="H76" t="n">
         <v>12073</v>
@@ -2631,7 +2631,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G78" t="n">
-        <v>2.13260746002197</v>
+        <v>2.13260769844055</v>
       </c>
       <c r="H78" t="n">
         <v>6844</v>
@@ -2718,7 +2718,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G81" t="n">
-        <v>2.21086835861206</v>
+        <v>2.21086859703064</v>
       </c>
       <c r="H81" t="n">
         <v>21509</v>
@@ -2776,7 +2776,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G83" t="n">
-        <v>2.21086835861206</v>
+        <v>2.21086859703064</v>
       </c>
       <c r="H83" t="n">
         <v>18856</v>
@@ -2805,7 +2805,7 @@
         <v>2.25</v>
       </c>
       <c r="G84" t="n">
-        <v>2.20108580589294</v>
+        <v>2.20108556747437</v>
       </c>
       <c r="H84" t="n">
         <v>5934</v>
@@ -2863,7 +2863,7 @@
         <v>2.25</v>
       </c>
       <c r="G86" t="n">
-        <v>2.20108580589294</v>
+        <v>2.20108556747437</v>
       </c>
       <c r="H86" t="n">
         <v>22122</v>
@@ -2979,7 +2979,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G90" t="n">
-        <v>2.19130325317383</v>
+        <v>2.19130301475525</v>
       </c>
       <c r="H90" t="n">
         <v>19878</v>
@@ -3008,7 +3008,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G91" t="n">
-        <v>2.33804249763489</v>
+        <v>2.33804225921631</v>
       </c>
       <c r="H91" t="n">
         <v>287103</v>
@@ -3066,7 +3066,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G93" t="n">
-        <v>2.32825946807861</v>
+        <v>2.32825970649719</v>
       </c>
       <c r="H93" t="n">
         <v>74115</v>
@@ -3269,7 +3269,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G100" t="n">
-        <v>2.33804249763489</v>
+        <v>2.33804225921631</v>
       </c>
       <c r="H100" t="n">
         <v>138592</v>
@@ -3327,7 +3327,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G102" t="n">
-        <v>2.42608547210693</v>
+        <v>2.42608571052551</v>
       </c>
       <c r="H102" t="n">
         <v>170798</v>
@@ -3385,7 +3385,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G104" t="n">
-        <v>2.6510853767395</v>
+        <v>2.65108561515808</v>
       </c>
       <c r="H104" t="n">
         <v>222446</v>
@@ -3472,7 +3472,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G107" t="n">
-        <v>2.69999814033508</v>
+        <v>2.69999837875366</v>
       </c>
       <c r="H107" t="n">
         <v>144356</v>
@@ -3559,7 +3559,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G110" t="n">
-        <v>2.61195516586304</v>
+        <v>2.61195492744446</v>
       </c>
       <c r="H110" t="n">
         <v>28158</v>
@@ -3588,7 +3588,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G111" t="n">
-        <v>2.53369426727295</v>
+        <v>2.53369402885437</v>
       </c>
       <c r="H111" t="n">
         <v>56152</v>
@@ -3675,7 +3675,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G114" t="n">
-        <v>2.53369426727295</v>
+        <v>2.53369402885437</v>
       </c>
       <c r="H114" t="n">
         <v>51806</v>
@@ -3733,7 +3733,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G116" t="n">
-        <v>2.51412868499756</v>
+        <v>2.51412892341614</v>
       </c>
       <c r="H116" t="n">
         <v>8588</v>
@@ -3820,7 +3820,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G119" t="n">
-        <v>2.51412868499756</v>
+        <v>2.51412892341614</v>
       </c>
       <c r="H119" t="n">
         <v>5450</v>
@@ -3907,7 +3907,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G122" t="n">
-        <v>2.39673805236816</v>
+        <v>2.39673781394958</v>
       </c>
       <c r="H122" t="n">
         <v>21012</v>
@@ -3965,7 +3965,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G124" t="n">
-        <v>2.31847667694092</v>
+        <v>2.3184769153595</v>
       </c>
       <c r="H124" t="n">
         <v>101860</v>
@@ -4052,7 +4052,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G127" t="n">
-        <v>2.53369426727295</v>
+        <v>2.53369402885437</v>
       </c>
       <c r="H127" t="n">
         <v>39898</v>
@@ -4255,7 +4255,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G134" t="n">
-        <v>2.51412868499756</v>
+        <v>2.51412892341614</v>
       </c>
       <c r="H134" t="n">
         <v>8450</v>
@@ -4371,7 +4371,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G138" t="n">
-        <v>2.39673805236816</v>
+        <v>2.39673781394958</v>
       </c>
       <c r="H138" t="n">
         <v>15772</v>
@@ -4400,7 +4400,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G139" t="n">
-        <v>2.31847667694092</v>
+        <v>2.3184769153595</v>
       </c>
       <c r="H139" t="n">
         <v>24490</v>
@@ -4516,7 +4516,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G143" t="n">
-        <v>2.42608547210693</v>
+        <v>2.42608571052551</v>
       </c>
       <c r="H143" t="n">
         <v>4605</v>
@@ -4545,7 +4545,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G144" t="n">
-        <v>2.42608547210693</v>
+        <v>2.42608571052551</v>
       </c>
       <c r="H144" t="n">
         <v>3188</v>
@@ -4574,7 +4574,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G145" t="n">
-        <v>2.42608547210693</v>
+        <v>2.42608571052551</v>
       </c>
       <c r="H145" t="n">
         <v>2500</v>
@@ -4719,7 +4719,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G150" t="n">
-        <v>2.42608547210693</v>
+        <v>2.42608571052551</v>
       </c>
       <c r="H150" t="n">
         <v>14700</v>
@@ -4748,7 +4748,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G151" t="n">
-        <v>2.39673805236816</v>
+        <v>2.39673781394958</v>
       </c>
       <c r="H151" t="n">
         <v>3252</v>
@@ -5009,7 +5009,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G160" t="n">
-        <v>2.39673805236816</v>
+        <v>2.39673781394958</v>
       </c>
       <c r="H160" t="n">
         <v>10392</v>
@@ -5038,7 +5038,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G161" t="n">
-        <v>2.42608547210693</v>
+        <v>2.42608571052551</v>
       </c>
       <c r="H161" t="n">
         <v>5543</v>
@@ -5067,7 +5067,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G162" t="n">
-        <v>2.42608547210693</v>
+        <v>2.42608571052551</v>
       </c>
       <c r="H162" t="n">
         <v>8850</v>
@@ -5096,7 +5096,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G163" t="n">
-        <v>2.61195516586304</v>
+        <v>2.61195492744446</v>
       </c>
       <c r="H163" t="n">
         <v>108022</v>
@@ -5241,7 +5241,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G168" t="n">
-        <v>2.905433177948</v>
+        <v>2.90543293952942</v>
       </c>
       <c r="H168" t="n">
         <v>40031</v>
@@ -5328,7 +5328,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G171" t="n">
-        <v>2.83695483207703</v>
+        <v>2.83695507049561</v>
       </c>
       <c r="H171" t="n">
         <v>69207</v>
@@ -5763,7 +5763,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G186" t="n">
-        <v>2.70978116989136</v>
+        <v>2.70978093147278</v>
       </c>
       <c r="H186" t="n">
         <v>22094</v>
@@ -5879,7 +5879,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G190" t="n">
-        <v>2.51412868499756</v>
+        <v>2.51412892341614</v>
       </c>
       <c r="H190" t="n">
         <v>117768</v>
@@ -5966,7 +5966,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G193" t="n">
-        <v>2.69999814033508</v>
+        <v>2.69999837875366</v>
       </c>
       <c r="H193" t="n">
         <v>8525</v>
@@ -6111,7 +6111,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G198" t="n">
-        <v>2.61195516586304</v>
+        <v>2.61195492744446</v>
       </c>
       <c r="H198" t="n">
         <v>20110</v>
@@ -6256,7 +6256,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G203" t="n">
-        <v>2.61195516586304</v>
+        <v>2.61195492744446</v>
       </c>
       <c r="H203" t="n">
         <v>23415</v>
@@ -6314,7 +6314,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G205" t="n">
-        <v>2.70978116989136</v>
+        <v>2.70978093147278</v>
       </c>
       <c r="H205" t="n">
         <v>51440</v>
@@ -6372,7 +6372,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G207" t="n">
-        <v>2.69999814033508</v>
+        <v>2.69999837875366</v>
       </c>
       <c r="H207" t="n">
         <v>49435</v>
@@ -6633,7 +6633,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G216" t="n">
-        <v>2.6510853767395</v>
+        <v>2.65108561515808</v>
       </c>
       <c r="H216" t="n">
         <v>13564</v>
@@ -43295,6 +43295,35 @@
         <v>2075</v>
       </c>
       <c r="I1480" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1481">
+      <c r="A1481" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1481" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C1481" t="n">
+        <v>8.01000022888184</v>
+      </c>
+      <c r="D1481" t="n">
+        <v>8.15999984741211</v>
+      </c>
+      <c r="E1481" t="n">
+        <v>7.84999990463257</v>
+      </c>
+      <c r="F1481" t="n">
+        <v>8.14999961853027</v>
+      </c>
+      <c r="G1481" t="n">
+        <v>8.14999961853027</v>
+      </c>
+      <c r="H1481" t="n">
+        <v>8525</v>
+      </c>
+      <c r="I1481" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/EVISO.MI.xlsx
+++ b/data/EVISO.MI.xlsx
@@ -456,7 +456,7 @@
         <v>2.25</v>
       </c>
       <c r="G3" t="n">
-        <v>2.20108556747437</v>
+        <v>2.20108580589294</v>
       </c>
       <c r="H3" t="n">
         <v>232547</v>
@@ -485,7 +485,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G4" t="n">
-        <v>2.11304259300232</v>
+        <v>2.11304235458374</v>
       </c>
       <c r="H4" t="n">
         <v>187476</v>
@@ -601,7 +601,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G8" t="n">
-        <v>2.09347701072693</v>
+        <v>2.09347724914551</v>
       </c>
       <c r="H8" t="n">
         <v>78941</v>
@@ -659,7 +659,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G10" t="n">
-        <v>1.99565076828003</v>
+        <v>1.99565100669861</v>
       </c>
       <c r="H10" t="n">
         <v>58105</v>
@@ -688,7 +688,7 @@
         <v>2</v>
       </c>
       <c r="G11" t="n">
-        <v>1.95652067661285</v>
+        <v>1.95652055740356</v>
       </c>
       <c r="H11" t="n">
         <v>87109</v>
@@ -717,7 +717,7 @@
         <v>2</v>
       </c>
       <c r="G12" t="n">
-        <v>1.95652067661285</v>
+        <v>1.95652055740356</v>
       </c>
       <c r="H12" t="n">
         <v>33913</v>
@@ -746,7 +746,7 @@
         <v>2</v>
       </c>
       <c r="G13" t="n">
-        <v>1.95652067661285</v>
+        <v>1.95652055740356</v>
       </c>
       <c r="H13" t="n">
         <v>67232</v>
@@ -775,7 +775,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G14" t="n">
-        <v>1.93695557117462</v>
+        <v>1.93695545196533</v>
       </c>
       <c r="H14" t="n">
         <v>32193</v>
@@ -804,7 +804,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G15" t="n">
-        <v>1.95162928104401</v>
+        <v>1.9516294002533</v>
       </c>
       <c r="H15" t="n">
         <v>23112</v>
@@ -891,7 +891,7 @@
         <v>2</v>
       </c>
       <c r="G18" t="n">
-        <v>1.95652067661285</v>
+        <v>1.95652055740356</v>
       </c>
       <c r="H18" t="n">
         <v>259672</v>
@@ -920,7 +920,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G19" t="n">
-        <v>1.96630311012268</v>
+        <v>1.96630322933197</v>
       </c>
       <c r="H19" t="n">
         <v>71780</v>
@@ -949,7 +949,7 @@
         <v>2</v>
       </c>
       <c r="G20" t="n">
-        <v>1.95652067661285</v>
+        <v>1.95652055740356</v>
       </c>
       <c r="H20" t="n">
         <v>44963</v>
@@ -978,7 +978,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G21" t="n">
-        <v>1.9858683347702</v>
+        <v>1.98586845397949</v>
       </c>
       <c r="H21" t="n">
         <v>29362</v>
@@ -1007,7 +1007,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G22" t="n">
-        <v>1.96630311012268</v>
+        <v>1.96630322933197</v>
       </c>
       <c r="H22" t="n">
         <v>29896</v>
@@ -1036,7 +1036,7 @@
         <v>2</v>
       </c>
       <c r="G23" t="n">
-        <v>1.95652067661285</v>
+        <v>1.95652055740356</v>
       </c>
       <c r="H23" t="n">
         <v>29935</v>
@@ -1065,7 +1065,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G24" t="n">
-        <v>1.99565076828003</v>
+        <v>1.99565100669861</v>
       </c>
       <c r="H24" t="n">
         <v>10648</v>
@@ -1094,7 +1094,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G25" t="n">
-        <v>1.96630311012268</v>
+        <v>1.96630322933197</v>
       </c>
       <c r="H25" t="n">
         <v>38840</v>
@@ -1123,7 +1123,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G26" t="n">
-        <v>1.96630311012268</v>
+        <v>1.96630322933197</v>
       </c>
       <c r="H26" t="n">
         <v>65217</v>
@@ -1152,7 +1152,7 @@
         <v>2</v>
       </c>
       <c r="G27" t="n">
-        <v>1.95652067661285</v>
+        <v>1.95652055740356</v>
       </c>
       <c r="H27" t="n">
         <v>20889</v>
@@ -1181,7 +1181,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G28" t="n">
-        <v>1.95162928104401</v>
+        <v>1.9516294002533</v>
       </c>
       <c r="H28" t="n">
         <v>19385</v>
@@ -1210,7 +1210,7 @@
         <v>2</v>
       </c>
       <c r="G29" t="n">
-        <v>1.95652067661285</v>
+        <v>1.95652055740356</v>
       </c>
       <c r="H29" t="n">
         <v>28897</v>
@@ -1326,7 +1326,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G33" t="n">
-        <v>2.13260769844055</v>
+        <v>2.13260746002197</v>
       </c>
       <c r="H33" t="n">
         <v>250444</v>
@@ -1384,7 +1384,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G35" t="n">
-        <v>2.33804225921631</v>
+        <v>2.33804249763489</v>
       </c>
       <c r="H35" t="n">
         <v>424591</v>
@@ -1413,7 +1413,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G36" t="n">
-        <v>2.25978136062622</v>
+        <v>2.25978112220764</v>
       </c>
       <c r="H36" t="n">
         <v>179668</v>
@@ -1442,7 +1442,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G37" t="n">
-        <v>2.21086859703064</v>
+        <v>2.21086835861206</v>
       </c>
       <c r="H37" t="n">
         <v>41476</v>
@@ -1471,7 +1471,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G38" t="n">
-        <v>2.28912878036499</v>
+        <v>2.28912901878357</v>
       </c>
       <c r="H38" t="n">
         <v>46638</v>
@@ -1500,7 +1500,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G39" t="n">
-        <v>2.26956367492676</v>
+        <v>2.26956391334534</v>
       </c>
       <c r="H39" t="n">
         <v>53117</v>
@@ -1558,7 +1558,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G41" t="n">
-        <v>2.3184769153595</v>
+        <v>2.31847667694092</v>
       </c>
       <c r="H41" t="n">
         <v>41735</v>
@@ -1616,7 +1616,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G43" t="n">
-        <v>2.32825970649719</v>
+        <v>2.32825946807861</v>
       </c>
       <c r="H43" t="n">
         <v>29630</v>
@@ -1674,7 +1674,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G45" t="n">
-        <v>2.25978136062622</v>
+        <v>2.25978112220764</v>
       </c>
       <c r="H45" t="n">
         <v>25346</v>
@@ -1703,7 +1703,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G46" t="n">
-        <v>2.28912878036499</v>
+        <v>2.28912901878357</v>
       </c>
       <c r="H46" t="n">
         <v>34385</v>
@@ -1761,7 +1761,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G48" t="n">
-        <v>2.28912878036499</v>
+        <v>2.28912901878357</v>
       </c>
       <c r="H48" t="n">
         <v>32533</v>
@@ -1790,7 +1790,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G49" t="n">
-        <v>2.26956367492676</v>
+        <v>2.26956391334534</v>
       </c>
       <c r="H49" t="n">
         <v>44339</v>
@@ -1819,7 +1819,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G50" t="n">
-        <v>2.28912878036499</v>
+        <v>2.28912901878357</v>
       </c>
       <c r="H50" t="n">
         <v>198858</v>
@@ -1848,7 +1848,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G51" t="n">
-        <v>2.26956367492676</v>
+        <v>2.26956391334534</v>
       </c>
       <c r="H51" t="n">
         <v>28573</v>
@@ -1877,7 +1877,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G52" t="n">
-        <v>2.25978136062622</v>
+        <v>2.25978112220764</v>
       </c>
       <c r="H52" t="n">
         <v>40111</v>
@@ -2022,7 +2022,7 @@
         <v>2.25</v>
       </c>
       <c r="G57" t="n">
-        <v>2.20108556747437</v>
+        <v>2.20108580589294</v>
       </c>
       <c r="H57" t="n">
         <v>56053</v>
@@ -2167,7 +2167,7 @@
         <v>2.25</v>
       </c>
       <c r="G62" t="n">
-        <v>2.20108556747437</v>
+        <v>2.20108580589294</v>
       </c>
       <c r="H62" t="n">
         <v>17852</v>
@@ -2196,7 +2196,7 @@
         <v>2.25</v>
       </c>
       <c r="G63" t="n">
-        <v>2.20108556747437</v>
+        <v>2.20108580589294</v>
       </c>
       <c r="H63" t="n">
         <v>4750</v>
@@ -2225,7 +2225,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G64" t="n">
-        <v>2.21086859703064</v>
+        <v>2.21086835861206</v>
       </c>
       <c r="H64" t="n">
         <v>43289</v>
@@ -2254,7 +2254,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G65" t="n">
-        <v>2.17173790931702</v>
+        <v>2.1717381477356</v>
       </c>
       <c r="H65" t="n">
         <v>41977</v>
@@ -2283,7 +2283,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G66" t="n">
-        <v>2.19130301475525</v>
+        <v>2.19130325317383</v>
       </c>
       <c r="H66" t="n">
         <v>23995</v>
@@ -2312,7 +2312,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G67" t="n">
-        <v>2.19130301475525</v>
+        <v>2.19130325317383</v>
       </c>
       <c r="H67" t="n">
         <v>651</v>
@@ -2370,7 +2370,7 @@
         <v>2.25</v>
       </c>
       <c r="G69" t="n">
-        <v>2.20108556747437</v>
+        <v>2.20108580589294</v>
       </c>
       <c r="H69" t="n">
         <v>21435</v>
@@ -2399,7 +2399,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G70" t="n">
-        <v>2.19130301475525</v>
+        <v>2.19130325317383</v>
       </c>
       <c r="H70" t="n">
         <v>19650</v>
@@ -2457,7 +2457,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G72" t="n">
-        <v>2.19130301475525</v>
+        <v>2.19130325317383</v>
       </c>
       <c r="H72" t="n">
         <v>13730</v>
@@ -2486,7 +2486,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G73" t="n">
-        <v>2.19130301475525</v>
+        <v>2.19130325317383</v>
       </c>
       <c r="H73" t="n">
         <v>10901</v>
@@ -2573,7 +2573,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G76" t="n">
-        <v>2.17173790931702</v>
+        <v>2.1717381477356</v>
       </c>
       <c r="H76" t="n">
         <v>12073</v>
@@ -2631,7 +2631,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G78" t="n">
-        <v>2.13260769844055</v>
+        <v>2.13260746002197</v>
       </c>
       <c r="H78" t="n">
         <v>6844</v>
@@ -2718,7 +2718,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G81" t="n">
-        <v>2.21086859703064</v>
+        <v>2.21086835861206</v>
       </c>
       <c r="H81" t="n">
         <v>21509</v>
@@ -2776,7 +2776,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G83" t="n">
-        <v>2.21086859703064</v>
+        <v>2.21086835861206</v>
       </c>
       <c r="H83" t="n">
         <v>18856</v>
@@ -2805,7 +2805,7 @@
         <v>2.25</v>
       </c>
       <c r="G84" t="n">
-        <v>2.20108556747437</v>
+        <v>2.20108580589294</v>
       </c>
       <c r="H84" t="n">
         <v>5934</v>
@@ -2863,7 +2863,7 @@
         <v>2.25</v>
       </c>
       <c r="G86" t="n">
-        <v>2.20108556747437</v>
+        <v>2.20108580589294</v>
       </c>
       <c r="H86" t="n">
         <v>22122</v>
@@ -2979,7 +2979,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G90" t="n">
-        <v>2.19130301475525</v>
+        <v>2.19130325317383</v>
       </c>
       <c r="H90" t="n">
         <v>19878</v>
@@ -3008,7 +3008,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G91" t="n">
-        <v>2.33804225921631</v>
+        <v>2.33804249763489</v>
       </c>
       <c r="H91" t="n">
         <v>287103</v>
@@ -3066,7 +3066,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G93" t="n">
-        <v>2.32825970649719</v>
+        <v>2.32825946807861</v>
       </c>
       <c r="H93" t="n">
         <v>74115</v>
@@ -3124,7 +3124,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G95" t="n">
-        <v>2.26956367492676</v>
+        <v>2.26956391334534</v>
       </c>
       <c r="H95" t="n">
         <v>10213</v>
@@ -3269,7 +3269,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G100" t="n">
-        <v>2.33804225921631</v>
+        <v>2.33804249763489</v>
       </c>
       <c r="H100" t="n">
         <v>138592</v>
@@ -3327,7 +3327,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G102" t="n">
-        <v>2.42608571052551</v>
+        <v>2.42608547210693</v>
       </c>
       <c r="H102" t="n">
         <v>170798</v>
@@ -3385,7 +3385,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G104" t="n">
-        <v>2.65108561515808</v>
+        <v>2.6510853767395</v>
       </c>
       <c r="H104" t="n">
         <v>222446</v>
@@ -3414,7 +3414,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G105" t="n">
-        <v>2.73912882804871</v>
+        <v>2.73912906646729</v>
       </c>
       <c r="H105" t="n">
         <v>254085</v>
@@ -3588,7 +3588,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G111" t="n">
-        <v>2.53369402885437</v>
+        <v>2.53369426727295</v>
       </c>
       <c r="H111" t="n">
         <v>56152</v>
@@ -3675,7 +3675,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G114" t="n">
-        <v>2.53369402885437</v>
+        <v>2.53369426727295</v>
       </c>
       <c r="H114" t="n">
         <v>51806</v>
@@ -3704,7 +3704,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G115" t="n">
-        <v>2.50434637069702</v>
+        <v>2.50434613227844</v>
       </c>
       <c r="H115" t="n">
         <v>101303</v>
@@ -3791,7 +3791,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G118" t="n">
-        <v>2.49456357955933</v>
+        <v>2.49456381797791</v>
       </c>
       <c r="H118" t="n">
         <v>42909</v>
@@ -3965,7 +3965,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G124" t="n">
-        <v>2.3184769153595</v>
+        <v>2.31847667694092</v>
       </c>
       <c r="H124" t="n">
         <v>101860</v>
@@ -4052,7 +4052,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G127" t="n">
-        <v>2.53369402885437</v>
+        <v>2.53369426727295</v>
       </c>
       <c r="H127" t="n">
         <v>39898</v>
@@ -4110,7 +4110,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G129" t="n">
-        <v>2.49456357955933</v>
+        <v>2.49456381797791</v>
       </c>
       <c r="H129" t="n">
         <v>3606</v>
@@ -4168,7 +4168,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G131" t="n">
-        <v>2.50434637069702</v>
+        <v>2.50434613227844</v>
       </c>
       <c r="H131" t="n">
         <v>17915</v>
@@ -4197,7 +4197,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G132" t="n">
-        <v>2.49456357955933</v>
+        <v>2.49456381797791</v>
       </c>
       <c r="H132" t="n">
         <v>6780</v>
@@ -4400,7 +4400,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G139" t="n">
-        <v>2.3184769153595</v>
+        <v>2.31847667694092</v>
       </c>
       <c r="H139" t="n">
         <v>24490</v>
@@ -4516,7 +4516,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G143" t="n">
-        <v>2.42608571052551</v>
+        <v>2.42608547210693</v>
       </c>
       <c r="H143" t="n">
         <v>4605</v>
@@ -4545,7 +4545,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G144" t="n">
-        <v>2.42608571052551</v>
+        <v>2.42608547210693</v>
       </c>
       <c r="H144" t="n">
         <v>3188</v>
@@ -4574,7 +4574,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G145" t="n">
-        <v>2.42608571052551</v>
+        <v>2.42608547210693</v>
       </c>
       <c r="H145" t="n">
         <v>2500</v>
@@ -4719,7 +4719,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G150" t="n">
-        <v>2.42608571052551</v>
+        <v>2.42608547210693</v>
       </c>
       <c r="H150" t="n">
         <v>14700</v>
@@ -4864,7 +4864,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G155" t="n">
-        <v>2.50434637069702</v>
+        <v>2.50434613227844</v>
       </c>
       <c r="H155" t="n">
         <v>11685</v>
@@ -4893,7 +4893,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G156" t="n">
-        <v>2.49456357955933</v>
+        <v>2.49456381797791</v>
       </c>
       <c r="H156" t="n">
         <v>10595</v>
@@ -4922,7 +4922,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G157" t="n">
-        <v>2.49456357955933</v>
+        <v>2.49456381797791</v>
       </c>
       <c r="H157" t="n">
         <v>21750</v>
@@ -5038,7 +5038,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G161" t="n">
-        <v>2.42608571052551</v>
+        <v>2.42608547210693</v>
       </c>
       <c r="H161" t="n">
         <v>5543</v>
@@ -5067,7 +5067,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G162" t="n">
-        <v>2.42608571052551</v>
+        <v>2.42608547210693</v>
       </c>
       <c r="H162" t="n">
         <v>8850</v>
@@ -5125,7 +5125,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G164" t="n">
-        <v>2.81738972663879</v>
+        <v>2.81738996505737</v>
       </c>
       <c r="H164" t="n">
         <v>432229</v>
@@ -5154,7 +5154,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G165" t="n">
-        <v>2.81738972663879</v>
+        <v>2.81738996505737</v>
       </c>
       <c r="H165" t="n">
         <v>148290</v>
@@ -5183,7 +5183,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G166" t="n">
-        <v>2.92499828338623</v>
+        <v>2.92499852180481</v>
       </c>
       <c r="H166" t="n">
         <v>225121</v>
@@ -5212,7 +5212,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G167" t="n">
-        <v>2.92499828338623</v>
+        <v>2.92499852180481</v>
       </c>
       <c r="H167" t="n">
         <v>82576</v>
@@ -5241,7 +5241,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G168" t="n">
-        <v>2.90543293952942</v>
+        <v>2.90543341636658</v>
       </c>
       <c r="H168" t="n">
         <v>40031</v>
@@ -5270,7 +5270,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G169" t="n">
-        <v>2.92499828338623</v>
+        <v>2.92499852180481</v>
       </c>
       <c r="H169" t="n">
         <v>43188</v>
@@ -5299,7 +5299,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G170" t="n">
-        <v>2.92499828338623</v>
+        <v>2.92499852180481</v>
       </c>
       <c r="H170" t="n">
         <v>21615</v>
@@ -5328,7 +5328,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G171" t="n">
-        <v>2.83695507049561</v>
+        <v>2.83695483207703</v>
       </c>
       <c r="H171" t="n">
         <v>69207</v>
@@ -5357,7 +5357,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G172" t="n">
-        <v>2.7489116191864</v>
+        <v>2.74891138076782</v>
       </c>
       <c r="H172" t="n">
         <v>92414</v>
@@ -5415,7 +5415,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G174" t="n">
-        <v>2.73912882804871</v>
+        <v>2.73912906646729</v>
       </c>
       <c r="H174" t="n">
         <v>33049</v>
@@ -5589,7 +5589,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G180" t="n">
-        <v>2.67065072059631</v>
+        <v>2.67065048217773</v>
       </c>
       <c r="H180" t="n">
         <v>5950</v>
@@ -5763,7 +5763,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G186" t="n">
-        <v>2.70978093147278</v>
+        <v>2.70978116989136</v>
       </c>
       <c r="H186" t="n">
         <v>22094</v>
@@ -5850,7 +5850,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G189" t="n">
-        <v>2.7489116191864</v>
+        <v>2.74891138076782</v>
       </c>
       <c r="H189" t="n">
         <v>35710</v>
@@ -5908,7 +5908,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G191" t="n">
-        <v>2.68043303489685</v>
+        <v>2.68043327331543</v>
       </c>
       <c r="H191" t="n">
         <v>61763</v>
@@ -5995,7 +5995,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G194" t="n">
-        <v>2.64130306243896</v>
+        <v>2.64130282402039</v>
       </c>
       <c r="H194" t="n">
         <v>13810</v>
@@ -6053,7 +6053,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G196" t="n">
-        <v>2.50434637069702</v>
+        <v>2.50434613227844</v>
       </c>
       <c r="H196" t="n">
         <v>18379</v>
@@ -6285,7 +6285,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G204" t="n">
-        <v>2.64130306243896</v>
+        <v>2.64130282402039</v>
       </c>
       <c r="H204" t="n">
         <v>60539</v>
@@ -6314,7 +6314,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G205" t="n">
-        <v>2.70978093147278</v>
+        <v>2.70978116989136</v>
       </c>
       <c r="H205" t="n">
         <v>51440</v>
@@ -6343,7 +6343,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G206" t="n">
-        <v>2.73912882804871</v>
+        <v>2.73912906646729</v>
       </c>
       <c r="H206" t="n">
         <v>36708</v>
@@ -6430,7 +6430,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G209" t="n">
-        <v>2.67065072059631</v>
+        <v>2.67065048217773</v>
       </c>
       <c r="H209" t="n">
         <v>30620</v>
@@ -6517,7 +6517,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G212" t="n">
-        <v>2.67065072059631</v>
+        <v>2.67065048217773</v>
       </c>
       <c r="H212" t="n">
         <v>9213</v>
@@ -6604,7 +6604,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G215" t="n">
-        <v>2.68043303489685</v>
+        <v>2.68043327331543</v>
       </c>
       <c r="H215" t="n">
         <v>17119</v>
@@ -6633,7 +6633,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G216" t="n">
-        <v>2.65108561515808</v>
+        <v>2.6510853767395</v>
       </c>
       <c r="H216" t="n">
         <v>13564</v>
@@ -6662,7 +6662,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G217" t="n">
-        <v>2.64130306243896</v>
+        <v>2.64130282402039</v>
       </c>
       <c r="H217" t="n">
         <v>19788</v>
@@ -43324,6 +43324,35 @@
         <v>8525</v>
       </c>
       <c r="I1481" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1482">
+      <c r="A1482" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1482" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C1482" t="n">
+        <v>8.10000038146973</v>
+      </c>
+      <c r="D1482" t="n">
+        <v>8.19999980926514</v>
+      </c>
+      <c r="E1482" t="n">
+        <v>8.02000045776367</v>
+      </c>
+      <c r="F1482" t="n">
+        <v>8.19999980926514</v>
+      </c>
+      <c r="G1482" t="n">
+        <v>8.19999980926514</v>
+      </c>
+      <c r="H1482" t="n">
+        <v>6812</v>
+      </c>
+      <c r="I1482" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/EVISO.MI.xlsx
+++ b/data/EVISO.MI.xlsx
@@ -456,7 +456,7 @@
         <v>2.25</v>
       </c>
       <c r="G3" t="n">
-        <v>2.20108580589294</v>
+        <v>2.20108556747437</v>
       </c>
       <c r="H3" t="n">
         <v>232547</v>
@@ -601,7 +601,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G8" t="n">
-        <v>2.09347724914551</v>
+        <v>2.09347701072693</v>
       </c>
       <c r="H8" t="n">
         <v>78941</v>
@@ -659,7 +659,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G10" t="n">
-        <v>1.99565100669861</v>
+        <v>1.9956511259079</v>
       </c>
       <c r="H10" t="n">
         <v>58105</v>
@@ -688,7 +688,7 @@
         <v>2</v>
       </c>
       <c r="G11" t="n">
-        <v>1.95652055740356</v>
+        <v>1.95652067661285</v>
       </c>
       <c r="H11" t="n">
         <v>87109</v>
@@ -717,7 +717,7 @@
         <v>2</v>
       </c>
       <c r="G12" t="n">
-        <v>1.95652055740356</v>
+        <v>1.95652067661285</v>
       </c>
       <c r="H12" t="n">
         <v>33913</v>
@@ -746,7 +746,7 @@
         <v>2</v>
       </c>
       <c r="G13" t="n">
-        <v>1.95652055740356</v>
+        <v>1.95652067661285</v>
       </c>
       <c r="H13" t="n">
         <v>67232</v>
@@ -804,7 +804,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G15" t="n">
-        <v>1.9516294002533</v>
+        <v>1.95162928104401</v>
       </c>
       <c r="H15" t="n">
         <v>23112</v>
@@ -833,7 +833,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G16" t="n">
-        <v>1.87825977802277</v>
+        <v>1.87825965881348</v>
       </c>
       <c r="H16" t="n">
         <v>30535</v>
@@ -891,7 +891,7 @@
         <v>2</v>
       </c>
       <c r="G18" t="n">
-        <v>1.95652055740356</v>
+        <v>1.95652067661285</v>
       </c>
       <c r="H18" t="n">
         <v>259672</v>
@@ -949,7 +949,7 @@
         <v>2</v>
       </c>
       <c r="G20" t="n">
-        <v>1.95652055740356</v>
+        <v>1.95652067661285</v>
       </c>
       <c r="H20" t="n">
         <v>44963</v>
@@ -978,7 +978,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G21" t="n">
-        <v>1.98586845397949</v>
+        <v>1.9858683347702</v>
       </c>
       <c r="H21" t="n">
         <v>29362</v>
@@ -1036,7 +1036,7 @@
         <v>2</v>
       </c>
       <c r="G23" t="n">
-        <v>1.95652055740356</v>
+        <v>1.95652067661285</v>
       </c>
       <c r="H23" t="n">
         <v>29935</v>
@@ -1065,7 +1065,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G24" t="n">
-        <v>1.99565100669861</v>
+        <v>1.9956511259079</v>
       </c>
       <c r="H24" t="n">
         <v>10648</v>
@@ -1152,7 +1152,7 @@
         <v>2</v>
       </c>
       <c r="G27" t="n">
-        <v>1.95652055740356</v>
+        <v>1.95652067661285</v>
       </c>
       <c r="H27" t="n">
         <v>20889</v>
@@ -1181,7 +1181,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G28" t="n">
-        <v>1.9516294002533</v>
+        <v>1.95162928104401</v>
       </c>
       <c r="H28" t="n">
         <v>19385</v>
@@ -1210,7 +1210,7 @@
         <v>2</v>
       </c>
       <c r="G29" t="n">
-        <v>1.95652055740356</v>
+        <v>1.95652067661285</v>
       </c>
       <c r="H29" t="n">
         <v>28897</v>
@@ -1239,7 +1239,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G30" t="n">
-        <v>2.08369445800781</v>
+        <v>2.08369469642639</v>
       </c>
       <c r="H30" t="n">
         <v>401332</v>
@@ -1326,7 +1326,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G33" t="n">
-        <v>2.13260746002197</v>
+        <v>2.13260769844055</v>
       </c>
       <c r="H33" t="n">
         <v>250444</v>
@@ -1384,7 +1384,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G35" t="n">
-        <v>2.33804249763489</v>
+        <v>2.33804202079773</v>
       </c>
       <c r="H35" t="n">
         <v>424591</v>
@@ -1413,7 +1413,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G36" t="n">
-        <v>2.25978112220764</v>
+        <v>2.25978136062622</v>
       </c>
       <c r="H36" t="n">
         <v>179668</v>
@@ -1558,7 +1558,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G41" t="n">
-        <v>2.31847667694092</v>
+        <v>2.3184769153595</v>
       </c>
       <c r="H41" t="n">
         <v>41735</v>
@@ -1616,7 +1616,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G43" t="n">
-        <v>2.32825946807861</v>
+        <v>2.32825970649719</v>
       </c>
       <c r="H43" t="n">
         <v>29630</v>
@@ -1645,7 +1645,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G44" t="n">
-        <v>2.27934646606445</v>
+        <v>2.27934670448303</v>
       </c>
       <c r="H44" t="n">
         <v>35829</v>
@@ -1674,7 +1674,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G45" t="n">
-        <v>2.25978112220764</v>
+        <v>2.25978136062622</v>
       </c>
       <c r="H45" t="n">
         <v>25346</v>
@@ -1877,7 +1877,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G52" t="n">
-        <v>2.25978112220764</v>
+        <v>2.25978136062622</v>
       </c>
       <c r="H52" t="n">
         <v>40111</v>
@@ -1906,7 +1906,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G53" t="n">
-        <v>2.2499988079071</v>
+        <v>2.24999856948853</v>
       </c>
       <c r="H53" t="n">
         <v>15349</v>
@@ -1964,7 +1964,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G55" t="n">
-        <v>2.2499988079071</v>
+        <v>2.24999856948853</v>
       </c>
       <c r="H55" t="n">
         <v>23715</v>
@@ -1993,7 +1993,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G56" t="n">
-        <v>2.2499988079071</v>
+        <v>2.24999856948853</v>
       </c>
       <c r="H56" t="n">
         <v>20720</v>
@@ -2022,7 +2022,7 @@
         <v>2.25</v>
       </c>
       <c r="G57" t="n">
-        <v>2.20108580589294</v>
+        <v>2.20108556747437</v>
       </c>
       <c r="H57" t="n">
         <v>56053</v>
@@ -2138,7 +2138,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G61" t="n">
-        <v>2.23043370246887</v>
+        <v>2.23043346405029</v>
       </c>
       <c r="H61" t="n">
         <v>30389</v>
@@ -2167,7 +2167,7 @@
         <v>2.25</v>
       </c>
       <c r="G62" t="n">
-        <v>2.20108580589294</v>
+        <v>2.20108556747437</v>
       </c>
       <c r="H62" t="n">
         <v>17852</v>
@@ -2196,7 +2196,7 @@
         <v>2.25</v>
       </c>
       <c r="G63" t="n">
-        <v>2.20108580589294</v>
+        <v>2.20108556747437</v>
       </c>
       <c r="H63" t="n">
         <v>4750</v>
@@ -2283,7 +2283,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G66" t="n">
-        <v>2.19130325317383</v>
+        <v>2.19130301475525</v>
       </c>
       <c r="H66" t="n">
         <v>23995</v>
@@ -2312,7 +2312,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G67" t="n">
-        <v>2.19130325317383</v>
+        <v>2.19130301475525</v>
       </c>
       <c r="H67" t="n">
         <v>651</v>
@@ -2341,7 +2341,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G68" t="n">
-        <v>2.23043370246887</v>
+        <v>2.23043346405029</v>
       </c>
       <c r="H68" t="n">
         <v>59507</v>
@@ -2370,7 +2370,7 @@
         <v>2.25</v>
       </c>
       <c r="G69" t="n">
-        <v>2.20108580589294</v>
+        <v>2.20108556747437</v>
       </c>
       <c r="H69" t="n">
         <v>21435</v>
@@ -2399,7 +2399,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G70" t="n">
-        <v>2.19130325317383</v>
+        <v>2.19130301475525</v>
       </c>
       <c r="H70" t="n">
         <v>19650</v>
@@ -2457,7 +2457,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G72" t="n">
-        <v>2.19130325317383</v>
+        <v>2.19130301475525</v>
       </c>
       <c r="H72" t="n">
         <v>13730</v>
@@ -2486,7 +2486,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G73" t="n">
-        <v>2.19130325317383</v>
+        <v>2.19130301475525</v>
       </c>
       <c r="H73" t="n">
         <v>10901</v>
@@ -2631,7 +2631,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G78" t="n">
-        <v>2.13260746002197</v>
+        <v>2.13260769844055</v>
       </c>
       <c r="H78" t="n">
         <v>6844</v>
@@ -2660,7 +2660,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G79" t="n">
-        <v>2.23043370246887</v>
+        <v>2.23043346405029</v>
       </c>
       <c r="H79" t="n">
         <v>133272</v>
@@ -2805,7 +2805,7 @@
         <v>2.25</v>
       </c>
       <c r="G84" t="n">
-        <v>2.20108580589294</v>
+        <v>2.20108556747437</v>
       </c>
       <c r="H84" t="n">
         <v>5934</v>
@@ -2863,7 +2863,7 @@
         <v>2.25</v>
       </c>
       <c r="G86" t="n">
-        <v>2.20108580589294</v>
+        <v>2.20108556747437</v>
       </c>
       <c r="H86" t="n">
         <v>22122</v>
@@ -2979,7 +2979,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G90" t="n">
-        <v>2.19130325317383</v>
+        <v>2.19130301475525</v>
       </c>
       <c r="H90" t="n">
         <v>19878</v>
@@ -3008,7 +3008,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G91" t="n">
-        <v>2.33804249763489</v>
+        <v>2.33804202079773</v>
       </c>
       <c r="H91" t="n">
         <v>287103</v>
@@ -3066,7 +3066,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G93" t="n">
-        <v>2.32825946807861</v>
+        <v>2.32825970649719</v>
       </c>
       <c r="H93" t="n">
         <v>74115</v>
@@ -3095,7 +3095,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G94" t="n">
-        <v>2.27934646606445</v>
+        <v>2.27934670448303</v>
       </c>
       <c r="H94" t="n">
         <v>66519</v>
@@ -3153,7 +3153,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G96" t="n">
-        <v>2.2499988079071</v>
+        <v>2.24999856948853</v>
       </c>
       <c r="H96" t="n">
         <v>23541</v>
@@ -3182,7 +3182,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G97" t="n">
-        <v>2.27934646606445</v>
+        <v>2.27934670448303</v>
       </c>
       <c r="H97" t="n">
         <v>9745</v>
@@ -3269,7 +3269,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G100" t="n">
-        <v>2.33804249763489</v>
+        <v>2.33804202079773</v>
       </c>
       <c r="H100" t="n">
         <v>138592</v>
@@ -3327,7 +3327,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G102" t="n">
-        <v>2.42608547210693</v>
+        <v>2.42608571052551</v>
       </c>
       <c r="H102" t="n">
         <v>170798</v>
@@ -3559,7 +3559,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G110" t="n">
-        <v>2.61195492744446</v>
+        <v>2.61195516586304</v>
       </c>
       <c r="H110" t="n">
         <v>28158</v>
@@ -3617,7 +3617,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G112" t="n">
-        <v>2.54347681999207</v>
+        <v>2.54347658157349</v>
       </c>
       <c r="H112" t="n">
         <v>34901</v>
@@ -3646,7 +3646,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G113" t="n">
-        <v>2.54347681999207</v>
+        <v>2.54347658157349</v>
       </c>
       <c r="H113" t="n">
         <v>36680</v>
@@ -3704,7 +3704,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G115" t="n">
-        <v>2.50434613227844</v>
+        <v>2.50434637069702</v>
       </c>
       <c r="H115" t="n">
         <v>101303</v>
@@ -3733,7 +3733,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G116" t="n">
-        <v>2.51412892341614</v>
+        <v>2.51412916183472</v>
       </c>
       <c r="H116" t="n">
         <v>8588</v>
@@ -3762,7 +3762,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G117" t="n">
-        <v>2.54347681999207</v>
+        <v>2.54347658157349</v>
       </c>
       <c r="H117" t="n">
         <v>39029</v>
@@ -3820,7 +3820,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G119" t="n">
-        <v>2.51412892341614</v>
+        <v>2.51412916183472</v>
       </c>
       <c r="H119" t="n">
         <v>5450</v>
@@ -3849,7 +3849,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G120" t="n">
-        <v>2.47499847412109</v>
+        <v>2.47499871253967</v>
       </c>
       <c r="H120" t="n">
         <v>9520</v>
@@ -3878,7 +3878,7 @@
         <v>2.5</v>
       </c>
       <c r="G121" t="n">
-        <v>2.44565081596375</v>
+        <v>2.44565057754517</v>
       </c>
       <c r="H121" t="n">
         <v>24840</v>
@@ -3965,7 +3965,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G124" t="n">
-        <v>2.31847667694092</v>
+        <v>2.3184769153595</v>
       </c>
       <c r="H124" t="n">
         <v>101860</v>
@@ -3994,7 +3994,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G125" t="n">
-        <v>2.4163031578064</v>
+        <v>2.41630291938782</v>
       </c>
       <c r="H125" t="n">
         <v>35694</v>
@@ -4081,7 +4081,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G128" t="n">
-        <v>2.48478102684021</v>
+        <v>2.48478126525879</v>
       </c>
       <c r="H128" t="n">
         <v>22629</v>
@@ -4139,7 +4139,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G130" t="n">
-        <v>2.52391171455383</v>
+        <v>2.52391147613525</v>
       </c>
       <c r="H130" t="n">
         <v>6239</v>
@@ -4168,7 +4168,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G131" t="n">
-        <v>2.50434613227844</v>
+        <v>2.50434637069702</v>
       </c>
       <c r="H131" t="n">
         <v>17915</v>
@@ -4255,7 +4255,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G134" t="n">
-        <v>2.51412892341614</v>
+        <v>2.51412916183472</v>
       </c>
       <c r="H134" t="n">
         <v>8450</v>
@@ -4284,7 +4284,7 @@
         <v>2.5</v>
       </c>
       <c r="G135" t="n">
-        <v>2.44565081596375</v>
+        <v>2.44565057754517</v>
       </c>
       <c r="H135" t="n">
         <v>40425</v>
@@ -4313,7 +4313,7 @@
         <v>2.5</v>
       </c>
       <c r="G136" t="n">
-        <v>2.44565081596375</v>
+        <v>2.44565057754517</v>
       </c>
       <c r="H136" t="n">
         <v>2530</v>
@@ -4342,7 +4342,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G137" t="n">
-        <v>2.47499847412109</v>
+        <v>2.47499871253967</v>
       </c>
       <c r="H137" t="n">
         <v>1750</v>
@@ -4400,7 +4400,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G139" t="n">
-        <v>2.31847667694092</v>
+        <v>2.3184769153595</v>
       </c>
       <c r="H139" t="n">
         <v>24490</v>
@@ -4458,7 +4458,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G141" t="n">
-        <v>2.4163031578064</v>
+        <v>2.41630291938782</v>
       </c>
       <c r="H141" t="n">
         <v>4028</v>
@@ -4516,7 +4516,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G143" t="n">
-        <v>2.42608547210693</v>
+        <v>2.42608571052551</v>
       </c>
       <c r="H143" t="n">
         <v>4605</v>
@@ -4545,7 +4545,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G144" t="n">
-        <v>2.42608547210693</v>
+        <v>2.42608571052551</v>
       </c>
       <c r="H144" t="n">
         <v>3188</v>
@@ -4574,7 +4574,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G145" t="n">
-        <v>2.42608547210693</v>
+        <v>2.42608571052551</v>
       </c>
       <c r="H145" t="n">
         <v>2500</v>
@@ -4603,7 +4603,7 @@
         <v>2.5</v>
       </c>
       <c r="G146" t="n">
-        <v>2.44565081596375</v>
+        <v>2.44565057754517</v>
       </c>
       <c r="H146" t="n">
         <v>5600</v>
@@ -4632,7 +4632,7 @@
         <v>2.5</v>
       </c>
       <c r="G147" t="n">
-        <v>2.44565081596375</v>
+        <v>2.44565057754517</v>
       </c>
       <c r="H147" t="n">
         <v>11043</v>
@@ -4719,7 +4719,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G150" t="n">
-        <v>2.42608547210693</v>
+        <v>2.42608571052551</v>
       </c>
       <c r="H150" t="n">
         <v>14700</v>
@@ -4777,7 +4777,7 @@
         <v>2.5</v>
       </c>
       <c r="G152" t="n">
-        <v>2.44565081596375</v>
+        <v>2.44565057754517</v>
       </c>
       <c r="H152" t="n">
         <v>10465</v>
@@ -4806,7 +4806,7 @@
         <v>2.5</v>
       </c>
       <c r="G153" t="n">
-        <v>2.44565081596375</v>
+        <v>2.44565057754517</v>
       </c>
       <c r="H153" t="n">
         <v>14241</v>
@@ -4835,7 +4835,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G154" t="n">
-        <v>2.48478102684021</v>
+        <v>2.48478126525879</v>
       </c>
       <c r="H154" t="n">
         <v>33850</v>
@@ -4864,7 +4864,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G155" t="n">
-        <v>2.50434613227844</v>
+        <v>2.50434637069702</v>
       </c>
       <c r="H155" t="n">
         <v>11685</v>
@@ -4980,7 +4980,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G159" t="n">
-        <v>2.4163031578064</v>
+        <v>2.41630291938782</v>
       </c>
       <c r="H159" t="n">
         <v>12350</v>
@@ -5038,7 +5038,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G161" t="n">
-        <v>2.42608547210693</v>
+        <v>2.42608571052551</v>
       </c>
       <c r="H161" t="n">
         <v>5543</v>
@@ -5067,7 +5067,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G162" t="n">
-        <v>2.42608547210693</v>
+        <v>2.42608571052551</v>
       </c>
       <c r="H162" t="n">
         <v>8850</v>
@@ -5096,7 +5096,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G163" t="n">
-        <v>2.61195492744446</v>
+        <v>2.61195516586304</v>
       </c>
       <c r="H163" t="n">
         <v>108022</v>
@@ -5241,7 +5241,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G168" t="n">
-        <v>2.90543341636658</v>
+        <v>2.905433177948</v>
       </c>
       <c r="H168" t="n">
         <v>40031</v>
@@ -5328,7 +5328,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G171" t="n">
-        <v>2.83695483207703</v>
+        <v>2.83695530891418</v>
       </c>
       <c r="H171" t="n">
         <v>69207</v>
@@ -5589,7 +5589,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G180" t="n">
-        <v>2.67065048217773</v>
+        <v>2.67065072059631</v>
       </c>
       <c r="H180" t="n">
         <v>5950</v>
@@ -5618,7 +5618,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G181" t="n">
-        <v>2.6608681678772</v>
+        <v>2.66086792945862</v>
       </c>
       <c r="H181" t="n">
         <v>6625</v>
@@ -5705,7 +5705,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G184" t="n">
-        <v>2.6608681678772</v>
+        <v>2.66086792945862</v>
       </c>
       <c r="H184" t="n">
         <v>12599</v>
@@ -5879,7 +5879,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G190" t="n">
-        <v>2.51412892341614</v>
+        <v>2.51412916183472</v>
       </c>
       <c r="H190" t="n">
         <v>117768</v>
@@ -5937,7 +5937,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G192" t="n">
-        <v>2.6608681678772</v>
+        <v>2.66086792945862</v>
       </c>
       <c r="H192" t="n">
         <v>32457</v>
@@ -6053,7 +6053,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G196" t="n">
-        <v>2.50434613227844</v>
+        <v>2.50434637069702</v>
       </c>
       <c r="H196" t="n">
         <v>18379</v>
@@ -6111,7 +6111,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G198" t="n">
-        <v>2.61195492744446</v>
+        <v>2.61195516586304</v>
       </c>
       <c r="H198" t="n">
         <v>20110</v>
@@ -6198,7 +6198,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G201" t="n">
-        <v>2.54347681999207</v>
+        <v>2.54347658157349</v>
       </c>
       <c r="H201" t="n">
         <v>32309</v>
@@ -6256,7 +6256,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G203" t="n">
-        <v>2.61195492744446</v>
+        <v>2.61195516586304</v>
       </c>
       <c r="H203" t="n">
         <v>23415</v>
@@ -6401,7 +6401,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G208" t="n">
-        <v>2.6608681678772</v>
+        <v>2.66086792945862</v>
       </c>
       <c r="H208" t="n">
         <v>13847</v>
@@ -6430,7 +6430,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G209" t="n">
-        <v>2.67065048217773</v>
+        <v>2.67065072059631</v>
       </c>
       <c r="H209" t="n">
         <v>30620</v>
@@ -6459,7 +6459,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G210" t="n">
-        <v>2.6608681678772</v>
+        <v>2.66086792945862</v>
       </c>
       <c r="H210" t="n">
         <v>23532</v>
@@ -6488,7 +6488,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G211" t="n">
-        <v>2.6608681678772</v>
+        <v>2.66086792945862</v>
       </c>
       <c r="H211" t="n">
         <v>16536</v>
@@ -6517,7 +6517,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G212" t="n">
-        <v>2.67065048217773</v>
+        <v>2.67065072059631</v>
       </c>
       <c r="H212" t="n">
         <v>9213</v>
@@ -6546,7 +6546,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G213" t="n">
-        <v>2.6608681678772</v>
+        <v>2.66086792945862</v>
       </c>
       <c r="H213" t="n">
         <v>11727</v>
@@ -6575,7 +6575,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G214" t="n">
-        <v>2.6608681678772</v>
+        <v>2.66086792945862</v>
       </c>
       <c r="H214" t="n">
         <v>22564</v>
@@ -6749,7 +6749,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G220" t="n">
-        <v>2.63691425323486</v>
+        <v>2.63691449165344</v>
       </c>
       <c r="H220" t="n">
         <v>54300</v>
@@ -6778,7 +6778,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G221" t="n">
-        <v>2.64675354957581</v>
+        <v>2.64675331115723</v>
       </c>
       <c r="H221" t="n">
         <v>42202</v>
@@ -6807,7 +6807,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G222" t="n">
-        <v>2.62707495689392</v>
+        <v>2.6270751953125</v>
       </c>
       <c r="H222" t="n">
         <v>18794</v>
@@ -6952,7 +6952,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G227" t="n">
-        <v>2.51884317398071</v>
+        <v>2.51884341239929</v>
       </c>
       <c r="H227" t="n">
         <v>30812</v>
@@ -6981,7 +6981,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G228" t="n">
-        <v>2.49916481971741</v>
+        <v>2.49916505813599</v>
       </c>
       <c r="H228" t="n">
         <v>48757</v>
@@ -7010,7 +7010,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G229" t="n">
-        <v>2.52868247032166</v>
+        <v>2.52868270874023</v>
       </c>
       <c r="H229" t="n">
         <v>15710</v>
@@ -7097,7 +7097,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G232" t="n">
-        <v>2.43029046058655</v>
+        <v>2.43029022216797</v>
       </c>
       <c r="H232" t="n">
         <v>31988</v>
@@ -7155,7 +7155,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G234" t="n">
-        <v>2.51884317398071</v>
+        <v>2.51884341239929</v>
       </c>
       <c r="H234" t="n">
         <v>39902</v>
@@ -7271,7 +7271,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G238" t="n">
-        <v>2.55820035934448</v>
+        <v>2.5582001209259</v>
       </c>
       <c r="H238" t="n">
         <v>26987</v>
@@ -7329,7 +7329,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G240" t="n">
-        <v>2.62707495689392</v>
+        <v>2.6270751953125</v>
       </c>
       <c r="H240" t="n">
         <v>3780</v>
@@ -7445,7 +7445,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G244" t="n">
-        <v>2.49916481971741</v>
+        <v>2.49916505813599</v>
       </c>
       <c r="H244" t="n">
         <v>24170</v>
@@ -7503,7 +7503,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G246" t="n">
-        <v>2.48932552337646</v>
+        <v>2.48932576179504</v>
       </c>
       <c r="H246" t="n">
         <v>1994</v>
@@ -7590,7 +7590,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G249" t="n">
-        <v>2.43029046058655</v>
+        <v>2.43029022216797</v>
       </c>
       <c r="H249" t="n">
         <v>5858</v>
@@ -7677,7 +7677,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G252" t="n">
-        <v>2.48932552337646</v>
+        <v>2.48932576179504</v>
       </c>
       <c r="H252" t="n">
         <v>810</v>
@@ -7793,7 +7793,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G256" t="n">
-        <v>2.42045116424561</v>
+        <v>2.42045092582703</v>
       </c>
       <c r="H256" t="n">
         <v>9824</v>
@@ -7822,7 +7822,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G257" t="n">
-        <v>2.42045116424561</v>
+        <v>2.42045092582703</v>
       </c>
       <c r="H257" t="n">
         <v>12307</v>
@@ -7880,7 +7880,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G259" t="n">
-        <v>2.48932552337646</v>
+        <v>2.48932576179504</v>
       </c>
       <c r="H259" t="n">
         <v>7500</v>
@@ -7909,7 +7909,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G260" t="n">
-        <v>2.48932552337646</v>
+        <v>2.48932576179504</v>
       </c>
       <c r="H260" t="n">
         <v>14171</v>
@@ -7967,7 +7967,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G262" t="n">
-        <v>2.42045116424561</v>
+        <v>2.42045092582703</v>
       </c>
       <c r="H262" t="n">
         <v>6545</v>
@@ -8025,7 +8025,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G264" t="n">
-        <v>2.43029046058655</v>
+        <v>2.43029022216797</v>
       </c>
       <c r="H264" t="n">
         <v>7020</v>
@@ -8141,7 +8141,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G268" t="n">
-        <v>2.43029046058655</v>
+        <v>2.43029022216797</v>
       </c>
       <c r="H268" t="n">
         <v>6909</v>
@@ -8170,7 +8170,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G269" t="n">
-        <v>2.42045116424561</v>
+        <v>2.42045092582703</v>
       </c>
       <c r="H269" t="n">
         <v>398</v>
@@ -8257,7 +8257,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G272" t="n">
-        <v>2.27286243438721</v>
+        <v>2.27286267280579</v>
       </c>
       <c r="H272" t="n">
         <v>19540</v>
@@ -8315,7 +8315,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G274" t="n">
-        <v>2.41061186790466</v>
+        <v>2.41061210632324</v>
       </c>
       <c r="H274" t="n">
         <v>2455</v>
@@ -8373,7 +8373,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G276" t="n">
-        <v>2.42045116424561</v>
+        <v>2.42045092582703</v>
       </c>
       <c r="H276" t="n">
         <v>4035</v>
@@ -8489,7 +8489,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G280" t="n">
-        <v>2.41061186790466</v>
+        <v>2.41061210632324</v>
       </c>
       <c r="H280" t="n">
         <v>2500</v>
@@ -8518,7 +8518,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G281" t="n">
-        <v>2.41061186790466</v>
+        <v>2.41061210632324</v>
       </c>
       <c r="H281" t="n">
         <v>3607</v>
@@ -8547,7 +8547,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G282" t="n">
-        <v>2.41061186790466</v>
+        <v>2.41061210632324</v>
       </c>
       <c r="H282" t="n">
         <v>3021</v>
@@ -8576,7 +8576,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G283" t="n">
-        <v>2.35157680511475</v>
+        <v>2.35157656669617</v>
       </c>
       <c r="H283" t="n">
         <v>3780</v>
@@ -8605,7 +8605,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G284" t="n">
-        <v>2.42045116424561</v>
+        <v>2.42045092582703</v>
       </c>
       <c r="H284" t="n">
         <v>7881</v>
@@ -8634,7 +8634,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G285" t="n">
-        <v>2.52868247032166</v>
+        <v>2.52868270874023</v>
       </c>
       <c r="H285" t="n">
         <v>42819</v>
@@ -8924,7 +8924,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G295" t="n">
-        <v>2.30238008499146</v>
+        <v>2.30238032341003</v>
       </c>
       <c r="H295" t="n">
         <v>44626</v>
@@ -9040,7 +9040,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G299" t="n">
-        <v>2.27286243438721</v>
+        <v>2.27286267280579</v>
       </c>
       <c r="H299" t="n">
         <v>50689</v>
@@ -9069,7 +9069,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G300" t="n">
-        <v>2.20398807525635</v>
+        <v>2.20398783683777</v>
       </c>
       <c r="H300" t="n">
         <v>34470</v>
@@ -9185,7 +9185,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G304" t="n">
-        <v>2.27286243438721</v>
+        <v>2.27286267280579</v>
       </c>
       <c r="H304" t="n">
         <v>15470</v>
@@ -9243,7 +9243,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G306" t="n">
-        <v>2.30238008499146</v>
+        <v>2.30238032341003</v>
       </c>
       <c r="H306" t="n">
         <v>1100</v>
@@ -9417,7 +9417,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G312" t="n">
-        <v>2.35157680511475</v>
+        <v>2.35157656669617</v>
       </c>
       <c r="H312" t="n">
         <v>25055</v>
@@ -9446,7 +9446,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G313" t="n">
-        <v>2.41061186790466</v>
+        <v>2.41061210632324</v>
       </c>
       <c r="H313" t="n">
         <v>37964</v>
@@ -9678,7 +9678,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G321" t="n">
-        <v>2.27286243438721</v>
+        <v>2.27286267280579</v>
       </c>
       <c r="H321" t="n">
         <v>3425</v>
@@ -9707,7 +9707,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G322" t="n">
-        <v>2.28270173072815</v>
+        <v>2.28270196914673</v>
       </c>
       <c r="H322" t="n">
         <v>16706</v>
@@ -9823,7 +9823,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G326" t="n">
-        <v>2.35157680511475</v>
+        <v>2.35157656669617</v>
       </c>
       <c r="H326" t="n">
         <v>2807</v>
@@ -9910,7 +9910,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G329" t="n">
-        <v>2.28270173072815</v>
+        <v>2.28270196914673</v>
       </c>
       <c r="H329" t="n">
         <v>4326</v>
@@ -9939,7 +9939,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G330" t="n">
-        <v>2.30238008499146</v>
+        <v>2.30238032341003</v>
       </c>
       <c r="H330" t="n">
         <v>2424</v>
@@ -9997,7 +9997,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G332" t="n">
-        <v>2.30238008499146</v>
+        <v>2.30238032341003</v>
       </c>
       <c r="H332" t="n">
         <v>1205</v>
@@ -10055,7 +10055,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G334" t="n">
-        <v>2.20398807525635</v>
+        <v>2.20398783683777</v>
       </c>
       <c r="H334" t="n">
         <v>12548</v>
@@ -10142,7 +10142,7 @@
         <v>2.25</v>
       </c>
       <c r="G337" t="n">
-        <v>2.21382737159729</v>
+        <v>2.21382713317871</v>
       </c>
       <c r="H337" t="n">
         <v>4451</v>
@@ -10316,7 +10316,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G343" t="n">
-        <v>2.41061186790466</v>
+        <v>2.41061210632324</v>
       </c>
       <c r="H343" t="n">
         <v>157345</v>
@@ -10345,7 +10345,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G344" t="n">
-        <v>2.41061186790466</v>
+        <v>2.41061210632324</v>
       </c>
       <c r="H344" t="n">
         <v>177569</v>
@@ -10374,7 +10374,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G345" t="n">
-        <v>2.28270173072815</v>
+        <v>2.28270196914673</v>
       </c>
       <c r="H345" t="n">
         <v>36620</v>
@@ -10490,7 +10490,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G349" t="n">
-        <v>2.35157680511475</v>
+        <v>2.35157656669617</v>
       </c>
       <c r="H349" t="n">
         <v>12100</v>
@@ -10548,7 +10548,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G351" t="n">
-        <v>2.28270173072815</v>
+        <v>2.28270196914673</v>
       </c>
       <c r="H351" t="n">
         <v>6350</v>
@@ -10606,7 +10606,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G353" t="n">
-        <v>2.28270173072815</v>
+        <v>2.28270196914673</v>
       </c>
       <c r="H353" t="n">
         <v>6000</v>
@@ -10635,7 +10635,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G354" t="n">
-        <v>2.28270173072815</v>
+        <v>2.28270196914673</v>
       </c>
       <c r="H354" t="n">
         <v>4900</v>
@@ -10664,7 +10664,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G355" t="n">
-        <v>2.27286243438721</v>
+        <v>2.27286267280579</v>
       </c>
       <c r="H355" t="n">
         <v>5466</v>
@@ -10693,7 +10693,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G356" t="n">
-        <v>2.28270173072815</v>
+        <v>2.28270196914673</v>
       </c>
       <c r="H356" t="n">
         <v>4255</v>
@@ -10751,7 +10751,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G358" t="n">
-        <v>2.28270173072815</v>
+        <v>2.28270196914673</v>
       </c>
       <c r="H358" t="n">
         <v>9650</v>
@@ -10780,7 +10780,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G359" t="n">
-        <v>2.27286243438721</v>
+        <v>2.27286267280579</v>
       </c>
       <c r="H359" t="n">
         <v>10142</v>
@@ -10809,7 +10809,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G360" t="n">
-        <v>2.28270173072815</v>
+        <v>2.28270196914673</v>
       </c>
       <c r="H360" t="n">
         <v>6650</v>
@@ -10838,7 +10838,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G361" t="n">
-        <v>2.30238008499146</v>
+        <v>2.30238032341003</v>
       </c>
       <c r="H361" t="n">
         <v>1405</v>
@@ -10867,7 +10867,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G362" t="n">
-        <v>2.30238008499146</v>
+        <v>2.30238032341003</v>
       </c>
       <c r="H362" t="n">
         <v>136082</v>
@@ -10896,7 +10896,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G363" t="n">
-        <v>2.30238008499146</v>
+        <v>2.30238032341003</v>
       </c>
       <c r="H363" t="n">
         <v>0</v>
@@ -10954,7 +10954,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G365" t="n">
-        <v>2.41061186790466</v>
+        <v>2.41061210632324</v>
       </c>
       <c r="H365" t="n">
         <v>46145</v>
@@ -11070,7 +11070,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G369" t="n">
-        <v>2.53852200508118</v>
+        <v>2.5385217666626</v>
       </c>
       <c r="H369" t="n">
         <v>58285</v>
@@ -11157,7 +11157,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G372" t="n">
-        <v>2.48932552337646</v>
+        <v>2.48932576179504</v>
       </c>
       <c r="H372" t="n">
         <v>30239</v>
@@ -11360,7 +11360,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G379" t="n">
-        <v>2.35157680511475</v>
+        <v>2.35157656669617</v>
       </c>
       <c r="H379" t="n">
         <v>1201</v>
@@ -11534,7 +11534,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G385" t="n">
-        <v>2.43029046058655</v>
+        <v>2.43029022216797</v>
       </c>
       <c r="H385" t="n">
         <v>25280</v>
@@ -11592,7 +11592,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G387" t="n">
-        <v>2.43029046058655</v>
+        <v>2.43029022216797</v>
       </c>
       <c r="H387" t="n">
         <v>13258</v>
@@ -11766,7 +11766,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G393" t="n">
-        <v>2.35157680511475</v>
+        <v>2.35157656669617</v>
       </c>
       <c r="H393" t="n">
         <v>1601</v>
@@ -12172,7 +12172,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G407" t="n">
-        <v>2.42045116424561</v>
+        <v>2.42045092582703</v>
       </c>
       <c r="H407" t="n">
         <v>11611</v>
@@ -12288,7 +12288,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G411" t="n">
-        <v>2.48932552337646</v>
+        <v>2.48932576179504</v>
       </c>
       <c r="H411" t="n">
         <v>11281</v>
@@ -12317,7 +12317,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G412" t="n">
-        <v>2.48932552337646</v>
+        <v>2.48932576179504</v>
       </c>
       <c r="H412" t="n">
         <v>951</v>
@@ -12346,7 +12346,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G413" t="n">
-        <v>2.42045116424561</v>
+        <v>2.42045092582703</v>
       </c>
       <c r="H413" t="n">
         <v>180</v>
@@ -12578,7 +12578,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G421" t="n">
-        <v>2.49916481971741</v>
+        <v>2.49916505813599</v>
       </c>
       <c r="H421" t="n">
         <v>16752</v>
@@ -12665,7 +12665,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G424" t="n">
-        <v>2.49916481971741</v>
+        <v>2.49916505813599</v>
       </c>
       <c r="H424" t="n">
         <v>35639</v>
@@ -12752,7 +12752,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G427" t="n">
-        <v>2.55820035934448</v>
+        <v>2.5582001209259</v>
       </c>
       <c r="H427" t="n">
         <v>559114</v>
@@ -12781,7 +12781,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G428" t="n">
-        <v>2.52868247032166</v>
+        <v>2.52868270874023</v>
       </c>
       <c r="H428" t="n">
         <v>29512</v>
@@ -12897,7 +12897,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G432" t="n">
-        <v>2.51884317398071</v>
+        <v>2.51884341239929</v>
       </c>
       <c r="H432" t="n">
         <v>60938</v>
@@ -12955,7 +12955,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G434" t="n">
-        <v>2.55820035934448</v>
+        <v>2.5582001209259</v>
       </c>
       <c r="H434" t="n">
         <v>47155</v>
@@ -12984,7 +12984,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G435" t="n">
-        <v>2.52868247032166</v>
+        <v>2.52868270874023</v>
       </c>
       <c r="H435" t="n">
         <v>20543</v>
@@ -13042,7 +13042,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G437" t="n">
-        <v>2.52868247032166</v>
+        <v>2.52868270874023</v>
       </c>
       <c r="H437" t="n">
         <v>12222</v>
@@ -13071,7 +13071,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G438" t="n">
-        <v>2.51884317398071</v>
+        <v>2.51884341239929</v>
       </c>
       <c r="H438" t="n">
         <v>18341</v>
@@ -13100,7 +13100,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G439" t="n">
-        <v>2.52868247032166</v>
+        <v>2.52868270874023</v>
       </c>
       <c r="H439" t="n">
         <v>19433</v>
@@ -13129,7 +13129,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G440" t="n">
-        <v>2.43029046058655</v>
+        <v>2.43029022216797</v>
       </c>
       <c r="H440" t="n">
         <v>23395</v>
@@ -13216,7 +13216,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G443" t="n">
-        <v>2.41061186790466</v>
+        <v>2.41061210632324</v>
       </c>
       <c r="H443" t="n">
         <v>15137</v>
@@ -13274,7 +13274,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G445" t="n">
-        <v>2.49916481971741</v>
+        <v>2.49916505813599</v>
       </c>
       <c r="H445" t="n">
         <v>52693</v>
@@ -13332,7 +13332,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G447" t="n">
-        <v>2.28270173072815</v>
+        <v>2.28270196914673</v>
       </c>
       <c r="H447" t="n">
         <v>23165</v>
@@ -13361,7 +13361,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G448" t="n">
-        <v>2.28270173072815</v>
+        <v>2.28270196914673</v>
       </c>
       <c r="H448" t="n">
         <v>40210</v>
@@ -13477,7 +13477,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G452" t="n">
-        <v>2.43029046058655</v>
+        <v>2.43029022216797</v>
       </c>
       <c r="H452" t="n">
         <v>37050</v>
@@ -13622,7 +13622,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G457" t="n">
-        <v>2.49916481971741</v>
+        <v>2.49916505813599</v>
       </c>
       <c r="H457" t="n">
         <v>35738</v>
@@ -13651,7 +13651,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G458" t="n">
-        <v>2.51884317398071</v>
+        <v>2.51884341239929</v>
       </c>
       <c r="H458" t="n">
         <v>18389</v>
@@ -13680,7 +13680,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G459" t="n">
-        <v>2.51884317398071</v>
+        <v>2.51884341239929</v>
       </c>
       <c r="H459" t="n">
         <v>0</v>
@@ -13709,7 +13709,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G460" t="n">
-        <v>2.43029046058655</v>
+        <v>2.43029022216797</v>
       </c>
       <c r="H460" t="n">
         <v>29119</v>
@@ -13825,7 +13825,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G464" t="n">
-        <v>2.42045116424561</v>
+        <v>2.42045092582703</v>
       </c>
       <c r="H464" t="n">
         <v>2155</v>
@@ -13854,7 +13854,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G465" t="n">
-        <v>2.41061186790466</v>
+        <v>2.41061210632324</v>
       </c>
       <c r="H465" t="n">
         <v>3505</v>
@@ -13941,7 +13941,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G468" t="n">
-        <v>2.42045116424561</v>
+        <v>2.42045092582703</v>
       </c>
       <c r="H468" t="n">
         <v>5886</v>
@@ -13970,7 +13970,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G469" t="n">
-        <v>2.42045116424561</v>
+        <v>2.42045092582703</v>
       </c>
       <c r="H469" t="n">
         <v>0</v>
@@ -14028,7 +14028,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G471" t="n">
-        <v>2.43029046058655</v>
+        <v>2.43029022216797</v>
       </c>
       <c r="H471" t="n">
         <v>8504</v>
@@ -14144,7 +14144,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G475" t="n">
-        <v>2.42045116424561</v>
+        <v>2.42045092582703</v>
       </c>
       <c r="H475" t="n">
         <v>5971</v>
@@ -14260,7 +14260,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G479" t="n">
-        <v>2.43029046058655</v>
+        <v>2.43029022216797</v>
       </c>
       <c r="H479" t="n">
         <v>7842</v>
@@ -14318,7 +14318,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G481" t="n">
-        <v>2.42045116424561</v>
+        <v>2.42045092582703</v>
       </c>
       <c r="H481" t="n">
         <v>3675</v>
@@ -14376,7 +14376,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G483" t="n">
-        <v>2.42045116424561</v>
+        <v>2.42045092582703</v>
       </c>
       <c r="H483" t="n">
         <v>6429</v>
@@ -14492,7 +14492,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G487" t="n">
-        <v>2.41061186790466</v>
+        <v>2.41061210632324</v>
       </c>
       <c r="H487" t="n">
         <v>1829</v>
@@ -14521,7 +14521,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G488" t="n">
-        <v>2.41061186790466</v>
+        <v>2.41061210632324</v>
       </c>
       <c r="H488" t="n">
         <v>0</v>
@@ -14579,7 +14579,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G490" t="n">
-        <v>2.41061186790466</v>
+        <v>2.41061210632324</v>
       </c>
       <c r="H490" t="n">
         <v>18612</v>
@@ -14666,7 +14666,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G493" t="n">
-        <v>2.41061186790466</v>
+        <v>2.41061210632324</v>
       </c>
       <c r="H493" t="n">
         <v>1</v>
@@ -14695,7 +14695,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G494" t="n">
-        <v>2.41061186790466</v>
+        <v>2.41061210632324</v>
       </c>
       <c r="H494" t="n">
         <v>0</v>
@@ -14724,7 +14724,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G495" t="n">
-        <v>2.41061186790466</v>
+        <v>2.41061210632324</v>
       </c>
       <c r="H495" t="n">
         <v>20619</v>
@@ -14869,7 +14869,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G500" t="n">
-        <v>2.48932552337646</v>
+        <v>2.48932576179504</v>
       </c>
       <c r="H500" t="n">
         <v>22406</v>
@@ -14898,7 +14898,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G501" t="n">
-        <v>2.41061186790466</v>
+        <v>2.41061210632324</v>
       </c>
       <c r="H501" t="n">
         <v>232</v>
@@ -14985,7 +14985,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G504" t="n">
-        <v>2.42045116424561</v>
+        <v>2.42045092582703</v>
       </c>
       <c r="H504" t="n">
         <v>3174</v>
@@ -15014,7 +15014,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G505" t="n">
-        <v>2.42045116424561</v>
+        <v>2.42045092582703</v>
       </c>
       <c r="H505" t="n">
         <v>0</v>
@@ -15072,7 +15072,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G507" t="n">
-        <v>2.42045116424561</v>
+        <v>2.42045092582703</v>
       </c>
       <c r="H507" t="n">
         <v>4</v>
@@ -15130,7 +15130,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G509" t="n">
-        <v>2.43029046058655</v>
+        <v>2.43029022216797</v>
       </c>
       <c r="H509" t="n">
         <v>6606</v>
@@ -15159,7 +15159,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G510" t="n">
-        <v>2.43029046058655</v>
+        <v>2.43029022216797</v>
       </c>
       <c r="H510" t="n">
         <v>4444</v>
@@ -15217,7 +15217,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G512" t="n">
-        <v>2.49916481971741</v>
+        <v>2.49916505813599</v>
       </c>
       <c r="H512" t="n">
         <v>18429</v>
@@ -15304,7 +15304,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G515" t="n">
-        <v>2.48932552337646</v>
+        <v>2.48932576179504</v>
       </c>
       <c r="H515" t="n">
         <v>421</v>
@@ -15536,7 +15536,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G523" t="n">
-        <v>2.55820035934448</v>
+        <v>2.5582001209259</v>
       </c>
       <c r="H523" t="n">
         <v>28775</v>
@@ -15681,7 +15681,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G528" t="n">
-        <v>2.55820035934448</v>
+        <v>2.5582001209259</v>
       </c>
       <c r="H528" t="n">
         <v>6832</v>
@@ -15710,7 +15710,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G529" t="n">
-        <v>2.52868247032166</v>
+        <v>2.52868270874023</v>
       </c>
       <c r="H529" t="n">
         <v>7700</v>
@@ -15739,7 +15739,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G530" t="n">
-        <v>2.55820035934448</v>
+        <v>2.5582001209259</v>
       </c>
       <c r="H530" t="n">
         <v>6304</v>
@@ -15826,7 +15826,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G533" t="n">
-        <v>2.63691425323486</v>
+        <v>2.63691449165344</v>
       </c>
       <c r="H533" t="n">
         <v>19150</v>
@@ -15884,7 +15884,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G535" t="n">
-        <v>2.53852200508118</v>
+        <v>2.5385217666626</v>
       </c>
       <c r="H535" t="n">
         <v>7600</v>
@@ -15913,7 +15913,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G536" t="n">
-        <v>2.55820035934448</v>
+        <v>2.5582001209259</v>
       </c>
       <c r="H536" t="n">
         <v>1850</v>
@@ -15971,7 +15971,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G538" t="n">
-        <v>2.55820035934448</v>
+        <v>2.5582001209259</v>
       </c>
       <c r="H538" t="n">
         <v>2300</v>
@@ -16000,7 +16000,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G539" t="n">
-        <v>2.55820035934448</v>
+        <v>2.5582001209259</v>
       </c>
       <c r="H539" t="n">
         <v>3806</v>
@@ -16029,7 +16029,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G540" t="n">
-        <v>2.53852200508118</v>
+        <v>2.5385217666626</v>
       </c>
       <c r="H540" t="n">
         <v>6800</v>
@@ -16058,7 +16058,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G541" t="n">
-        <v>2.55820035934448</v>
+        <v>2.5582001209259</v>
       </c>
       <c r="H541" t="n">
         <v>8509</v>
@@ -16087,7 +16087,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G542" t="n">
-        <v>2.55820035934448</v>
+        <v>2.5582001209259</v>
       </c>
       <c r="H542" t="n">
         <v>6554</v>
@@ -16145,7 +16145,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G544" t="n">
-        <v>2.64675354957581</v>
+        <v>2.64675331115723</v>
       </c>
       <c r="H544" t="n">
         <v>29045</v>
@@ -16174,7 +16174,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G545" t="n">
-        <v>2.64675354957581</v>
+        <v>2.64675331115723</v>
       </c>
       <c r="H545" t="n">
         <v>24168</v>
@@ -16232,7 +16232,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G547" t="n">
-        <v>2.35157680511475</v>
+        <v>2.35157656669617</v>
       </c>
       <c r="H547" t="n">
         <v>106601</v>
@@ -16319,7 +16319,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G550" t="n">
-        <v>2.30238008499146</v>
+        <v>2.30238032341003</v>
       </c>
       <c r="H550" t="n">
         <v>10856</v>
@@ -16406,7 +16406,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G553" t="n">
-        <v>2.28270173072815</v>
+        <v>2.28270196914673</v>
       </c>
       <c r="H553" t="n">
         <v>7360</v>
@@ -16522,7 +16522,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G557" t="n">
-        <v>2.27286243438721</v>
+        <v>2.27286267280579</v>
       </c>
       <c r="H557" t="n">
         <v>3150</v>
@@ -16551,7 +16551,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G558" t="n">
-        <v>2.27286243438721</v>
+        <v>2.27286267280579</v>
       </c>
       <c r="H558" t="n">
         <v>0</v>
@@ -16580,7 +16580,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G559" t="n">
-        <v>2.27286243438721</v>
+        <v>2.27286267280579</v>
       </c>
       <c r="H559" t="n">
         <v>4065</v>
@@ -16609,7 +16609,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G560" t="n">
-        <v>2.28270173072815</v>
+        <v>2.28270196914673</v>
       </c>
       <c r="H560" t="n">
         <v>890</v>
@@ -16667,7 +16667,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G562" t="n">
-        <v>2.24334502220154</v>
+        <v>2.24334478378296</v>
       </c>
       <c r="H562" t="n">
         <v>11905</v>
@@ -16696,7 +16696,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G563" t="n">
-        <v>2.20398807525635</v>
+        <v>2.20398783683777</v>
       </c>
       <c r="H563" t="n">
         <v>34790</v>
@@ -16754,7 +16754,7 @@
         <v>2.25</v>
       </c>
       <c r="G565" t="n">
-        <v>2.21382737159729</v>
+        <v>2.21382713317871</v>
       </c>
       <c r="H565" t="n">
         <v>1201</v>
@@ -16783,7 +16783,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G566" t="n">
-        <v>2.27286243438721</v>
+        <v>2.27286267280579</v>
       </c>
       <c r="H566" t="n">
         <v>500</v>
@@ -16899,7 +16899,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G570" t="n">
-        <v>2.24334502220154</v>
+        <v>2.24334478378296</v>
       </c>
       <c r="H570" t="n">
         <v>18090</v>
@@ -16986,7 +16986,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G573" t="n">
-        <v>2.28270173072815</v>
+        <v>2.28270196914673</v>
       </c>
       <c r="H573" t="n">
         <v>2415</v>
@@ -17015,7 +17015,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G574" t="n">
-        <v>2.20398807525635</v>
+        <v>2.20398783683777</v>
       </c>
       <c r="H574" t="n">
         <v>24592</v>
@@ -17131,7 +17131,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G578" t="n">
-        <v>2.28270173072815</v>
+        <v>2.28270196914673</v>
       </c>
       <c r="H578" t="n">
         <v>2017</v>
@@ -17189,7 +17189,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G580" t="n">
-        <v>2.27286243438721</v>
+        <v>2.27286267280579</v>
       </c>
       <c r="H580" t="n">
         <v>2648</v>
@@ -17218,7 +17218,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G581" t="n">
-        <v>2.28270173072815</v>
+        <v>2.28270196914673</v>
       </c>
       <c r="H581" t="n">
         <v>1455</v>
@@ -17276,7 +17276,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G583" t="n">
-        <v>2.30238008499146</v>
+        <v>2.30238032341003</v>
       </c>
       <c r="H583" t="n">
         <v>4608</v>
@@ -17653,7 +17653,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G596" t="n">
-        <v>2.28270173072815</v>
+        <v>2.28270196914673</v>
       </c>
       <c r="H596" t="n">
         <v>3802</v>
@@ -17740,7 +17740,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G599" t="n">
-        <v>2.30238008499146</v>
+        <v>2.30238032341003</v>
       </c>
       <c r="H599" t="n">
         <v>2949</v>
@@ -17798,7 +17798,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G601" t="n">
-        <v>2.24334502220154</v>
+        <v>2.24334478378296</v>
       </c>
       <c r="H601" t="n">
         <v>17283</v>
@@ -17827,7 +17827,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G602" t="n">
-        <v>2.27286243438721</v>
+        <v>2.27286267280579</v>
       </c>
       <c r="H602" t="n">
         <v>2094</v>
@@ -17856,7 +17856,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G603" t="n">
-        <v>2.27286243438721</v>
+        <v>2.27286267280579</v>
       </c>
       <c r="H603" t="n">
         <v>4262</v>
@@ -17914,7 +17914,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G605" t="n">
-        <v>2.30238008499146</v>
+        <v>2.30238032341003</v>
       </c>
       <c r="H605" t="n">
         <v>3421</v>
@@ -17943,7 +17943,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G606" t="n">
-        <v>2.30238008499146</v>
+        <v>2.30238032341003</v>
       </c>
       <c r="H606" t="n">
         <v>1394</v>
@@ -17972,7 +17972,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G607" t="n">
-        <v>2.30238008499146</v>
+        <v>2.30238032341003</v>
       </c>
       <c r="H607" t="n">
         <v>1488</v>
@@ -18001,7 +18001,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G608" t="n">
-        <v>2.30238008499146</v>
+        <v>2.30238032341003</v>
       </c>
       <c r="H608" t="n">
         <v>1944</v>
@@ -18030,7 +18030,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G609" t="n">
-        <v>2.30238008499146</v>
+        <v>2.30238032341003</v>
       </c>
       <c r="H609" t="n">
         <v>1543</v>
@@ -18088,7 +18088,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G611" t="n">
-        <v>2.30238008499146</v>
+        <v>2.30238032341003</v>
       </c>
       <c r="H611" t="n">
         <v>1209</v>
@@ -18146,7 +18146,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G613" t="n">
-        <v>2.27286243438721</v>
+        <v>2.27286267280579</v>
       </c>
       <c r="H613" t="n">
         <v>3339</v>
@@ -18407,7 +18407,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G622" t="n">
-        <v>2.24334502220154</v>
+        <v>2.24334478378296</v>
       </c>
       <c r="H622" t="n">
         <v>729</v>
@@ -18436,7 +18436,7 @@
         <v>2.25</v>
       </c>
       <c r="G623" t="n">
-        <v>2.21382737159729</v>
+        <v>2.21382713317871</v>
       </c>
       <c r="H623" t="n">
         <v>3507</v>
@@ -18494,7 +18494,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G625" t="n">
-        <v>2.24334502220154</v>
+        <v>2.24334478378296</v>
       </c>
       <c r="H625" t="n">
         <v>3357</v>
@@ -18610,7 +18610,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G629" t="n">
-        <v>2.24334502220154</v>
+        <v>2.24334478378296</v>
       </c>
       <c r="H629" t="n">
         <v>1003</v>
@@ -18639,7 +18639,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G630" t="n">
-        <v>2.28270173072815</v>
+        <v>2.28270196914673</v>
       </c>
       <c r="H630" t="n">
         <v>26686</v>
@@ -18668,7 +18668,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G631" t="n">
-        <v>2.28270173072815</v>
+        <v>2.28270196914673</v>
       </c>
       <c r="H631" t="n">
         <v>1654</v>
@@ -18726,7 +18726,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G633" t="n">
-        <v>2.28270173072815</v>
+        <v>2.28270196914673</v>
       </c>
       <c r="H633" t="n">
         <v>1752</v>
@@ -18755,7 +18755,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G634" t="n">
-        <v>2.28270173072815</v>
+        <v>2.28270196914673</v>
       </c>
       <c r="H634" t="n">
         <v>3413</v>
@@ -18900,7 +18900,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G639" t="n">
-        <v>2.27286243438721</v>
+        <v>2.27286267280579</v>
       </c>
       <c r="H639" t="n">
         <v>2152</v>
@@ -18929,7 +18929,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G640" t="n">
-        <v>2.28270173072815</v>
+        <v>2.28270196914673</v>
       </c>
       <c r="H640" t="n">
         <v>2342</v>
@@ -18987,7 +18987,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G642" t="n">
-        <v>2.24334502220154</v>
+        <v>2.24334478378296</v>
       </c>
       <c r="H642" t="n">
         <v>3219</v>
@@ -19074,7 +19074,7 @@
         <v>2.25</v>
       </c>
       <c r="G645" t="n">
-        <v>2.21382737159729</v>
+        <v>2.21382713317871</v>
       </c>
       <c r="H645" t="n">
         <v>5907</v>
@@ -19132,7 +19132,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G647" t="n">
-        <v>2.20398807525635</v>
+        <v>2.20398783683777</v>
       </c>
       <c r="H647" t="n">
         <v>2247</v>
@@ -19190,7 +19190,7 @@
         <v>2.25</v>
       </c>
       <c r="G649" t="n">
-        <v>2.21382737159729</v>
+        <v>2.21382713317871</v>
       </c>
       <c r="H649" t="n">
         <v>1413</v>
@@ -19306,7 +19306,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G653" t="n">
-        <v>2.13511323928833</v>
+        <v>2.13511347770691</v>
       </c>
       <c r="H653" t="n">
         <v>4940</v>
@@ -19335,7 +19335,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G654" t="n">
-        <v>2.14495253562927</v>
+        <v>2.14495277404785</v>
       </c>
       <c r="H654" t="n">
         <v>4916</v>
@@ -19480,7 +19480,7 @@
         <v>2.25</v>
       </c>
       <c r="G659" t="n">
-        <v>2.21382737159729</v>
+        <v>2.21382713317871</v>
       </c>
       <c r="H659" t="n">
         <v>8762</v>
@@ -19538,7 +19538,7 @@
         <v>2.25</v>
       </c>
       <c r="G661" t="n">
-        <v>2.21382737159729</v>
+        <v>2.21382713317871</v>
       </c>
       <c r="H661" t="n">
         <v>6280</v>
@@ -19683,7 +19683,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G666" t="n">
-        <v>2.24334502220154</v>
+        <v>2.24334478378296</v>
       </c>
       <c r="H666" t="n">
         <v>10498</v>
@@ -19799,7 +19799,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G670" t="n">
-        <v>2.20398807525635</v>
+        <v>2.20398783683777</v>
       </c>
       <c r="H670" t="n">
         <v>7844</v>
@@ -19828,7 +19828,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G671" t="n">
-        <v>2.24334502220154</v>
+        <v>2.24334478378296</v>
       </c>
       <c r="H671" t="n">
         <v>7122</v>
@@ -19857,7 +19857,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G672" t="n">
-        <v>2.24334502220154</v>
+        <v>2.24334478378296</v>
       </c>
       <c r="H672" t="n">
         <v>3472</v>
@@ -19886,7 +19886,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G673" t="n">
-        <v>2.24334502220154</v>
+        <v>2.24334478378296</v>
       </c>
       <c r="H673" t="n">
         <v>4302</v>
@@ -19973,7 +19973,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G676" t="n">
-        <v>2.20398807525635</v>
+        <v>2.20398783683777</v>
       </c>
       <c r="H676" t="n">
         <v>2219</v>
@@ -20118,7 +20118,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G681" t="n">
-        <v>2.27286243438721</v>
+        <v>2.27286267280579</v>
       </c>
       <c r="H681" t="n">
         <v>3394</v>
@@ -20234,7 +20234,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G685" t="n">
-        <v>2.35157680511475</v>
+        <v>2.35157656669617</v>
       </c>
       <c r="H685" t="n">
         <v>14060</v>
@@ -20321,7 +20321,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G688" t="n">
-        <v>2.35157680511475</v>
+        <v>2.35157656669617</v>
       </c>
       <c r="H688" t="n">
         <v>3921</v>
@@ -20756,7 +20756,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G703" t="n">
-        <v>2.30238008499146</v>
+        <v>2.30238032341003</v>
       </c>
       <c r="H703" t="n">
         <v>18619</v>
@@ -20785,7 +20785,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G704" t="n">
-        <v>2.30238008499146</v>
+        <v>2.30238032341003</v>
       </c>
       <c r="H704" t="n">
         <v>5776</v>
@@ -20814,7 +20814,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G705" t="n">
-        <v>2.30238008499146</v>
+        <v>2.30238032341003</v>
       </c>
       <c r="H705" t="n">
         <v>4067</v>
@@ -20843,7 +20843,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G706" t="n">
-        <v>2.28270173072815</v>
+        <v>2.28270196914673</v>
       </c>
       <c r="H706" t="n">
         <v>2590</v>
@@ -20872,7 +20872,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G707" t="n">
-        <v>2.24334502220154</v>
+        <v>2.24334478378296</v>
       </c>
       <c r="H707" t="n">
         <v>10831</v>
@@ -20988,7 +20988,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G711" t="n">
-        <v>2.43029046058655</v>
+        <v>2.43029022216797</v>
       </c>
       <c r="H711" t="n">
         <v>15029</v>
@@ -21017,7 +21017,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G712" t="n">
-        <v>2.43029046058655</v>
+        <v>2.43029022216797</v>
       </c>
       <c r="H712" t="n">
         <v>8791</v>
@@ -21133,7 +21133,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G716" t="n">
-        <v>2.35157680511475</v>
+        <v>2.35157656669617</v>
       </c>
       <c r="H716" t="n">
         <v>16386</v>
@@ -21162,7 +21162,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G717" t="n">
-        <v>2.43029046058655</v>
+        <v>2.43029022216797</v>
       </c>
       <c r="H717" t="n">
         <v>59441</v>
@@ -21307,7 +21307,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G722" t="n">
-        <v>2.35157680511475</v>
+        <v>2.35157656669617</v>
       </c>
       <c r="H722" t="n">
         <v>15797</v>
@@ -21365,7 +21365,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G724" t="n">
-        <v>2.35157680511475</v>
+        <v>2.35157656669617</v>
       </c>
       <c r="H724" t="n">
         <v>6782</v>
@@ -21423,7 +21423,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G726" t="n">
-        <v>2.41061186790466</v>
+        <v>2.41061210632324</v>
       </c>
       <c r="H726" t="n">
         <v>10601</v>
@@ -21452,7 +21452,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G727" t="n">
-        <v>2.43029046058655</v>
+        <v>2.43029022216797</v>
       </c>
       <c r="H727" t="n">
         <v>6641</v>
@@ -21481,7 +21481,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G728" t="n">
-        <v>2.43029046058655</v>
+        <v>2.43029022216797</v>
       </c>
       <c r="H728" t="n">
         <v>7749</v>
@@ -21597,7 +21597,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G732" t="n">
-        <v>2.41061186790466</v>
+        <v>2.41061210632324</v>
       </c>
       <c r="H732" t="n">
         <v>8506</v>
@@ -21771,7 +21771,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G738" t="n">
-        <v>2.35157680511475</v>
+        <v>2.35157656669617</v>
       </c>
       <c r="H738" t="n">
         <v>9988</v>
@@ -21887,7 +21887,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G742" t="n">
-        <v>2.49916481971741</v>
+        <v>2.49916505813599</v>
       </c>
       <c r="H742" t="n">
         <v>34943</v>
@@ -21945,7 +21945,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G744" t="n">
-        <v>2.48932552337646</v>
+        <v>2.48932576179504</v>
       </c>
       <c r="H744" t="n">
         <v>39865</v>
@@ -22003,7 +22003,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G746" t="n">
-        <v>2.48932552337646</v>
+        <v>2.48932576179504</v>
       </c>
       <c r="H746" t="n">
         <v>18877</v>
@@ -22032,7 +22032,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G747" t="n">
-        <v>2.51884317398071</v>
+        <v>2.51884341239929</v>
       </c>
       <c r="H747" t="n">
         <v>44586</v>
@@ -22061,7 +22061,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G748" t="n">
-        <v>2.52868247032166</v>
+        <v>2.52868270874023</v>
       </c>
       <c r="H748" t="n">
         <v>45070</v>
@@ -22206,7 +22206,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G753" t="n">
-        <v>2.63691425323486</v>
+        <v>2.63691449165344</v>
       </c>
       <c r="H753" t="n">
         <v>58392</v>
@@ -22264,7 +22264,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G755" t="n">
-        <v>2.77466344833374</v>
+        <v>2.77466320991516</v>
       </c>
       <c r="H755" t="n">
         <v>152514</v>
@@ -22322,7 +22322,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G757" t="n">
-        <v>2.71562790870667</v>
+        <v>2.71562814712524</v>
       </c>
       <c r="H757" t="n">
         <v>170397</v>
@@ -22380,7 +22380,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G759" t="n">
-        <v>2.77466344833374</v>
+        <v>2.77466320991516</v>
       </c>
       <c r="H759" t="n">
         <v>21143</v>
@@ -22409,7 +22409,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G760" t="n">
-        <v>2.77466344833374</v>
+        <v>2.77466320991516</v>
       </c>
       <c r="H760" t="n">
         <v>14482</v>
@@ -22438,7 +22438,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G761" t="n">
-        <v>2.77466344833374</v>
+        <v>2.77466320991516</v>
       </c>
       <c r="H761" t="n">
         <v>13481</v>
@@ -22583,7 +22583,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G766" t="n">
-        <v>2.77466344833374</v>
+        <v>2.77466320991516</v>
       </c>
       <c r="H766" t="n">
         <v>11073</v>
@@ -22641,7 +22641,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G768" t="n">
-        <v>2.77466344833374</v>
+        <v>2.77466320991516</v>
       </c>
       <c r="H768" t="n">
         <v>16757</v>
@@ -22786,7 +22786,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G773" t="n">
-        <v>3.00096583366394</v>
+        <v>3.00096559524536</v>
       </c>
       <c r="H773" t="n">
         <v>78428</v>
@@ -22873,7 +22873,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G776" t="n">
-        <v>3.00096583366394</v>
+        <v>3.00096559524536</v>
       </c>
       <c r="H776" t="n">
         <v>13843</v>
@@ -22960,7 +22960,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G779" t="n">
-        <v>3.00096583366394</v>
+        <v>3.00096559524536</v>
       </c>
       <c r="H779" t="n">
         <v>12842</v>
@@ -23018,7 +23018,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G781" t="n">
-        <v>3.00096583366394</v>
+        <v>3.00096559524536</v>
       </c>
       <c r="H781" t="n">
         <v>25556</v>
@@ -23221,7 +23221,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G788" t="n">
-        <v>2.9124128818512</v>
+        <v>2.91241264343262</v>
       </c>
       <c r="H788" t="n">
         <v>28876</v>
@@ -23279,7 +23279,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G790" t="n">
-        <v>2.84353804588318</v>
+        <v>2.84353828430176</v>
       </c>
       <c r="H790" t="n">
         <v>12028</v>
@@ -23308,7 +23308,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G791" t="n">
-        <v>2.92225217819214</v>
+        <v>2.92225193977356</v>
       </c>
       <c r="H791" t="n">
         <v>36996</v>
@@ -23366,7 +23366,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G793" t="n">
-        <v>2.92225217819214</v>
+        <v>2.92225193977356</v>
       </c>
       <c r="H793" t="n">
         <v>20612</v>
@@ -23395,7 +23395,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G794" t="n">
-        <v>2.90257334709167</v>
+        <v>2.90257358551025</v>
       </c>
       <c r="H794" t="n">
         <v>5153</v>
@@ -23511,7 +23511,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G798" t="n">
-        <v>2.9124128818512</v>
+        <v>2.91241264343262</v>
       </c>
       <c r="H798" t="n">
         <v>29046</v>
@@ -23743,7 +23743,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G806" t="n">
-        <v>3.09935832023621</v>
+        <v>3.09935808181763</v>
       </c>
       <c r="H806" t="n">
         <v>21409</v>
@@ -23801,7 +23801,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G808" t="n">
-        <v>3.1387152671814</v>
+        <v>3.13871502876282</v>
       </c>
       <c r="H808" t="n">
         <v>29053</v>
@@ -24004,7 +24004,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G815" t="n">
-        <v>3.16823267936707</v>
+        <v>3.16823291778564</v>
       </c>
       <c r="H815" t="n">
         <v>40945</v>
@@ -24207,7 +24207,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G822" t="n">
-        <v>3.32566070556641</v>
+        <v>3.32566046714783</v>
       </c>
       <c r="H822" t="n">
         <v>8250</v>
@@ -24352,7 +24352,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G827" t="n">
-        <v>3.41421341896057</v>
+        <v>3.41421365737915</v>
       </c>
       <c r="H827" t="n">
         <v>49728</v>
@@ -24381,7 +24381,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G828" t="n">
-        <v>3.42405271530151</v>
+        <v>3.42405295372009</v>
       </c>
       <c r="H828" t="n">
         <v>21052</v>
@@ -24410,7 +24410,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G829" t="n">
-        <v>3.48308825492859</v>
+        <v>3.48308801651001</v>
       </c>
       <c r="H829" t="n">
         <v>56595</v>
@@ -24468,7 +24468,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G831" t="n">
-        <v>3.57164144515991</v>
+        <v>3.57164120674133</v>
       </c>
       <c r="H831" t="n">
         <v>31184</v>
@@ -24555,7 +24555,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G834" t="n">
-        <v>4.12263822555542</v>
+        <v>4.12263870239258</v>
       </c>
       <c r="H834" t="n">
         <v>162852</v>
@@ -24584,7 +24584,7 @@
         <v>4.25</v>
       </c>
       <c r="G835" t="n">
-        <v>4.18167400360107</v>
+        <v>4.18167352676392</v>
       </c>
       <c r="H835" t="n">
         <v>105792</v>
@@ -24700,7 +24700,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G839" t="n">
-        <v>4.22103071212769</v>
+        <v>4.22103023529053</v>
       </c>
       <c r="H839" t="n">
         <v>31763</v>
@@ -24758,7 +24758,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G841" t="n">
-        <v>4.28990507125854</v>
+        <v>4.2899055480957</v>
       </c>
       <c r="H841" t="n">
         <v>33142</v>
@@ -24816,7 +24816,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G843" t="n">
-        <v>4.39813661575317</v>
+        <v>4.39813613891602</v>
       </c>
       <c r="H843" t="n">
         <v>122860</v>
@@ -24990,7 +24990,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G849" t="n">
-        <v>5.07704401016235</v>
+        <v>5.0770435333252</v>
       </c>
       <c r="H849" t="n">
         <v>125520</v>
@@ -25019,7 +25019,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G850" t="n">
-        <v>4.99832963943481</v>
+        <v>4.99833011627197</v>
       </c>
       <c r="H850" t="n">
         <v>94101</v>
@@ -25077,7 +25077,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G852" t="n">
-        <v>5.03768634796143</v>
+        <v>5.03768682479858</v>
       </c>
       <c r="H852" t="n">
         <v>39665</v>
@@ -25222,7 +25222,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G857" t="n">
-        <v>5.03768634796143</v>
+        <v>5.03768682479858</v>
       </c>
       <c r="H857" t="n">
         <v>29318</v>
@@ -25280,7 +25280,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G859" t="n">
-        <v>4.8605809211731</v>
+        <v>4.86058044433594</v>
       </c>
       <c r="H859" t="n">
         <v>18569</v>
@@ -25309,7 +25309,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G860" t="n">
-        <v>4.83106279373169</v>
+        <v>4.83106327056885</v>
       </c>
       <c r="H860" t="n">
         <v>56243</v>
@@ -25338,7 +25338,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G861" t="n">
-        <v>4.89009857177734</v>
+        <v>4.89009809494019</v>
       </c>
       <c r="H861" t="n">
         <v>26996</v>
@@ -25425,7 +25425,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G864" t="n">
-        <v>4.89009857177734</v>
+        <v>4.89009809494019</v>
       </c>
       <c r="H864" t="n">
         <v>17018</v>
@@ -25512,7 +25512,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G867" t="n">
-        <v>5.29350709915161</v>
+        <v>5.29350662231445</v>
       </c>
       <c r="H867" t="n">
         <v>54581</v>
@@ -25570,7 +25570,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G869" t="n">
-        <v>5.70675468444824</v>
+        <v>5.7067551612854</v>
       </c>
       <c r="H869" t="n">
         <v>193218</v>
@@ -25599,7 +25599,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G870" t="n">
-        <v>5.80514669418335</v>
+        <v>5.80514717102051</v>
       </c>
       <c r="H870" t="n">
         <v>93551</v>
@@ -25628,7 +25628,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G871" t="n">
-        <v>5.68707609176636</v>
+        <v>5.68707656860352</v>
       </c>
       <c r="H871" t="n">
         <v>93418</v>
@@ -25686,7 +25686,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G873" t="n">
-        <v>5.43125581741333</v>
+        <v>5.43125629425049</v>
       </c>
       <c r="H873" t="n">
         <v>19758</v>
@@ -25773,7 +25773,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G876" t="n">
-        <v>5.27382850646973</v>
+        <v>5.27382898330688</v>
       </c>
       <c r="H876" t="n">
         <v>74967</v>
@@ -25802,7 +25802,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G877" t="n">
-        <v>5.29350709915161</v>
+        <v>5.29350662231445</v>
       </c>
       <c r="H877" t="n">
         <v>29227</v>
@@ -25860,7 +25860,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G879" t="n">
-        <v>5.05736494064331</v>
+        <v>5.05736541748047</v>
       </c>
       <c r="H879" t="n">
         <v>31367</v>
@@ -25918,7 +25918,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G881" t="n">
-        <v>5.03768634796143</v>
+        <v>5.03768682479858</v>
       </c>
       <c r="H881" t="n">
         <v>10417</v>
@@ -25976,7 +25976,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G883" t="n">
-        <v>5.03768634796143</v>
+        <v>5.03768682479858</v>
       </c>
       <c r="H883" t="n">
         <v>19220</v>
@@ -26034,7 +26034,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G885" t="n">
-        <v>5.07704401016235</v>
+        <v>5.0770435333252</v>
       </c>
       <c r="H885" t="n">
         <v>8947</v>
@@ -26208,7 +26208,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G891" t="n">
-        <v>5.27382850646973</v>
+        <v>5.27382898330688</v>
       </c>
       <c r="H891" t="n">
         <v>7249</v>
@@ -26237,7 +26237,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G892" t="n">
-        <v>5.11640071868896</v>
+        <v>5.11640024185181</v>
       </c>
       <c r="H892" t="n">
         <v>12636</v>
@@ -26266,7 +26266,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G893" t="n">
-        <v>5.05736494064331</v>
+        <v>5.05736541748047</v>
       </c>
       <c r="H893" t="n">
         <v>9316</v>
@@ -26295,7 +26295,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G894" t="n">
-        <v>5.03768634796143</v>
+        <v>5.03768682479858</v>
       </c>
       <c r="H894" t="n">
         <v>6814</v>
@@ -26324,7 +26324,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G895" t="n">
-        <v>5.03768634796143</v>
+        <v>5.03768682479858</v>
       </c>
       <c r="H895" t="n">
         <v>7477</v>
@@ -26382,7 +26382,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G897" t="n">
-        <v>5.11640071868896</v>
+        <v>5.11640024185181</v>
       </c>
       <c r="H897" t="n">
         <v>6128</v>
@@ -26411,7 +26411,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G898" t="n">
-        <v>4.99832963943481</v>
+        <v>4.99833011627197</v>
       </c>
       <c r="H898" t="n">
         <v>29460</v>
@@ -26440,7 +26440,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G899" t="n">
-        <v>4.83106279373169</v>
+        <v>4.83106327056885</v>
       </c>
       <c r="H899" t="n">
         <v>72320</v>
@@ -26556,7 +26556,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G903" t="n">
-        <v>4.28990507125854</v>
+        <v>4.2899055480957</v>
       </c>
       <c r="H903" t="n">
         <v>28901</v>
@@ -26585,7 +26585,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G904" t="n">
-        <v>4.5654034614563</v>
+        <v>4.56540393829346</v>
       </c>
       <c r="H904" t="n">
         <v>47385</v>
@@ -26643,7 +26643,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G906" t="n">
-        <v>4.83106279373169</v>
+        <v>4.83106327056885</v>
       </c>
       <c r="H906" t="n">
         <v>107459</v>
@@ -26672,7 +26672,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G907" t="n">
-        <v>4.89009857177734</v>
+        <v>4.89009809494019</v>
       </c>
       <c r="H907" t="n">
         <v>18622</v>
@@ -26730,7 +26730,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G909" t="n">
-        <v>4.84090232849121</v>
+        <v>4.84090185165405</v>
       </c>
       <c r="H909" t="n">
         <v>11135</v>
@@ -26759,7 +26759,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G910" t="n">
-        <v>4.83106279373169</v>
+        <v>4.83106327056885</v>
       </c>
       <c r="H910" t="n">
         <v>9284</v>
@@ -26817,7 +26817,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G912" t="n">
-        <v>4.89009857177734</v>
+        <v>4.89009809494019</v>
       </c>
       <c r="H912" t="n">
         <v>3683</v>
@@ -26933,7 +26933,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G916" t="n">
-        <v>4.82122373580933</v>
+        <v>4.82122421264648</v>
       </c>
       <c r="H916" t="n">
         <v>15220</v>
@@ -26991,7 +26991,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G918" t="n">
-        <v>5.03768634796143</v>
+        <v>5.03768682479858</v>
       </c>
       <c r="H918" t="n">
         <v>45309</v>
@@ -27020,7 +27020,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G919" t="n">
-        <v>5.07704401016235</v>
+        <v>5.0770435333252</v>
       </c>
       <c r="H919" t="n">
         <v>22506</v>
@@ -27107,7 +27107,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G922" t="n">
-        <v>5.11640071868896</v>
+        <v>5.11640024185181</v>
       </c>
       <c r="H922" t="n">
         <v>20658</v>
@@ -27223,7 +27223,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G926" t="n">
-        <v>5.25414991378784</v>
+        <v>5.254150390625</v>
       </c>
       <c r="H926" t="n">
         <v>16523</v>
@@ -27281,7 +27281,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G928" t="n">
-        <v>5.27382850646973</v>
+        <v>5.27382898330688</v>
       </c>
       <c r="H928" t="n">
         <v>14860</v>
@@ -27310,7 +27310,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G929" t="n">
-        <v>5.29350709915161</v>
+        <v>5.29350662231445</v>
       </c>
       <c r="H929" t="n">
         <v>8491</v>
@@ -27339,7 +27339,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G930" t="n">
-        <v>5.29350709915161</v>
+        <v>5.29350662231445</v>
       </c>
       <c r="H930" t="n">
         <v>4930</v>
@@ -27542,7 +27542,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G937" t="n">
-        <v>5.11640071868896</v>
+        <v>5.11640024185181</v>
       </c>
       <c r="H937" t="n">
         <v>12717</v>
@@ -27600,7 +27600,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G939" t="n">
-        <v>5.11640071868896</v>
+        <v>5.11640024185181</v>
       </c>
       <c r="H939" t="n">
         <v>9615</v>
@@ -27658,7 +27658,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G941" t="n">
-        <v>5.07704401016235</v>
+        <v>5.0770435333252</v>
       </c>
       <c r="H941" t="n">
         <v>9588</v>
@@ -27745,7 +27745,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G944" t="n">
-        <v>5.13607931137085</v>
+        <v>5.13607883453369</v>
       </c>
       <c r="H944" t="n">
         <v>6542</v>
@@ -27890,7 +27890,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G949" t="n">
-        <v>5.25414991378784</v>
+        <v>5.254150390625</v>
       </c>
       <c r="H949" t="n">
         <v>10195</v>
@@ -27919,7 +27919,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G950" t="n">
-        <v>5.29350709915161</v>
+        <v>5.29350662231445</v>
       </c>
       <c r="H950" t="n">
         <v>11103</v>
@@ -28151,7 +28151,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G958" t="n">
-        <v>5.68707609176636</v>
+        <v>5.68707656860352</v>
       </c>
       <c r="H958" t="n">
         <v>24892</v>
@@ -28180,7 +28180,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G959" t="n">
-        <v>5.68707609176636</v>
+        <v>5.68707656860352</v>
       </c>
       <c r="H959" t="n">
         <v>8965</v>
@@ -28267,7 +28267,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G962" t="n">
-        <v>5.80514669418335</v>
+        <v>5.80514717102051</v>
       </c>
       <c r="H962" t="n">
         <v>18409</v>
@@ -28354,7 +28354,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G965" t="n">
-        <v>5.80514669418335</v>
+        <v>5.80514717102051</v>
       </c>
       <c r="H965" t="n">
         <v>16785</v>
@@ -28470,7 +28470,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G969" t="n">
-        <v>6.1396803855896</v>
+        <v>6.13968086242676</v>
       </c>
       <c r="H969" t="n">
         <v>75849</v>
@@ -28499,7 +28499,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G970" t="n">
-        <v>6.19871664047241</v>
+        <v>6.19871616363525</v>
       </c>
       <c r="H970" t="n">
         <v>62814</v>
@@ -28528,7 +28528,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G971" t="n">
-        <v>6.33646535873413</v>
+        <v>6.33646583557129</v>
       </c>
       <c r="H971" t="n">
         <v>50014</v>
@@ -28557,7 +28557,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G972" t="n">
-        <v>6.27743053436279</v>
+        <v>6.27743005752563</v>
       </c>
       <c r="H972" t="n">
         <v>43290</v>
@@ -28615,7 +28615,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G974" t="n">
-        <v>6.1396803855896</v>
+        <v>6.13968086242676</v>
       </c>
       <c r="H974" t="n">
         <v>10830</v>
@@ -28702,7 +28702,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G977" t="n">
-        <v>6.00193166732788</v>
+        <v>6.00193119049072</v>
       </c>
       <c r="H977" t="n">
         <v>35007</v>
@@ -43353,6 +43353,35 @@
         <v>6812</v>
       </c>
       <c r="I1482" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1483">
+      <c r="A1483" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1483" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C1483" t="n">
+        <v>8.03999996185303</v>
+      </c>
+      <c r="D1483" t="n">
+        <v>8.19999980926514</v>
+      </c>
+      <c r="E1483" t="n">
+        <v>8.01000022888184</v>
+      </c>
+      <c r="F1483" t="n">
+        <v>8.01000022888184</v>
+      </c>
+      <c r="G1483" t="n">
+        <v>8.01000022888184</v>
+      </c>
+      <c r="H1483" t="n">
+        <v>13060</v>
+      </c>
+      <c r="I1483" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/EVISO.MI.xlsx
+++ b/data/EVISO.MI.xlsx
@@ -485,7 +485,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G4" t="n">
-        <v>2.11304235458374</v>
+        <v>2.11304259300232</v>
       </c>
       <c r="H4" t="n">
         <v>187476</v>
@@ -659,7 +659,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G10" t="n">
-        <v>1.9956511259079</v>
+        <v>1.99565076828003</v>
       </c>
       <c r="H10" t="n">
         <v>58105</v>
@@ -775,7 +775,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G14" t="n">
-        <v>1.93695545196533</v>
+        <v>1.93695557117462</v>
       </c>
       <c r="H14" t="n">
         <v>32193</v>
@@ -833,7 +833,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G16" t="n">
-        <v>1.87825965881348</v>
+        <v>1.87825977802277</v>
       </c>
       <c r="H16" t="n">
         <v>30535</v>
@@ -920,7 +920,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G19" t="n">
-        <v>1.96630322933197</v>
+        <v>1.96630311012268</v>
       </c>
       <c r="H19" t="n">
         <v>71780</v>
@@ -1007,7 +1007,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G22" t="n">
-        <v>1.96630322933197</v>
+        <v>1.96630311012268</v>
       </c>
       <c r="H22" t="n">
         <v>29896</v>
@@ -1065,7 +1065,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G24" t="n">
-        <v>1.9956511259079</v>
+        <v>1.99565076828003</v>
       </c>
       <c r="H24" t="n">
         <v>10648</v>
@@ -1094,7 +1094,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G25" t="n">
-        <v>1.96630322933197</v>
+        <v>1.96630311012268</v>
       </c>
       <c r="H25" t="n">
         <v>38840</v>
@@ -1123,7 +1123,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G26" t="n">
-        <v>1.96630322933197</v>
+        <v>1.96630311012268</v>
       </c>
       <c r="H26" t="n">
         <v>65217</v>
@@ -1239,7 +1239,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G30" t="n">
-        <v>2.08369469642639</v>
+        <v>2.08369445800781</v>
       </c>
       <c r="H30" t="n">
         <v>401332</v>
@@ -1384,7 +1384,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G35" t="n">
-        <v>2.33804202079773</v>
+        <v>2.33804225921631</v>
       </c>
       <c r="H35" t="n">
         <v>424591</v>
@@ -1442,7 +1442,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G37" t="n">
-        <v>2.21086835861206</v>
+        <v>2.21086859703064</v>
       </c>
       <c r="H37" t="n">
         <v>41476</v>
@@ -1471,7 +1471,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G38" t="n">
-        <v>2.28912901878357</v>
+        <v>2.28912878036499</v>
       </c>
       <c r="H38" t="n">
         <v>46638</v>
@@ -1500,7 +1500,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G39" t="n">
-        <v>2.26956391334534</v>
+        <v>2.26956367492676</v>
       </c>
       <c r="H39" t="n">
         <v>53117</v>
@@ -1645,7 +1645,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G44" t="n">
-        <v>2.27934670448303</v>
+        <v>2.27934646606445</v>
       </c>
       <c r="H44" t="n">
         <v>35829</v>
@@ -1703,7 +1703,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G46" t="n">
-        <v>2.28912901878357</v>
+        <v>2.28912878036499</v>
       </c>
       <c r="H46" t="n">
         <v>34385</v>
@@ -1761,7 +1761,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G48" t="n">
-        <v>2.28912901878357</v>
+        <v>2.28912878036499</v>
       </c>
       <c r="H48" t="n">
         <v>32533</v>
@@ -1790,7 +1790,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G49" t="n">
-        <v>2.26956391334534</v>
+        <v>2.26956367492676</v>
       </c>
       <c r="H49" t="n">
         <v>44339</v>
@@ -1819,7 +1819,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G50" t="n">
-        <v>2.28912901878357</v>
+        <v>2.28912878036499</v>
       </c>
       <c r="H50" t="n">
         <v>198858</v>
@@ -1848,7 +1848,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G51" t="n">
-        <v>2.26956391334534</v>
+        <v>2.26956367492676</v>
       </c>
       <c r="H51" t="n">
         <v>28573</v>
@@ -1906,7 +1906,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G53" t="n">
-        <v>2.24999856948853</v>
+        <v>2.2499988079071</v>
       </c>
       <c r="H53" t="n">
         <v>15349</v>
@@ -1964,7 +1964,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G55" t="n">
-        <v>2.24999856948853</v>
+        <v>2.2499988079071</v>
       </c>
       <c r="H55" t="n">
         <v>23715</v>
@@ -1993,7 +1993,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G56" t="n">
-        <v>2.24999856948853</v>
+        <v>2.2499988079071</v>
       </c>
       <c r="H56" t="n">
         <v>20720</v>
@@ -2138,7 +2138,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G61" t="n">
-        <v>2.23043346405029</v>
+        <v>2.23043370246887</v>
       </c>
       <c r="H61" t="n">
         <v>30389</v>
@@ -2225,7 +2225,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G64" t="n">
-        <v>2.21086835861206</v>
+        <v>2.21086859703064</v>
       </c>
       <c r="H64" t="n">
         <v>43289</v>
@@ -2254,7 +2254,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G65" t="n">
-        <v>2.1717381477356</v>
+        <v>2.17173790931702</v>
       </c>
       <c r="H65" t="n">
         <v>41977</v>
@@ -2341,7 +2341,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G68" t="n">
-        <v>2.23043346405029</v>
+        <v>2.23043370246887</v>
       </c>
       <c r="H68" t="n">
         <v>59507</v>
@@ -2573,7 +2573,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G76" t="n">
-        <v>2.1717381477356</v>
+        <v>2.17173790931702</v>
       </c>
       <c r="H76" t="n">
         <v>12073</v>
@@ -2660,7 +2660,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G79" t="n">
-        <v>2.23043346405029</v>
+        <v>2.23043370246887</v>
       </c>
       <c r="H79" t="n">
         <v>133272</v>
@@ -2718,7 +2718,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G81" t="n">
-        <v>2.21086835861206</v>
+        <v>2.21086859703064</v>
       </c>
       <c r="H81" t="n">
         <v>21509</v>
@@ -2776,7 +2776,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G83" t="n">
-        <v>2.21086835861206</v>
+        <v>2.21086859703064</v>
       </c>
       <c r="H83" t="n">
         <v>18856</v>
@@ -3008,7 +3008,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G91" t="n">
-        <v>2.33804202079773</v>
+        <v>2.33804225921631</v>
       </c>
       <c r="H91" t="n">
         <v>287103</v>
@@ -3095,7 +3095,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G94" t="n">
-        <v>2.27934670448303</v>
+        <v>2.27934646606445</v>
       </c>
       <c r="H94" t="n">
         <v>66519</v>
@@ -3124,7 +3124,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G95" t="n">
-        <v>2.26956391334534</v>
+        <v>2.26956367492676</v>
       </c>
       <c r="H95" t="n">
         <v>10213</v>
@@ -3153,7 +3153,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G96" t="n">
-        <v>2.24999856948853</v>
+        <v>2.2499988079071</v>
       </c>
       <c r="H96" t="n">
         <v>23541</v>
@@ -3182,7 +3182,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G97" t="n">
-        <v>2.27934670448303</v>
+        <v>2.27934646606445</v>
       </c>
       <c r="H97" t="n">
         <v>9745</v>
@@ -3269,7 +3269,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G100" t="n">
-        <v>2.33804202079773</v>
+        <v>2.33804225921631</v>
       </c>
       <c r="H100" t="n">
         <v>138592</v>
@@ -3385,7 +3385,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G104" t="n">
-        <v>2.6510853767395</v>
+        <v>2.65108561515808</v>
       </c>
       <c r="H104" t="n">
         <v>222446</v>
@@ -3414,7 +3414,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G105" t="n">
-        <v>2.73912906646729</v>
+        <v>2.73912882804871</v>
       </c>
       <c r="H105" t="n">
         <v>254085</v>
@@ -3559,7 +3559,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G110" t="n">
-        <v>2.61195516586304</v>
+        <v>2.61195492744446</v>
       </c>
       <c r="H110" t="n">
         <v>28158</v>
@@ -3588,7 +3588,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G111" t="n">
-        <v>2.53369426727295</v>
+        <v>2.53369402885437</v>
       </c>
       <c r="H111" t="n">
         <v>56152</v>
@@ -3617,7 +3617,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G112" t="n">
-        <v>2.54347658157349</v>
+        <v>2.54347681999207</v>
       </c>
       <c r="H112" t="n">
         <v>34901</v>
@@ -3646,7 +3646,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G113" t="n">
-        <v>2.54347658157349</v>
+        <v>2.54347681999207</v>
       </c>
       <c r="H113" t="n">
         <v>36680</v>
@@ -3675,7 +3675,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G114" t="n">
-        <v>2.53369426727295</v>
+        <v>2.53369402885437</v>
       </c>
       <c r="H114" t="n">
         <v>51806</v>
@@ -3733,7 +3733,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G116" t="n">
-        <v>2.51412916183472</v>
+        <v>2.51412892341614</v>
       </c>
       <c r="H116" t="n">
         <v>8588</v>
@@ -3762,7 +3762,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G117" t="n">
-        <v>2.54347658157349</v>
+        <v>2.54347681999207</v>
       </c>
       <c r="H117" t="n">
         <v>39029</v>
@@ -3791,7 +3791,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G118" t="n">
-        <v>2.49456381797791</v>
+        <v>2.49456357955933</v>
       </c>
       <c r="H118" t="n">
         <v>42909</v>
@@ -3820,7 +3820,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G119" t="n">
-        <v>2.51412916183472</v>
+        <v>2.51412892341614</v>
       </c>
       <c r="H119" t="n">
         <v>5450</v>
@@ -3849,7 +3849,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G120" t="n">
-        <v>2.47499871253967</v>
+        <v>2.47499847412109</v>
       </c>
       <c r="H120" t="n">
         <v>9520</v>
@@ -3878,7 +3878,7 @@
         <v>2.5</v>
       </c>
       <c r="G121" t="n">
-        <v>2.44565057754517</v>
+        <v>2.44565081596375</v>
       </c>
       <c r="H121" t="n">
         <v>24840</v>
@@ -3994,7 +3994,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G125" t="n">
-        <v>2.41630291938782</v>
+        <v>2.4163031578064</v>
       </c>
       <c r="H125" t="n">
         <v>35694</v>
@@ -4052,7 +4052,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G127" t="n">
-        <v>2.53369426727295</v>
+        <v>2.53369402885437</v>
       </c>
       <c r="H127" t="n">
         <v>39898</v>
@@ -4081,7 +4081,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G128" t="n">
-        <v>2.48478126525879</v>
+        <v>2.48478102684021</v>
       </c>
       <c r="H128" t="n">
         <v>22629</v>
@@ -4110,7 +4110,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G129" t="n">
-        <v>2.49456381797791</v>
+        <v>2.49456357955933</v>
       </c>
       <c r="H129" t="n">
         <v>3606</v>
@@ -4139,7 +4139,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G130" t="n">
-        <v>2.52391147613525</v>
+        <v>2.52391171455383</v>
       </c>
       <c r="H130" t="n">
         <v>6239</v>
@@ -4197,7 +4197,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G132" t="n">
-        <v>2.49456381797791</v>
+        <v>2.49456357955933</v>
       </c>
       <c r="H132" t="n">
         <v>6780</v>
@@ -4255,7 +4255,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G134" t="n">
-        <v>2.51412916183472</v>
+        <v>2.51412892341614</v>
       </c>
       <c r="H134" t="n">
         <v>8450</v>
@@ -4284,7 +4284,7 @@
         <v>2.5</v>
       </c>
       <c r="G135" t="n">
-        <v>2.44565057754517</v>
+        <v>2.44565081596375</v>
       </c>
       <c r="H135" t="n">
         <v>40425</v>
@@ -4313,7 +4313,7 @@
         <v>2.5</v>
       </c>
       <c r="G136" t="n">
-        <v>2.44565057754517</v>
+        <v>2.44565081596375</v>
       </c>
       <c r="H136" t="n">
         <v>2530</v>
@@ -4342,7 +4342,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G137" t="n">
-        <v>2.47499871253967</v>
+        <v>2.47499847412109</v>
       </c>
       <c r="H137" t="n">
         <v>1750</v>
@@ -4458,7 +4458,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G141" t="n">
-        <v>2.41630291938782</v>
+        <v>2.4163031578064</v>
       </c>
       <c r="H141" t="n">
         <v>4028</v>
@@ -4603,7 +4603,7 @@
         <v>2.5</v>
       </c>
       <c r="G146" t="n">
-        <v>2.44565057754517</v>
+        <v>2.44565081596375</v>
       </c>
       <c r="H146" t="n">
         <v>5600</v>
@@ -4632,7 +4632,7 @@
         <v>2.5</v>
       </c>
       <c r="G147" t="n">
-        <v>2.44565057754517</v>
+        <v>2.44565081596375</v>
       </c>
       <c r="H147" t="n">
         <v>11043</v>
@@ -4777,7 +4777,7 @@
         <v>2.5</v>
       </c>
       <c r="G152" t="n">
-        <v>2.44565057754517</v>
+        <v>2.44565081596375</v>
       </c>
       <c r="H152" t="n">
         <v>10465</v>
@@ -4806,7 +4806,7 @@
         <v>2.5</v>
       </c>
       <c r="G153" t="n">
-        <v>2.44565057754517</v>
+        <v>2.44565081596375</v>
       </c>
       <c r="H153" t="n">
         <v>14241</v>
@@ -4835,7 +4835,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G154" t="n">
-        <v>2.48478126525879</v>
+        <v>2.48478102684021</v>
       </c>
       <c r="H154" t="n">
         <v>33850</v>
@@ -4893,7 +4893,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G156" t="n">
-        <v>2.49456381797791</v>
+        <v>2.49456357955933</v>
       </c>
       <c r="H156" t="n">
         <v>10595</v>
@@ -4922,7 +4922,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G157" t="n">
-        <v>2.49456381797791</v>
+        <v>2.49456357955933</v>
       </c>
       <c r="H157" t="n">
         <v>21750</v>
@@ -4980,7 +4980,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G159" t="n">
-        <v>2.41630291938782</v>
+        <v>2.4163031578064</v>
       </c>
       <c r="H159" t="n">
         <v>12350</v>
@@ -5096,7 +5096,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G163" t="n">
-        <v>2.61195516586304</v>
+        <v>2.61195492744446</v>
       </c>
       <c r="H163" t="n">
         <v>108022</v>
@@ -5125,7 +5125,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G164" t="n">
-        <v>2.81738996505737</v>
+        <v>2.81738972663879</v>
       </c>
       <c r="H164" t="n">
         <v>432229</v>
@@ -5154,7 +5154,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G165" t="n">
-        <v>2.81738996505737</v>
+        <v>2.81738972663879</v>
       </c>
       <c r="H165" t="n">
         <v>148290</v>
@@ -5183,7 +5183,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G166" t="n">
-        <v>2.92499852180481</v>
+        <v>2.92499828338623</v>
       </c>
       <c r="H166" t="n">
         <v>225121</v>
@@ -5212,7 +5212,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G167" t="n">
-        <v>2.92499852180481</v>
+        <v>2.92499828338623</v>
       </c>
       <c r="H167" t="n">
         <v>82576</v>
@@ -5241,7 +5241,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G168" t="n">
-        <v>2.905433177948</v>
+        <v>2.90543293952942</v>
       </c>
       <c r="H168" t="n">
         <v>40031</v>
@@ -5270,7 +5270,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G169" t="n">
-        <v>2.92499852180481</v>
+        <v>2.92499828338623</v>
       </c>
       <c r="H169" t="n">
         <v>43188</v>
@@ -5299,7 +5299,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G170" t="n">
-        <v>2.92499852180481</v>
+        <v>2.92499828338623</v>
       </c>
       <c r="H170" t="n">
         <v>21615</v>
@@ -5328,7 +5328,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G171" t="n">
-        <v>2.83695530891418</v>
+        <v>2.83695507049561</v>
       </c>
       <c r="H171" t="n">
         <v>69207</v>
@@ -5357,7 +5357,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G172" t="n">
-        <v>2.74891138076782</v>
+        <v>2.7489116191864</v>
       </c>
       <c r="H172" t="n">
         <v>92414</v>
@@ -5415,7 +5415,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G174" t="n">
-        <v>2.73912906646729</v>
+        <v>2.73912882804871</v>
       </c>
       <c r="H174" t="n">
         <v>33049</v>
@@ -5618,7 +5618,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G181" t="n">
-        <v>2.66086792945862</v>
+        <v>2.6608681678772</v>
       </c>
       <c r="H181" t="n">
         <v>6625</v>
@@ -5705,7 +5705,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G184" t="n">
-        <v>2.66086792945862</v>
+        <v>2.6608681678772</v>
       </c>
       <c r="H184" t="n">
         <v>12599</v>
@@ -5763,7 +5763,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G186" t="n">
-        <v>2.70978116989136</v>
+        <v>2.70978093147278</v>
       </c>
       <c r="H186" t="n">
         <v>22094</v>
@@ -5850,7 +5850,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G189" t="n">
-        <v>2.74891138076782</v>
+        <v>2.7489116191864</v>
       </c>
       <c r="H189" t="n">
         <v>35710</v>
@@ -5879,7 +5879,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G190" t="n">
-        <v>2.51412916183472</v>
+        <v>2.51412892341614</v>
       </c>
       <c r="H190" t="n">
         <v>117768</v>
@@ -5908,7 +5908,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G191" t="n">
-        <v>2.68043327331543</v>
+        <v>2.68043303489685</v>
       </c>
       <c r="H191" t="n">
         <v>61763</v>
@@ -5937,7 +5937,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G192" t="n">
-        <v>2.66086792945862</v>
+        <v>2.6608681678772</v>
       </c>
       <c r="H192" t="n">
         <v>32457</v>
@@ -5995,7 +5995,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G194" t="n">
-        <v>2.64130282402039</v>
+        <v>2.64130306243896</v>
       </c>
       <c r="H194" t="n">
         <v>13810</v>
@@ -6111,7 +6111,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G198" t="n">
-        <v>2.61195516586304</v>
+        <v>2.61195492744446</v>
       </c>
       <c r="H198" t="n">
         <v>20110</v>
@@ -6198,7 +6198,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G201" t="n">
-        <v>2.54347658157349</v>
+        <v>2.54347681999207</v>
       </c>
       <c r="H201" t="n">
         <v>32309</v>
@@ -6256,7 +6256,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G203" t="n">
-        <v>2.61195516586304</v>
+        <v>2.61195492744446</v>
       </c>
       <c r="H203" t="n">
         <v>23415</v>
@@ -6285,7 +6285,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G204" t="n">
-        <v>2.64130282402039</v>
+        <v>2.64130306243896</v>
       </c>
       <c r="H204" t="n">
         <v>60539</v>
@@ -6314,7 +6314,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G205" t="n">
-        <v>2.70978116989136</v>
+        <v>2.70978093147278</v>
       </c>
       <c r="H205" t="n">
         <v>51440</v>
@@ -6343,7 +6343,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G206" t="n">
-        <v>2.73912906646729</v>
+        <v>2.73912882804871</v>
       </c>
       <c r="H206" t="n">
         <v>36708</v>
@@ -6401,7 +6401,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G208" t="n">
-        <v>2.66086792945862</v>
+        <v>2.6608681678772</v>
       </c>
       <c r="H208" t="n">
         <v>13847</v>
@@ -6459,7 +6459,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G210" t="n">
-        <v>2.66086792945862</v>
+        <v>2.6608681678772</v>
       </c>
       <c r="H210" t="n">
         <v>23532</v>
@@ -6488,7 +6488,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G211" t="n">
-        <v>2.66086792945862</v>
+        <v>2.6608681678772</v>
       </c>
       <c r="H211" t="n">
         <v>16536</v>
@@ -6546,7 +6546,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G213" t="n">
-        <v>2.66086792945862</v>
+        <v>2.6608681678772</v>
       </c>
       <c r="H213" t="n">
         <v>11727</v>
@@ -6575,7 +6575,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G214" t="n">
-        <v>2.66086792945862</v>
+        <v>2.6608681678772</v>
       </c>
       <c r="H214" t="n">
         <v>22564</v>
@@ -6604,7 +6604,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G215" t="n">
-        <v>2.68043327331543</v>
+        <v>2.68043303489685</v>
       </c>
       <c r="H215" t="n">
         <v>17119</v>
@@ -6633,7 +6633,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G216" t="n">
-        <v>2.6510853767395</v>
+        <v>2.65108561515808</v>
       </c>
       <c r="H216" t="n">
         <v>13564</v>
@@ -6662,7 +6662,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G217" t="n">
-        <v>2.64130282402039</v>
+        <v>2.64130306243896</v>
       </c>
       <c r="H217" t="n">
         <v>19788</v>
@@ -6749,7 +6749,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G220" t="n">
-        <v>2.63691449165344</v>
+        <v>2.63691425323486</v>
       </c>
       <c r="H220" t="n">
         <v>54300</v>
@@ -6778,7 +6778,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G221" t="n">
-        <v>2.64675331115723</v>
+        <v>2.64675354957581</v>
       </c>
       <c r="H221" t="n">
         <v>42202</v>
@@ -6807,7 +6807,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G222" t="n">
-        <v>2.6270751953125</v>
+        <v>2.62707495689392</v>
       </c>
       <c r="H222" t="n">
         <v>18794</v>
@@ -6952,7 +6952,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G227" t="n">
-        <v>2.51884341239929</v>
+        <v>2.51884317398071</v>
       </c>
       <c r="H227" t="n">
         <v>30812</v>
@@ -6981,7 +6981,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G228" t="n">
-        <v>2.49916505813599</v>
+        <v>2.49916481971741</v>
       </c>
       <c r="H228" t="n">
         <v>48757</v>
@@ -7010,7 +7010,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G229" t="n">
-        <v>2.52868270874023</v>
+        <v>2.52868247032166</v>
       </c>
       <c r="H229" t="n">
         <v>15710</v>
@@ -7097,7 +7097,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G232" t="n">
-        <v>2.43029022216797</v>
+        <v>2.43029046058655</v>
       </c>
       <c r="H232" t="n">
         <v>31988</v>
@@ -7155,7 +7155,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G234" t="n">
-        <v>2.51884341239929</v>
+        <v>2.51884317398071</v>
       </c>
       <c r="H234" t="n">
         <v>39902</v>
@@ -7271,7 +7271,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G238" t="n">
-        <v>2.5582001209259</v>
+        <v>2.55820035934448</v>
       </c>
       <c r="H238" t="n">
         <v>26987</v>
@@ -7329,7 +7329,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G240" t="n">
-        <v>2.6270751953125</v>
+        <v>2.62707495689392</v>
       </c>
       <c r="H240" t="n">
         <v>3780</v>
@@ -7445,7 +7445,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G244" t="n">
-        <v>2.49916505813599</v>
+        <v>2.49916481971741</v>
       </c>
       <c r="H244" t="n">
         <v>24170</v>
@@ -7503,7 +7503,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G246" t="n">
-        <v>2.48932576179504</v>
+        <v>2.48932552337646</v>
       </c>
       <c r="H246" t="n">
         <v>1994</v>
@@ -7590,7 +7590,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G249" t="n">
-        <v>2.43029022216797</v>
+        <v>2.43029046058655</v>
       </c>
       <c r="H249" t="n">
         <v>5858</v>
@@ -7677,7 +7677,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G252" t="n">
-        <v>2.48932576179504</v>
+        <v>2.48932552337646</v>
       </c>
       <c r="H252" t="n">
         <v>810</v>
@@ -7793,7 +7793,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G256" t="n">
-        <v>2.42045092582703</v>
+        <v>2.42045116424561</v>
       </c>
       <c r="H256" t="n">
         <v>9824</v>
@@ -7822,7 +7822,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G257" t="n">
-        <v>2.42045092582703</v>
+        <v>2.42045116424561</v>
       </c>
       <c r="H257" t="n">
         <v>12307</v>
@@ -7880,7 +7880,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G259" t="n">
-        <v>2.48932576179504</v>
+        <v>2.48932552337646</v>
       </c>
       <c r="H259" t="n">
         <v>7500</v>
@@ -7909,7 +7909,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G260" t="n">
-        <v>2.48932576179504</v>
+        <v>2.48932552337646</v>
       </c>
       <c r="H260" t="n">
         <v>14171</v>
@@ -7967,7 +7967,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G262" t="n">
-        <v>2.42045092582703</v>
+        <v>2.42045116424561</v>
       </c>
       <c r="H262" t="n">
         <v>6545</v>
@@ -8025,7 +8025,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G264" t="n">
-        <v>2.43029022216797</v>
+        <v>2.43029046058655</v>
       </c>
       <c r="H264" t="n">
         <v>7020</v>
@@ -8141,7 +8141,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G268" t="n">
-        <v>2.43029022216797</v>
+        <v>2.43029046058655</v>
       </c>
       <c r="H268" t="n">
         <v>6909</v>
@@ -8170,7 +8170,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G269" t="n">
-        <v>2.42045092582703</v>
+        <v>2.42045116424561</v>
       </c>
       <c r="H269" t="n">
         <v>398</v>
@@ -8257,7 +8257,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G272" t="n">
-        <v>2.27286267280579</v>
+        <v>2.27286243438721</v>
       </c>
       <c r="H272" t="n">
         <v>19540</v>
@@ -8315,7 +8315,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G274" t="n">
-        <v>2.41061210632324</v>
+        <v>2.41061186790466</v>
       </c>
       <c r="H274" t="n">
         <v>2455</v>
@@ -8373,7 +8373,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G276" t="n">
-        <v>2.42045092582703</v>
+        <v>2.42045116424561</v>
       </c>
       <c r="H276" t="n">
         <v>4035</v>
@@ -8489,7 +8489,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G280" t="n">
-        <v>2.41061210632324</v>
+        <v>2.41061186790466</v>
       </c>
       <c r="H280" t="n">
         <v>2500</v>
@@ -8518,7 +8518,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G281" t="n">
-        <v>2.41061210632324</v>
+        <v>2.41061186790466</v>
       </c>
       <c r="H281" t="n">
         <v>3607</v>
@@ -8547,7 +8547,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G282" t="n">
-        <v>2.41061210632324</v>
+        <v>2.41061186790466</v>
       </c>
       <c r="H282" t="n">
         <v>3021</v>
@@ -8576,7 +8576,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G283" t="n">
-        <v>2.35157656669617</v>
+        <v>2.35157680511475</v>
       </c>
       <c r="H283" t="n">
         <v>3780</v>
@@ -8605,7 +8605,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G284" t="n">
-        <v>2.42045092582703</v>
+        <v>2.42045116424561</v>
       </c>
       <c r="H284" t="n">
         <v>7881</v>
@@ -8634,7 +8634,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G285" t="n">
-        <v>2.52868270874023</v>
+        <v>2.52868247032166</v>
       </c>
       <c r="H285" t="n">
         <v>42819</v>
@@ -8924,7 +8924,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G295" t="n">
-        <v>2.30238032341003</v>
+        <v>2.30238008499146</v>
       </c>
       <c r="H295" t="n">
         <v>44626</v>
@@ -9040,7 +9040,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G299" t="n">
-        <v>2.27286267280579</v>
+        <v>2.27286243438721</v>
       </c>
       <c r="H299" t="n">
         <v>50689</v>
@@ -9069,7 +9069,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G300" t="n">
-        <v>2.20398783683777</v>
+        <v>2.20398807525635</v>
       </c>
       <c r="H300" t="n">
         <v>34470</v>
@@ -9185,7 +9185,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G304" t="n">
-        <v>2.27286267280579</v>
+        <v>2.27286243438721</v>
       </c>
       <c r="H304" t="n">
         <v>15470</v>
@@ -9243,7 +9243,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G306" t="n">
-        <v>2.30238032341003</v>
+        <v>2.30238008499146</v>
       </c>
       <c r="H306" t="n">
         <v>1100</v>
@@ -9417,7 +9417,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G312" t="n">
-        <v>2.35157656669617</v>
+        <v>2.35157680511475</v>
       </c>
       <c r="H312" t="n">
         <v>25055</v>
@@ -9446,7 +9446,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G313" t="n">
-        <v>2.41061210632324</v>
+        <v>2.41061186790466</v>
       </c>
       <c r="H313" t="n">
         <v>37964</v>
@@ -9678,7 +9678,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G321" t="n">
-        <v>2.27286267280579</v>
+        <v>2.27286243438721</v>
       </c>
       <c r="H321" t="n">
         <v>3425</v>
@@ -9707,7 +9707,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G322" t="n">
-        <v>2.28270196914673</v>
+        <v>2.28270173072815</v>
       </c>
       <c r="H322" t="n">
         <v>16706</v>
@@ -9823,7 +9823,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G326" t="n">
-        <v>2.35157656669617</v>
+        <v>2.35157680511475</v>
       </c>
       <c r="H326" t="n">
         <v>2807</v>
@@ -9910,7 +9910,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G329" t="n">
-        <v>2.28270196914673</v>
+        <v>2.28270173072815</v>
       </c>
       <c r="H329" t="n">
         <v>4326</v>
@@ -9939,7 +9939,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G330" t="n">
-        <v>2.30238032341003</v>
+        <v>2.30238008499146</v>
       </c>
       <c r="H330" t="n">
         <v>2424</v>
@@ -9997,7 +9997,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G332" t="n">
-        <v>2.30238032341003</v>
+        <v>2.30238008499146</v>
       </c>
       <c r="H332" t="n">
         <v>1205</v>
@@ -10055,7 +10055,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G334" t="n">
-        <v>2.20398783683777</v>
+        <v>2.20398807525635</v>
       </c>
       <c r="H334" t="n">
         <v>12548</v>
@@ -10142,7 +10142,7 @@
         <v>2.25</v>
       </c>
       <c r="G337" t="n">
-        <v>2.21382713317871</v>
+        <v>2.21382737159729</v>
       </c>
       <c r="H337" t="n">
         <v>4451</v>
@@ -10316,7 +10316,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G343" t="n">
-        <v>2.41061210632324</v>
+        <v>2.41061186790466</v>
       </c>
       <c r="H343" t="n">
         <v>157345</v>
@@ -10345,7 +10345,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G344" t="n">
-        <v>2.41061210632324</v>
+        <v>2.41061186790466</v>
       </c>
       <c r="H344" t="n">
         <v>177569</v>
@@ -10374,7 +10374,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G345" t="n">
-        <v>2.28270196914673</v>
+        <v>2.28270173072815</v>
       </c>
       <c r="H345" t="n">
         <v>36620</v>
@@ -10490,7 +10490,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G349" t="n">
-        <v>2.35157656669617</v>
+        <v>2.35157680511475</v>
       </c>
       <c r="H349" t="n">
         <v>12100</v>
@@ -10548,7 +10548,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G351" t="n">
-        <v>2.28270196914673</v>
+        <v>2.28270173072815</v>
       </c>
       <c r="H351" t="n">
         <v>6350</v>
@@ -10606,7 +10606,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G353" t="n">
-        <v>2.28270196914673</v>
+        <v>2.28270173072815</v>
       </c>
       <c r="H353" t="n">
         <v>6000</v>
@@ -10635,7 +10635,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G354" t="n">
-        <v>2.28270196914673</v>
+        <v>2.28270173072815</v>
       </c>
       <c r="H354" t="n">
         <v>4900</v>
@@ -10664,7 +10664,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G355" t="n">
-        <v>2.27286267280579</v>
+        <v>2.27286243438721</v>
       </c>
       <c r="H355" t="n">
         <v>5466</v>
@@ -10693,7 +10693,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G356" t="n">
-        <v>2.28270196914673</v>
+        <v>2.28270173072815</v>
       </c>
       <c r="H356" t="n">
         <v>4255</v>
@@ -10751,7 +10751,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G358" t="n">
-        <v>2.28270196914673</v>
+        <v>2.28270173072815</v>
       </c>
       <c r="H358" t="n">
         <v>9650</v>
@@ -10780,7 +10780,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G359" t="n">
-        <v>2.27286267280579</v>
+        <v>2.27286243438721</v>
       </c>
       <c r="H359" t="n">
         <v>10142</v>
@@ -10809,7 +10809,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G360" t="n">
-        <v>2.28270196914673</v>
+        <v>2.28270173072815</v>
       </c>
       <c r="H360" t="n">
         <v>6650</v>
@@ -10838,7 +10838,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G361" t="n">
-        <v>2.30238032341003</v>
+        <v>2.30238008499146</v>
       </c>
       <c r="H361" t="n">
         <v>1405</v>
@@ -10867,7 +10867,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G362" t="n">
-        <v>2.30238032341003</v>
+        <v>2.30238008499146</v>
       </c>
       <c r="H362" t="n">
         <v>136082</v>
@@ -10896,7 +10896,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G363" t="n">
-        <v>2.30238032341003</v>
+        <v>2.30238008499146</v>
       </c>
       <c r="H363" t="n">
         <v>0</v>
@@ -10954,7 +10954,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G365" t="n">
-        <v>2.41061210632324</v>
+        <v>2.41061186790466</v>
       </c>
       <c r="H365" t="n">
         <v>46145</v>
@@ -11070,7 +11070,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G369" t="n">
-        <v>2.5385217666626</v>
+        <v>2.53852200508118</v>
       </c>
       <c r="H369" t="n">
         <v>58285</v>
@@ -11157,7 +11157,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G372" t="n">
-        <v>2.48932576179504</v>
+        <v>2.48932552337646</v>
       </c>
       <c r="H372" t="n">
         <v>30239</v>
@@ -11360,7 +11360,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G379" t="n">
-        <v>2.35157656669617</v>
+        <v>2.35157680511475</v>
       </c>
       <c r="H379" t="n">
         <v>1201</v>
@@ -11534,7 +11534,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G385" t="n">
-        <v>2.43029022216797</v>
+        <v>2.43029046058655</v>
       </c>
       <c r="H385" t="n">
         <v>25280</v>
@@ -11592,7 +11592,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G387" t="n">
-        <v>2.43029022216797</v>
+        <v>2.43029046058655</v>
       </c>
       <c r="H387" t="n">
         <v>13258</v>
@@ -11766,7 +11766,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G393" t="n">
-        <v>2.35157656669617</v>
+        <v>2.35157680511475</v>
       </c>
       <c r="H393" t="n">
         <v>1601</v>
@@ -12172,7 +12172,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G407" t="n">
-        <v>2.42045092582703</v>
+        <v>2.42045116424561</v>
       </c>
       <c r="H407" t="n">
         <v>11611</v>
@@ -12288,7 +12288,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G411" t="n">
-        <v>2.48932576179504</v>
+        <v>2.48932552337646</v>
       </c>
       <c r="H411" t="n">
         <v>11281</v>
@@ -12317,7 +12317,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G412" t="n">
-        <v>2.48932576179504</v>
+        <v>2.48932552337646</v>
       </c>
       <c r="H412" t="n">
         <v>951</v>
@@ -12346,7 +12346,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G413" t="n">
-        <v>2.42045092582703</v>
+        <v>2.42045116424561</v>
       </c>
       <c r="H413" t="n">
         <v>180</v>
@@ -12578,7 +12578,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G421" t="n">
-        <v>2.49916505813599</v>
+        <v>2.49916481971741</v>
       </c>
       <c r="H421" t="n">
         <v>16752</v>
@@ -12665,7 +12665,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G424" t="n">
-        <v>2.49916505813599</v>
+        <v>2.49916481971741</v>
       </c>
       <c r="H424" t="n">
         <v>35639</v>
@@ -12752,7 +12752,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G427" t="n">
-        <v>2.5582001209259</v>
+        <v>2.55820035934448</v>
       </c>
       <c r="H427" t="n">
         <v>559114</v>
@@ -12781,7 +12781,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G428" t="n">
-        <v>2.52868270874023</v>
+        <v>2.52868247032166</v>
       </c>
       <c r="H428" t="n">
         <v>29512</v>
@@ -12897,7 +12897,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G432" t="n">
-        <v>2.51884341239929</v>
+        <v>2.51884317398071</v>
       </c>
       <c r="H432" t="n">
         <v>60938</v>
@@ -12955,7 +12955,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G434" t="n">
-        <v>2.5582001209259</v>
+        <v>2.55820035934448</v>
       </c>
       <c r="H434" t="n">
         <v>47155</v>
@@ -12984,7 +12984,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G435" t="n">
-        <v>2.52868270874023</v>
+        <v>2.52868247032166</v>
       </c>
       <c r="H435" t="n">
         <v>20543</v>
@@ -13042,7 +13042,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G437" t="n">
-        <v>2.52868270874023</v>
+        <v>2.52868247032166</v>
       </c>
       <c r="H437" t="n">
         <v>12222</v>
@@ -13071,7 +13071,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G438" t="n">
-        <v>2.51884341239929</v>
+        <v>2.51884317398071</v>
       </c>
       <c r="H438" t="n">
         <v>18341</v>
@@ -13100,7 +13100,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G439" t="n">
-        <v>2.52868270874023</v>
+        <v>2.52868247032166</v>
       </c>
       <c r="H439" t="n">
         <v>19433</v>
@@ -13129,7 +13129,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G440" t="n">
-        <v>2.43029022216797</v>
+        <v>2.43029046058655</v>
       </c>
       <c r="H440" t="n">
         <v>23395</v>
@@ -13216,7 +13216,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G443" t="n">
-        <v>2.41061210632324</v>
+        <v>2.41061186790466</v>
       </c>
       <c r="H443" t="n">
         <v>15137</v>
@@ -13274,7 +13274,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G445" t="n">
-        <v>2.49916505813599</v>
+        <v>2.49916481971741</v>
       </c>
       <c r="H445" t="n">
         <v>52693</v>
@@ -13332,7 +13332,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G447" t="n">
-        <v>2.28270196914673</v>
+        <v>2.28270173072815</v>
       </c>
       <c r="H447" t="n">
         <v>23165</v>
@@ -13361,7 +13361,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G448" t="n">
-        <v>2.28270196914673</v>
+        <v>2.28270173072815</v>
       </c>
       <c r="H448" t="n">
         <v>40210</v>
@@ -13477,7 +13477,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G452" t="n">
-        <v>2.43029022216797</v>
+        <v>2.43029046058655</v>
       </c>
       <c r="H452" t="n">
         <v>37050</v>
@@ -13622,7 +13622,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G457" t="n">
-        <v>2.49916505813599</v>
+        <v>2.49916481971741</v>
       </c>
       <c r="H457" t="n">
         <v>35738</v>
@@ -13651,7 +13651,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G458" t="n">
-        <v>2.51884341239929</v>
+        <v>2.51884317398071</v>
       </c>
       <c r="H458" t="n">
         <v>18389</v>
@@ -13680,7 +13680,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G459" t="n">
-        <v>2.51884341239929</v>
+        <v>2.51884317398071</v>
       </c>
       <c r="H459" t="n">
         <v>0</v>
@@ -13709,7 +13709,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G460" t="n">
-        <v>2.43029022216797</v>
+        <v>2.43029046058655</v>
       </c>
       <c r="H460" t="n">
         <v>29119</v>
@@ -13825,7 +13825,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G464" t="n">
-        <v>2.42045092582703</v>
+        <v>2.42045116424561</v>
       </c>
       <c r="H464" t="n">
         <v>2155</v>
@@ -13854,7 +13854,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G465" t="n">
-        <v>2.41061210632324</v>
+        <v>2.41061186790466</v>
       </c>
       <c r="H465" t="n">
         <v>3505</v>
@@ -13941,7 +13941,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G468" t="n">
-        <v>2.42045092582703</v>
+        <v>2.42045116424561</v>
       </c>
       <c r="H468" t="n">
         <v>5886</v>
@@ -13970,7 +13970,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G469" t="n">
-        <v>2.42045092582703</v>
+        <v>2.42045116424561</v>
       </c>
       <c r="H469" t="n">
         <v>0</v>
@@ -14028,7 +14028,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G471" t="n">
-        <v>2.43029022216797</v>
+        <v>2.43029046058655</v>
       </c>
       <c r="H471" t="n">
         <v>8504</v>
@@ -14144,7 +14144,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G475" t="n">
-        <v>2.42045092582703</v>
+        <v>2.42045116424561</v>
       </c>
       <c r="H475" t="n">
         <v>5971</v>
@@ -14260,7 +14260,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G479" t="n">
-        <v>2.43029022216797</v>
+        <v>2.43029046058655</v>
       </c>
       <c r="H479" t="n">
         <v>7842</v>
@@ -14318,7 +14318,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G481" t="n">
-        <v>2.42045092582703</v>
+        <v>2.42045116424561</v>
       </c>
       <c r="H481" t="n">
         <v>3675</v>
@@ -14376,7 +14376,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G483" t="n">
-        <v>2.42045092582703</v>
+        <v>2.42045116424561</v>
       </c>
       <c r="H483" t="n">
         <v>6429</v>
@@ -14492,7 +14492,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G487" t="n">
-        <v>2.41061210632324</v>
+        <v>2.41061186790466</v>
       </c>
       <c r="H487" t="n">
         <v>1829</v>
@@ -14521,7 +14521,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G488" t="n">
-        <v>2.41061210632324</v>
+        <v>2.41061186790466</v>
       </c>
       <c r="H488" t="n">
         <v>0</v>
@@ -14579,7 +14579,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G490" t="n">
-        <v>2.41061210632324</v>
+        <v>2.41061186790466</v>
       </c>
       <c r="H490" t="n">
         <v>18612</v>
@@ -14666,7 +14666,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G493" t="n">
-        <v>2.41061210632324</v>
+        <v>2.41061186790466</v>
       </c>
       <c r="H493" t="n">
         <v>1</v>
@@ -14695,7 +14695,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G494" t="n">
-        <v>2.41061210632324</v>
+        <v>2.41061186790466</v>
       </c>
       <c r="H494" t="n">
         <v>0</v>
@@ -14724,7 +14724,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G495" t="n">
-        <v>2.41061210632324</v>
+        <v>2.41061186790466</v>
       </c>
       <c r="H495" t="n">
         <v>20619</v>
@@ -14869,7 +14869,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G500" t="n">
-        <v>2.48932576179504</v>
+        <v>2.48932552337646</v>
       </c>
       <c r="H500" t="n">
         <v>22406</v>
@@ -14898,7 +14898,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G501" t="n">
-        <v>2.41061210632324</v>
+        <v>2.41061186790466</v>
       </c>
       <c r="H501" t="n">
         <v>232</v>
@@ -14985,7 +14985,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G504" t="n">
-        <v>2.42045092582703</v>
+        <v>2.42045116424561</v>
       </c>
       <c r="H504" t="n">
         <v>3174</v>
@@ -15014,7 +15014,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G505" t="n">
-        <v>2.42045092582703</v>
+        <v>2.42045116424561</v>
       </c>
       <c r="H505" t="n">
         <v>0</v>
@@ -15072,7 +15072,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G507" t="n">
-        <v>2.42045092582703</v>
+        <v>2.42045116424561</v>
       </c>
       <c r="H507" t="n">
         <v>4</v>
@@ -15130,7 +15130,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G509" t="n">
-        <v>2.43029022216797</v>
+        <v>2.43029046058655</v>
       </c>
       <c r="H509" t="n">
         <v>6606</v>
@@ -15159,7 +15159,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G510" t="n">
-        <v>2.43029022216797</v>
+        <v>2.43029046058655</v>
       </c>
       <c r="H510" t="n">
         <v>4444</v>
@@ -15217,7 +15217,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G512" t="n">
-        <v>2.49916505813599</v>
+        <v>2.49916481971741</v>
       </c>
       <c r="H512" t="n">
         <v>18429</v>
@@ -15304,7 +15304,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G515" t="n">
-        <v>2.48932576179504</v>
+        <v>2.48932552337646</v>
       </c>
       <c r="H515" t="n">
         <v>421</v>
@@ -15536,7 +15536,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G523" t="n">
-        <v>2.5582001209259</v>
+        <v>2.55820035934448</v>
       </c>
       <c r="H523" t="n">
         <v>28775</v>
@@ -15681,7 +15681,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G528" t="n">
-        <v>2.5582001209259</v>
+        <v>2.55820035934448</v>
       </c>
       <c r="H528" t="n">
         <v>6832</v>
@@ -15710,7 +15710,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G529" t="n">
-        <v>2.52868270874023</v>
+        <v>2.52868247032166</v>
       </c>
       <c r="H529" t="n">
         <v>7700</v>
@@ -15739,7 +15739,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G530" t="n">
-        <v>2.5582001209259</v>
+        <v>2.55820035934448</v>
       </c>
       <c r="H530" t="n">
         <v>6304</v>
@@ -15826,7 +15826,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G533" t="n">
-        <v>2.63691449165344</v>
+        <v>2.63691425323486</v>
       </c>
       <c r="H533" t="n">
         <v>19150</v>
@@ -15884,7 +15884,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G535" t="n">
-        <v>2.5385217666626</v>
+        <v>2.53852200508118</v>
       </c>
       <c r="H535" t="n">
         <v>7600</v>
@@ -15913,7 +15913,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G536" t="n">
-        <v>2.5582001209259</v>
+        <v>2.55820035934448</v>
       </c>
       <c r="H536" t="n">
         <v>1850</v>
@@ -15971,7 +15971,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G538" t="n">
-        <v>2.5582001209259</v>
+        <v>2.55820035934448</v>
       </c>
       <c r="H538" t="n">
         <v>2300</v>
@@ -16000,7 +16000,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G539" t="n">
-        <v>2.5582001209259</v>
+        <v>2.55820035934448</v>
       </c>
       <c r="H539" t="n">
         <v>3806</v>
@@ -16029,7 +16029,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G540" t="n">
-        <v>2.5385217666626</v>
+        <v>2.53852200508118</v>
       </c>
       <c r="H540" t="n">
         <v>6800</v>
@@ -16058,7 +16058,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G541" t="n">
-        <v>2.5582001209259</v>
+        <v>2.55820035934448</v>
       </c>
       <c r="H541" t="n">
         <v>8509</v>
@@ -16087,7 +16087,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G542" t="n">
-        <v>2.5582001209259</v>
+        <v>2.55820035934448</v>
       </c>
       <c r="H542" t="n">
         <v>6554</v>
@@ -16145,7 +16145,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G544" t="n">
-        <v>2.64675331115723</v>
+        <v>2.64675354957581</v>
       </c>
       <c r="H544" t="n">
         <v>29045</v>
@@ -16174,7 +16174,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G545" t="n">
-        <v>2.64675331115723</v>
+        <v>2.64675354957581</v>
       </c>
       <c r="H545" t="n">
         <v>24168</v>
@@ -16232,7 +16232,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G547" t="n">
-        <v>2.35157656669617</v>
+        <v>2.35157680511475</v>
       </c>
       <c r="H547" t="n">
         <v>106601</v>
@@ -16319,7 +16319,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G550" t="n">
-        <v>2.30238032341003</v>
+        <v>2.30238008499146</v>
       </c>
       <c r="H550" t="n">
         <v>10856</v>
@@ -16406,7 +16406,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G553" t="n">
-        <v>2.28270196914673</v>
+        <v>2.28270173072815</v>
       </c>
       <c r="H553" t="n">
         <v>7360</v>
@@ -16522,7 +16522,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G557" t="n">
-        <v>2.27286267280579</v>
+        <v>2.27286243438721</v>
       </c>
       <c r="H557" t="n">
         <v>3150</v>
@@ -16551,7 +16551,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G558" t="n">
-        <v>2.27286267280579</v>
+        <v>2.27286243438721</v>
       </c>
       <c r="H558" t="n">
         <v>0</v>
@@ -16580,7 +16580,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G559" t="n">
-        <v>2.27286267280579</v>
+        <v>2.27286243438721</v>
       </c>
       <c r="H559" t="n">
         <v>4065</v>
@@ -16609,7 +16609,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G560" t="n">
-        <v>2.28270196914673</v>
+        <v>2.28270173072815</v>
       </c>
       <c r="H560" t="n">
         <v>890</v>
@@ -16667,7 +16667,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G562" t="n">
-        <v>2.24334478378296</v>
+        <v>2.24334502220154</v>
       </c>
       <c r="H562" t="n">
         <v>11905</v>
@@ -16696,7 +16696,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G563" t="n">
-        <v>2.20398783683777</v>
+        <v>2.20398807525635</v>
       </c>
       <c r="H563" t="n">
         <v>34790</v>
@@ -16754,7 +16754,7 @@
         <v>2.25</v>
       </c>
       <c r="G565" t="n">
-        <v>2.21382713317871</v>
+        <v>2.21382737159729</v>
       </c>
       <c r="H565" t="n">
         <v>1201</v>
@@ -16783,7 +16783,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G566" t="n">
-        <v>2.27286267280579</v>
+        <v>2.27286243438721</v>
       </c>
       <c r="H566" t="n">
         <v>500</v>
@@ -16899,7 +16899,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G570" t="n">
-        <v>2.24334478378296</v>
+        <v>2.24334502220154</v>
       </c>
       <c r="H570" t="n">
         <v>18090</v>
@@ -16986,7 +16986,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G573" t="n">
-        <v>2.28270196914673</v>
+        <v>2.28270173072815</v>
       </c>
       <c r="H573" t="n">
         <v>2415</v>
@@ -17015,7 +17015,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G574" t="n">
-        <v>2.20398783683777</v>
+        <v>2.20398807525635</v>
       </c>
       <c r="H574" t="n">
         <v>24592</v>
@@ -17131,7 +17131,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G578" t="n">
-        <v>2.28270196914673</v>
+        <v>2.28270173072815</v>
       </c>
       <c r="H578" t="n">
         <v>2017</v>
@@ -17189,7 +17189,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G580" t="n">
-        <v>2.27286267280579</v>
+        <v>2.27286243438721</v>
       </c>
       <c r="H580" t="n">
         <v>2648</v>
@@ -17218,7 +17218,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G581" t="n">
-        <v>2.28270196914673</v>
+        <v>2.28270173072815</v>
       </c>
       <c r="H581" t="n">
         <v>1455</v>
@@ -17276,7 +17276,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G583" t="n">
-        <v>2.30238032341003</v>
+        <v>2.30238008499146</v>
       </c>
       <c r="H583" t="n">
         <v>4608</v>
@@ -17653,7 +17653,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G596" t="n">
-        <v>2.28270196914673</v>
+        <v>2.28270173072815</v>
       </c>
       <c r="H596" t="n">
         <v>3802</v>
@@ -17740,7 +17740,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G599" t="n">
-        <v>2.30238032341003</v>
+        <v>2.30238008499146</v>
       </c>
       <c r="H599" t="n">
         <v>2949</v>
@@ -17798,7 +17798,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G601" t="n">
-        <v>2.24334478378296</v>
+        <v>2.24334502220154</v>
       </c>
       <c r="H601" t="n">
         <v>17283</v>
@@ -17827,7 +17827,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G602" t="n">
-        <v>2.27286267280579</v>
+        <v>2.27286243438721</v>
       </c>
       <c r="H602" t="n">
         <v>2094</v>
@@ -17856,7 +17856,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G603" t="n">
-        <v>2.27286267280579</v>
+        <v>2.27286243438721</v>
       </c>
       <c r="H603" t="n">
         <v>4262</v>
@@ -17914,7 +17914,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G605" t="n">
-        <v>2.30238032341003</v>
+        <v>2.30238008499146</v>
       </c>
       <c r="H605" t="n">
         <v>3421</v>
@@ -17943,7 +17943,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G606" t="n">
-        <v>2.30238032341003</v>
+        <v>2.30238008499146</v>
       </c>
       <c r="H606" t="n">
         <v>1394</v>
@@ -17972,7 +17972,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G607" t="n">
-        <v>2.30238032341003</v>
+        <v>2.30238008499146</v>
       </c>
       <c r="H607" t="n">
         <v>1488</v>
@@ -18001,7 +18001,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G608" t="n">
-        <v>2.30238032341003</v>
+        <v>2.30238008499146</v>
       </c>
       <c r="H608" t="n">
         <v>1944</v>
@@ -18030,7 +18030,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G609" t="n">
-        <v>2.30238032341003</v>
+        <v>2.30238008499146</v>
       </c>
       <c r="H609" t="n">
         <v>1543</v>
@@ -18088,7 +18088,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G611" t="n">
-        <v>2.30238032341003</v>
+        <v>2.30238008499146</v>
       </c>
       <c r="H611" t="n">
         <v>1209</v>
@@ -18146,7 +18146,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G613" t="n">
-        <v>2.27286267280579</v>
+        <v>2.27286243438721</v>
       </c>
       <c r="H613" t="n">
         <v>3339</v>
@@ -18407,7 +18407,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G622" t="n">
-        <v>2.24334478378296</v>
+        <v>2.24334502220154</v>
       </c>
       <c r="H622" t="n">
         <v>729</v>
@@ -18436,7 +18436,7 @@
         <v>2.25</v>
       </c>
       <c r="G623" t="n">
-        <v>2.21382713317871</v>
+        <v>2.21382737159729</v>
       </c>
       <c r="H623" t="n">
         <v>3507</v>
@@ -18494,7 +18494,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G625" t="n">
-        <v>2.24334478378296</v>
+        <v>2.24334502220154</v>
       </c>
       <c r="H625" t="n">
         <v>3357</v>
@@ -18610,7 +18610,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G629" t="n">
-        <v>2.24334478378296</v>
+        <v>2.24334502220154</v>
       </c>
       <c r="H629" t="n">
         <v>1003</v>
@@ -18639,7 +18639,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G630" t="n">
-        <v>2.28270196914673</v>
+        <v>2.28270173072815</v>
       </c>
       <c r="H630" t="n">
         <v>26686</v>
@@ -18668,7 +18668,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G631" t="n">
-        <v>2.28270196914673</v>
+        <v>2.28270173072815</v>
       </c>
       <c r="H631" t="n">
         <v>1654</v>
@@ -18726,7 +18726,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G633" t="n">
-        <v>2.28270196914673</v>
+        <v>2.28270173072815</v>
       </c>
       <c r="H633" t="n">
         <v>1752</v>
@@ -18755,7 +18755,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G634" t="n">
-        <v>2.28270196914673</v>
+        <v>2.28270173072815</v>
       </c>
       <c r="H634" t="n">
         <v>3413</v>
@@ -18900,7 +18900,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G639" t="n">
-        <v>2.27286267280579</v>
+        <v>2.27286243438721</v>
       </c>
       <c r="H639" t="n">
         <v>2152</v>
@@ -18929,7 +18929,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G640" t="n">
-        <v>2.28270196914673</v>
+        <v>2.28270173072815</v>
       </c>
       <c r="H640" t="n">
         <v>2342</v>
@@ -18987,7 +18987,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G642" t="n">
-        <v>2.24334478378296</v>
+        <v>2.24334502220154</v>
       </c>
       <c r="H642" t="n">
         <v>3219</v>
@@ -19074,7 +19074,7 @@
         <v>2.25</v>
       </c>
       <c r="G645" t="n">
-        <v>2.21382713317871</v>
+        <v>2.21382737159729</v>
       </c>
       <c r="H645" t="n">
         <v>5907</v>
@@ -19132,7 +19132,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G647" t="n">
-        <v>2.20398783683777</v>
+        <v>2.20398807525635</v>
       </c>
       <c r="H647" t="n">
         <v>2247</v>
@@ -19190,7 +19190,7 @@
         <v>2.25</v>
       </c>
       <c r="G649" t="n">
-        <v>2.21382713317871</v>
+        <v>2.21382737159729</v>
       </c>
       <c r="H649" t="n">
         <v>1413</v>
@@ -19306,7 +19306,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G653" t="n">
-        <v>2.13511347770691</v>
+        <v>2.13511323928833</v>
       </c>
       <c r="H653" t="n">
         <v>4940</v>
@@ -19335,7 +19335,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G654" t="n">
-        <v>2.14495277404785</v>
+        <v>2.14495253562927</v>
       </c>
       <c r="H654" t="n">
         <v>4916</v>
@@ -19480,7 +19480,7 @@
         <v>2.25</v>
       </c>
       <c r="G659" t="n">
-        <v>2.21382713317871</v>
+        <v>2.21382737159729</v>
       </c>
       <c r="H659" t="n">
         <v>8762</v>
@@ -19538,7 +19538,7 @@
         <v>2.25</v>
       </c>
       <c r="G661" t="n">
-        <v>2.21382713317871</v>
+        <v>2.21382737159729</v>
       </c>
       <c r="H661" t="n">
         <v>6280</v>
@@ -19683,7 +19683,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G666" t="n">
-        <v>2.24334478378296</v>
+        <v>2.24334502220154</v>
       </c>
       <c r="H666" t="n">
         <v>10498</v>
@@ -19799,7 +19799,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G670" t="n">
-        <v>2.20398783683777</v>
+        <v>2.20398807525635</v>
       </c>
       <c r="H670" t="n">
         <v>7844</v>
@@ -19828,7 +19828,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G671" t="n">
-        <v>2.24334478378296</v>
+        <v>2.24334502220154</v>
       </c>
       <c r="H671" t="n">
         <v>7122</v>
@@ -19857,7 +19857,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G672" t="n">
-        <v>2.24334478378296</v>
+        <v>2.24334502220154</v>
       </c>
       <c r="H672" t="n">
         <v>3472</v>
@@ -19886,7 +19886,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G673" t="n">
-        <v>2.24334478378296</v>
+        <v>2.24334502220154</v>
       </c>
       <c r="H673" t="n">
         <v>4302</v>
@@ -19973,7 +19973,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G676" t="n">
-        <v>2.20398783683777</v>
+        <v>2.20398807525635</v>
       </c>
       <c r="H676" t="n">
         <v>2219</v>
@@ -20118,7 +20118,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G681" t="n">
-        <v>2.27286267280579</v>
+        <v>2.27286243438721</v>
       </c>
       <c r="H681" t="n">
         <v>3394</v>
@@ -20234,7 +20234,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G685" t="n">
-        <v>2.35157656669617</v>
+        <v>2.35157680511475</v>
       </c>
       <c r="H685" t="n">
         <v>14060</v>
@@ -20321,7 +20321,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G688" t="n">
-        <v>2.35157656669617</v>
+        <v>2.35157680511475</v>
       </c>
       <c r="H688" t="n">
         <v>3921</v>
@@ -20756,7 +20756,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G703" t="n">
-        <v>2.30238032341003</v>
+        <v>2.30238008499146</v>
       </c>
       <c r="H703" t="n">
         <v>18619</v>
@@ -20785,7 +20785,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G704" t="n">
-        <v>2.30238032341003</v>
+        <v>2.30238008499146</v>
       </c>
       <c r="H704" t="n">
         <v>5776</v>
@@ -20814,7 +20814,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G705" t="n">
-        <v>2.30238032341003</v>
+        <v>2.30238008499146</v>
       </c>
       <c r="H705" t="n">
         <v>4067</v>
@@ -20843,7 +20843,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G706" t="n">
-        <v>2.28270196914673</v>
+        <v>2.28270173072815</v>
       </c>
       <c r="H706" t="n">
         <v>2590</v>
@@ -20872,7 +20872,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G707" t="n">
-        <v>2.24334478378296</v>
+        <v>2.24334502220154</v>
       </c>
       <c r="H707" t="n">
         <v>10831</v>
@@ -20988,7 +20988,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G711" t="n">
-        <v>2.43029022216797</v>
+        <v>2.43029046058655</v>
       </c>
       <c r="H711" t="n">
         <v>15029</v>
@@ -21017,7 +21017,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G712" t="n">
-        <v>2.43029022216797</v>
+        <v>2.43029046058655</v>
       </c>
       <c r="H712" t="n">
         <v>8791</v>
@@ -21133,7 +21133,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G716" t="n">
-        <v>2.35157656669617</v>
+        <v>2.35157680511475</v>
       </c>
       <c r="H716" t="n">
         <v>16386</v>
@@ -21162,7 +21162,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G717" t="n">
-        <v>2.43029022216797</v>
+        <v>2.43029046058655</v>
       </c>
       <c r="H717" t="n">
         <v>59441</v>
@@ -21307,7 +21307,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G722" t="n">
-        <v>2.35157656669617</v>
+        <v>2.35157680511475</v>
       </c>
       <c r="H722" t="n">
         <v>15797</v>
@@ -21365,7 +21365,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G724" t="n">
-        <v>2.35157656669617</v>
+        <v>2.35157680511475</v>
       </c>
       <c r="H724" t="n">
         <v>6782</v>
@@ -21423,7 +21423,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G726" t="n">
-        <v>2.41061210632324</v>
+        <v>2.41061186790466</v>
       </c>
       <c r="H726" t="n">
         <v>10601</v>
@@ -21452,7 +21452,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G727" t="n">
-        <v>2.43029022216797</v>
+        <v>2.43029046058655</v>
       </c>
       <c r="H727" t="n">
         <v>6641</v>
@@ -21481,7 +21481,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G728" t="n">
-        <v>2.43029022216797</v>
+        <v>2.43029046058655</v>
       </c>
       <c r="H728" t="n">
         <v>7749</v>
@@ -21597,7 +21597,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G732" t="n">
-        <v>2.41061210632324</v>
+        <v>2.41061186790466</v>
       </c>
       <c r="H732" t="n">
         <v>8506</v>
@@ -21771,7 +21771,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G738" t="n">
-        <v>2.35157656669617</v>
+        <v>2.35157680511475</v>
       </c>
       <c r="H738" t="n">
         <v>9988</v>
@@ -21887,7 +21887,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G742" t="n">
-        <v>2.49916505813599</v>
+        <v>2.49916481971741</v>
       </c>
       <c r="H742" t="n">
         <v>34943</v>
@@ -21945,7 +21945,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G744" t="n">
-        <v>2.48932576179504</v>
+        <v>2.48932552337646</v>
       </c>
       <c r="H744" t="n">
         <v>39865</v>
@@ -22003,7 +22003,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G746" t="n">
-        <v>2.48932576179504</v>
+        <v>2.48932552337646</v>
       </c>
       <c r="H746" t="n">
         <v>18877</v>
@@ -22032,7 +22032,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G747" t="n">
-        <v>2.51884341239929</v>
+        <v>2.51884317398071</v>
       </c>
       <c r="H747" t="n">
         <v>44586</v>
@@ -22061,7 +22061,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G748" t="n">
-        <v>2.52868270874023</v>
+        <v>2.52868247032166</v>
       </c>
       <c r="H748" t="n">
         <v>45070</v>
@@ -22206,7 +22206,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G753" t="n">
-        <v>2.63691449165344</v>
+        <v>2.63691425323486</v>
       </c>
       <c r="H753" t="n">
         <v>58392</v>
@@ -22264,7 +22264,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G755" t="n">
-        <v>2.77466320991516</v>
+        <v>2.77466344833374</v>
       </c>
       <c r="H755" t="n">
         <v>152514</v>
@@ -22322,7 +22322,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G757" t="n">
-        <v>2.71562814712524</v>
+        <v>2.71562790870667</v>
       </c>
       <c r="H757" t="n">
         <v>170397</v>
@@ -22380,7 +22380,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G759" t="n">
-        <v>2.77466320991516</v>
+        <v>2.77466344833374</v>
       </c>
       <c r="H759" t="n">
         <v>21143</v>
@@ -22409,7 +22409,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G760" t="n">
-        <v>2.77466320991516</v>
+        <v>2.77466344833374</v>
       </c>
       <c r="H760" t="n">
         <v>14482</v>
@@ -22438,7 +22438,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G761" t="n">
-        <v>2.77466320991516</v>
+        <v>2.77466344833374</v>
       </c>
       <c r="H761" t="n">
         <v>13481</v>
@@ -22583,7 +22583,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G766" t="n">
-        <v>2.77466320991516</v>
+        <v>2.77466344833374</v>
       </c>
       <c r="H766" t="n">
         <v>11073</v>
@@ -22641,7 +22641,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G768" t="n">
-        <v>2.77466320991516</v>
+        <v>2.77466344833374</v>
       </c>
       <c r="H768" t="n">
         <v>16757</v>
@@ -22786,7 +22786,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G773" t="n">
-        <v>3.00096559524536</v>
+        <v>3.00096583366394</v>
       </c>
       <c r="H773" t="n">
         <v>78428</v>
@@ -22873,7 +22873,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G776" t="n">
-        <v>3.00096559524536</v>
+        <v>3.00096583366394</v>
       </c>
       <c r="H776" t="n">
         <v>13843</v>
@@ -22960,7 +22960,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G779" t="n">
-        <v>3.00096559524536</v>
+        <v>3.00096583366394</v>
       </c>
       <c r="H779" t="n">
         <v>12842</v>
@@ -23018,7 +23018,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G781" t="n">
-        <v>3.00096559524536</v>
+        <v>3.00096583366394</v>
       </c>
       <c r="H781" t="n">
         <v>25556</v>
@@ -23221,7 +23221,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G788" t="n">
-        <v>2.91241264343262</v>
+        <v>2.9124128818512</v>
       </c>
       <c r="H788" t="n">
         <v>28876</v>
@@ -23279,7 +23279,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G790" t="n">
-        <v>2.84353828430176</v>
+        <v>2.84353804588318</v>
       </c>
       <c r="H790" t="n">
         <v>12028</v>
@@ -23308,7 +23308,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G791" t="n">
-        <v>2.92225193977356</v>
+        <v>2.92225217819214</v>
       </c>
       <c r="H791" t="n">
         <v>36996</v>
@@ -23366,7 +23366,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G793" t="n">
-        <v>2.92225193977356</v>
+        <v>2.92225217819214</v>
       </c>
       <c r="H793" t="n">
         <v>20612</v>
@@ -23395,7 +23395,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G794" t="n">
-        <v>2.90257358551025</v>
+        <v>2.90257334709167</v>
       </c>
       <c r="H794" t="n">
         <v>5153</v>
@@ -23511,7 +23511,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G798" t="n">
-        <v>2.91241264343262</v>
+        <v>2.9124128818512</v>
       </c>
       <c r="H798" t="n">
         <v>29046</v>
@@ -23743,7 +23743,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G806" t="n">
-        <v>3.09935808181763</v>
+        <v>3.09935832023621</v>
       </c>
       <c r="H806" t="n">
         <v>21409</v>
@@ -23801,7 +23801,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G808" t="n">
-        <v>3.13871502876282</v>
+        <v>3.1387152671814</v>
       </c>
       <c r="H808" t="n">
         <v>29053</v>
@@ -24004,7 +24004,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G815" t="n">
-        <v>3.16823291778564</v>
+        <v>3.16823267936707</v>
       </c>
       <c r="H815" t="n">
         <v>40945</v>
@@ -24207,7 +24207,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G822" t="n">
-        <v>3.32566046714783</v>
+        <v>3.32566070556641</v>
       </c>
       <c r="H822" t="n">
         <v>8250</v>
@@ -24352,7 +24352,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G827" t="n">
-        <v>3.41421365737915</v>
+        <v>3.41421341896057</v>
       </c>
       <c r="H827" t="n">
         <v>49728</v>
@@ -24381,7 +24381,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G828" t="n">
-        <v>3.42405295372009</v>
+        <v>3.42405271530151</v>
       </c>
       <c r="H828" t="n">
         <v>21052</v>
@@ -24410,7 +24410,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G829" t="n">
-        <v>3.48308801651001</v>
+        <v>3.48308825492859</v>
       </c>
       <c r="H829" t="n">
         <v>56595</v>
@@ -24468,7 +24468,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G831" t="n">
-        <v>3.57164120674133</v>
+        <v>3.57164144515991</v>
       </c>
       <c r="H831" t="n">
         <v>31184</v>
@@ -24555,7 +24555,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G834" t="n">
-        <v>4.12263870239258</v>
+        <v>4.12263822555542</v>
       </c>
       <c r="H834" t="n">
         <v>162852</v>
@@ -24584,7 +24584,7 @@
         <v>4.25</v>
       </c>
       <c r="G835" t="n">
-        <v>4.18167352676392</v>
+        <v>4.18167400360107</v>
       </c>
       <c r="H835" t="n">
         <v>105792</v>
@@ -24700,7 +24700,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G839" t="n">
-        <v>4.22103023529053</v>
+        <v>4.22103071212769</v>
       </c>
       <c r="H839" t="n">
         <v>31763</v>
@@ -24758,7 +24758,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G841" t="n">
-        <v>4.2899055480957</v>
+        <v>4.28990507125854</v>
       </c>
       <c r="H841" t="n">
         <v>33142</v>
@@ -24816,7 +24816,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G843" t="n">
-        <v>4.39813613891602</v>
+        <v>4.39813661575317</v>
       </c>
       <c r="H843" t="n">
         <v>122860</v>
@@ -24990,7 +24990,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G849" t="n">
-        <v>5.0770435333252</v>
+        <v>5.07704401016235</v>
       </c>
       <c r="H849" t="n">
         <v>125520</v>
@@ -25019,7 +25019,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G850" t="n">
-        <v>4.99833011627197</v>
+        <v>4.99832963943481</v>
       </c>
       <c r="H850" t="n">
         <v>94101</v>
@@ -25077,7 +25077,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G852" t="n">
-        <v>5.03768682479858</v>
+        <v>5.03768634796143</v>
       </c>
       <c r="H852" t="n">
         <v>39665</v>
@@ -25222,7 +25222,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G857" t="n">
-        <v>5.03768682479858</v>
+        <v>5.03768634796143</v>
       </c>
       <c r="H857" t="n">
         <v>29318</v>
@@ -25280,7 +25280,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G859" t="n">
-        <v>4.86058044433594</v>
+        <v>4.8605809211731</v>
       </c>
       <c r="H859" t="n">
         <v>18569</v>
@@ -25309,7 +25309,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G860" t="n">
-        <v>4.83106327056885</v>
+        <v>4.83106279373169</v>
       </c>
       <c r="H860" t="n">
         <v>56243</v>
@@ -25338,7 +25338,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G861" t="n">
-        <v>4.89009809494019</v>
+        <v>4.89009857177734</v>
       </c>
       <c r="H861" t="n">
         <v>26996</v>
@@ -25425,7 +25425,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G864" t="n">
-        <v>4.89009809494019</v>
+        <v>4.89009857177734</v>
       </c>
       <c r="H864" t="n">
         <v>17018</v>
@@ -25512,7 +25512,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G867" t="n">
-        <v>5.29350662231445</v>
+        <v>5.29350709915161</v>
       </c>
       <c r="H867" t="n">
         <v>54581</v>
@@ -25570,7 +25570,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G869" t="n">
-        <v>5.7067551612854</v>
+        <v>5.70675468444824</v>
       </c>
       <c r="H869" t="n">
         <v>193218</v>
@@ -25599,7 +25599,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G870" t="n">
-        <v>5.80514717102051</v>
+        <v>5.80514669418335</v>
       </c>
       <c r="H870" t="n">
         <v>93551</v>
@@ -25628,7 +25628,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G871" t="n">
-        <v>5.68707656860352</v>
+        <v>5.68707609176636</v>
       </c>
       <c r="H871" t="n">
         <v>93418</v>
@@ -25686,7 +25686,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G873" t="n">
-        <v>5.43125629425049</v>
+        <v>5.43125581741333</v>
       </c>
       <c r="H873" t="n">
         <v>19758</v>
@@ -25773,7 +25773,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G876" t="n">
-        <v>5.27382898330688</v>
+        <v>5.27382850646973</v>
       </c>
       <c r="H876" t="n">
         <v>74967</v>
@@ -25802,7 +25802,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G877" t="n">
-        <v>5.29350662231445</v>
+        <v>5.29350709915161</v>
       </c>
       <c r="H877" t="n">
         <v>29227</v>
@@ -25860,7 +25860,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G879" t="n">
-        <v>5.05736541748047</v>
+        <v>5.05736494064331</v>
       </c>
       <c r="H879" t="n">
         <v>31367</v>
@@ -25918,7 +25918,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G881" t="n">
-        <v>5.03768682479858</v>
+        <v>5.03768634796143</v>
       </c>
       <c r="H881" t="n">
         <v>10417</v>
@@ -25976,7 +25976,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G883" t="n">
-        <v>5.03768682479858</v>
+        <v>5.03768634796143</v>
       </c>
       <c r="H883" t="n">
         <v>19220</v>
@@ -26034,7 +26034,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G885" t="n">
-        <v>5.0770435333252</v>
+        <v>5.07704401016235</v>
       </c>
       <c r="H885" t="n">
         <v>8947</v>
@@ -26208,7 +26208,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G891" t="n">
-        <v>5.27382898330688</v>
+        <v>5.27382850646973</v>
       </c>
       <c r="H891" t="n">
         <v>7249</v>
@@ -26237,7 +26237,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G892" t="n">
-        <v>5.11640024185181</v>
+        <v>5.11640071868896</v>
       </c>
       <c r="H892" t="n">
         <v>12636</v>
@@ -26266,7 +26266,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G893" t="n">
-        <v>5.05736541748047</v>
+        <v>5.05736494064331</v>
       </c>
       <c r="H893" t="n">
         <v>9316</v>
@@ -26295,7 +26295,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G894" t="n">
-        <v>5.03768682479858</v>
+        <v>5.03768634796143</v>
       </c>
       <c r="H894" t="n">
         <v>6814</v>
@@ -26324,7 +26324,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G895" t="n">
-        <v>5.03768682479858</v>
+        <v>5.03768634796143</v>
       </c>
       <c r="H895" t="n">
         <v>7477</v>
@@ -26382,7 +26382,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G897" t="n">
-        <v>5.11640024185181</v>
+        <v>5.11640071868896</v>
       </c>
       <c r="H897" t="n">
         <v>6128</v>
@@ -26411,7 +26411,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G898" t="n">
-        <v>4.99833011627197</v>
+        <v>4.99832963943481</v>
       </c>
       <c r="H898" t="n">
         <v>29460</v>
@@ -26440,7 +26440,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G899" t="n">
-        <v>4.83106327056885</v>
+        <v>4.83106279373169</v>
       </c>
       <c r="H899" t="n">
         <v>72320</v>
@@ -26556,7 +26556,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G903" t="n">
-        <v>4.2899055480957</v>
+        <v>4.28990507125854</v>
       </c>
       <c r="H903" t="n">
         <v>28901</v>
@@ -26585,7 +26585,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G904" t="n">
-        <v>4.56540393829346</v>
+        <v>4.5654034614563</v>
       </c>
       <c r="H904" t="n">
         <v>47385</v>
@@ -26643,7 +26643,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G906" t="n">
-        <v>4.83106327056885</v>
+        <v>4.83106279373169</v>
       </c>
       <c r="H906" t="n">
         <v>107459</v>
@@ -26672,7 +26672,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G907" t="n">
-        <v>4.89009809494019</v>
+        <v>4.89009857177734</v>
       </c>
       <c r="H907" t="n">
         <v>18622</v>
@@ -26730,7 +26730,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G909" t="n">
-        <v>4.84090185165405</v>
+        <v>4.84090232849121</v>
       </c>
       <c r="H909" t="n">
         <v>11135</v>
@@ -26759,7 +26759,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G910" t="n">
-        <v>4.83106327056885</v>
+        <v>4.83106279373169</v>
       </c>
       <c r="H910" t="n">
         <v>9284</v>
@@ -26817,7 +26817,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G912" t="n">
-        <v>4.89009809494019</v>
+        <v>4.89009857177734</v>
       </c>
       <c r="H912" t="n">
         <v>3683</v>
@@ -26933,7 +26933,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G916" t="n">
-        <v>4.82122421264648</v>
+        <v>4.82122373580933</v>
       </c>
       <c r="H916" t="n">
         <v>15220</v>
@@ -26991,7 +26991,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G918" t="n">
-        <v>5.03768682479858</v>
+        <v>5.03768634796143</v>
       </c>
       <c r="H918" t="n">
         <v>45309</v>
@@ -27020,7 +27020,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G919" t="n">
-        <v>5.0770435333252</v>
+        <v>5.07704401016235</v>
       </c>
       <c r="H919" t="n">
         <v>22506</v>
@@ -27107,7 +27107,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G922" t="n">
-        <v>5.11640024185181</v>
+        <v>5.11640071868896</v>
       </c>
       <c r="H922" t="n">
         <v>20658</v>
@@ -27223,7 +27223,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G926" t="n">
-        <v>5.254150390625</v>
+        <v>5.25414991378784</v>
       </c>
       <c r="H926" t="n">
         <v>16523</v>
@@ -27281,7 +27281,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G928" t="n">
-        <v>5.27382898330688</v>
+        <v>5.27382850646973</v>
       </c>
       <c r="H928" t="n">
         <v>14860</v>
@@ -27310,7 +27310,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G929" t="n">
-        <v>5.29350662231445</v>
+        <v>5.29350709915161</v>
       </c>
       <c r="H929" t="n">
         <v>8491</v>
@@ -27339,7 +27339,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G930" t="n">
-        <v>5.29350662231445</v>
+        <v>5.29350709915161</v>
       </c>
       <c r="H930" t="n">
         <v>4930</v>
@@ -27542,7 +27542,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G937" t="n">
-        <v>5.11640024185181</v>
+        <v>5.11640071868896</v>
       </c>
       <c r="H937" t="n">
         <v>12717</v>
@@ -27600,7 +27600,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G939" t="n">
-        <v>5.11640024185181</v>
+        <v>5.11640071868896</v>
       </c>
       <c r="H939" t="n">
         <v>9615</v>
@@ -27658,7 +27658,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G941" t="n">
-        <v>5.0770435333252</v>
+        <v>5.07704401016235</v>
       </c>
       <c r="H941" t="n">
         <v>9588</v>
@@ -27745,7 +27745,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G944" t="n">
-        <v>5.13607883453369</v>
+        <v>5.13607931137085</v>
       </c>
       <c r="H944" t="n">
         <v>6542</v>
@@ -27890,7 +27890,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G949" t="n">
-        <v>5.254150390625</v>
+        <v>5.25414991378784</v>
       </c>
       <c r="H949" t="n">
         <v>10195</v>
@@ -27919,7 +27919,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G950" t="n">
-        <v>5.29350662231445</v>
+        <v>5.29350709915161</v>
       </c>
       <c r="H950" t="n">
         <v>11103</v>
@@ -28151,7 +28151,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G958" t="n">
-        <v>5.68707656860352</v>
+        <v>5.68707609176636</v>
       </c>
       <c r="H958" t="n">
         <v>24892</v>
@@ -28180,7 +28180,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G959" t="n">
-        <v>5.68707656860352</v>
+        <v>5.68707609176636</v>
       </c>
       <c r="H959" t="n">
         <v>8965</v>
@@ -28267,7 +28267,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G962" t="n">
-        <v>5.80514717102051</v>
+        <v>5.80514669418335</v>
       </c>
       <c r="H962" t="n">
         <v>18409</v>
@@ -28354,7 +28354,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G965" t="n">
-        <v>5.80514717102051</v>
+        <v>5.80514669418335</v>
       </c>
       <c r="H965" t="n">
         <v>16785</v>
@@ -28470,7 +28470,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G969" t="n">
-        <v>6.13968086242676</v>
+        <v>6.1396803855896</v>
       </c>
       <c r="H969" t="n">
         <v>75849</v>
@@ -28499,7 +28499,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G970" t="n">
-        <v>6.19871616363525</v>
+        <v>6.19871664047241</v>
       </c>
       <c r="H970" t="n">
         <v>62814</v>
@@ -28528,7 +28528,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G971" t="n">
-        <v>6.33646583557129</v>
+        <v>6.33646535873413</v>
       </c>
       <c r="H971" t="n">
         <v>50014</v>
@@ -28557,7 +28557,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G972" t="n">
-        <v>6.27743005752563</v>
+        <v>6.27743053436279</v>
       </c>
       <c r="H972" t="n">
         <v>43290</v>
@@ -28615,7 +28615,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G974" t="n">
-        <v>6.13968086242676</v>
+        <v>6.1396803855896</v>
       </c>
       <c r="H974" t="n">
         <v>10830</v>
@@ -28702,7 +28702,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G977" t="n">
-        <v>6.00193119049072</v>
+        <v>6.00193166732788</v>
       </c>
       <c r="H977" t="n">
         <v>35007</v>
@@ -43382,6 +43382,35 @@
         <v>13060</v>
       </c>
       <c r="I1483" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1484">
+      <c r="A1484" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1484" s="1" t="n">
+        <v>46325.3333333333</v>
+      </c>
+      <c r="C1484" t="n">
+        <v>7.92999982833862</v>
+      </c>
+      <c r="D1484" t="n">
+        <v>8.23999977111816</v>
+      </c>
+      <c r="E1484" t="n">
+        <v>7.84000015258789</v>
+      </c>
+      <c r="F1484" t="n">
+        <v>7.86999988555908</v>
+      </c>
+      <c r="G1484" t="n">
+        <v>7.86999988555908</v>
+      </c>
+      <c r="H1484" t="n">
+        <v>9002</v>
+      </c>
+      <c r="I1484" t="s">
         <v>9</v>
       </c>
     </row>
